--- a/output/TRANSFERENCIA_atual.xlsx
+++ b/output/TRANSFERENCIA_atual.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Taxa de Transferência" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Taxa de Transferência" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Taxa de Transferência'!$A$1:$E$20</definedName>

--- a/output/TRANSFERENCIA_atual.xlsx
+++ b/output/TRANSFERENCIA_atual.xlsx
@@ -473,16 +473,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2569</v>
+        <v>1945</v>
       </c>
       <c r="C2" t="n">
-        <v>2537</v>
+        <v>1910</v>
       </c>
       <c r="D2" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.9875</v>
+        <v>0.982</v>
       </c>
     </row>
     <row r="3">
@@ -492,16 +492,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2638</v>
+        <v>4842</v>
       </c>
       <c r="C3" t="n">
-        <v>2563</v>
+        <v>2691</v>
       </c>
       <c r="D3" t="n">
-        <v>75</v>
+        <v>2151</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.9716</v>
+        <v>0.5558</v>
       </c>
     </row>
     <row r="4">
@@ -511,16 +511,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2678</v>
+        <v>2455</v>
       </c>
       <c r="C4" t="n">
-        <v>2674</v>
+        <v>2441</v>
       </c>
       <c r="D4" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.9984999999999999</v>
+        <v>0.9943000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -530,16 +530,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1054</v>
+        <v>651</v>
       </c>
       <c r="C5" t="n">
-        <v>989</v>
+        <v>648</v>
       </c>
       <c r="D5" t="n">
-        <v>65</v>
+        <v>3</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.9383</v>
+        <v>0.9954000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -549,16 +549,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>23395</v>
+        <v>15929</v>
       </c>
       <c r="C6" t="n">
-        <v>17286</v>
+        <v>9345</v>
       </c>
       <c r="D6" t="n">
-        <v>6109</v>
+        <v>6584</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.7389</v>
+        <v>0.5867</v>
       </c>
     </row>
     <row r="7">
@@ -568,16 +568,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>53238</v>
+        <v>34438</v>
       </c>
       <c r="C7" t="n">
-        <v>42663</v>
+        <v>33343</v>
       </c>
       <c r="D7" t="n">
-        <v>10575</v>
+        <v>1095</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.8014</v>
+        <v>0.9681999999999999</v>
       </c>
     </row>
     <row r="8">
@@ -587,16 +587,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9620</v>
+        <v>13420</v>
       </c>
       <c r="C8" t="n">
-        <v>633</v>
+        <v>2133</v>
       </c>
       <c r="D8" t="n">
-        <v>8987</v>
+        <v>11287</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.0658</v>
+        <v>0.1589</v>
       </c>
     </row>
     <row r="9">
@@ -606,16 +606,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>11358</v>
+        <v>44565</v>
       </c>
       <c r="C9" t="n">
-        <v>8716</v>
+        <v>37579</v>
       </c>
       <c r="D9" t="n">
-        <v>2642</v>
+        <v>6986</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0.7674</v>
+        <v>0.8431999999999999</v>
       </c>
     </row>
     <row r="10">
@@ -625,16 +625,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>25613</v>
+        <v>35788</v>
       </c>
       <c r="C10" t="n">
-        <v>19063</v>
+        <v>25656</v>
       </c>
       <c r="D10" t="n">
-        <v>6550</v>
+        <v>10132</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0.7443000000000001</v>
+        <v>0.7169</v>
       </c>
     </row>
     <row r="11">
@@ -644,10 +644,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>72951</v>
+        <v>138294</v>
       </c>
       <c r="C11" t="n">
-        <v>72951</v>
+        <v>138294</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -663,16 +663,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2559</v>
+        <v>2718</v>
       </c>
       <c r="C12" t="n">
-        <v>1787</v>
+        <v>1757</v>
       </c>
       <c r="D12" t="n">
-        <v>772</v>
+        <v>961</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>0.6983</v>
+        <v>0.6464</v>
       </c>
     </row>
     <row r="13">
@@ -682,10 +682,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3148</v>
+        <v>2785</v>
       </c>
       <c r="C13" t="n">
-        <v>3148</v>
+        <v>2785</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
@@ -701,16 +701,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>6195</v>
+        <v>7661</v>
       </c>
       <c r="C14" t="n">
-        <v>6141</v>
+        <v>7326</v>
       </c>
       <c r="D14" t="n">
-        <v>54</v>
+        <v>335</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0.9913</v>
+        <v>0.9562999999999999</v>
       </c>
     </row>
     <row r="15">
@@ -720,16 +720,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>442</v>
+        <v>426</v>
       </c>
       <c r="C15" t="n">
-        <v>442</v>
+        <v>423</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>1</v>
+        <v>0.993</v>
       </c>
     </row>
     <row r="16">
@@ -739,16 +739,16 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>944</v>
+        <v>307</v>
       </c>
       <c r="C16" t="n">
-        <v>941</v>
+        <v>289</v>
       </c>
       <c r="D16" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>0.9968</v>
+        <v>0.9414</v>
       </c>
     </row>
     <row r="17">
@@ -758,10 +758,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>9170</v>
+        <v>13775</v>
       </c>
       <c r="C17" t="n">
-        <v>9170</v>
+        <v>13775</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
@@ -777,16 +777,16 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>903</v>
+        <v>804</v>
       </c>
       <c r="C18" t="n">
-        <v>860</v>
+        <v>795</v>
       </c>
       <c r="D18" t="n">
-        <v>43</v>
+        <v>9</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>0.9523999999999999</v>
+        <v>0.9887999999999999</v>
       </c>
     </row>
     <row r="19">
@@ -796,16 +796,16 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1018</v>
+        <v>829</v>
       </c>
       <c r="C19" t="n">
-        <v>1012</v>
+        <v>820</v>
       </c>
       <c r="D19" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>0.9941</v>
+        <v>0.9891</v>
       </c>
     </row>
     <row r="20">
@@ -815,16 +815,16 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4839</v>
+        <v>5310</v>
       </c>
       <c r="C20" t="n">
-        <v>4258</v>
+        <v>5175</v>
       </c>
       <c r="D20" t="n">
-        <v>581</v>
+        <v>135</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>0.8798999999999999</v>
+        <v>0.9745999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/output/TRANSFERENCIA_atual.xlsx
+++ b/output/TRANSFERENCIA_atual.xlsx
@@ -473,16 +473,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1945</v>
+        <v>2002</v>
       </c>
       <c r="C2" t="n">
-        <v>1910</v>
+        <v>1977</v>
       </c>
       <c r="D2" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.982</v>
+        <v>0.9875</v>
       </c>
     </row>
     <row r="3">
@@ -492,16 +492,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4842</v>
+        <v>1583</v>
       </c>
       <c r="C3" t="n">
-        <v>2691</v>
+        <v>659</v>
       </c>
       <c r="D3" t="n">
-        <v>2151</v>
+        <v>924</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.5558</v>
+        <v>0.4163</v>
       </c>
     </row>
     <row r="4">
@@ -511,16 +511,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2455</v>
+        <v>2347</v>
       </c>
       <c r="C4" t="n">
-        <v>2441</v>
+        <v>2292</v>
       </c>
       <c r="D4" t="n">
-        <v>14</v>
+        <v>55</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.9943000000000001</v>
+        <v>0.9765999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -530,16 +530,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>651</v>
+        <v>406</v>
       </c>
       <c r="C5" t="n">
-        <v>648</v>
+        <v>398</v>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.9954000000000001</v>
+        <v>0.9803000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -549,16 +549,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>15929</v>
+        <v>10262</v>
       </c>
       <c r="C6" t="n">
-        <v>9345</v>
+        <v>4550</v>
       </c>
       <c r="D6" t="n">
-        <v>6584</v>
+        <v>5712</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.5867</v>
+        <v>0.4434</v>
       </c>
     </row>
     <row r="7">
@@ -568,16 +568,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>34438</v>
+        <v>22056</v>
       </c>
       <c r="C7" t="n">
-        <v>33343</v>
+        <v>20627</v>
       </c>
       <c r="D7" t="n">
-        <v>1095</v>
+        <v>1429</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.9681999999999999</v>
+        <v>0.9351999999999999</v>
       </c>
     </row>
     <row r="8">
@@ -587,16 +587,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13420</v>
+        <v>7896</v>
       </c>
       <c r="C8" t="n">
-        <v>2133</v>
+        <v>1501</v>
       </c>
       <c r="D8" t="n">
-        <v>11287</v>
+        <v>6395</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.1589</v>
+        <v>0.1901</v>
       </c>
     </row>
     <row r="9">
@@ -606,16 +606,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>44565</v>
+        <v>26629</v>
       </c>
       <c r="C9" t="n">
-        <v>37579</v>
+        <v>22517</v>
       </c>
       <c r="D9" t="n">
-        <v>6986</v>
+        <v>4112</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0.8431999999999999</v>
+        <v>0.8456</v>
       </c>
     </row>
     <row r="10">
@@ -625,16 +625,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>35788</v>
+        <v>20256</v>
       </c>
       <c r="C10" t="n">
-        <v>25656</v>
+        <v>10548</v>
       </c>
       <c r="D10" t="n">
-        <v>10132</v>
+        <v>9708</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0.7169</v>
+        <v>0.5207000000000001</v>
       </c>
     </row>
     <row r="11">
@@ -644,10 +644,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>138294</v>
+        <v>119233</v>
       </c>
       <c r="C11" t="n">
-        <v>138294</v>
+        <v>119233</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -663,16 +663,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2718</v>
+        <v>2239</v>
       </c>
       <c r="C12" t="n">
-        <v>1757</v>
+        <v>390</v>
       </c>
       <c r="D12" t="n">
-        <v>961</v>
+        <v>1849</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>0.6464</v>
+        <v>0.1742</v>
       </c>
     </row>
     <row r="13">
@@ -682,10 +682,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2785</v>
+        <v>2628</v>
       </c>
       <c r="C13" t="n">
-        <v>2785</v>
+        <v>2628</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
@@ -701,16 +701,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>7661</v>
+        <v>7523</v>
       </c>
       <c r="C14" t="n">
-        <v>7326</v>
+        <v>7369</v>
       </c>
       <c r="D14" t="n">
-        <v>335</v>
+        <v>154</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0.9562999999999999</v>
+        <v>0.9795</v>
       </c>
     </row>
     <row r="15">
@@ -720,16 +720,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>426</v>
+        <v>707</v>
       </c>
       <c r="C15" t="n">
-        <v>423</v>
+        <v>704</v>
       </c>
       <c r="D15" t="n">
         <v>3</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>0.993</v>
+        <v>0.9958</v>
       </c>
     </row>
     <row r="16">
@@ -739,17 +739,15 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>307</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>289</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>18</v>
-      </c>
-      <c r="E16" s="2" t="n">
-        <v>0.9414</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E16" s="2" t="n"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -758,10 +756,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>13775</v>
+        <v>11475</v>
       </c>
       <c r="C17" t="n">
-        <v>13775</v>
+        <v>11475</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
@@ -777,16 +775,16 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>804</v>
+        <v>467</v>
       </c>
       <c r="C18" t="n">
-        <v>795</v>
+        <v>429</v>
       </c>
       <c r="D18" t="n">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>0.9887999999999999</v>
+        <v>0.9186</v>
       </c>
     </row>
     <row r="19">
@@ -796,16 +794,16 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>829</v>
+        <v>730</v>
       </c>
       <c r="C19" t="n">
-        <v>820</v>
+        <v>728</v>
       </c>
       <c r="D19" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>0.9891</v>
+        <v>0.9973000000000001</v>
       </c>
     </row>
     <row r="20">
@@ -815,16 +813,16 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5310</v>
+        <v>3647</v>
       </c>
       <c r="C20" t="n">
-        <v>5175</v>
+        <v>3452</v>
       </c>
       <c r="D20" t="n">
-        <v>135</v>
+        <v>195</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>0.9745999999999999</v>
+        <v>0.9465</v>
       </c>
     </row>
   </sheetData>

--- a/output/TRANSFERENCIA_atual.xlsx
+++ b/output/TRANSFERENCIA_atual.xlsx
@@ -473,16 +473,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2002</v>
+        <v>1735</v>
       </c>
       <c r="C2" t="n">
-        <v>1977</v>
+        <v>1688</v>
       </c>
       <c r="D2" t="n">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.9875</v>
+        <v>0.9729000000000001</v>
       </c>
     </row>
     <row r="3">
@@ -492,16 +492,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1583</v>
+        <v>2396</v>
       </c>
       <c r="C3" t="n">
-        <v>659</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>924</v>
+        <v>2396</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.4163</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -511,17 +511,15 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2347</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>2292</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>55</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>0.9765999999999999</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -530,17 +528,15 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>406</v>
+        <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>398</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>8</v>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>0.9803000000000001</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E5" s="2" t="n"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -549,17 +545,15 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10262</v>
+        <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>4550</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>5712</v>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>0.4434</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -568,16 +562,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>22056</v>
+        <v>24504</v>
       </c>
       <c r="C7" t="n">
-        <v>20627</v>
+        <v>23614</v>
       </c>
       <c r="D7" t="n">
-        <v>1429</v>
+        <v>890</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.9351999999999999</v>
+        <v>0.9637</v>
       </c>
     </row>
     <row r="8">
@@ -587,16 +581,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7896</v>
+        <v>6695</v>
       </c>
       <c r="C8" t="n">
-        <v>1501</v>
+        <v>3822</v>
       </c>
       <c r="D8" t="n">
-        <v>6395</v>
+        <v>2873</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.1901</v>
+        <v>0.5709000000000001</v>
       </c>
     </row>
     <row r="9">
@@ -606,16 +600,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>26629</v>
+        <v>296</v>
       </c>
       <c r="C9" t="n">
-        <v>22517</v>
+        <v>263</v>
       </c>
       <c r="D9" t="n">
-        <v>4112</v>
+        <v>33</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0.8456</v>
+        <v>0.8885</v>
       </c>
     </row>
     <row r="10">
@@ -625,17 +619,15 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>20256</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>10548</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>9708</v>
-      </c>
-      <c r="E10" s="2" t="n">
-        <v>0.5207000000000001</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E10" s="2" t="n"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -644,10 +636,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>119233</v>
+        <v>127520</v>
       </c>
       <c r="C11" t="n">
-        <v>119233</v>
+        <v>127520</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -663,16 +655,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2239</v>
+        <v>1059</v>
       </c>
       <c r="C12" t="n">
-        <v>390</v>
+        <v>1059</v>
       </c>
       <c r="D12" t="n">
-        <v>1849</v>
+        <v>0</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>0.1742</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -682,10 +674,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2628</v>
+        <v>2488</v>
       </c>
       <c r="C13" t="n">
-        <v>2628</v>
+        <v>2488</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
@@ -701,16 +693,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>7523</v>
+        <v>5525</v>
       </c>
       <c r="C14" t="n">
-        <v>7369</v>
+        <v>5523</v>
       </c>
       <c r="D14" t="n">
-        <v>154</v>
+        <v>2</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0.9795</v>
+        <v>0.9995999999999999</v>
       </c>
     </row>
     <row r="15">
@@ -720,17 +712,15 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>707</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>704</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>3</v>
-      </c>
-      <c r="E15" s="2" t="n">
-        <v>0.9958</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E15" s="2" t="n"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -756,10 +746,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>11475</v>
+        <v>11379</v>
       </c>
       <c r="C17" t="n">
-        <v>11475</v>
+        <v>11379</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
@@ -775,17 +765,15 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>467</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>429</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
-      </c>
-      <c r="E18" s="2" t="n">
-        <v>0.9186</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E18" s="2" t="n"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -794,17 +782,15 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>730</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>728</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>2</v>
-      </c>
-      <c r="E19" s="2" t="n">
-        <v>0.9973000000000001</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E19" s="2" t="n"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -813,16 +799,16 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3647</v>
+        <v>4924</v>
       </c>
       <c r="C20" t="n">
-        <v>3452</v>
+        <v>4889</v>
       </c>
       <c r="D20" t="n">
-        <v>195</v>
+        <v>35</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>0.9465</v>
+        <v>0.9929000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/output/TRANSFERENCIA_atual.xlsx
+++ b/output/TRANSFERENCIA_atual.xlsx
@@ -473,17 +473,15 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1735</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>1688</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>47</v>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>0.9729000000000001</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -492,17 +490,15 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2396</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>2396</v>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -562,16 +558,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>24504</v>
+        <v>54</v>
       </c>
       <c r="C7" t="n">
-        <v>23614</v>
+        <v>54</v>
       </c>
       <c r="D7" t="n">
-        <v>890</v>
+        <v>0</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.9637</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -581,16 +577,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6695</v>
+        <v>8254</v>
       </c>
       <c r="C8" t="n">
-        <v>3822</v>
+        <v>5363</v>
       </c>
       <c r="D8" t="n">
-        <v>2873</v>
+        <v>2891</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.5709000000000001</v>
+        <v>0.6496999999999999</v>
       </c>
     </row>
     <row r="9">
@@ -600,17 +596,15 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>296</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>263</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>33</v>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>0.8885</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E9" s="2" t="n"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -636,10 +630,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>127520</v>
+        <v>129499</v>
       </c>
       <c r="C11" t="n">
-        <v>127520</v>
+        <v>129499</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -655,10 +649,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1059</v>
+        <v>101</v>
       </c>
       <c r="C12" t="n">
-        <v>1059</v>
+        <v>101</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
@@ -674,10 +668,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2488</v>
+        <v>1192</v>
       </c>
       <c r="C13" t="n">
-        <v>2488</v>
+        <v>1192</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
@@ -693,17 +687,15 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>5525</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>5523</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>2</v>
-      </c>
-      <c r="E14" s="2" t="n">
-        <v>0.9995999999999999</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E14" s="2" t="n"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -746,10 +738,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>11379</v>
+        <v>8335</v>
       </c>
       <c r="C17" t="n">
-        <v>11379</v>
+        <v>8335</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
@@ -799,16 +791,16 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4924</v>
+        <v>2241</v>
       </c>
       <c r="C20" t="n">
-        <v>4889</v>
+        <v>2238</v>
       </c>
       <c r="D20" t="n">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>0.9929000000000001</v>
+        <v>0.9987</v>
       </c>
     </row>
   </sheetData>

--- a/output/TRANSFERENCIA_atual.xlsx
+++ b/output/TRANSFERENCIA_atual.xlsx
@@ -473,15 +473,17 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>2025</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>1996</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" s="2" t="n"/>
+        <v>29</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>0.9856999999999999</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -490,15 +492,17 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>5349</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>3231</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" s="2" t="n"/>
+        <v>2118</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>0.604</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -507,15 +511,17 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>3815</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>3810</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" s="2" t="n"/>
+        <v>5</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>0.9987</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -524,15 +530,17 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>508</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>508</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
-      <c r="E5" s="2" t="n"/>
+      <c r="E5" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -558,16 +566,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>54</v>
+        <v>158</v>
       </c>
       <c r="C7" t="n">
-        <v>54</v>
+        <v>140</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>1</v>
+        <v>0.8861</v>
       </c>
     </row>
     <row r="8">
@@ -577,16 +585,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8254</v>
+        <v>1560</v>
       </c>
       <c r="C8" t="n">
-        <v>5363</v>
+        <v>1542</v>
       </c>
       <c r="D8" t="n">
-        <v>2891</v>
+        <v>18</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.6496999999999999</v>
+        <v>0.9884999999999999</v>
       </c>
     </row>
     <row r="9">
@@ -596,15 +604,17 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>23370</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>21200</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" s="2" t="n"/>
+        <v>2170</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>0.9070999999999999</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -630,10 +640,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>129499</v>
+        <v>55869</v>
       </c>
       <c r="C11" t="n">
-        <v>129499</v>
+        <v>55869</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -649,16 +659,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>101</v>
+        <v>3723</v>
       </c>
       <c r="C12" t="n">
-        <v>101</v>
+        <v>3329</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>394</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>1</v>
+        <v>0.8942</v>
       </c>
     </row>
     <row r="13">
@@ -668,17 +678,15 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1192</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>1192</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
       </c>
-      <c r="E13" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="E13" s="2" t="n"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -687,15 +695,17 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>6556</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>6554</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" s="2" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>0.9997</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -704,15 +714,17 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>479</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>478</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" s="2" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>0.9979</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -721,15 +733,17 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>285</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>257</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" s="2" t="n"/>
+        <v>28</v>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>0.9018</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -738,10 +752,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>8335</v>
+        <v>4405</v>
       </c>
       <c r="C17" t="n">
-        <v>8335</v>
+        <v>4405</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
@@ -774,15 +788,17 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>1530</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>1524</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" s="2" t="n"/>
+        <v>6</v>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>0.9961</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -791,16 +807,16 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2241</v>
+        <v>7321</v>
       </c>
       <c r="C20" t="n">
-        <v>2238</v>
+        <v>7183</v>
       </c>
       <c r="D20" t="n">
-        <v>3</v>
+        <v>138</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>0.9987</v>
+        <v>0.9812000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/output/TRANSFERENCIA_atual.xlsx
+++ b/output/TRANSFERENCIA_atual.xlsx
@@ -473,16 +473,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2025</v>
+        <v>2430</v>
       </c>
       <c r="C2" t="n">
-        <v>1996</v>
+        <v>2383</v>
       </c>
       <c r="D2" t="n">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.9856999999999999</v>
+        <v>0.9806999999999999</v>
       </c>
     </row>
     <row r="3">
@@ -492,16 +492,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5349</v>
+        <v>1713</v>
       </c>
       <c r="C3" t="n">
-        <v>3231</v>
+        <v>977</v>
       </c>
       <c r="D3" t="n">
-        <v>2118</v>
+        <v>736</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.604</v>
+        <v>0.5703</v>
       </c>
     </row>
     <row r="4">
@@ -511,13 +511,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3815</v>
+        <v>757</v>
       </c>
       <c r="C4" t="n">
-        <v>3810</v>
+        <v>756</v>
       </c>
       <c r="D4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>0.9987</v>
@@ -530,16 +530,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>508</v>
+        <v>807</v>
       </c>
       <c r="C5" t="n">
-        <v>508</v>
+        <v>800</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>1</v>
+        <v>0.9913</v>
       </c>
     </row>
     <row r="6">
@@ -549,15 +549,17 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>9711</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>9711</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
-      <c r="E6" s="2" t="n"/>
+      <c r="E6" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -566,16 +568,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>3061</v>
       </c>
       <c r="C7" t="n">
-        <v>140</v>
+        <v>3040</v>
       </c>
       <c r="D7" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.8861</v>
+        <v>0.9931</v>
       </c>
     </row>
     <row r="8">
@@ -585,16 +587,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1560</v>
+        <v>7889</v>
       </c>
       <c r="C8" t="n">
-        <v>1542</v>
+        <v>7052</v>
       </c>
       <c r="D8" t="n">
-        <v>18</v>
+        <v>837</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.9884999999999999</v>
+        <v>0.8939</v>
       </c>
     </row>
     <row r="9">
@@ -604,16 +606,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>23370</v>
+        <v>24993</v>
       </c>
       <c r="C9" t="n">
-        <v>21200</v>
+        <v>23346</v>
       </c>
       <c r="D9" t="n">
-        <v>2170</v>
+        <v>1647</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0.9070999999999999</v>
+        <v>0.9340999999999999</v>
       </c>
     </row>
     <row r="10">
@@ -640,10 +642,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>55869</v>
+        <v>120648</v>
       </c>
       <c r="C11" t="n">
-        <v>55869</v>
+        <v>120648</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -659,16 +661,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3723</v>
+        <v>3050</v>
       </c>
       <c r="C12" t="n">
-        <v>3329</v>
+        <v>2760</v>
       </c>
       <c r="D12" t="n">
-        <v>394</v>
+        <v>290</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>0.8942</v>
+        <v>0.9048999999999999</v>
       </c>
     </row>
     <row r="13">
@@ -678,15 +680,17 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2070</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>2070</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
       </c>
-      <c r="E13" s="2" t="n"/>
+      <c r="E13" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -695,16 +699,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>6556</v>
+        <v>8466</v>
       </c>
       <c r="C14" t="n">
-        <v>6554</v>
+        <v>8465</v>
       </c>
       <c r="D14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0.9997</v>
+        <v>0.9998999999999999</v>
       </c>
     </row>
     <row r="15">
@@ -714,16 +718,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>479</v>
+        <v>775</v>
       </c>
       <c r="C15" t="n">
-        <v>478</v>
+        <v>774</v>
       </c>
       <c r="D15" t="n">
         <v>1</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>0.9979</v>
+        <v>0.9987</v>
       </c>
     </row>
     <row r="16">
@@ -733,16 +737,16 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>285</v>
+        <v>535</v>
       </c>
       <c r="C16" t="n">
-        <v>257</v>
+        <v>534</v>
       </c>
       <c r="D16" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>0.9018</v>
+        <v>0.9981</v>
       </c>
     </row>
     <row r="17">
@@ -752,10 +756,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4405</v>
+        <v>2856</v>
       </c>
       <c r="C17" t="n">
-        <v>4405</v>
+        <v>2856</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
@@ -788,16 +792,16 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1530</v>
+        <v>1013</v>
       </c>
       <c r="C19" t="n">
-        <v>1524</v>
+        <v>1011</v>
       </c>
       <c r="D19" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>0.9961</v>
+        <v>0.998</v>
       </c>
     </row>
     <row r="20">
@@ -807,16 +811,16 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>7321</v>
+        <v>5903</v>
       </c>
       <c r="C20" t="n">
-        <v>7183</v>
+        <v>5839</v>
       </c>
       <c r="D20" t="n">
-        <v>138</v>
+        <v>64</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>0.9812000000000001</v>
+        <v>0.9892</v>
       </c>
     </row>
   </sheetData>

--- a/output/TRANSFERENCIA_atual.xlsx
+++ b/output/TRANSFERENCIA_atual.xlsx
@@ -473,16 +473,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2430</v>
+        <v>1704</v>
       </c>
       <c r="C2" t="n">
-        <v>2383</v>
+        <v>1637</v>
       </c>
       <c r="D2" t="n">
-        <v>47</v>
+        <v>67</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.9806999999999999</v>
+        <v>0.9606999999999999</v>
       </c>
     </row>
     <row r="3">
@@ -492,16 +492,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1713</v>
+        <v>2242</v>
       </c>
       <c r="C3" t="n">
-        <v>977</v>
+        <v>2157</v>
       </c>
       <c r="D3" t="n">
-        <v>736</v>
+        <v>85</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.5703</v>
+        <v>0.9621</v>
       </c>
     </row>
     <row r="4">
@@ -511,16 +511,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>757</v>
+        <v>738</v>
       </c>
       <c r="C4" t="n">
-        <v>756</v>
+        <v>733</v>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.9987</v>
+        <v>0.9932</v>
       </c>
     </row>
     <row r="5">
@@ -530,16 +530,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>807</v>
+        <v>444</v>
       </c>
       <c r="C5" t="n">
-        <v>800</v>
+        <v>389</v>
       </c>
       <c r="D5" t="n">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.9913</v>
+        <v>0.8761</v>
       </c>
     </row>
     <row r="6">
@@ -549,10 +549,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9711</v>
+        <v>21764</v>
       </c>
       <c r="C6" t="n">
-        <v>9711</v>
+        <v>21764</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -568,16 +568,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3061</v>
+        <v>25897</v>
       </c>
       <c r="C7" t="n">
-        <v>3040</v>
+        <v>22885</v>
       </c>
       <c r="D7" t="n">
-        <v>21</v>
+        <v>3012</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.9931</v>
+        <v>0.8837</v>
       </c>
     </row>
     <row r="8">
@@ -587,16 +587,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7889</v>
+        <v>16240</v>
       </c>
       <c r="C8" t="n">
-        <v>7052</v>
+        <v>11476</v>
       </c>
       <c r="D8" t="n">
-        <v>837</v>
+        <v>4764</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.8939</v>
+        <v>0.7067</v>
       </c>
     </row>
     <row r="9">
@@ -606,16 +606,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>24993</v>
+        <v>43757</v>
       </c>
       <c r="C9" t="n">
-        <v>23346</v>
+        <v>36955</v>
       </c>
       <c r="D9" t="n">
-        <v>1647</v>
+        <v>6802</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0.9340999999999999</v>
+        <v>0.8445999999999999</v>
       </c>
     </row>
     <row r="10">
@@ -642,10 +642,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>120648</v>
+        <v>191778</v>
       </c>
       <c r="C11" t="n">
-        <v>120648</v>
+        <v>191778</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -661,16 +661,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3050</v>
+        <v>2807</v>
       </c>
       <c r="C12" t="n">
-        <v>2760</v>
+        <v>2429</v>
       </c>
       <c r="D12" t="n">
-        <v>290</v>
+        <v>378</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>0.9048999999999999</v>
+        <v>0.8653</v>
       </c>
     </row>
     <row r="13">
@@ -680,10 +680,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2070</v>
+        <v>3624</v>
       </c>
       <c r="C13" t="n">
-        <v>2070</v>
+        <v>3624</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
@@ -699,16 +699,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>8466</v>
+        <v>4016</v>
       </c>
       <c r="C14" t="n">
-        <v>8465</v>
+        <v>3710</v>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>306</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0.9998999999999999</v>
+        <v>0.9238</v>
       </c>
     </row>
     <row r="15">
@@ -718,16 +718,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>775</v>
+        <v>647</v>
       </c>
       <c r="C15" t="n">
-        <v>774</v>
+        <v>647</v>
       </c>
       <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="E15" s="2" t="n">
-        <v>0.9987</v>
       </c>
     </row>
     <row r="16">
@@ -737,16 +737,16 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>535</v>
+        <v>167</v>
       </c>
       <c r="C16" t="n">
-        <v>534</v>
+        <v>135</v>
       </c>
       <c r="D16" t="n">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>0.9981</v>
+        <v>0.8084</v>
       </c>
     </row>
     <row r="17">
@@ -756,10 +756,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2856</v>
+        <v>6878</v>
       </c>
       <c r="C17" t="n">
-        <v>2856</v>
+        <v>6878</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
@@ -792,16 +792,16 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1013</v>
+        <v>1393</v>
       </c>
       <c r="C19" t="n">
-        <v>1011</v>
+        <v>1393</v>
       </c>
       <c r="D19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>0.998</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -811,16 +811,16 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5903</v>
+        <v>6217</v>
       </c>
       <c r="C20" t="n">
-        <v>5839</v>
+        <v>6061</v>
       </c>
       <c r="D20" t="n">
-        <v>64</v>
+        <v>156</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>0.9892</v>
+        <v>0.9749</v>
       </c>
     </row>
   </sheetData>

--- a/output/TRANSFERENCIA_atual.xlsx
+++ b/output/TRANSFERENCIA_atual.xlsx
@@ -473,16 +473,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1704</v>
+        <v>2234</v>
       </c>
       <c r="C2" t="n">
-        <v>1637</v>
+        <v>2205</v>
       </c>
       <c r="D2" t="n">
-        <v>67</v>
+        <v>29</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.9606999999999999</v>
+        <v>0.987</v>
       </c>
     </row>
     <row r="3">
@@ -492,16 +492,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2242</v>
+        <v>3607</v>
       </c>
       <c r="C3" t="n">
-        <v>2157</v>
+        <v>3463</v>
       </c>
       <c r="D3" t="n">
-        <v>85</v>
+        <v>144</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.9621</v>
+        <v>0.9601000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -511,16 +511,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>738</v>
+        <v>700</v>
       </c>
       <c r="C4" t="n">
-        <v>733</v>
+        <v>699</v>
       </c>
       <c r="D4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.9932</v>
+        <v>0.9986</v>
       </c>
     </row>
     <row r="5">
@@ -530,16 +530,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>444</v>
+        <v>344</v>
       </c>
       <c r="C5" t="n">
-        <v>389</v>
+        <v>344</v>
       </c>
       <c r="D5" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.8761</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -549,10 +549,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>21764</v>
+        <v>24134</v>
       </c>
       <c r="C6" t="n">
-        <v>21764</v>
+        <v>24134</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -568,16 +568,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>25897</v>
+        <v>24681</v>
       </c>
       <c r="C7" t="n">
-        <v>22885</v>
+        <v>22789</v>
       </c>
       <c r="D7" t="n">
-        <v>3012</v>
+        <v>1892</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.8837</v>
+        <v>0.9233</v>
       </c>
     </row>
     <row r="8">
@@ -587,16 +587,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>16240</v>
+        <v>19240</v>
       </c>
       <c r="C8" t="n">
-        <v>11476</v>
+        <v>10024</v>
       </c>
       <c r="D8" t="n">
-        <v>4764</v>
+        <v>9216</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.7067</v>
+        <v>0.521</v>
       </c>
     </row>
     <row r="9">
@@ -606,16 +606,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>43757</v>
+        <v>37330</v>
       </c>
       <c r="C9" t="n">
-        <v>36955</v>
+        <v>31302</v>
       </c>
       <c r="D9" t="n">
-        <v>6802</v>
+        <v>6028</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0.8445999999999999</v>
+        <v>0.8384999999999999</v>
       </c>
     </row>
     <row r="10">
@@ -642,10 +642,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>191778</v>
+        <v>131740</v>
       </c>
       <c r="C11" t="n">
-        <v>191778</v>
+        <v>131740</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -661,16 +661,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2807</v>
+        <v>3118</v>
       </c>
       <c r="C12" t="n">
-        <v>2429</v>
+        <v>2904</v>
       </c>
       <c r="D12" t="n">
-        <v>378</v>
+        <v>214</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>0.8653</v>
+        <v>0.9314</v>
       </c>
     </row>
     <row r="13">
@@ -680,10 +680,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3624</v>
+        <v>2542</v>
       </c>
       <c r="C13" t="n">
-        <v>3624</v>
+        <v>2542</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
@@ -699,16 +699,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4016</v>
+        <v>4562</v>
       </c>
       <c r="C14" t="n">
-        <v>3710</v>
+        <v>4221</v>
       </c>
       <c r="D14" t="n">
-        <v>306</v>
+        <v>341</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0.9238</v>
+        <v>0.9253</v>
       </c>
     </row>
     <row r="15">
@@ -718,16 +718,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>647</v>
+        <v>662</v>
       </c>
       <c r="C15" t="n">
-        <v>647</v>
+        <v>653</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>1</v>
+        <v>0.9864000000000001</v>
       </c>
     </row>
     <row r="16">
@@ -737,16 +737,16 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>167</v>
+        <v>281</v>
       </c>
       <c r="C16" t="n">
-        <v>135</v>
+        <v>271</v>
       </c>
       <c r="D16" t="n">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>0.8084</v>
+        <v>0.9643999999999999</v>
       </c>
     </row>
     <row r="17">
@@ -756,10 +756,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>6878</v>
+        <v>8729</v>
       </c>
       <c r="C17" t="n">
-        <v>6878</v>
+        <v>8729</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
@@ -792,16 +792,16 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1393</v>
+        <v>3903</v>
       </c>
       <c r="C19" t="n">
-        <v>1393</v>
+        <v>3859</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>1</v>
+        <v>0.9887</v>
       </c>
     </row>
     <row r="20">
@@ -811,16 +811,16 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>6217</v>
+        <v>6868</v>
       </c>
       <c r="C20" t="n">
-        <v>6061</v>
+        <v>6847</v>
       </c>
       <c r="D20" t="n">
-        <v>156</v>
+        <v>21</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>0.9749</v>
+        <v>0.9969</v>
       </c>
     </row>
   </sheetData>

--- a/output/TRANSFERENCIA_atual.xlsx
+++ b/output/TRANSFERENCIA_atual.xlsx
@@ -473,16 +473,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2234</v>
+        <v>1809</v>
       </c>
       <c r="C2" t="n">
-        <v>2205</v>
+        <v>1789</v>
       </c>
       <c r="D2" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.987</v>
+        <v>0.9889</v>
       </c>
     </row>
     <row r="3">
@@ -492,16 +492,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3607</v>
+        <v>1470</v>
       </c>
       <c r="C3" t="n">
-        <v>3463</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>144</v>
+        <v>1470</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.9601000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -511,16 +511,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>700</v>
+        <v>936</v>
       </c>
       <c r="C4" t="n">
-        <v>699</v>
+        <v>916</v>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.9986</v>
+        <v>0.9786</v>
       </c>
     </row>
     <row r="5">
@@ -530,16 +530,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>344</v>
+        <v>523</v>
       </c>
       <c r="C5" t="n">
-        <v>344</v>
+        <v>516</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>1</v>
+        <v>0.9865999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -549,10 +549,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>24134</v>
+        <v>21796</v>
       </c>
       <c r="C6" t="n">
-        <v>24134</v>
+        <v>21796</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -568,16 +568,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>24681</v>
+        <v>22344</v>
       </c>
       <c r="C7" t="n">
-        <v>22789</v>
+        <v>21008</v>
       </c>
       <c r="D7" t="n">
-        <v>1892</v>
+        <v>1336</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.9233</v>
+        <v>0.9401999999999999</v>
       </c>
     </row>
     <row r="8">
@@ -587,16 +587,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>19240</v>
+        <v>21540</v>
       </c>
       <c r="C8" t="n">
-        <v>10024</v>
+        <v>9549</v>
       </c>
       <c r="D8" t="n">
-        <v>9216</v>
+        <v>11991</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.521</v>
+        <v>0.4433</v>
       </c>
     </row>
     <row r="9">
@@ -606,16 +606,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>37330</v>
+        <v>30343</v>
       </c>
       <c r="C9" t="n">
-        <v>31302</v>
+        <v>27787</v>
       </c>
       <c r="D9" t="n">
-        <v>6028</v>
+        <v>2556</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0.8384999999999999</v>
+        <v>0.9157999999999999</v>
       </c>
     </row>
     <row r="10">
@@ -642,10 +642,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>131740</v>
+        <v>135609</v>
       </c>
       <c r="C11" t="n">
-        <v>131740</v>
+        <v>135609</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -661,16 +661,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3118</v>
+        <v>2539</v>
       </c>
       <c r="C12" t="n">
-        <v>2904</v>
+        <v>2532</v>
       </c>
       <c r="D12" t="n">
-        <v>214</v>
+        <v>7</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>0.9314</v>
+        <v>0.9972</v>
       </c>
     </row>
     <row r="13">
@@ -680,10 +680,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2542</v>
+        <v>2238</v>
       </c>
       <c r="C13" t="n">
-        <v>2542</v>
+        <v>2238</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
@@ -699,16 +699,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4562</v>
+        <v>3793</v>
       </c>
       <c r="C14" t="n">
-        <v>4221</v>
+        <v>3789</v>
       </c>
       <c r="D14" t="n">
-        <v>341</v>
+        <v>4</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0.9253</v>
+        <v>0.9989</v>
       </c>
     </row>
     <row r="15">
@@ -718,16 +718,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>662</v>
+        <v>418</v>
       </c>
       <c r="C15" t="n">
-        <v>653</v>
+        <v>415</v>
       </c>
       <c r="D15" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>0.9864000000000001</v>
+        <v>0.9928</v>
       </c>
     </row>
     <row r="16">
@@ -737,16 +737,16 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>281</v>
+        <v>200</v>
       </c>
       <c r="C16" t="n">
-        <v>271</v>
+        <v>191</v>
       </c>
       <c r="D16" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>0.9643999999999999</v>
+        <v>0.955</v>
       </c>
     </row>
     <row r="17">
@@ -756,10 +756,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>8729</v>
+        <v>6376</v>
       </c>
       <c r="C17" t="n">
-        <v>8729</v>
+        <v>6376</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
@@ -792,16 +792,16 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3903</v>
+        <v>1933</v>
       </c>
       <c r="C19" t="n">
-        <v>3859</v>
+        <v>1930</v>
       </c>
       <c r="D19" t="n">
-        <v>44</v>
+        <v>3</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>0.9887</v>
+        <v>0.9984000000000001</v>
       </c>
     </row>
     <row r="20">
@@ -811,16 +811,16 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>6868</v>
+        <v>6990</v>
       </c>
       <c r="C20" t="n">
-        <v>6847</v>
+        <v>6921</v>
       </c>
       <c r="D20" t="n">
-        <v>21</v>
+        <v>69</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>0.9969</v>
+        <v>0.9901000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/output/TRANSFERENCIA_atual.xlsx
+++ b/output/TRANSFERENCIA_atual.xlsx
@@ -473,16 +473,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1809</v>
+        <v>1997</v>
       </c>
       <c r="C2" t="n">
-        <v>1789</v>
+        <v>1977</v>
       </c>
       <c r="D2" t="n">
         <v>20</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.9889</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="3">
@@ -492,16 +492,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1470</v>
+        <v>1642</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>1587</v>
       </c>
       <c r="D3" t="n">
-        <v>1470</v>
+        <v>55</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0</v>
+        <v>0.9665</v>
       </c>
     </row>
     <row r="4">
@@ -511,17 +511,15 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>936</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>916</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>20</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>0.9786</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -530,17 +528,15 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>523</v>
+        <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>516</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>7</v>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>0.9865999999999999</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E5" s="2" t="n"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -549,10 +545,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>21796</v>
+        <v>17967</v>
       </c>
       <c r="C6" t="n">
-        <v>21796</v>
+        <v>17967</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -568,16 +564,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>22344</v>
+        <v>38129</v>
       </c>
       <c r="C7" t="n">
-        <v>21008</v>
+        <v>35028</v>
       </c>
       <c r="D7" t="n">
-        <v>1336</v>
+        <v>3101</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.9401999999999999</v>
+        <v>0.9187000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -587,16 +583,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>21540</v>
+        <v>19082</v>
       </c>
       <c r="C8" t="n">
-        <v>9549</v>
+        <v>10592</v>
       </c>
       <c r="D8" t="n">
-        <v>11991</v>
+        <v>8490</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.4433</v>
+        <v>0.5550999999999999</v>
       </c>
     </row>
     <row r="9">
@@ -606,16 +602,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>30343</v>
+        <v>7398</v>
       </c>
       <c r="C9" t="n">
-        <v>27787</v>
+        <v>6168</v>
       </c>
       <c r="D9" t="n">
-        <v>2556</v>
+        <v>1230</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0.9157999999999999</v>
+        <v>0.8337</v>
       </c>
     </row>
     <row r="10">
@@ -642,10 +638,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>135609</v>
+        <v>162317</v>
       </c>
       <c r="C11" t="n">
-        <v>135609</v>
+        <v>162317</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -661,16 +657,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2539</v>
+        <v>1565</v>
       </c>
       <c r="C12" t="n">
-        <v>2532</v>
+        <v>1565</v>
       </c>
       <c r="D12" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>0.9972</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -680,10 +676,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2238</v>
+        <v>1865</v>
       </c>
       <c r="C13" t="n">
-        <v>2238</v>
+        <v>1865</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
@@ -699,16 +695,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3793</v>
+        <v>3373</v>
       </c>
       <c r="C14" t="n">
-        <v>3789</v>
+        <v>3367</v>
       </c>
       <c r="D14" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0.9989</v>
+        <v>0.9982</v>
       </c>
     </row>
     <row r="15">
@@ -718,17 +714,15 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>418</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>415</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>3</v>
-      </c>
-      <c r="E15" s="2" t="n">
-        <v>0.9928</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E15" s="2" t="n"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -737,17 +731,15 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>191</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
-      </c>
-      <c r="E16" s="2" t="n">
-        <v>0.955</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E16" s="2" t="n"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -756,10 +748,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>6376</v>
+        <v>5140</v>
       </c>
       <c r="C17" t="n">
-        <v>6376</v>
+        <v>5140</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
@@ -792,17 +784,15 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1933</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>1930</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>3</v>
-      </c>
-      <c r="E19" s="2" t="n">
-        <v>0.9984000000000001</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E19" s="2" t="n"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -811,16 +801,16 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>6990</v>
+        <v>4592</v>
       </c>
       <c r="C20" t="n">
-        <v>6921</v>
+        <v>4591</v>
       </c>
       <c r="D20" t="n">
-        <v>69</v>
+        <v>1</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>0.9901000000000001</v>
+        <v>0.9998</v>
       </c>
     </row>
   </sheetData>

--- a/output/TRANSFERENCIA_atual.xlsx
+++ b/output/TRANSFERENCIA_atual.xlsx
@@ -473,17 +473,15 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1997</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>1977</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>20</v>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>0.99</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -492,17 +490,15 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1642</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>1587</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>55</v>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>0.9665</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -545,10 +541,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>17967</v>
+        <v>8252</v>
       </c>
       <c r="C6" t="n">
-        <v>17967</v>
+        <v>8252</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -564,16 +560,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>38129</v>
+        <v>10</v>
       </c>
       <c r="C7" t="n">
-        <v>35028</v>
+        <v>10</v>
       </c>
       <c r="D7" t="n">
-        <v>3101</v>
+        <v>0</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.9187000000000001</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -583,16 +579,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>19082</v>
+        <v>8431</v>
       </c>
       <c r="C8" t="n">
-        <v>10592</v>
+        <v>6643</v>
       </c>
       <c r="D8" t="n">
-        <v>8490</v>
+        <v>1788</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.5550999999999999</v>
+        <v>0.7879</v>
       </c>
     </row>
     <row r="9">
@@ -602,17 +598,15 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7398</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>6168</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>1230</v>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>0.8337</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E9" s="2" t="n"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -638,10 +632,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>162317</v>
+        <v>172221</v>
       </c>
       <c r="C11" t="n">
-        <v>162317</v>
+        <v>172221</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -657,17 +651,15 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1565</v>
+        <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>1565</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
-      <c r="E12" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="E12" s="2" t="n"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -676,10 +668,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1865</v>
+        <v>615</v>
       </c>
       <c r="C13" t="n">
-        <v>1865</v>
+        <v>615</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
@@ -695,17 +687,15 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3373</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>3367</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>6</v>
-      </c>
-      <c r="E14" s="2" t="n">
-        <v>0.9982</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E14" s="2" t="n"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -748,10 +738,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>5140</v>
+        <v>7174</v>
       </c>
       <c r="C17" t="n">
-        <v>5140</v>
+        <v>7174</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
@@ -801,16 +791,16 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4592</v>
+        <v>1499</v>
       </c>
       <c r="C20" t="n">
-        <v>4591</v>
+        <v>1498</v>
       </c>
       <c r="D20" t="n">
         <v>1</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>0.9998</v>
+        <v>0.9993000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/output/TRANSFERENCIA_atual.xlsx
+++ b/output/TRANSFERENCIA_atual.xlsx
@@ -473,15 +473,17 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>3901</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>3852</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" s="2" t="n"/>
+        <v>49</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>0.9873999999999999</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -490,15 +492,17 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>2933</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>2851</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" s="2" t="n"/>
+        <v>82</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>0.972</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -507,15 +511,17 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>1506</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>1504</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" s="2" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>0.9987</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -524,15 +530,17 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>693</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>690</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" s="2" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>0.9956999999999999</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -541,17 +549,15 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8252</v>
+        <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>8252</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
-      <c r="E6" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="E6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -560,16 +566,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="C7" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="8">
@@ -579,17 +585,15 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8431</v>
+        <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>6643</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>1788</v>
-      </c>
-      <c r="E8" s="2" t="n">
-        <v>0.7879</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E8" s="2" t="n"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -598,15 +602,17 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>21521</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>17543</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" s="2" t="n"/>
+        <v>3978</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>0.8151999999999999</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -632,10 +638,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>172221</v>
+        <v>84903</v>
       </c>
       <c r="C11" t="n">
-        <v>172221</v>
+        <v>84903</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -651,15 +657,17 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>3175</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>3019</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" s="2" t="n"/>
+        <v>156</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>0.9509000000000001</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -668,17 +676,15 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>615</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>615</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
       </c>
-      <c r="E13" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="E13" s="2" t="n"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -687,15 +693,17 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>4503</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>4502</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" s="2" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>0.9998</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -704,15 +712,17 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>894</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>894</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
       </c>
-      <c r="E15" s="2" t="n"/>
+      <c r="E15" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -721,15 +731,17 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>420</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>418</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" s="2" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>0.9952</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -738,10 +750,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>7174</v>
+        <v>5175</v>
       </c>
       <c r="C17" t="n">
-        <v>7174</v>
+        <v>5175</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
@@ -774,15 +786,17 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>2621</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>2550</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" s="2" t="n"/>
+        <v>71</v>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>0.9729000000000001</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -791,16 +805,16 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1499</v>
+        <v>8326</v>
       </c>
       <c r="C20" t="n">
-        <v>1498</v>
+        <v>8085</v>
       </c>
       <c r="D20" t="n">
-        <v>1</v>
+        <v>241</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>0.9993000000000001</v>
+        <v>0.9711</v>
       </c>
     </row>
   </sheetData>

--- a/output/TRANSFERENCIA_atual.xlsx
+++ b/output/TRANSFERENCIA_atual.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Taxa de Transferência" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Taxa de Transferência'!$A$1:$E$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Taxa de Transferência'!$A$1:$F$34</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,14 +429,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:F34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -447,20 +448,25 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Tipo</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>Total de Entregas</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Entregues no Prazo</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Fora do Prazo</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Taxa de Transferência</t>
         </is>
@@ -472,17 +478,22 @@
           <t>PA CEA-SP</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>3901</v>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
       </c>
       <c r="C2" t="n">
-        <v>3852</v>
+        <v>3270</v>
       </c>
       <c r="D2" t="n">
-        <v>49</v>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>0.9873999999999999</v>
+        <v>3218</v>
+      </c>
+      <c r="E2" t="n">
+        <v>52</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>0.9841</v>
       </c>
     </row>
     <row r="3">
@@ -491,17 +502,22 @@
           <t>PA CUBBO-EMB-SP</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>2933</v>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
       </c>
       <c r="C3" t="n">
-        <v>2851</v>
+        <v>1850</v>
       </c>
       <c r="D3" t="n">
-        <v>82</v>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>0.972</v>
+        <v>1805</v>
+      </c>
+      <c r="E3" t="n">
+        <v>45</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>0.9756999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -510,16 +526,21 @@
           <t>PA ESTOCA-VGP-SP</t>
         </is>
       </c>
-      <c r="B4" t="n">
-        <v>1506</v>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
       </c>
       <c r="C4" t="n">
-        <v>1504</v>
+        <v>1575</v>
       </c>
       <c r="D4" t="n">
+        <v>1573</v>
+      </c>
+      <c r="E4" t="n">
         <v>2</v>
       </c>
-      <c r="E4" s="2" t="n">
+      <c r="F4" s="2" t="n">
         <v>0.9987</v>
       </c>
     </row>
@@ -529,17 +550,22 @@
           <t>PA INFRA-SP</t>
         </is>
       </c>
-      <c r="B5" t="n">
-        <v>693</v>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
       </c>
       <c r="C5" t="n">
-        <v>690</v>
+        <v>1014</v>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>0.9956999999999999</v>
+        <v>972</v>
+      </c>
+      <c r="E5" t="n">
+        <v>42</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>0.9586</v>
       </c>
     </row>
     <row r="6">
@@ -548,16 +574,23 @@
           <t>PA MANDAE-SP</t>
         </is>
       </c>
-      <c r="B6" t="n">
-        <v>0</v>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>8937</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" s="2" t="n"/>
+        <v>8937</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -565,17 +598,22 @@
           <t>PA MELI-BRE-SP</t>
         </is>
       </c>
-      <c r="B7" t="n">
-        <v>25</v>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
       </c>
       <c r="C7" t="n">
-        <v>23</v>
+        <v>11208</v>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
-      </c>
-      <c r="E7" s="2" t="n">
-        <v>0.92</v>
+        <v>10904</v>
+      </c>
+      <c r="E7" t="n">
+        <v>304</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>0.9729000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -584,16 +622,23 @@
           <t>PA MELI-CJM 02-SP</t>
         </is>
       </c>
-      <c r="B8" t="n">
-        <v>0</v>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>9156</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="2" t="n"/>
+        <v>4603</v>
+      </c>
+      <c r="E8" t="n">
+        <v>4553</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>0.5027</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -601,17 +646,22 @@
           <t>PA MELI-CJM 04-SP</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>21521</v>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
       </c>
       <c r="C9" t="n">
-        <v>17543</v>
+        <v>30087</v>
       </c>
       <c r="D9" t="n">
-        <v>3978</v>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>0.8151999999999999</v>
+        <v>25286</v>
+      </c>
+      <c r="E9" t="n">
+        <v>4801</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>0.8404</v>
       </c>
     </row>
     <row r="10">
@@ -620,8 +670,10 @@
           <t>PA MELI-CJM 14-SP</t>
         </is>
       </c>
-      <c r="B10" t="n">
-        <v>0</v>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
       </c>
       <c r="C10" t="n">
         <v>0</v>
@@ -629,7 +681,10 @@
       <c r="D10" t="n">
         <v>0</v>
       </c>
-      <c r="E10" s="2" t="n"/>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="2" t="n"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -637,16 +692,21 @@
           <t>PA MELI-CJM-SP</t>
         </is>
       </c>
-      <c r="B11" t="n">
-        <v>84903</v>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
       </c>
       <c r="C11" t="n">
-        <v>84903</v>
+        <v>114867</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" s="2" t="n">
+        <v>114867</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -656,17 +716,22 @@
           <t>PA NESTLE-SP</t>
         </is>
       </c>
-      <c r="B12" t="n">
-        <v>3175</v>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
       </c>
       <c r="C12" t="n">
-        <v>3019</v>
+        <v>2781</v>
       </c>
       <c r="D12" t="n">
-        <v>156</v>
-      </c>
-      <c r="E12" s="2" t="n">
-        <v>0.9509000000000001</v>
+        <v>2674</v>
+      </c>
+      <c r="E12" t="n">
+        <v>107</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>0.9615</v>
       </c>
     </row>
     <row r="13">
@@ -675,16 +740,23 @@
           <t>PA OLIST-SP</t>
         </is>
       </c>
-      <c r="B13" t="n">
-        <v>0</v>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>2172</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" s="2" t="n"/>
+        <v>2172</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -692,17 +764,22 @@
           <t>PA RENNER-CAB-SP</t>
         </is>
       </c>
-      <c r="B14" t="n">
-        <v>4503</v>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
       </c>
       <c r="C14" t="n">
-        <v>4502</v>
+        <v>5181</v>
       </c>
       <c r="D14" t="n">
+        <v>5181</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="E14" s="2" t="n">
-        <v>0.9998</v>
       </c>
     </row>
     <row r="15">
@@ -711,17 +788,22 @@
           <t>PA SATELITAL-SP</t>
         </is>
       </c>
-      <c r="B15" t="n">
-        <v>894</v>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
       </c>
       <c r="C15" t="n">
-        <v>894</v>
+        <v>1309</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" s="2" t="n">
+        <v>1308</v>
+      </c>
+      <c r="E15" t="n">
         <v>1</v>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>0.9992</v>
       </c>
     </row>
     <row r="16">
@@ -730,17 +812,22 @@
           <t>PA SATELITAL-VGP-SP</t>
         </is>
       </c>
-      <c r="B16" t="n">
-        <v>420</v>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
       </c>
       <c r="C16" t="n">
-        <v>418</v>
+        <v>390</v>
       </c>
       <c r="D16" t="n">
-        <v>2</v>
-      </c>
-      <c r="E16" s="2" t="n">
-        <v>0.9952</v>
+        <v>389</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>0.9974</v>
       </c>
     </row>
     <row r="17">
@@ -749,16 +836,21 @@
           <t>PA SHOPEE-BRE-SP</t>
         </is>
       </c>
-      <c r="B17" t="n">
-        <v>5175</v>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
       </c>
       <c r="C17" t="n">
-        <v>5175</v>
+        <v>2414</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" s="2" t="n">
+        <v>2414</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -768,8 +860,10 @@
           <t>PA VIA-SP</t>
         </is>
       </c>
-      <c r="B18" t="n">
-        <v>0</v>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
       </c>
       <c r="C18" t="n">
         <v>0</v>
@@ -777,7 +871,10 @@
       <c r="D18" t="n">
         <v>0</v>
       </c>
-      <c r="E18" s="2" t="n"/>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="2" t="n"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -785,17 +882,22 @@
           <t>PA WEPINK-ITP 02-SP</t>
         </is>
       </c>
-      <c r="B19" t="n">
-        <v>2621</v>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
       </c>
       <c r="C19" t="n">
-        <v>2550</v>
+        <v>1376</v>
       </c>
       <c r="D19" t="n">
-        <v>71</v>
-      </c>
-      <c r="E19" s="2" t="n">
-        <v>0.9729000000000001</v>
+        <v>1376</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -804,21 +906,350 @@
           <t>PA WEPINK-ITP-SP</t>
         </is>
       </c>
-      <c r="B20" t="n">
-        <v>8326</v>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
       </c>
       <c r="C20" t="n">
-        <v>8085</v>
+        <v>9499</v>
       </c>
       <c r="D20" t="n">
-        <v>241</v>
-      </c>
-      <c r="E20" s="2" t="n">
-        <v>0.9711</v>
-      </c>
+        <v>9318</v>
+      </c>
+      <c r="E20" t="n">
+        <v>181</v>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>0.9809</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>CARAP 02-SP</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="2" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>CARAP-SP</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>3620</v>
+      </c>
+      <c r="D22" t="n">
+        <v>3520</v>
+      </c>
+      <c r="E22" t="n">
+        <v>100</v>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>0.9723999999999999</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>35150</v>
+      </c>
+      <c r="D23" t="n">
+        <v>33481</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1669</v>
+      </c>
+      <c r="F23" s="2" t="n">
+        <v>0.9525</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" s="2" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>COT-SP</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>50167</v>
+      </c>
+      <c r="D25" t="n">
+        <v>48640</v>
+      </c>
+      <c r="E25" t="n">
+        <v>1527</v>
+      </c>
+      <c r="F25" s="2" t="n">
+        <v>0.9695999999999999</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>12885</v>
+      </c>
+      <c r="D26" t="n">
+        <v>7795</v>
+      </c>
+      <c r="E26" t="n">
+        <v>5090</v>
+      </c>
+      <c r="F26" s="2" t="n">
+        <v>0.605</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>10222</v>
+      </c>
+      <c r="D27" t="n">
+        <v>1193</v>
+      </c>
+      <c r="E27" t="n">
+        <v>9029</v>
+      </c>
+      <c r="F27" s="2" t="n">
+        <v>0.1167</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" s="2" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>167</v>
+      </c>
+      <c r="D29" t="n">
+        <v>59</v>
+      </c>
+      <c r="E29" t="n">
+        <v>108</v>
+      </c>
+      <c r="F29" s="2" t="n">
+        <v>0.3533</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" s="2" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>OSC 02-SP</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" s="2" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>OSC-SP</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>6887</v>
+      </c>
+      <c r="D32" t="n">
+        <v>6097</v>
+      </c>
+      <c r="E32" t="n">
+        <v>790</v>
+      </c>
+      <c r="F32" s="2" t="n">
+        <v>0.8853</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>5395</v>
+      </c>
+      <c r="D33" t="n">
+        <v>5395</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" s="2" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E20"/>
+  <autoFilter ref="A1:F34"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/TRANSFERENCIA_atual.xlsx
+++ b/output/TRANSFERENCIA_atual.xlsx
@@ -484,16 +484,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3270</v>
+        <v>1934</v>
       </c>
       <c r="D2" t="n">
-        <v>3218</v>
+        <v>1899</v>
       </c>
       <c r="E2" t="n">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.9841</v>
+        <v>0.9819</v>
       </c>
     </row>
     <row r="3">
@@ -508,13 +508,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1850</v>
+        <v>1399</v>
       </c>
       <c r="D3" t="n">
-        <v>1805</v>
+        <v>1365</v>
       </c>
       <c r="E3" t="n">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>0.9756999999999999</v>
@@ -532,16 +532,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1575</v>
+        <v>1530</v>
       </c>
       <c r="D4" t="n">
-        <v>1573</v>
+        <v>1517</v>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.9987</v>
+        <v>0.9915</v>
       </c>
     </row>
     <row r="5">
@@ -556,16 +556,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1014</v>
+        <v>255</v>
       </c>
       <c r="D5" t="n">
-        <v>972</v>
+        <v>253</v>
       </c>
       <c r="E5" t="n">
-        <v>42</v>
+        <v>2</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.9586</v>
+        <v>0.9922</v>
       </c>
     </row>
     <row r="6">
@@ -580,10 +580,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>8937</v>
+        <v>21812</v>
       </c>
       <c r="D6" t="n">
-        <v>8937</v>
+        <v>21812</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -604,16 +604,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>11208</v>
+        <v>21510</v>
       </c>
       <c r="D7" t="n">
-        <v>10904</v>
+        <v>12344</v>
       </c>
       <c r="E7" t="n">
-        <v>304</v>
+        <v>9166</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.9729000000000001</v>
+        <v>0.5739</v>
       </c>
     </row>
     <row r="8">
@@ -628,16 +628,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>9156</v>
+        <v>19612</v>
       </c>
       <c r="D8" t="n">
-        <v>4603</v>
+        <v>11773</v>
       </c>
       <c r="E8" t="n">
-        <v>4553</v>
+        <v>7839</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.5027</v>
+        <v>0.6003000000000001</v>
       </c>
     </row>
     <row r="9">
@@ -652,16 +652,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>30087</v>
+        <v>27190</v>
       </c>
       <c r="D9" t="n">
-        <v>25286</v>
+        <v>17018</v>
       </c>
       <c r="E9" t="n">
-        <v>4801</v>
+        <v>10172</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0.8404</v>
+        <v>0.6259</v>
       </c>
     </row>
     <row r="10">
@@ -698,10 +698,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>114867</v>
+        <v>175900</v>
       </c>
       <c r="D11" t="n">
-        <v>114867</v>
+        <v>175900</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -722,16 +722,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2781</v>
+        <v>3112</v>
       </c>
       <c r="D12" t="n">
-        <v>2674</v>
+        <v>2716</v>
       </c>
       <c r="E12" t="n">
-        <v>107</v>
+        <v>396</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>0.9615</v>
+        <v>0.8728</v>
       </c>
     </row>
     <row r="13">
@@ -746,10 +746,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2172</v>
+        <v>3656</v>
       </c>
       <c r="D13" t="n">
-        <v>2172</v>
+        <v>3656</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -770,16 +770,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>5181</v>
+        <v>4279</v>
       </c>
       <c r="D14" t="n">
-        <v>5181</v>
+        <v>4277</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>1</v>
+        <v>0.9995000000000001</v>
       </c>
     </row>
     <row r="15">
@@ -794,16 +794,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1309</v>
+        <v>462</v>
       </c>
       <c r="D15" t="n">
-        <v>1308</v>
+        <v>462</v>
       </c>
       <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="F15" s="2" t="n">
-        <v>0.9992</v>
       </c>
     </row>
     <row r="16">
@@ -818,16 +818,16 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>390</v>
+        <v>836</v>
       </c>
       <c r="D16" t="n">
-        <v>389</v>
+        <v>795</v>
       </c>
       <c r="E16" t="n">
-        <v>1</v>
+        <v>41</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>0.9974</v>
+        <v>0.951</v>
       </c>
     </row>
     <row r="17">
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>2414</v>
+        <v>6433</v>
       </c>
       <c r="D17" t="n">
-        <v>2414</v>
+        <v>6433</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -888,16 +888,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1376</v>
+        <v>1177</v>
       </c>
       <c r="D19" t="n">
-        <v>1376</v>
+        <v>1142</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>1</v>
+        <v>0.9703000000000001</v>
       </c>
     </row>
     <row r="20">
@@ -912,16 +912,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>9499</v>
+        <v>8534</v>
       </c>
       <c r="D20" t="n">
-        <v>9318</v>
+        <v>6622</v>
       </c>
       <c r="E20" t="n">
-        <v>181</v>
+        <v>1912</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>0.9809</v>
+        <v>0.7759999999999999</v>
       </c>
     </row>
     <row r="21">
@@ -958,16 +958,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>3620</v>
+        <v>2737</v>
       </c>
       <c r="D22" t="n">
-        <v>3520</v>
+        <v>2616</v>
       </c>
       <c r="E22" t="n">
-        <v>100</v>
+        <v>121</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>0.9723999999999999</v>
+        <v>0.9558</v>
       </c>
     </row>
     <row r="23">
@@ -982,16 +982,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>35150</v>
+        <v>20138</v>
       </c>
       <c r="D23" t="n">
-        <v>33481</v>
+        <v>19605</v>
       </c>
       <c r="E23" t="n">
-        <v>1669</v>
+        <v>533</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>0.9525</v>
+        <v>0.9734999999999999</v>
       </c>
     </row>
     <row r="24">
@@ -1028,16 +1028,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>50167</v>
+        <v>39681</v>
       </c>
       <c r="D25" t="n">
-        <v>48640</v>
+        <v>38889</v>
       </c>
       <c r="E25" t="n">
-        <v>1527</v>
+        <v>792</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>0.9695999999999999</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="26">
@@ -1052,16 +1052,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>12885</v>
+        <v>20456</v>
       </c>
       <c r="D26" t="n">
-        <v>7795</v>
+        <v>15202</v>
       </c>
       <c r="E26" t="n">
-        <v>5090</v>
+        <v>5254</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>0.605</v>
+        <v>0.7432</v>
       </c>
     </row>
     <row r="27">
@@ -1076,16 +1076,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>10222</v>
+        <v>16714</v>
       </c>
       <c r="D27" t="n">
-        <v>1193</v>
+        <v>7380</v>
       </c>
       <c r="E27" t="n">
-        <v>9029</v>
+        <v>9334</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>0.1167</v>
+        <v>0.4415</v>
       </c>
     </row>
     <row r="28">
@@ -1122,16 +1122,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>167</v>
+        <v>2444</v>
       </c>
       <c r="D29" t="n">
-        <v>59</v>
+        <v>2085</v>
       </c>
       <c r="E29" t="n">
-        <v>108</v>
+        <v>359</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>0.3533</v>
+        <v>0.8531</v>
       </c>
     </row>
     <row r="30">
@@ -1146,15 +1146,17 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
       </c>
-      <c r="F30" s="2" t="n"/>
+      <c r="F30" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1190,16 +1192,16 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>6887</v>
+        <v>6441</v>
       </c>
       <c r="D32" t="n">
-        <v>6097</v>
+        <v>6298</v>
       </c>
       <c r="E32" t="n">
-        <v>790</v>
+        <v>143</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>0.8853</v>
+        <v>0.9778</v>
       </c>
     </row>
     <row r="33">
@@ -1214,16 +1216,16 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>5395</v>
+        <v>23633</v>
       </c>
       <c r="D33" t="n">
-        <v>5395</v>
+        <v>23191</v>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>442</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>1</v>
+        <v>0.9813</v>
       </c>
     </row>
     <row r="34">

--- a/output/TRANSFERENCIA_atual.xlsx
+++ b/output/TRANSFERENCIA_atual.xlsx
@@ -484,16 +484,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1934</v>
+        <v>2416</v>
       </c>
       <c r="D2" t="n">
-        <v>1899</v>
+        <v>2391</v>
       </c>
       <c r="E2" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.9819</v>
+        <v>0.9897</v>
       </c>
     </row>
     <row r="3">
@@ -508,16 +508,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1399</v>
+        <v>875</v>
       </c>
       <c r="D3" t="n">
-        <v>1365</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>34</v>
+        <v>875</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.9756999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -532,17 +532,15 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1530</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>1517</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>13</v>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>0.9915</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -556,17 +554,15 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>255</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>253</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>2</v>
-      </c>
-      <c r="F5" s="2" t="n">
-        <v>0.9922</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F5" s="2" t="n"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -580,10 +576,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>21812</v>
+        <v>18824</v>
       </c>
       <c r="D6" t="n">
-        <v>21812</v>
+        <v>18824</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -604,16 +600,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>21510</v>
+        <v>37132</v>
       </c>
       <c r="D7" t="n">
-        <v>12344</v>
+        <v>14526</v>
       </c>
       <c r="E7" t="n">
-        <v>9166</v>
+        <v>22606</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.5739</v>
+        <v>0.3912</v>
       </c>
     </row>
     <row r="8">
@@ -628,16 +624,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>19612</v>
+        <v>14496</v>
       </c>
       <c r="D8" t="n">
-        <v>11773</v>
+        <v>10589</v>
       </c>
       <c r="E8" t="n">
-        <v>7839</v>
+        <v>3907</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.6003000000000001</v>
+        <v>0.7304999999999999</v>
       </c>
     </row>
     <row r="9">
@@ -652,16 +648,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>27190</v>
+        <v>7294</v>
       </c>
       <c r="D9" t="n">
-        <v>17018</v>
+        <v>6316</v>
       </c>
       <c r="E9" t="n">
-        <v>10172</v>
+        <v>978</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0.6259</v>
+        <v>0.8659</v>
       </c>
     </row>
     <row r="10">
@@ -698,10 +694,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>175900</v>
+        <v>155143</v>
       </c>
       <c r="D11" t="n">
-        <v>175900</v>
+        <v>155143</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -722,16 +718,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>3112</v>
+        <v>1269</v>
       </c>
       <c r="D12" t="n">
-        <v>2716</v>
+        <v>1268</v>
       </c>
       <c r="E12" t="n">
-        <v>396</v>
+        <v>1</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>0.8728</v>
+        <v>0.9992</v>
       </c>
     </row>
     <row r="13">
@@ -746,10 +742,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3656</v>
+        <v>2428</v>
       </c>
       <c r="D13" t="n">
-        <v>3656</v>
+        <v>2428</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -770,16 +766,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>4279</v>
+        <v>2775</v>
       </c>
       <c r="D14" t="n">
-        <v>4277</v>
+        <v>2775</v>
       </c>
       <c r="E14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0.9995000000000001</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -794,17 +790,15 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>462</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>462</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
       </c>
-      <c r="F15" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="F15" s="2" t="n"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -818,17 +812,15 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>836</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>795</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>41</v>
-      </c>
-      <c r="F16" s="2" t="n">
-        <v>0.951</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F16" s="2" t="n"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -842,10 +834,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>6433</v>
+        <v>8661</v>
       </c>
       <c r="D17" t="n">
-        <v>6433</v>
+        <v>8661</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -888,17 +880,15 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1177</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>1142</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>35</v>
-      </c>
-      <c r="F19" s="2" t="n">
-        <v>0.9703000000000001</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F19" s="2" t="n"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -912,16 +902,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>8534</v>
+        <v>5703</v>
       </c>
       <c r="D20" t="n">
-        <v>6622</v>
+        <v>5605</v>
       </c>
       <c r="E20" t="n">
-        <v>1912</v>
+        <v>98</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>0.7759999999999999</v>
+        <v>0.9828</v>
       </c>
     </row>
     <row r="21">
@@ -958,16 +948,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>2737</v>
+        <v>1360</v>
       </c>
       <c r="D22" t="n">
-        <v>2616</v>
+        <v>1356</v>
       </c>
       <c r="E22" t="n">
-        <v>121</v>
+        <v>4</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>0.9558</v>
+        <v>0.9971</v>
       </c>
     </row>
     <row r="23">
@@ -982,16 +972,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>20138</v>
+        <v>8573</v>
       </c>
       <c r="D23" t="n">
-        <v>19605</v>
+        <v>8571</v>
       </c>
       <c r="E23" t="n">
-        <v>533</v>
+        <v>2</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>0.9734999999999999</v>
+        <v>0.9998</v>
       </c>
     </row>
     <row r="24">
@@ -1028,16 +1018,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>39681</v>
+        <v>18281</v>
       </c>
       <c r="D25" t="n">
-        <v>38889</v>
+        <v>18278</v>
       </c>
       <c r="E25" t="n">
-        <v>792</v>
+        <v>3</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>0.98</v>
+        <v>0.9998</v>
       </c>
     </row>
     <row r="26">
@@ -1052,16 +1042,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>20456</v>
+        <v>11910</v>
       </c>
       <c r="D26" t="n">
-        <v>15202</v>
+        <v>11529</v>
       </c>
       <c r="E26" t="n">
-        <v>5254</v>
+        <v>381</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>0.7432</v>
+        <v>0.968</v>
       </c>
     </row>
     <row r="27">
@@ -1076,16 +1066,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>16714</v>
+        <v>13891</v>
       </c>
       <c r="D27" t="n">
-        <v>7380</v>
+        <v>13644</v>
       </c>
       <c r="E27" t="n">
-        <v>9334</v>
+        <v>247</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>0.4415</v>
+        <v>0.9822</v>
       </c>
     </row>
     <row r="28">
@@ -1100,15 +1090,17 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
-      </c>
-      <c r="F28" s="2" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="F28" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1122,16 +1114,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>2444</v>
+        <v>3740</v>
       </c>
       <c r="D29" t="n">
-        <v>2085</v>
+        <v>3444</v>
       </c>
       <c r="E29" t="n">
-        <v>359</v>
+        <v>296</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>0.8531</v>
+        <v>0.9209000000000001</v>
       </c>
     </row>
     <row r="30">
@@ -1146,16 +1138,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>5</v>
+        <v>366</v>
       </c>
       <c r="D30" t="n">
-        <v>5</v>
+        <v>353</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>1</v>
+        <v>0.9645</v>
       </c>
     </row>
     <row r="31">
@@ -1192,16 +1184,16 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>6441</v>
+        <v>3830</v>
       </c>
       <c r="D32" t="n">
-        <v>6298</v>
+        <v>3829</v>
       </c>
       <c r="E32" t="n">
-        <v>143</v>
+        <v>1</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>0.9778</v>
+        <v>0.9997</v>
       </c>
     </row>
     <row r="33">
@@ -1216,16 +1208,16 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>23633</v>
+        <v>29860</v>
       </c>
       <c r="D33" t="n">
-        <v>23191</v>
+        <v>29443</v>
       </c>
       <c r="E33" t="n">
-        <v>442</v>
+        <v>417</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>0.9813</v>
+        <v>0.986</v>
       </c>
     </row>
     <row r="34">

--- a/output/TRANSFERENCIA_atual.xlsx
+++ b/output/TRANSFERENCIA_atual.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Taxa de Transferência" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Taxa de Transferência" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Taxa de Transferência'!$A$1:$F$34</definedName>
@@ -484,16 +484,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2416</v>
+        <v>5209</v>
       </c>
       <c r="D2" t="n">
-        <v>2391</v>
+        <v>5151</v>
       </c>
       <c r="E2" t="n">
-        <v>25</v>
+        <v>58</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.9897</v>
+        <v>0.9889</v>
       </c>
     </row>
     <row r="3">
@@ -508,16 +508,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>875</v>
+        <v>2002</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>1106</v>
       </c>
       <c r="E3" t="n">
-        <v>875</v>
+        <v>896</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0</v>
+        <v>0.5524</v>
       </c>
     </row>
     <row r="4">
@@ -532,15 +532,17 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>1158</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>1132</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" s="2" t="n"/>
+        <v>26</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>0.9775</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -554,15 +556,17 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>438</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>357</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="2" t="n"/>
+        <v>81</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>0.8151</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -576,10 +580,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>18824</v>
+        <v>23717</v>
       </c>
       <c r="D6" t="n">
-        <v>18824</v>
+        <v>23717</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -600,16 +604,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>37132</v>
+        <v>53771</v>
       </c>
       <c r="D7" t="n">
-        <v>14526</v>
+        <v>28158</v>
       </c>
       <c r="E7" t="n">
-        <v>22606</v>
+        <v>25613</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.3912</v>
+        <v>0.5236999999999999</v>
       </c>
     </row>
     <row r="8">
@@ -624,16 +628,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>14496</v>
+        <v>20023</v>
       </c>
       <c r="D8" t="n">
-        <v>10589</v>
+        <v>13836</v>
       </c>
       <c r="E8" t="n">
-        <v>3907</v>
+        <v>6187</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.7304999999999999</v>
+        <v>0.6909999999999999</v>
       </c>
     </row>
     <row r="9">
@@ -648,16 +652,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>7294</v>
+        <v>22280</v>
       </c>
       <c r="D9" t="n">
-        <v>6316</v>
+        <v>18216</v>
       </c>
       <c r="E9" t="n">
-        <v>978</v>
+        <v>4064</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0.8659</v>
+        <v>0.8176000000000001</v>
       </c>
     </row>
     <row r="10">
@@ -694,10 +698,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>155143</v>
+        <v>141958</v>
       </c>
       <c r="D11" t="n">
-        <v>155143</v>
+        <v>141958</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -718,16 +722,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1269</v>
+        <v>3375</v>
       </c>
       <c r="D12" t="n">
-        <v>1268</v>
+        <v>3186</v>
       </c>
       <c r="E12" t="n">
-        <v>1</v>
+        <v>189</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>0.9992</v>
+        <v>0.9440000000000001</v>
       </c>
     </row>
     <row r="13">
@@ -742,10 +746,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2428</v>
+        <v>2530</v>
       </c>
       <c r="D13" t="n">
-        <v>2428</v>
+        <v>2530</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -766,16 +770,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2775</v>
+        <v>6301</v>
       </c>
       <c r="D14" t="n">
-        <v>2775</v>
+        <v>6293</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>1</v>
+        <v>0.9987</v>
       </c>
     </row>
     <row r="15">
@@ -812,15 +816,17 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>1049</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>1009</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" s="2" t="n"/>
+        <v>40</v>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>0.9619</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -834,10 +840,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>8661</v>
+        <v>7990</v>
       </c>
       <c r="D17" t="n">
-        <v>8661</v>
+        <v>7990</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -880,15 +886,17 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>1452</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>1444</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" s="2" t="n"/>
+        <v>8</v>
+      </c>
+      <c r="F19" s="2" t="n">
+        <v>0.9945000000000001</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -902,16 +910,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>5703</v>
+        <v>12867</v>
       </c>
       <c r="D20" t="n">
-        <v>5605</v>
+        <v>12738</v>
       </c>
       <c r="E20" t="n">
-        <v>98</v>
+        <v>129</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>0.9828</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="21">
@@ -948,16 +956,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1360</v>
+        <v>3762</v>
       </c>
       <c r="D22" t="n">
-        <v>1356</v>
+        <v>3685</v>
       </c>
       <c r="E22" t="n">
-        <v>4</v>
+        <v>77</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>0.9971</v>
+        <v>0.9795</v>
       </c>
     </row>
     <row r="23">
@@ -972,16 +980,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>8573</v>
+        <v>27769</v>
       </c>
       <c r="D23" t="n">
-        <v>8571</v>
+        <v>27267</v>
       </c>
       <c r="E23" t="n">
-        <v>2</v>
+        <v>502</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>0.9998</v>
+        <v>0.9819</v>
       </c>
     </row>
     <row r="24">
@@ -1018,16 +1026,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>18281</v>
+        <v>49921</v>
       </c>
       <c r="D25" t="n">
-        <v>18278</v>
+        <v>49457</v>
       </c>
       <c r="E25" t="n">
-        <v>3</v>
+        <v>464</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>0.9998</v>
+        <v>0.9906999999999999</v>
       </c>
     </row>
     <row r="26">
@@ -1042,16 +1050,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>11910</v>
+        <v>13526</v>
       </c>
       <c r="D26" t="n">
-        <v>11529</v>
+        <v>13046</v>
       </c>
       <c r="E26" t="n">
-        <v>381</v>
+        <v>480</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>0.968</v>
+        <v>0.9645</v>
       </c>
     </row>
     <row r="27">
@@ -1066,16 +1074,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>13891</v>
+        <v>14057</v>
       </c>
       <c r="D27" t="n">
-        <v>13644</v>
+        <v>13781</v>
       </c>
       <c r="E27" t="n">
-        <v>247</v>
+        <v>276</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>0.9822</v>
+        <v>0.9804</v>
       </c>
     </row>
     <row r="28">
@@ -1090,13 +1098,13 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="F28" s="2" t="n">
         <v>0</v>
@@ -1114,16 +1122,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>3740</v>
+        <v>3631</v>
       </c>
       <c r="D29" t="n">
-        <v>3444</v>
+        <v>2693</v>
       </c>
       <c r="E29" t="n">
-        <v>296</v>
+        <v>938</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>0.9209000000000001</v>
+        <v>0.7417</v>
       </c>
     </row>
     <row r="30">
@@ -1138,16 +1146,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>366</v>
+        <v>806</v>
       </c>
       <c r="D30" t="n">
-        <v>353</v>
+        <v>798</v>
       </c>
       <c r="E30" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>0.9645</v>
+        <v>0.9901000000000001</v>
       </c>
     </row>
     <row r="31">
@@ -1184,16 +1192,16 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>3830</v>
+        <v>12032</v>
       </c>
       <c r="D32" t="n">
-        <v>3829</v>
+        <v>11663</v>
       </c>
       <c r="E32" t="n">
-        <v>1</v>
+        <v>369</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>0.9997</v>
+        <v>0.9693000000000001</v>
       </c>
     </row>
     <row r="33">
@@ -1208,16 +1216,16 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>29860</v>
+        <v>31066</v>
       </c>
       <c r="D33" t="n">
-        <v>29443</v>
+        <v>30625</v>
       </c>
       <c r="E33" t="n">
-        <v>417</v>
+        <v>441</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>0.986</v>
+        <v>0.9858</v>
       </c>
     </row>
     <row r="34">

--- a/output/TRANSFERENCIA_atual.xlsx
+++ b/output/TRANSFERENCIA_atual.xlsx
@@ -484,16 +484,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2416</v>
+        <v>1409</v>
       </c>
       <c r="D2" t="n">
-        <v>2391</v>
+        <v>1409</v>
       </c>
       <c r="E2" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.9897</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -508,17 +508,15 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>875</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>875</v>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -576,10 +574,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>18824</v>
+        <v>7447</v>
       </c>
       <c r="D6" t="n">
-        <v>18824</v>
+        <v>7447</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -600,16 +598,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>37132</v>
+        <v>9</v>
       </c>
       <c r="D7" t="n">
-        <v>14526</v>
+        <v>9</v>
       </c>
       <c r="E7" t="n">
-        <v>22606</v>
+        <v>0</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.3912</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -624,16 +622,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>14496</v>
+        <v>5095</v>
       </c>
       <c r="D8" t="n">
-        <v>10589</v>
+        <v>4294</v>
       </c>
       <c r="E8" t="n">
-        <v>3907</v>
+        <v>801</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.7304999999999999</v>
+        <v>0.8428</v>
       </c>
     </row>
     <row r="9">
@@ -648,17 +646,15 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>7294</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>6316</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>978</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>0.8659</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F9" s="2" t="n"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -694,10 +690,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>155143</v>
+        <v>148607</v>
       </c>
       <c r="D11" t="n">
-        <v>155143</v>
+        <v>148607</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -718,16 +714,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1269</v>
+        <v>54</v>
       </c>
       <c r="D12" t="n">
-        <v>1268</v>
+        <v>54</v>
       </c>
       <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="F12" s="2" t="n">
-        <v>0.9992</v>
       </c>
     </row>
     <row r="13">
@@ -742,10 +738,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2428</v>
+        <v>1313</v>
       </c>
       <c r="D13" t="n">
-        <v>2428</v>
+        <v>1313</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -766,17 +762,15 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2775</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>2775</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
       </c>
-      <c r="F14" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="F14" s="2" t="n"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -834,10 +828,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>8661</v>
+        <v>8075</v>
       </c>
       <c r="D17" t="n">
-        <v>8661</v>
+        <v>8075</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -902,16 +896,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>5703</v>
+        <v>3609</v>
       </c>
       <c r="D20" t="n">
-        <v>5605</v>
+        <v>3609</v>
       </c>
       <c r="E20" t="n">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>0.9828</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -948,16 +942,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1360</v>
+        <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>1356</v>
+        <v>1</v>
       </c>
       <c r="E22" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>0.9971</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -972,17 +966,15 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>8573</v>
+        <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>8571</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>2</v>
-      </c>
-      <c r="F23" s="2" t="n">
-        <v>0.9998</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F23" s="2" t="n"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1018,16 +1010,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>18281</v>
+        <v>16779</v>
       </c>
       <c r="D25" t="n">
-        <v>18278</v>
+        <v>16779</v>
       </c>
       <c r="E25" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>0.9998</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1042,16 +1034,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>11910</v>
+        <v>7138</v>
       </c>
       <c r="D26" t="n">
-        <v>11529</v>
+        <v>6935</v>
       </c>
       <c r="E26" t="n">
-        <v>381</v>
+        <v>203</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>0.968</v>
+        <v>0.9716</v>
       </c>
     </row>
     <row r="27">
@@ -1066,16 +1058,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>13891</v>
+        <v>10379</v>
       </c>
       <c r="D27" t="n">
-        <v>13644</v>
+        <v>10196</v>
       </c>
       <c r="E27" t="n">
-        <v>247</v>
+        <v>183</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>0.9822</v>
+        <v>0.9823999999999999</v>
       </c>
     </row>
     <row r="28">
@@ -1090,17 +1082,15 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>4</v>
-      </c>
-      <c r="F28" s="2" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F28" s="2" t="n"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1114,16 +1104,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>3740</v>
+        <v>2863</v>
       </c>
       <c r="D29" t="n">
-        <v>3444</v>
+        <v>2781</v>
       </c>
       <c r="E29" t="n">
-        <v>296</v>
+        <v>82</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>0.9209000000000001</v>
+        <v>0.9714</v>
       </c>
     </row>
     <row r="30">
@@ -1138,16 +1128,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>366</v>
+        <v>929</v>
       </c>
       <c r="D30" t="n">
-        <v>353</v>
+        <v>907</v>
       </c>
       <c r="E30" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>0.9645</v>
+        <v>0.9762999999999999</v>
       </c>
     </row>
     <row r="31">
@@ -1184,17 +1174,15 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>3830</v>
+        <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>3829</v>
+        <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>1</v>
-      </c>
-      <c r="F32" s="2" t="n">
-        <v>0.9997</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F32" s="2" t="n"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1208,16 +1196,16 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>29860</v>
+        <v>27661</v>
       </c>
       <c r="D33" t="n">
-        <v>29443</v>
+        <v>27346</v>
       </c>
       <c r="E33" t="n">
-        <v>417</v>
+        <v>315</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>0.986</v>
+        <v>0.9886</v>
       </c>
     </row>
     <row r="34">

--- a/output/TRANSFERENCIA_atual.xlsx
+++ b/output/TRANSFERENCIA_atual.xlsx
@@ -484,16 +484,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1409</v>
+        <v>4593</v>
       </c>
       <c r="D2" t="n">
-        <v>1409</v>
+        <v>4485</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>108</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>1</v>
+        <v>0.9765</v>
       </c>
     </row>
     <row r="3">
@@ -508,15 +508,17 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>1531</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>1505</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" s="2" t="n"/>
+        <v>26</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>0.983</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -530,15 +532,17 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>2701</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>2693</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" s="2" t="n"/>
+        <v>8</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>0.997</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -552,15 +556,17 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>705</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>705</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
-      <c r="F5" s="2" t="n"/>
+      <c r="F5" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -574,17 +580,15 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>7447</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>7447</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
-      <c r="F6" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="F6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -598,16 +602,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="D7" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="8">
@@ -622,17 +626,15 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>5095</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>4294</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>801</v>
-      </c>
-      <c r="F8" s="2" t="n">
-        <v>0.8428</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F8" s="2" t="n"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -646,15 +648,17 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>20576</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>14922</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="2" t="n"/>
+        <v>5654</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>0.7252</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -690,10 +694,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>148607</v>
+        <v>68105</v>
       </c>
       <c r="D11" t="n">
-        <v>148607</v>
+        <v>68105</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -714,16 +718,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>54</v>
+        <v>3080</v>
       </c>
       <c r="D12" t="n">
-        <v>54</v>
+        <v>3039</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>1</v>
+        <v>0.9867</v>
       </c>
     </row>
     <row r="13">
@@ -738,17 +742,15 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1313</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>1313</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
-      <c r="F13" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="F13" s="2" t="n"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -762,15 +764,17 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>3905</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>3905</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
       </c>
-      <c r="F14" s="2" t="n"/>
+      <c r="F14" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -806,15 +810,17 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>770</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>757</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" s="2" t="n"/>
+        <v>13</v>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>0.9831</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -828,10 +834,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>8075</v>
+        <v>4974</v>
       </c>
       <c r="D17" t="n">
-        <v>8075</v>
+        <v>4974</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -874,15 +880,17 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>676</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>658</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" s="2" t="n"/>
+        <v>18</v>
+      </c>
+      <c r="F19" s="2" t="n">
+        <v>0.9734</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -896,16 +904,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>3609</v>
+        <v>12499</v>
       </c>
       <c r="D20" t="n">
-        <v>3609</v>
+        <v>8707</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>3792</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>1</v>
+        <v>0.6966</v>
       </c>
     </row>
     <row r="21">
@@ -942,16 +950,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1</v>
+        <v>5190</v>
       </c>
       <c r="D22" t="n">
-        <v>1</v>
+        <v>5005</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>185</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>1</v>
+        <v>0.9643999999999999</v>
       </c>
     </row>
     <row r="23">
@@ -966,15 +974,17 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>36867</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>29975</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" s="2" t="n"/>
+        <v>6892</v>
+      </c>
+      <c r="F23" s="2" t="n">
+        <v>0.8131</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1010,16 +1020,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>16779</v>
+        <v>78729</v>
       </c>
       <c r="D25" t="n">
-        <v>16779</v>
+        <v>77502</v>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>1227</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>1</v>
+        <v>0.9843999999999999</v>
       </c>
     </row>
     <row r="26">
@@ -1034,16 +1044,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>7138</v>
+        <v>892</v>
       </c>
       <c r="D26" t="n">
-        <v>6935</v>
+        <v>872</v>
       </c>
       <c r="E26" t="n">
-        <v>203</v>
+        <v>20</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>0.9716</v>
+        <v>0.9776</v>
       </c>
     </row>
     <row r="27">
@@ -1058,16 +1068,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>10379</v>
+        <v>3768</v>
       </c>
       <c r="D27" t="n">
-        <v>10196</v>
+        <v>3706</v>
       </c>
       <c r="E27" t="n">
-        <v>183</v>
+        <v>62</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>0.9823999999999999</v>
+        <v>0.9834999999999999</v>
       </c>
     </row>
     <row r="28">
@@ -1104,16 +1114,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>2863</v>
+        <v>978</v>
       </c>
       <c r="D29" t="n">
-        <v>2781</v>
+        <v>890</v>
       </c>
       <c r="E29" t="n">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>0.9714</v>
+        <v>0.91</v>
       </c>
     </row>
     <row r="30">
@@ -1128,16 +1138,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>929</v>
+        <v>694</v>
       </c>
       <c r="D30" t="n">
-        <v>907</v>
+        <v>683</v>
       </c>
       <c r="E30" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>0.9762999999999999</v>
+        <v>0.9841</v>
       </c>
     </row>
     <row r="31">
@@ -1174,15 +1184,17 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0</v>
+        <v>9581</v>
       </c>
       <c r="D32" t="n">
-        <v>0</v>
+        <v>9376</v>
       </c>
       <c r="E32" t="n">
-        <v>0</v>
-      </c>
-      <c r="F32" s="2" t="n"/>
+        <v>205</v>
+      </c>
+      <c r="F32" s="2" t="n">
+        <v>0.9786</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1196,16 +1208,16 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>27661</v>
+        <v>19251</v>
       </c>
       <c r="D33" t="n">
-        <v>27346</v>
+        <v>19083</v>
       </c>
       <c r="E33" t="n">
-        <v>315</v>
+        <v>168</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>0.9886</v>
+        <v>0.9913</v>
       </c>
     </row>
     <row r="34">

--- a/output/TRANSFERENCIA_atual.xlsx
+++ b/output/TRANSFERENCIA_atual.xlsx
@@ -484,17 +484,15 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4593</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>4485</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>108</v>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>0.9765</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -508,17 +506,15 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1531</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>1505</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>26</v>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>0.983</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -532,17 +528,15 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2701</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>2693</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>8</v>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>0.997</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -556,17 +550,15 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>705</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>705</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
-      <c r="F5" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="F5" s="2" t="n"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -602,17 +594,15 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F7" s="2" t="n">
-        <v>0.95</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F7" s="2" t="n"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -648,17 +638,15 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>20576</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>14922</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>5654</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>0.7252</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F9" s="2" t="n"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -694,17 +682,15 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>68105</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>68105</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
       </c>
-      <c r="F11" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="F11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -718,17 +704,15 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>3080</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>3039</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>41</v>
-      </c>
-      <c r="F12" s="2" t="n">
-        <v>0.9867</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F12" s="2" t="n"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -764,17 +748,15 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>3905</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>3905</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
       </c>
-      <c r="F14" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="F14" s="2" t="n"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -810,17 +792,15 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>770</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>757</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>13</v>
-      </c>
-      <c r="F16" s="2" t="n">
-        <v>0.9831</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F16" s="2" t="n"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -834,10 +814,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>4974</v>
+        <v>396</v>
       </c>
       <c r="D17" t="n">
-        <v>4974</v>
+        <v>396</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -880,17 +860,15 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>676</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>658</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>18</v>
-      </c>
-      <c r="F19" s="2" t="n">
-        <v>0.9734</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F19" s="2" t="n"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -904,17 +882,15 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>12499</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>8707</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>3792</v>
-      </c>
-      <c r="F20" s="2" t="n">
-        <v>0.6966</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F20" s="2" t="n"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -950,17 +926,15 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>5190</v>
+        <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>5005</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>185</v>
-      </c>
-      <c r="F22" s="2" t="n">
-        <v>0.9643999999999999</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F22" s="2" t="n"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -974,17 +948,15 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>36867</v>
+        <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>29975</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>6892</v>
-      </c>
-      <c r="F23" s="2" t="n">
-        <v>0.8131</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F23" s="2" t="n"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1020,17 +992,15 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>78729</v>
+        <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>77502</v>
+        <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>1227</v>
-      </c>
-      <c r="F25" s="2" t="n">
-        <v>0.9843999999999999</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F25" s="2" t="n"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1044,17 +1014,15 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>892</v>
+        <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>872</v>
+        <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>20</v>
-      </c>
-      <c r="F26" s="2" t="n">
-        <v>0.9776</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F26" s="2" t="n"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1068,17 +1036,15 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>3768</v>
+        <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>3706</v>
+        <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>62</v>
-      </c>
-      <c r="F27" s="2" t="n">
-        <v>0.9834999999999999</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F27" s="2" t="n"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1114,17 +1080,15 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>978</v>
+        <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>890</v>
+        <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>88</v>
-      </c>
-      <c r="F29" s="2" t="n">
-        <v>0.91</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F29" s="2" t="n"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1138,16 +1102,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>694</v>
+        <v>4</v>
       </c>
       <c r="D30" t="n">
-        <v>683</v>
+        <v>4</v>
       </c>
       <c r="E30" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>0.9841</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -1184,17 +1148,15 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>9581</v>
+        <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>9376</v>
+        <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>205</v>
-      </c>
-      <c r="F32" s="2" t="n">
-        <v>0.9786</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F32" s="2" t="n"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1208,16 +1170,16 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>19251</v>
+        <v>5434</v>
       </c>
       <c r="D33" t="n">
-        <v>19083</v>
+        <v>5434</v>
       </c>
       <c r="E33" t="n">
-        <v>168</v>
+        <v>0</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>0.9913</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34">

--- a/output/TRANSFERENCIA_atual.xlsx
+++ b/output/TRANSFERENCIA_atual.xlsx
@@ -484,15 +484,17 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>2914</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>2907</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" s="2" t="n"/>
+        <v>7</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>0.9976</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -506,15 +508,17 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>1750</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" s="2" t="n"/>
+        <v>1748</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>0.0011</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -528,15 +532,17 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>987</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>985</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" s="2" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>0.998</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -550,15 +556,17 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>645</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>641</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="2" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>0.9937999999999999</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -572,15 +580,17 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>9006</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>9006</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
-      <c r="F6" s="2" t="n"/>
+      <c r="F6" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -594,15 +604,17 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>2676</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>2611</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="2" t="n"/>
+        <v>65</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>0.9756999999999999</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -616,15 +628,17 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>5872</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>2867</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="2" t="n"/>
+        <v>3005</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>0.4882</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -638,15 +652,17 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>22400</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>18198</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="2" t="n"/>
+        <v>4202</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>0.8123999999999999</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -682,15 +698,17 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>67187</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>67187</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
       </c>
-      <c r="F11" s="2" t="n"/>
+      <c r="F11" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -704,15 +722,17 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>3255</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>3197</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" s="2" t="n"/>
+        <v>58</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>0.9822</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -726,15 +746,17 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>2088</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>2088</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
-      <c r="F13" s="2" t="n"/>
+      <c r="F13" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -748,15 +770,17 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>4716</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>4716</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
       </c>
-      <c r="F14" s="2" t="n"/>
+      <c r="F14" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -792,15 +816,17 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>951</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>942</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" s="2" t="n"/>
+        <v>9</v>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>0.9904999999999999</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -814,10 +840,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>396</v>
+        <v>2411</v>
       </c>
       <c r="D17" t="n">
-        <v>396</v>
+        <v>2411</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -860,15 +886,17 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>832</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>827</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" s="2" t="n"/>
+        <v>5</v>
+      </c>
+      <c r="F19" s="2" t="n">
+        <v>0.9940000000000001</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -882,15 +910,17 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>9666</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>9053</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" s="2" t="n"/>
+        <v>613</v>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>0.9366</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -926,15 +956,17 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>3330</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>3294</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" s="2" t="n"/>
+        <v>36</v>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>0.9892</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -948,15 +980,17 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>35902</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>33390</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" s="2" t="n"/>
+        <v>2512</v>
+      </c>
+      <c r="F23" s="2" t="n">
+        <v>0.93</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -992,15 +1026,17 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>54521</v>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>52431</v>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
-      </c>
-      <c r="F25" s="2" t="n"/>
+        <v>2090</v>
+      </c>
+      <c r="F25" s="2" t="n">
+        <v>0.9617</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1014,15 +1050,17 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>12356</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>5880</v>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
-      </c>
-      <c r="F26" s="2" t="n"/>
+        <v>6476</v>
+      </c>
+      <c r="F26" s="2" t="n">
+        <v>0.4759</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1036,15 +1074,17 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>11981</v>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>6538</v>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
-      </c>
-      <c r="F27" s="2" t="n"/>
+        <v>5443</v>
+      </c>
+      <c r="F27" s="2" t="n">
+        <v>0.5457</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1058,15 +1098,17 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
-      </c>
-      <c r="F28" s="2" t="n"/>
+        <v>13</v>
+      </c>
+      <c r="F28" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1080,15 +1122,17 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>4161</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>2517</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F29" s="2" t="n"/>
+        <v>1644</v>
+      </c>
+      <c r="F29" s="2" t="n">
+        <v>0.6049</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1148,15 +1192,17 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0</v>
+        <v>11855</v>
       </c>
       <c r="D32" t="n">
-        <v>0</v>
+        <v>11254</v>
       </c>
       <c r="E32" t="n">
-        <v>0</v>
-      </c>
-      <c r="F32" s="2" t="n"/>
+        <v>601</v>
+      </c>
+      <c r="F32" s="2" t="n">
+        <v>0.9493</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">

--- a/output/TRANSFERENCIA_atual.xlsx
+++ b/output/TRANSFERENCIA_atual.xlsx
@@ -484,17 +484,15 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2914</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>2907</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>7</v>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>0.9976</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -508,17 +506,15 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1750</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>1748</v>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>0.0011</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -532,17 +528,15 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>987</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>985</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>0.998</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -556,17 +550,15 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>645</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>641</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>4</v>
-      </c>
-      <c r="F5" s="2" t="n">
-        <v>0.9937999999999999</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F5" s="2" t="n"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -604,17 +596,15 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2676</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>2611</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>65</v>
-      </c>
-      <c r="F7" s="2" t="n">
-        <v>0.9756999999999999</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F7" s="2" t="n"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -652,17 +642,15 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>22400</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>18198</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>4202</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>0.8123999999999999</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F9" s="2" t="n"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -722,17 +710,15 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>3255</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>3197</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>58</v>
-      </c>
-      <c r="F12" s="2" t="n">
-        <v>0.9822</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F12" s="2" t="n"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -770,17 +756,15 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>4716</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>4716</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
       </c>
-      <c r="F14" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="F14" s="2" t="n"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -816,17 +800,15 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>951</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>942</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>9</v>
-      </c>
-      <c r="F16" s="2" t="n">
-        <v>0.9904999999999999</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F16" s="2" t="n"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -840,10 +822,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>2411</v>
+        <v>2015</v>
       </c>
       <c r="D17" t="n">
-        <v>2411</v>
+        <v>2015</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -886,17 +868,15 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>832</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>827</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>5</v>
-      </c>
-      <c r="F19" s="2" t="n">
-        <v>0.9940000000000001</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F19" s="2" t="n"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -910,17 +890,15 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>9666</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>9053</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>613</v>
-      </c>
-      <c r="F20" s="2" t="n">
-        <v>0.9366</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F20" s="2" t="n"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -956,17 +934,15 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>3330</v>
+        <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>3294</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>36</v>
-      </c>
-      <c r="F22" s="2" t="n">
-        <v>0.9892</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F22" s="2" t="n"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -980,17 +956,15 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>35902</v>
+        <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>33390</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>2512</v>
-      </c>
-      <c r="F23" s="2" t="n">
-        <v>0.93</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F23" s="2" t="n"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1026,17 +1000,15 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>54521</v>
+        <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>52431</v>
+        <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>2090</v>
-      </c>
-      <c r="F25" s="2" t="n">
-        <v>0.9617</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F25" s="2" t="n"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1122,16 +1094,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>4161</v>
+        <v>4108</v>
       </c>
       <c r="D29" t="n">
-        <v>2517</v>
+        <v>2516</v>
       </c>
       <c r="E29" t="n">
-        <v>1644</v>
+        <v>1592</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>0.6049</v>
+        <v>0.6125</v>
       </c>
     </row>
     <row r="30">
@@ -1146,17 +1118,15 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
       </c>
-      <c r="F30" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="F30" s="2" t="n"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1192,17 +1162,15 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>11855</v>
+        <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>11254</v>
+        <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>601</v>
-      </c>
-      <c r="F32" s="2" t="n">
-        <v>0.9493</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F32" s="2" t="n"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1216,17 +1184,15 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>5434</v>
+        <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>5434</v>
+        <v>0</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
       </c>
-      <c r="F33" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="F33" s="2" t="n"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">

--- a/output/TRANSFERENCIA_atual.xlsx
+++ b/output/TRANSFERENCIA_atual.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Taxa de Transferência" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Taxa de Transferência" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Taxa de Transferência'!$A$1:$F$34</definedName>
@@ -484,15 +484,17 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>3744</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>3678</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" s="2" t="n"/>
+        <v>66</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>0.9823999999999999</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -506,15 +508,17 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>1863</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>1853</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" s="2" t="n"/>
+        <v>10</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>0.9945999999999999</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -528,15 +532,17 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>1144</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>1137</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" s="2" t="n"/>
+        <v>7</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>0.9939</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -550,15 +556,17 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>459</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>443</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="2" t="n"/>
+        <v>16</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>0.9651000000000001</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -572,10 +580,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>9006</v>
+        <v>20520</v>
       </c>
       <c r="D6" t="n">
-        <v>9006</v>
+        <v>20520</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -596,15 +604,17 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>18492</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>13851</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="2" t="n"/>
+        <v>4641</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>0.7490000000000001</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -618,16 +628,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>5872</v>
+        <v>7613</v>
       </c>
       <c r="D8" t="n">
-        <v>2867</v>
+        <v>4595</v>
       </c>
       <c r="E8" t="n">
-        <v>3005</v>
+        <v>3018</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.4882</v>
+        <v>0.6036</v>
       </c>
     </row>
     <row r="9">
@@ -642,15 +652,17 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>20210</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>19286</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="2" t="n"/>
+        <v>924</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>0.9543</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -686,10 +698,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>67187</v>
+        <v>127528</v>
       </c>
       <c r="D11" t="n">
-        <v>67187</v>
+        <v>127528</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -710,15 +722,17 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>2566</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>2398</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" s="2" t="n"/>
+        <v>168</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>0.9345</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -732,16 +746,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2088</v>
+        <v>4027</v>
       </c>
       <c r="D13" t="n">
-        <v>2088</v>
+        <v>4026</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>1</v>
+        <v>0.9998</v>
       </c>
     </row>
     <row r="14">
@@ -756,15 +770,17 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>5207</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>5205</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" s="2" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>0.9995999999999999</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -800,15 +816,17 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>595</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>585</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" s="2" t="n"/>
+        <v>10</v>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>0.9832</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -822,10 +840,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>2015</v>
+        <v>5556</v>
       </c>
       <c r="D17" t="n">
-        <v>2015</v>
+        <v>5556</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -868,15 +886,17 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>1342</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>1336</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" s="2" t="n"/>
+        <v>6</v>
+      </c>
+      <c r="F19" s="2" t="n">
+        <v>0.9954999999999999</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -890,15 +910,17 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>9466</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>9298</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" s="2" t="n"/>
+        <v>168</v>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>0.9823000000000001</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -934,15 +956,17 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>2831</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>2780</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" s="2" t="n"/>
+        <v>51</v>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>0.982</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -956,15 +980,17 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>30099</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>29250</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" s="2" t="n"/>
+        <v>849</v>
+      </c>
+      <c r="F23" s="2" t="n">
+        <v>0.9718000000000001</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1000,15 +1026,17 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>51339</v>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>50410</v>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
-      </c>
-      <c r="F25" s="2" t="n"/>
+        <v>929</v>
+      </c>
+      <c r="F25" s="2" t="n">
+        <v>0.9819</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1022,16 +1050,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>12356</v>
+        <v>22446</v>
       </c>
       <c r="D26" t="n">
-        <v>5880</v>
+        <v>12693</v>
       </c>
       <c r="E26" t="n">
-        <v>6476</v>
+        <v>9753</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>0.4759</v>
+        <v>0.5655</v>
       </c>
     </row>
     <row r="27">
@@ -1046,16 +1074,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>11981</v>
+        <v>22818</v>
       </c>
       <c r="D27" t="n">
-        <v>6538</v>
+        <v>15173</v>
       </c>
       <c r="E27" t="n">
-        <v>5443</v>
+        <v>7645</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>0.5457</v>
+        <v>0.665</v>
       </c>
     </row>
     <row r="28">
@@ -1094,16 +1122,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>4108</v>
+        <v>8850</v>
       </c>
       <c r="D29" t="n">
-        <v>2516</v>
+        <v>5450</v>
       </c>
       <c r="E29" t="n">
-        <v>1592</v>
+        <v>3400</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>0.6125</v>
+        <v>0.6158</v>
       </c>
     </row>
     <row r="30">
@@ -1118,15 +1146,17 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>1128</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>1112</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
-      </c>
-      <c r="F30" s="2" t="n"/>
+        <v>16</v>
+      </c>
+      <c r="F30" s="2" t="n">
+        <v>0.9858</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1162,15 +1192,17 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0</v>
+        <v>10073</v>
       </c>
       <c r="D32" t="n">
-        <v>0</v>
+        <v>9975</v>
       </c>
       <c r="E32" t="n">
-        <v>0</v>
-      </c>
-      <c r="F32" s="2" t="n"/>
+        <v>98</v>
+      </c>
+      <c r="F32" s="2" t="n">
+        <v>0.9903</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1184,15 +1216,17 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0</v>
+        <v>25750</v>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>25239</v>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
-      </c>
-      <c r="F33" s="2" t="n"/>
+        <v>511</v>
+      </c>
+      <c r="F33" s="2" t="n">
+        <v>0.9802</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">

--- a/output/TRANSFERENCIA_atual.xlsx
+++ b/output/TRANSFERENCIA_atual.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Taxa de Transferência" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Taxa de Transferência" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Taxa de Transferência'!$A$1:$F$34</definedName>

--- a/output/TRANSFERENCIA_atual.xlsx
+++ b/output/TRANSFERENCIA_atual.xlsx
@@ -484,16 +484,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3744</v>
+        <v>2657</v>
       </c>
       <c r="D2" t="n">
-        <v>3678</v>
+        <v>2633</v>
       </c>
       <c r="E2" t="n">
-        <v>66</v>
+        <v>24</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.9823999999999999</v>
+        <v>0.991</v>
       </c>
     </row>
     <row r="3">
@@ -508,16 +508,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1863</v>
+        <v>2227</v>
       </c>
       <c r="D3" t="n">
-        <v>1853</v>
+        <v>2194</v>
       </c>
       <c r="E3" t="n">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.9945999999999999</v>
+        <v>0.9852</v>
       </c>
     </row>
     <row r="4">
@@ -532,16 +532,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1144</v>
+        <v>1220</v>
       </c>
       <c r="D4" t="n">
-        <v>1137</v>
+        <v>1219</v>
       </c>
       <c r="E4" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.9939</v>
+        <v>0.9992</v>
       </c>
     </row>
     <row r="5">
@@ -556,16 +556,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>459</v>
+        <v>530</v>
       </c>
       <c r="D5" t="n">
-        <v>443</v>
+        <v>469</v>
       </c>
       <c r="E5" t="n">
-        <v>16</v>
+        <v>61</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.9651000000000001</v>
+        <v>0.8848999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -580,10 +580,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>20520</v>
+        <v>22813</v>
       </c>
       <c r="D6" t="n">
-        <v>20520</v>
+        <v>22813</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -604,16 +604,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>18492</v>
+        <v>14525</v>
       </c>
       <c r="D7" t="n">
-        <v>13851</v>
+        <v>14100</v>
       </c>
       <c r="E7" t="n">
-        <v>4641</v>
+        <v>425</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.7490000000000001</v>
+        <v>0.9706999999999999</v>
       </c>
     </row>
     <row r="8">
@@ -628,16 +628,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>7613</v>
+        <v>14802</v>
       </c>
       <c r="D8" t="n">
-        <v>4595</v>
+        <v>8159</v>
       </c>
       <c r="E8" t="n">
-        <v>3018</v>
+        <v>6643</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.6036</v>
+        <v>0.5512</v>
       </c>
     </row>
     <row r="9">
@@ -652,16 +652,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>20210</v>
+        <v>16846</v>
       </c>
       <c r="D9" t="n">
-        <v>19286</v>
+        <v>14929</v>
       </c>
       <c r="E9" t="n">
-        <v>924</v>
+        <v>1917</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0.9543</v>
+        <v>0.8862000000000001</v>
       </c>
     </row>
     <row r="10">
@@ -698,10 +698,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>127528</v>
+        <v>115843</v>
       </c>
       <c r="D11" t="n">
-        <v>127528</v>
+        <v>115843</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -722,16 +722,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2566</v>
+        <v>2590</v>
       </c>
       <c r="D12" t="n">
-        <v>2398</v>
+        <v>2555</v>
       </c>
       <c r="E12" t="n">
-        <v>168</v>
+        <v>35</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>0.9345</v>
+        <v>0.9865</v>
       </c>
     </row>
     <row r="13">
@@ -746,16 +746,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>4027</v>
+        <v>3552</v>
       </c>
       <c r="D13" t="n">
-        <v>4026</v>
+        <v>3551</v>
       </c>
       <c r="E13" t="n">
         <v>1</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>0.9998</v>
+        <v>0.9997</v>
       </c>
     </row>
     <row r="14">
@@ -770,10 +770,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>5207</v>
+        <v>4703</v>
       </c>
       <c r="D14" t="n">
-        <v>5205</v>
+        <v>4701</v>
       </c>
       <c r="E14" t="n">
         <v>2</v>
@@ -816,16 +816,16 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>595</v>
+        <v>551</v>
       </c>
       <c r="D16" t="n">
-        <v>585</v>
+        <v>548</v>
       </c>
       <c r="E16" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>0.9832</v>
+        <v>0.9945999999999999</v>
       </c>
     </row>
     <row r="17">
@@ -840,10 +840,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>5556</v>
+        <v>7762</v>
       </c>
       <c r="D17" t="n">
-        <v>5556</v>
+        <v>7762</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -886,16 +886,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1342</v>
+        <v>235</v>
       </c>
       <c r="D19" t="n">
-        <v>1336</v>
+        <v>233</v>
       </c>
       <c r="E19" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>0.9954999999999999</v>
+        <v>0.9915</v>
       </c>
     </row>
     <row r="20">
@@ -910,16 +910,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>9466</v>
+        <v>8492</v>
       </c>
       <c r="D20" t="n">
-        <v>9298</v>
+        <v>8345</v>
       </c>
       <c r="E20" t="n">
-        <v>168</v>
+        <v>147</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>0.9823000000000001</v>
+        <v>0.9826999999999999</v>
       </c>
     </row>
     <row r="21">
@@ -956,16 +956,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>2831</v>
+        <v>3080</v>
       </c>
       <c r="D22" t="n">
-        <v>2780</v>
+        <v>2998</v>
       </c>
       <c r="E22" t="n">
-        <v>51</v>
+        <v>82</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>0.982</v>
+        <v>0.9734</v>
       </c>
     </row>
     <row r="23">
@@ -980,16 +980,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>30099</v>
+        <v>35526</v>
       </c>
       <c r="D23" t="n">
-        <v>29250</v>
+        <v>34103</v>
       </c>
       <c r="E23" t="n">
-        <v>849</v>
+        <v>1423</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>0.9718000000000001</v>
+        <v>0.9599</v>
       </c>
     </row>
     <row r="24">
@@ -1026,16 +1026,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>51339</v>
+        <v>43894</v>
       </c>
       <c r="D25" t="n">
-        <v>50410</v>
+        <v>32543</v>
       </c>
       <c r="E25" t="n">
-        <v>929</v>
+        <v>11351</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>0.9819</v>
+        <v>0.7414000000000001</v>
       </c>
     </row>
     <row r="26">
@@ -1050,16 +1050,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>22446</v>
+        <v>16240</v>
       </c>
       <c r="D26" t="n">
-        <v>12693</v>
+        <v>10081</v>
       </c>
       <c r="E26" t="n">
-        <v>9753</v>
+        <v>6159</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>0.5655</v>
+        <v>0.6208</v>
       </c>
     </row>
     <row r="27">
@@ -1074,16 +1074,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>22818</v>
+        <v>18575</v>
       </c>
       <c r="D27" t="n">
-        <v>15173</v>
+        <v>16218</v>
       </c>
       <c r="E27" t="n">
-        <v>7645</v>
+        <v>2357</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>0.665</v>
+        <v>0.8731</v>
       </c>
     </row>
     <row r="28">
@@ -1098,16 +1098,16 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>0</v>
+        <v>0.1765</v>
       </c>
     </row>
     <row r="29">
@@ -1122,16 +1122,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>8850</v>
+        <v>10562</v>
       </c>
       <c r="D29" t="n">
-        <v>5450</v>
+        <v>6903</v>
       </c>
       <c r="E29" t="n">
-        <v>3400</v>
+        <v>3659</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>0.6158</v>
+        <v>0.6536</v>
       </c>
     </row>
     <row r="30">
@@ -1146,16 +1146,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1128</v>
+        <v>2426</v>
       </c>
       <c r="D30" t="n">
-        <v>1112</v>
+        <v>2379</v>
       </c>
       <c r="E30" t="n">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>0.9858</v>
+        <v>0.9806</v>
       </c>
     </row>
     <row r="31">
@@ -1192,16 +1192,16 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>10073</v>
+        <v>12052</v>
       </c>
       <c r="D32" t="n">
-        <v>9975</v>
+        <v>11925</v>
       </c>
       <c r="E32" t="n">
-        <v>98</v>
+        <v>127</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>0.9903</v>
+        <v>0.9895</v>
       </c>
     </row>
     <row r="33">
@@ -1216,16 +1216,16 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>25750</v>
+        <v>43603</v>
       </c>
       <c r="D33" t="n">
-        <v>25239</v>
+        <v>42821</v>
       </c>
       <c r="E33" t="n">
-        <v>511</v>
+        <v>782</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>0.9802</v>
+        <v>0.9821</v>
       </c>
     </row>
     <row r="34">

--- a/output/TRANSFERENCIA_atual.xlsx
+++ b/output/TRANSFERENCIA_atual.xlsx
@@ -484,16 +484,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2657</v>
+        <v>2848</v>
       </c>
       <c r="D2" t="n">
-        <v>2633</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>24</v>
+        <v>2848</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.991</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -508,16 +508,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2227</v>
+        <v>2104</v>
       </c>
       <c r="D3" t="n">
-        <v>2194</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>33</v>
+        <v>2104</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.9852</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -532,16 +532,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1220</v>
+        <v>1035</v>
       </c>
       <c r="D4" t="n">
-        <v>1219</v>
+        <v>1034</v>
       </c>
       <c r="E4" t="n">
         <v>1</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.9992</v>
+        <v>0.9990000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -556,16 +556,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>530</v>
+        <v>407</v>
       </c>
       <c r="D5" t="n">
-        <v>469</v>
+        <v>372</v>
       </c>
       <c r="E5" t="n">
-        <v>61</v>
+        <v>35</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.8848999999999999</v>
+        <v>0.914</v>
       </c>
     </row>
     <row r="6">
@@ -580,13 +580,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>22813</v>
+        <v>21197</v>
       </c>
       <c r="D6" t="n">
-        <v>22813</v>
+        <v>21196</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>1</v>
@@ -604,16 +604,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>14525</v>
+        <v>14153</v>
       </c>
       <c r="D7" t="n">
-        <v>14100</v>
+        <v>13534</v>
       </c>
       <c r="E7" t="n">
-        <v>425</v>
+        <v>619</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.9706999999999999</v>
+        <v>0.9562999999999999</v>
       </c>
     </row>
     <row r="8">
@@ -628,16 +628,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>14802</v>
+        <v>22555</v>
       </c>
       <c r="D8" t="n">
-        <v>8159</v>
+        <v>13575</v>
       </c>
       <c r="E8" t="n">
-        <v>6643</v>
+        <v>8980</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.5512</v>
+        <v>0.6019</v>
       </c>
     </row>
     <row r="9">
@@ -652,16 +652,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>16846</v>
+        <v>8778</v>
       </c>
       <c r="D9" t="n">
-        <v>14929</v>
+        <v>7849</v>
       </c>
       <c r="E9" t="n">
-        <v>1917</v>
+        <v>929</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0.8862000000000001</v>
+        <v>0.8942</v>
       </c>
     </row>
     <row r="10">
@@ -698,10 +698,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>115843</v>
+        <v>130625</v>
       </c>
       <c r="D11" t="n">
-        <v>115843</v>
+        <v>130625</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -722,16 +722,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2590</v>
+        <v>3338</v>
       </c>
       <c r="D12" t="n">
-        <v>2555</v>
+        <v>2805</v>
       </c>
       <c r="E12" t="n">
-        <v>35</v>
+        <v>533</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>0.9865</v>
+        <v>0.8403</v>
       </c>
     </row>
     <row r="13">
@@ -746,16 +746,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3552</v>
+        <v>2882</v>
       </c>
       <c r="D13" t="n">
-        <v>3551</v>
+        <v>2882</v>
       </c>
       <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="F13" s="2" t="n">
-        <v>0.9997</v>
       </c>
     </row>
     <row r="14">
@@ -770,16 +770,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>4703</v>
+        <v>4168</v>
       </c>
       <c r="D14" t="n">
-        <v>4701</v>
+        <v>4167</v>
       </c>
       <c r="E14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0.9995999999999999</v>
+        <v>0.9998</v>
       </c>
     </row>
     <row r="15">
@@ -816,16 +816,16 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>551</v>
+        <v>410</v>
       </c>
       <c r="D16" t="n">
-        <v>548</v>
+        <v>407</v>
       </c>
       <c r="E16" t="n">
         <v>3</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>0.9945999999999999</v>
+        <v>0.9926999999999999</v>
       </c>
     </row>
     <row r="17">
@@ -840,10 +840,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>7762</v>
+        <v>9854</v>
       </c>
       <c r="D17" t="n">
-        <v>7762</v>
+        <v>9854</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -886,16 +886,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>235</v>
+        <v>588</v>
       </c>
       <c r="D19" t="n">
-        <v>233</v>
+        <v>588</v>
       </c>
       <c r="E19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>0.9915</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -910,16 +910,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>8492</v>
+        <v>9627</v>
       </c>
       <c r="D20" t="n">
-        <v>8345</v>
+        <v>9625</v>
       </c>
       <c r="E20" t="n">
-        <v>147</v>
+        <v>2</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>0.9826999999999999</v>
+        <v>0.9998</v>
       </c>
     </row>
     <row r="21">
@@ -956,16 +956,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>3080</v>
+        <v>2745</v>
       </c>
       <c r="D22" t="n">
-        <v>2998</v>
+        <v>2701</v>
       </c>
       <c r="E22" t="n">
-        <v>82</v>
+        <v>44</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>0.9734</v>
+        <v>0.9840000000000001</v>
       </c>
     </row>
     <row r="23">
@@ -980,16 +980,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>35526</v>
+        <v>26682</v>
       </c>
       <c r="D23" t="n">
-        <v>34103</v>
+        <v>24136</v>
       </c>
       <c r="E23" t="n">
-        <v>1423</v>
+        <v>2546</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>0.9599</v>
+        <v>0.9046</v>
       </c>
     </row>
     <row r="24">
@@ -1026,16 +1026,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>43894</v>
+        <v>41813</v>
       </c>
       <c r="D25" t="n">
-        <v>32543</v>
+        <v>31737</v>
       </c>
       <c r="E25" t="n">
-        <v>11351</v>
+        <v>10076</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>0.7414000000000001</v>
+        <v>0.759</v>
       </c>
     </row>
     <row r="26">
@@ -1050,16 +1050,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>16240</v>
+        <v>9193</v>
       </c>
       <c r="D26" t="n">
-        <v>10081</v>
+        <v>5736</v>
       </c>
       <c r="E26" t="n">
-        <v>6159</v>
+        <v>3457</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>0.6208</v>
+        <v>0.624</v>
       </c>
     </row>
     <row r="27">
@@ -1074,16 +1074,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>18575</v>
+        <v>16022</v>
       </c>
       <c r="D27" t="n">
-        <v>16218</v>
+        <v>15725</v>
       </c>
       <c r="E27" t="n">
-        <v>2357</v>
+        <v>297</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>0.8731</v>
+        <v>0.9815</v>
       </c>
     </row>
     <row r="28">
@@ -1098,16 +1098,16 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="D28" t="n">
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>0.1765</v>
+        <v>0.1071</v>
       </c>
     </row>
     <row r="29">
@@ -1122,16 +1122,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>10562</v>
+        <v>10000</v>
       </c>
       <c r="D29" t="n">
-        <v>6903</v>
+        <v>7415</v>
       </c>
       <c r="E29" t="n">
-        <v>3659</v>
+        <v>2585</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>0.6536</v>
+        <v>0.7415</v>
       </c>
     </row>
     <row r="30">
@@ -1146,16 +1146,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>2426</v>
+        <v>2189</v>
       </c>
       <c r="D30" t="n">
-        <v>2379</v>
+        <v>2156</v>
       </c>
       <c r="E30" t="n">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>0.9806</v>
+        <v>0.9849</v>
       </c>
     </row>
     <row r="31">
@@ -1192,16 +1192,16 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>12052</v>
+        <v>12453</v>
       </c>
       <c r="D32" t="n">
-        <v>11925</v>
+        <v>12083</v>
       </c>
       <c r="E32" t="n">
-        <v>127</v>
+        <v>370</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>0.9895</v>
+        <v>0.9703000000000001</v>
       </c>
     </row>
     <row r="33">
@@ -1216,16 +1216,16 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>43603</v>
+        <v>33640</v>
       </c>
       <c r="D33" t="n">
-        <v>42821</v>
+        <v>32478</v>
       </c>
       <c r="E33" t="n">
-        <v>782</v>
+        <v>1162</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>0.9821</v>
+        <v>0.9655</v>
       </c>
     </row>
     <row r="34">

--- a/output/TRANSFERENCIA_atual.xlsx
+++ b/output/TRANSFERENCIA_atual.xlsx
@@ -484,16 +484,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2848</v>
+        <v>2939</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>2917</v>
       </c>
       <c r="E2" t="n">
-        <v>2848</v>
+        <v>22</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0</v>
+        <v>0.9925</v>
       </c>
     </row>
     <row r="3">
@@ -508,16 +508,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2104</v>
+        <v>1918</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>1916</v>
       </c>
       <c r="E3" t="n">
-        <v>2104</v>
+        <v>2</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0</v>
+        <v>0.9990000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -532,17 +532,15 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1035</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>1034</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>0.9990000000000001</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -556,17 +554,15 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>407</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>372</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>35</v>
-      </c>
-      <c r="F5" s="2" t="n">
-        <v>0.914</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F5" s="2" t="n"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -580,16 +576,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>21197</v>
+        <v>21488</v>
       </c>
       <c r="D6" t="n">
-        <v>21196</v>
+        <v>21486</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>1</v>
+        <v>0.9998999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -604,16 +600,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>14153</v>
+        <v>29036</v>
       </c>
       <c r="D7" t="n">
-        <v>13534</v>
+        <v>14115</v>
       </c>
       <c r="E7" t="n">
-        <v>619</v>
+        <v>14921</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.9562999999999999</v>
+        <v>0.4861</v>
       </c>
     </row>
     <row r="8">
@@ -628,16 +624,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>22555</v>
+        <v>12251</v>
       </c>
       <c r="D8" t="n">
-        <v>13575</v>
+        <v>7144</v>
       </c>
       <c r="E8" t="n">
-        <v>8980</v>
+        <v>5107</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.6019</v>
+        <v>0.5831000000000001</v>
       </c>
     </row>
     <row r="9">
@@ -652,16 +648,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>8778</v>
+        <v>3354</v>
       </c>
       <c r="D9" t="n">
-        <v>7849</v>
+        <v>2980</v>
       </c>
       <c r="E9" t="n">
-        <v>929</v>
+        <v>374</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0.8942</v>
+        <v>0.8885</v>
       </c>
     </row>
     <row r="10">
@@ -698,10 +694,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>130625</v>
+        <v>138051</v>
       </c>
       <c r="D11" t="n">
-        <v>130625</v>
+        <v>138051</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -722,16 +718,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>3338</v>
+        <v>1737</v>
       </c>
       <c r="D12" t="n">
-        <v>2805</v>
+        <v>1728</v>
       </c>
       <c r="E12" t="n">
-        <v>533</v>
+        <v>9</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>0.8403</v>
+        <v>0.9948</v>
       </c>
     </row>
     <row r="13">
@@ -746,10 +742,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2882</v>
+        <v>2551</v>
       </c>
       <c r="D13" t="n">
-        <v>2882</v>
+        <v>2551</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -770,16 +766,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>4168</v>
+        <v>3385</v>
       </c>
       <c r="D14" t="n">
-        <v>4167</v>
+        <v>3385</v>
       </c>
       <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="F14" s="2" t="n">
-        <v>0.9998</v>
       </c>
     </row>
     <row r="15">
@@ -816,17 +812,15 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>410</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>407</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>3</v>
-      </c>
-      <c r="F16" s="2" t="n">
-        <v>0.9926999999999999</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F16" s="2" t="n"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -840,10 +834,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>9854</v>
+        <v>11228</v>
       </c>
       <c r="D17" t="n">
-        <v>9854</v>
+        <v>11228</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -886,17 +880,15 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>588</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>588</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
       </c>
-      <c r="F19" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="F19" s="2" t="n"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -910,16 +902,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>9627</v>
+        <v>9681</v>
       </c>
       <c r="D20" t="n">
-        <v>9625</v>
+        <v>9661</v>
       </c>
       <c r="E20" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>0.9998</v>
+        <v>0.9979</v>
       </c>
     </row>
     <row r="21">
@@ -956,16 +948,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>2745</v>
+        <v>863</v>
       </c>
       <c r="D22" t="n">
-        <v>2701</v>
+        <v>4</v>
       </c>
       <c r="E22" t="n">
-        <v>44</v>
+        <v>859</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>0.9840000000000001</v>
+        <v>0.0046</v>
       </c>
     </row>
     <row r="23">
@@ -980,16 +972,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>26682</v>
+        <v>13700</v>
       </c>
       <c r="D23" t="n">
-        <v>24136</v>
+        <v>13696</v>
       </c>
       <c r="E23" t="n">
-        <v>2546</v>
+        <v>4</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>0.9046</v>
+        <v>0.9997</v>
       </c>
     </row>
     <row r="24">
@@ -1026,16 +1018,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>41813</v>
+        <v>24124</v>
       </c>
       <c r="D25" t="n">
-        <v>31737</v>
+        <v>24044</v>
       </c>
       <c r="E25" t="n">
-        <v>10076</v>
+        <v>80</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>0.759</v>
+        <v>0.9967</v>
       </c>
     </row>
     <row r="26">
@@ -1050,16 +1042,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>9193</v>
+        <v>7167</v>
       </c>
       <c r="D26" t="n">
-        <v>5736</v>
+        <v>5283</v>
       </c>
       <c r="E26" t="n">
-        <v>3457</v>
+        <v>1884</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>0.624</v>
+        <v>0.7371</v>
       </c>
     </row>
     <row r="27">
@@ -1074,16 +1066,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>16022</v>
+        <v>16104</v>
       </c>
       <c r="D27" t="n">
-        <v>15725</v>
+        <v>15865</v>
       </c>
       <c r="E27" t="n">
-        <v>297</v>
+        <v>239</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>0.9815</v>
+        <v>0.9852</v>
       </c>
     </row>
     <row r="28">
@@ -1098,16 +1090,16 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="D28" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>0.1071</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -1122,16 +1114,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>10000</v>
+        <v>9270</v>
       </c>
       <c r="D29" t="n">
-        <v>7415</v>
+        <v>5686</v>
       </c>
       <c r="E29" t="n">
-        <v>2585</v>
+        <v>3584</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>0.7415</v>
+        <v>0.6134000000000001</v>
       </c>
     </row>
     <row r="30">
@@ -1146,16 +1138,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>2189</v>
+        <v>1355</v>
       </c>
       <c r="D30" t="n">
-        <v>2156</v>
+        <v>1349</v>
       </c>
       <c r="E30" t="n">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>0.9849</v>
+        <v>0.9956</v>
       </c>
     </row>
     <row r="31">
@@ -1192,16 +1184,16 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>12453</v>
+        <v>3662</v>
       </c>
       <c r="D32" t="n">
-        <v>12083</v>
+        <v>3662</v>
       </c>
       <c r="E32" t="n">
-        <v>370</v>
+        <v>0</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>0.9703000000000001</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -1216,16 +1208,16 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>33640</v>
+        <v>28327</v>
       </c>
       <c r="D33" t="n">
-        <v>32478</v>
+        <v>27281</v>
       </c>
       <c r="E33" t="n">
-        <v>1162</v>
+        <v>1046</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>0.9655</v>
+        <v>0.9631000000000001</v>
       </c>
     </row>
     <row r="34">
@@ -1240,15 +1232,17 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E34" t="n">
         <v>0</v>
       </c>
-      <c r="F34" s="2" t="n"/>
+      <c r="F34" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F34"/>

--- a/output/TRANSFERENCIA_atual.xlsx
+++ b/output/TRANSFERENCIA_atual.xlsx
@@ -484,17 +484,15 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2939</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>2917</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>22</v>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>0.9925</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -508,17 +506,15 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1918</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>1916</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>2</v>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>0.9990000000000001</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -576,13 +572,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>21488</v>
+        <v>11590</v>
       </c>
       <c r="D6" t="n">
-        <v>21486</v>
+        <v>11589</v>
       </c>
       <c r="E6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>0.9998999999999999</v>
@@ -600,16 +596,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>29036</v>
+        <v>7</v>
       </c>
       <c r="D7" t="n">
-        <v>14115</v>
+        <v>7</v>
       </c>
       <c r="E7" t="n">
-        <v>14921</v>
+        <v>0</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.4861</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -624,16 +620,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>12251</v>
+        <v>3189</v>
       </c>
       <c r="D8" t="n">
-        <v>7144</v>
+        <v>432</v>
       </c>
       <c r="E8" t="n">
-        <v>5107</v>
+        <v>2757</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.5831000000000001</v>
+        <v>0.1355</v>
       </c>
     </row>
     <row r="9">
@@ -648,17 +644,15 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3354</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>2980</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>374</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>0.8885</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F9" s="2" t="n"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -694,10 +688,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>138051</v>
+        <v>106001</v>
       </c>
       <c r="D11" t="n">
-        <v>138051</v>
+        <v>106001</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -718,17 +712,15 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1737</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>1728</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>9</v>
-      </c>
-      <c r="F12" s="2" t="n">
-        <v>0.9948</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F12" s="2" t="n"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -742,10 +734,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2551</v>
+        <v>1282</v>
       </c>
       <c r="D13" t="n">
-        <v>2551</v>
+        <v>1282</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -766,17 +758,15 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>3385</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>3385</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
       </c>
-      <c r="F14" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="F14" s="2" t="n"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -834,10 +824,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>11228</v>
+        <v>8603</v>
       </c>
       <c r="D17" t="n">
-        <v>11228</v>
+        <v>8603</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -902,16 +892,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>9681</v>
+        <v>3208</v>
       </c>
       <c r="D20" t="n">
-        <v>9661</v>
+        <v>3204</v>
       </c>
       <c r="E20" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>0.9979</v>
+        <v>0.9987999999999999</v>
       </c>
     </row>
     <row r="21">
@@ -948,16 +938,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>863</v>
+        <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E22" t="n">
-        <v>859</v>
+        <v>0</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>0.0046</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -972,16 +962,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>13700</v>
+        <v>6</v>
       </c>
       <c r="D23" t="n">
-        <v>13696</v>
+        <v>6</v>
       </c>
       <c r="E23" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>0.9997</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1018,16 +1008,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>24124</v>
+        <v>16985</v>
       </c>
       <c r="D25" t="n">
-        <v>24044</v>
+        <v>16942</v>
       </c>
       <c r="E25" t="n">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>0.9967</v>
+        <v>0.9975000000000001</v>
       </c>
     </row>
     <row r="26">
@@ -1042,16 +1032,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>7167</v>
+        <v>4691</v>
       </c>
       <c r="D26" t="n">
-        <v>5283</v>
+        <v>3372</v>
       </c>
       <c r="E26" t="n">
-        <v>1884</v>
+        <v>1319</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>0.7371</v>
+        <v>0.7188</v>
       </c>
     </row>
     <row r="27">
@@ -1066,16 +1056,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>16104</v>
+        <v>8743</v>
       </c>
       <c r="D27" t="n">
-        <v>15865</v>
+        <v>8638</v>
       </c>
       <c r="E27" t="n">
-        <v>239</v>
+        <v>105</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>0.9852</v>
+        <v>0.988</v>
       </c>
     </row>
     <row r="28">
@@ -1090,13 +1080,13 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="F28" s="2" t="n">
         <v>0</v>
@@ -1114,16 +1104,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>9270</v>
+        <v>6785</v>
       </c>
       <c r="D29" t="n">
-        <v>5686</v>
+        <v>4073</v>
       </c>
       <c r="E29" t="n">
-        <v>3584</v>
+        <v>2712</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>0.6134000000000001</v>
+        <v>0.6003000000000001</v>
       </c>
     </row>
     <row r="30">
@@ -1138,16 +1128,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1355</v>
+        <v>878</v>
       </c>
       <c r="D30" t="n">
-        <v>1349</v>
+        <v>870</v>
       </c>
       <c r="E30" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>0.9956</v>
+        <v>0.9909</v>
       </c>
     </row>
     <row r="31">
@@ -1184,17 +1174,15 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>3662</v>
+        <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>3662</v>
+        <v>0</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
       </c>
-      <c r="F32" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="F32" s="2" t="n"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1208,16 +1196,16 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>28327</v>
+        <v>25013</v>
       </c>
       <c r="D33" t="n">
-        <v>27281</v>
+        <v>24742</v>
       </c>
       <c r="E33" t="n">
-        <v>1046</v>
+        <v>271</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>0.9631000000000001</v>
+        <v>0.9892</v>
       </c>
     </row>
     <row r="34">

--- a/output/TRANSFERENCIA_atual.xlsx
+++ b/output/TRANSFERENCIA_atual.xlsx
@@ -484,15 +484,17 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>1574</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>1562</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" s="2" t="n"/>
+        <v>12</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>0.9923999999999999</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -506,15 +508,17 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>5305</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>5237</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" s="2" t="n"/>
+        <v>68</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>0.9872</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -572,17 +576,15 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>11590</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>11589</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>0.9998999999999999</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -596,16 +598,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D7" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="8">
@@ -620,16 +622,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>3189</v>
+        <v>432</v>
       </c>
       <c r="D8" t="n">
         <v>432</v>
       </c>
       <c r="E8" t="n">
-        <v>2757</v>
+        <v>0</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.1355</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -644,15 +646,17 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>15719</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>14213</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="2" t="n"/>
+        <v>1506</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>0.9042</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -688,10 +692,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>106001</v>
+        <v>43073</v>
       </c>
       <c r="D11" t="n">
-        <v>106001</v>
+        <v>43073</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -734,17 +738,15 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1282</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>1282</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
-      <c r="F13" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="F13" s="2" t="n"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -758,15 +760,17 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>3036</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>3008</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" s="2" t="n"/>
+        <v>28</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>0.9908</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -824,10 +828,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>8603</v>
+        <v>3278</v>
       </c>
       <c r="D17" t="n">
-        <v>8603</v>
+        <v>3278</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -892,16 +896,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>3208</v>
+        <v>9169</v>
       </c>
       <c r="D20" t="n">
-        <v>3204</v>
+        <v>8914</v>
       </c>
       <c r="E20" t="n">
-        <v>4</v>
+        <v>255</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>0.9987999999999999</v>
+        <v>0.9722</v>
       </c>
     </row>
     <row r="21">
@@ -938,16 +942,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1</v>
+        <v>1603</v>
       </c>
       <c r="D22" t="n">
-        <v>1</v>
+        <v>1597</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>1</v>
+        <v>0.9963</v>
       </c>
     </row>
     <row r="23">
@@ -962,16 +966,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>6</v>
+        <v>6459</v>
       </c>
       <c r="D23" t="n">
-        <v>6</v>
+        <v>6414</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>1</v>
+        <v>0.993</v>
       </c>
     </row>
     <row r="24">
@@ -1008,16 +1012,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>16985</v>
+        <v>53524</v>
       </c>
       <c r="D25" t="n">
-        <v>16942</v>
+        <v>51070</v>
       </c>
       <c r="E25" t="n">
-        <v>43</v>
+        <v>2454</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>0.9975000000000001</v>
+        <v>0.9542</v>
       </c>
     </row>
     <row r="26">
@@ -1032,16 +1036,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>4691</v>
+        <v>567</v>
       </c>
       <c r="D26" t="n">
-        <v>3372</v>
+        <v>557</v>
       </c>
       <c r="E26" t="n">
-        <v>1319</v>
+        <v>10</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>0.7188</v>
+        <v>0.9823999999999999</v>
       </c>
     </row>
     <row r="27">
@@ -1056,16 +1060,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>8743</v>
+        <v>923</v>
       </c>
       <c r="D27" t="n">
-        <v>8638</v>
+        <v>915</v>
       </c>
       <c r="E27" t="n">
-        <v>105</v>
+        <v>8</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>0.988</v>
+        <v>0.9913</v>
       </c>
     </row>
     <row r="28">
@@ -1080,17 +1084,15 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>24</v>
-      </c>
-      <c r="F28" s="2" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F28" s="2" t="n"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1104,16 +1106,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>6785</v>
+        <v>1995</v>
       </c>
       <c r="D29" t="n">
-        <v>4073</v>
+        <v>1970</v>
       </c>
       <c r="E29" t="n">
-        <v>2712</v>
+        <v>25</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>0.6003000000000001</v>
+        <v>0.9875</v>
       </c>
     </row>
     <row r="30">
@@ -1128,16 +1130,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>878</v>
+        <v>473</v>
       </c>
       <c r="D30" t="n">
-        <v>870</v>
+        <v>468</v>
       </c>
       <c r="E30" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>0.9909</v>
+        <v>0.9893999999999999</v>
       </c>
     </row>
     <row r="31">
@@ -1174,15 +1176,17 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0</v>
+        <v>6516</v>
       </c>
       <c r="D32" t="n">
-        <v>0</v>
+        <v>6321</v>
       </c>
       <c r="E32" t="n">
-        <v>0</v>
-      </c>
-      <c r="F32" s="2" t="n"/>
+        <v>195</v>
+      </c>
+      <c r="F32" s="2" t="n">
+        <v>0.9701000000000001</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1196,16 +1200,16 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>25013</v>
+        <v>15260</v>
       </c>
       <c r="D33" t="n">
-        <v>24742</v>
+        <v>15144</v>
       </c>
       <c r="E33" t="n">
-        <v>271</v>
+        <v>116</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>0.9892</v>
+        <v>0.9923999999999999</v>
       </c>
     </row>
     <row r="34">
@@ -1220,17 +1224,15 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E34" t="n">
         <v>0</v>
       </c>
-      <c r="F34" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="F34" s="2" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:F34"/>

--- a/output/TRANSFERENCIA_atual.xlsx
+++ b/output/TRANSFERENCIA_atual.xlsx
@@ -484,16 +484,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1574</v>
+        <v>4789</v>
       </c>
       <c r="D2" t="n">
-        <v>1562</v>
+        <v>4765</v>
       </c>
       <c r="E2" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.9923999999999999</v>
+        <v>0.995</v>
       </c>
     </row>
     <row r="3">
@@ -508,16 +508,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5305</v>
+        <v>2620</v>
       </c>
       <c r="D3" t="n">
-        <v>5237</v>
+        <v>2598</v>
       </c>
       <c r="E3" t="n">
-        <v>68</v>
+        <v>22</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.9872</v>
+        <v>0.9915999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -532,15 +532,17 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>4349</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>4334</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" s="2" t="n"/>
+        <v>15</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>0.9965999999999999</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -554,15 +556,17 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>935</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>301</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="2" t="n"/>
+        <v>634</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>0.3219</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -598,16 +602,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>10</v>
+        <v>1922</v>
       </c>
       <c r="D7" t="n">
-        <v>9</v>
+        <v>1879</v>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>43</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.9</v>
+        <v>0.9776</v>
       </c>
     </row>
     <row r="8">
@@ -622,16 +626,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>432</v>
+        <v>8000</v>
       </c>
       <c r="D8" t="n">
-        <v>432</v>
+        <v>3664</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>4336</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>1</v>
+        <v>0.458</v>
       </c>
     </row>
     <row r="9">
@@ -646,16 +650,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>15719</v>
+        <v>25659</v>
       </c>
       <c r="D9" t="n">
-        <v>14213</v>
+        <v>23905</v>
       </c>
       <c r="E9" t="n">
-        <v>1506</v>
+        <v>1754</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0.9042</v>
+        <v>0.9316</v>
       </c>
     </row>
     <row r="10">
@@ -692,10 +696,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>43073</v>
+        <v>53144</v>
       </c>
       <c r="D11" t="n">
-        <v>43073</v>
+        <v>53144</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -716,15 +720,17 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>2786</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>2780</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" s="2" t="n"/>
+        <v>6</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>0.9978</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -760,16 +766,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>3036</v>
+        <v>4215</v>
       </c>
       <c r="D14" t="n">
-        <v>3008</v>
+        <v>4215</v>
       </c>
       <c r="E14" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0.9908</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -806,15 +812,17 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>248</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>247</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" s="2" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>0.996</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -828,10 +836,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>3278</v>
+        <v>1664</v>
       </c>
       <c r="D17" t="n">
-        <v>3278</v>
+        <v>1664</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -874,15 +882,17 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>1287</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>1286</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" s="2" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="F19" s="2" t="n">
+        <v>0.9992</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -896,16 +906,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>9169</v>
+        <v>10062</v>
       </c>
       <c r="D20" t="n">
-        <v>8914</v>
+        <v>10052</v>
       </c>
       <c r="E20" t="n">
-        <v>255</v>
+        <v>10</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>0.9722</v>
+        <v>0.9990000000000001</v>
       </c>
     </row>
     <row r="21">
@@ -942,16 +952,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1603</v>
+        <v>8166</v>
       </c>
       <c r="D22" t="n">
-        <v>1597</v>
+        <v>3251</v>
       </c>
       <c r="E22" t="n">
-        <v>6</v>
+        <v>4915</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>0.9963</v>
+        <v>0.3981</v>
       </c>
     </row>
     <row r="23">
@@ -966,16 +976,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>6459</v>
+        <v>56899</v>
       </c>
       <c r="D23" t="n">
-        <v>6414</v>
+        <v>53080</v>
       </c>
       <c r="E23" t="n">
-        <v>45</v>
+        <v>3819</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>0.993</v>
+        <v>0.9329000000000001</v>
       </c>
     </row>
     <row r="24">
@@ -1012,16 +1022,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>53524</v>
+        <v>52852</v>
       </c>
       <c r="D25" t="n">
-        <v>51070</v>
+        <v>31384</v>
       </c>
       <c r="E25" t="n">
-        <v>2454</v>
+        <v>21468</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>0.9542</v>
+        <v>0.5938</v>
       </c>
     </row>
     <row r="26">
@@ -1036,16 +1046,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>567</v>
+        <v>4039</v>
       </c>
       <c r="D26" t="n">
-        <v>557</v>
+        <v>3097</v>
       </c>
       <c r="E26" t="n">
-        <v>10</v>
+        <v>942</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>0.9823999999999999</v>
+        <v>0.7668</v>
       </c>
     </row>
     <row r="27">
@@ -1060,16 +1070,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>923</v>
+        <v>3414</v>
       </c>
       <c r="D27" t="n">
-        <v>915</v>
+        <v>3373</v>
       </c>
       <c r="E27" t="n">
-        <v>8</v>
+        <v>41</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>0.9913</v>
+        <v>0.988</v>
       </c>
     </row>
     <row r="28">
@@ -1106,16 +1116,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1995</v>
+        <v>3801</v>
       </c>
       <c r="D29" t="n">
-        <v>1970</v>
+        <v>2062</v>
       </c>
       <c r="E29" t="n">
-        <v>25</v>
+        <v>1739</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>0.9875</v>
+        <v>0.5425</v>
       </c>
     </row>
     <row r="30">
@@ -1130,16 +1140,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>473</v>
+        <v>59</v>
       </c>
       <c r="D30" t="n">
-        <v>468</v>
+        <v>58</v>
       </c>
       <c r="E30" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>0.9893999999999999</v>
+        <v>0.9831</v>
       </c>
     </row>
     <row r="31">
@@ -1176,16 +1186,16 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>6516</v>
+        <v>13829</v>
       </c>
       <c r="D32" t="n">
-        <v>6321</v>
+        <v>13517</v>
       </c>
       <c r="E32" t="n">
-        <v>195</v>
+        <v>312</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>0.9701000000000001</v>
+        <v>0.9773999999999999</v>
       </c>
     </row>
     <row r="33">
@@ -1200,16 +1210,16 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>15260</v>
+        <v>2787</v>
       </c>
       <c r="D33" t="n">
-        <v>15144</v>
+        <v>2787</v>
       </c>
       <c r="E33" t="n">
-        <v>116</v>
+        <v>0</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>0.9923999999999999</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34">

--- a/output/TRANSFERENCIA_atual.xlsx
+++ b/output/TRANSFERENCIA_atual.xlsx
@@ -484,16 +484,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4789</v>
+        <v>3856</v>
       </c>
       <c r="D2" t="n">
-        <v>4765</v>
+        <v>3819</v>
       </c>
       <c r="E2" t="n">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.995</v>
+        <v>0.9904000000000001</v>
       </c>
     </row>
     <row r="3">
@@ -508,16 +508,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2620</v>
+        <v>1933</v>
       </c>
       <c r="D3" t="n">
-        <v>2598</v>
+        <v>1647</v>
       </c>
       <c r="E3" t="n">
-        <v>22</v>
+        <v>286</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.9915999999999999</v>
+        <v>0.852</v>
       </c>
     </row>
     <row r="4">
@@ -532,16 +532,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>4349</v>
+        <v>989</v>
       </c>
       <c r="D4" t="n">
-        <v>4334</v>
+        <v>967</v>
       </c>
       <c r="E4" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.9965999999999999</v>
+        <v>0.9778</v>
       </c>
     </row>
     <row r="5">
@@ -556,16 +556,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>935</v>
+        <v>501</v>
       </c>
       <c r="D5" t="n">
-        <v>301</v>
+        <v>477</v>
       </c>
       <c r="E5" t="n">
-        <v>634</v>
+        <v>24</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.3219</v>
+        <v>0.9520999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -580,15 +580,17 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>4481</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>4481</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
-      <c r="F6" s="2" t="n"/>
+      <c r="F6" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -602,16 +604,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1922</v>
+        <v>2242</v>
       </c>
       <c r="D7" t="n">
-        <v>1879</v>
+        <v>2192</v>
       </c>
       <c r="E7" t="n">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.9776</v>
+        <v>0.9777</v>
       </c>
     </row>
     <row r="8">
@@ -626,16 +628,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>8000</v>
+        <v>18162</v>
       </c>
       <c r="D8" t="n">
-        <v>3664</v>
+        <v>4791</v>
       </c>
       <c r="E8" t="n">
-        <v>4336</v>
+        <v>13371</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.458</v>
+        <v>0.2638</v>
       </c>
     </row>
     <row r="9">
@@ -650,16 +652,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>25659</v>
+        <v>16027</v>
       </c>
       <c r="D9" t="n">
-        <v>23905</v>
+        <v>12868</v>
       </c>
       <c r="E9" t="n">
-        <v>1754</v>
+        <v>3159</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0.9316</v>
+        <v>0.8029000000000001</v>
       </c>
     </row>
     <row r="10">
@@ -696,10 +698,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>53144</v>
+        <v>86712</v>
       </c>
       <c r="D11" t="n">
-        <v>53144</v>
+        <v>86712</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -720,16 +722,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2786</v>
+        <v>4569</v>
       </c>
       <c r="D12" t="n">
-        <v>2780</v>
+        <v>4200</v>
       </c>
       <c r="E12" t="n">
-        <v>6</v>
+        <v>369</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>0.9978</v>
+        <v>0.9192</v>
       </c>
     </row>
     <row r="13">
@@ -744,15 +746,17 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>3178</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>3178</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
-      <c r="F13" s="2" t="n"/>
+      <c r="F13" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -766,16 +770,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>4215</v>
+        <v>6903</v>
       </c>
       <c r="D14" t="n">
-        <v>4215</v>
+        <v>6890</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>1</v>
+        <v>0.9981</v>
       </c>
     </row>
     <row r="15">
@@ -812,16 +816,16 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>248</v>
+        <v>572</v>
       </c>
       <c r="D16" t="n">
-        <v>247</v>
+        <v>557</v>
       </c>
       <c r="E16" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>0.996</v>
+        <v>0.9738</v>
       </c>
     </row>
     <row r="17">
@@ -836,10 +840,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1664</v>
+        <v>3981</v>
       </c>
       <c r="D17" t="n">
-        <v>1664</v>
+        <v>3981</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -882,16 +886,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1287</v>
+        <v>776</v>
       </c>
       <c r="D19" t="n">
-        <v>1286</v>
+        <v>773</v>
       </c>
       <c r="E19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>0.9992</v>
+        <v>0.9961</v>
       </c>
     </row>
     <row r="20">
@@ -906,16 +910,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>10062</v>
+        <v>9613</v>
       </c>
       <c r="D20" t="n">
-        <v>10052</v>
+        <v>9513</v>
       </c>
       <c r="E20" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>0.9990000000000001</v>
+        <v>0.9895999999999999</v>
       </c>
     </row>
     <row r="21">
@@ -952,16 +956,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>8166</v>
+        <v>3871</v>
       </c>
       <c r="D22" t="n">
-        <v>3251</v>
+        <v>3732</v>
       </c>
       <c r="E22" t="n">
-        <v>4915</v>
+        <v>139</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>0.3981</v>
+        <v>0.9641</v>
       </c>
     </row>
     <row r="23">
@@ -976,16 +980,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>56899</v>
+        <v>44366</v>
       </c>
       <c r="D23" t="n">
-        <v>53080</v>
+        <v>38855</v>
       </c>
       <c r="E23" t="n">
-        <v>3819</v>
+        <v>5511</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>0.9329000000000001</v>
+        <v>0.8758</v>
       </c>
     </row>
     <row r="24">
@@ -1022,16 +1026,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>52852</v>
+        <v>65760</v>
       </c>
       <c r="D25" t="n">
-        <v>31384</v>
+        <v>56032</v>
       </c>
       <c r="E25" t="n">
-        <v>21468</v>
+        <v>9728</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>0.5938</v>
+        <v>0.8521</v>
       </c>
     </row>
     <row r="26">
@@ -1046,16 +1050,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>4039</v>
+        <v>9594</v>
       </c>
       <c r="D26" t="n">
-        <v>3097</v>
+        <v>8474</v>
       </c>
       <c r="E26" t="n">
-        <v>942</v>
+        <v>1120</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>0.7668</v>
+        <v>0.8833</v>
       </c>
     </row>
     <row r="27">
@@ -1070,16 +1074,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>3414</v>
+        <v>14420</v>
       </c>
       <c r="D27" t="n">
-        <v>3373</v>
+        <v>7656</v>
       </c>
       <c r="E27" t="n">
-        <v>41</v>
+        <v>6764</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>0.988</v>
+        <v>0.5309</v>
       </c>
     </row>
     <row r="28">
@@ -1094,15 +1098,17 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
-      </c>
-      <c r="F28" s="2" t="n"/>
+        <v>41</v>
+      </c>
+      <c r="F28" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1116,16 +1122,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>3801</v>
+        <v>17829</v>
       </c>
       <c r="D29" t="n">
-        <v>2062</v>
+        <v>9830</v>
       </c>
       <c r="E29" t="n">
-        <v>1739</v>
+        <v>7999</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>0.5425</v>
+        <v>0.5513</v>
       </c>
     </row>
     <row r="30">
@@ -1140,17 +1146,15 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>1</v>
-      </c>
-      <c r="F30" s="2" t="n">
-        <v>0.9831</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F30" s="2" t="n"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1186,16 +1190,16 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>13829</v>
+        <v>19541</v>
       </c>
       <c r="D32" t="n">
-        <v>13517</v>
+        <v>18283</v>
       </c>
       <c r="E32" t="n">
-        <v>312</v>
+        <v>1258</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>0.9773999999999999</v>
+        <v>0.9356</v>
       </c>
     </row>
     <row r="33">
@@ -1210,10 +1214,10 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>2787</v>
+        <v>931</v>
       </c>
       <c r="D33" t="n">
-        <v>2787</v>
+        <v>931</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>

--- a/output/TRANSFERENCIA_atual.xlsx
+++ b/output/TRANSFERENCIA_atual.xlsx
@@ -484,16 +484,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3856</v>
+        <v>5050</v>
       </c>
       <c r="D2" t="n">
-        <v>3819</v>
+        <v>4981</v>
       </c>
       <c r="E2" t="n">
-        <v>37</v>
+        <v>69</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.9904000000000001</v>
+        <v>0.9863</v>
       </c>
     </row>
     <row r="3">
@@ -508,16 +508,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1933</v>
+        <v>4826</v>
       </c>
       <c r="D3" t="n">
-        <v>1647</v>
+        <v>2340</v>
       </c>
       <c r="E3" t="n">
-        <v>286</v>
+        <v>2486</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.852</v>
+        <v>0.4849</v>
       </c>
     </row>
     <row r="4">
@@ -532,16 +532,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>989</v>
+        <v>956</v>
       </c>
       <c r="D4" t="n">
-        <v>967</v>
+        <v>928</v>
       </c>
       <c r="E4" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.9778</v>
+        <v>0.9706999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -556,16 +556,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>501</v>
+        <v>841</v>
       </c>
       <c r="D5" t="n">
-        <v>477</v>
+        <v>840</v>
       </c>
       <c r="E5" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.9520999999999999</v>
+        <v>0.9987999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -580,10 +580,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>4481</v>
+        <v>18741</v>
       </c>
       <c r="D6" t="n">
-        <v>4481</v>
+        <v>18741</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -604,16 +604,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2242</v>
+        <v>13296</v>
       </c>
       <c r="D7" t="n">
-        <v>2192</v>
+        <v>12739</v>
       </c>
       <c r="E7" t="n">
-        <v>50</v>
+        <v>557</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.9777</v>
+        <v>0.9581000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -628,16 +628,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>18162</v>
+        <v>20749</v>
       </c>
       <c r="D8" t="n">
-        <v>4791</v>
+        <v>2846</v>
       </c>
       <c r="E8" t="n">
-        <v>13371</v>
+        <v>17903</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.2638</v>
+        <v>0.1372</v>
       </c>
     </row>
     <row r="9">
@@ -652,16 +652,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>16027</v>
+        <v>26292</v>
       </c>
       <c r="D9" t="n">
-        <v>12868</v>
+        <v>23542</v>
       </c>
       <c r="E9" t="n">
-        <v>3159</v>
+        <v>2750</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0.8029000000000001</v>
+        <v>0.8954000000000001</v>
       </c>
     </row>
     <row r="10">
@@ -698,16 +698,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>86712</v>
+        <v>73706</v>
       </c>
       <c r="D11" t="n">
-        <v>86712</v>
+        <v>71688</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>2018</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>1</v>
+        <v>0.9726</v>
       </c>
     </row>
     <row r="12">
@@ -722,16 +722,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>4569</v>
+        <v>5773</v>
       </c>
       <c r="D12" t="n">
-        <v>4200</v>
+        <v>5379</v>
       </c>
       <c r="E12" t="n">
-        <v>369</v>
+        <v>394</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>0.9192</v>
+        <v>0.9318000000000001</v>
       </c>
     </row>
     <row r="13">
@@ -746,10 +746,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3178</v>
+        <v>4955</v>
       </c>
       <c r="D13" t="n">
-        <v>3178</v>
+        <v>4955</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -770,16 +770,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>6903</v>
+        <v>4984</v>
       </c>
       <c r="D14" t="n">
-        <v>6890</v>
+        <v>4984</v>
       </c>
       <c r="E14" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0.9981</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -816,16 +816,16 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>572</v>
+        <v>789</v>
       </c>
       <c r="D16" t="n">
-        <v>557</v>
+        <v>784</v>
       </c>
       <c r="E16" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>0.9738</v>
+        <v>0.9937</v>
       </c>
     </row>
     <row r="17">
@@ -840,10 +840,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>3981</v>
+        <v>5400</v>
       </c>
       <c r="D17" t="n">
-        <v>3981</v>
+        <v>5400</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -886,16 +886,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>776</v>
+        <v>1141</v>
       </c>
       <c r="D19" t="n">
-        <v>773</v>
+        <v>1136</v>
       </c>
       <c r="E19" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>0.9961</v>
+        <v>0.9956</v>
       </c>
     </row>
     <row r="20">
@@ -910,16 +910,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>9613</v>
+        <v>10430</v>
       </c>
       <c r="D20" t="n">
-        <v>9513</v>
+        <v>7291</v>
       </c>
       <c r="E20" t="n">
-        <v>100</v>
+        <v>3139</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>0.9895999999999999</v>
+        <v>0.6990000000000001</v>
       </c>
     </row>
     <row r="21">
@@ -956,16 +956,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>3871</v>
+        <v>3957</v>
       </c>
       <c r="D22" t="n">
-        <v>3732</v>
+        <v>3808</v>
       </c>
       <c r="E22" t="n">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>0.9641</v>
+        <v>0.9623</v>
       </c>
     </row>
     <row r="23">
@@ -980,16 +980,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>44366</v>
+        <v>34456</v>
       </c>
       <c r="D23" t="n">
-        <v>38855</v>
+        <v>30185</v>
       </c>
       <c r="E23" t="n">
-        <v>5511</v>
+        <v>4271</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>0.8758</v>
+        <v>0.8759999999999999</v>
       </c>
     </row>
     <row r="24">
@@ -1026,16 +1026,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>65760</v>
+        <v>45768</v>
       </c>
       <c r="D25" t="n">
-        <v>56032</v>
+        <v>41434</v>
       </c>
       <c r="E25" t="n">
-        <v>9728</v>
+        <v>4334</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>0.8521</v>
+        <v>0.9053</v>
       </c>
     </row>
     <row r="26">
@@ -1050,16 +1050,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>9594</v>
+        <v>12263</v>
       </c>
       <c r="D26" t="n">
-        <v>8474</v>
+        <v>11196</v>
       </c>
       <c r="E26" t="n">
-        <v>1120</v>
+        <v>1067</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>0.8833</v>
+        <v>0.9129999999999999</v>
       </c>
     </row>
     <row r="27">
@@ -1074,16 +1074,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>14420</v>
+        <v>11027</v>
       </c>
       <c r="D27" t="n">
-        <v>7656</v>
+        <v>4304</v>
       </c>
       <c r="E27" t="n">
-        <v>6764</v>
+        <v>6723</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>0.5309</v>
+        <v>0.3903</v>
       </c>
     </row>
     <row r="28">
@@ -1098,13 +1098,13 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="F28" s="2" t="n">
         <v>0</v>
@@ -1122,16 +1122,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>17829</v>
+        <v>23930</v>
       </c>
       <c r="D29" t="n">
-        <v>9830</v>
+        <v>14681</v>
       </c>
       <c r="E29" t="n">
-        <v>7999</v>
+        <v>9249</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>0.5513</v>
+        <v>0.6135</v>
       </c>
     </row>
     <row r="30">
@@ -1146,15 +1146,17 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>1090</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>1086</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
-      </c>
-      <c r="F30" s="2" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="F30" s="2" t="n">
+        <v>0.9963</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1190,16 +1192,16 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>19541</v>
+        <v>9128</v>
       </c>
       <c r="D32" t="n">
-        <v>18283</v>
+        <v>8878</v>
       </c>
       <c r="E32" t="n">
-        <v>1258</v>
+        <v>250</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>0.9356</v>
+        <v>0.9726</v>
       </c>
     </row>
     <row r="33">
@@ -1214,16 +1216,16 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>931</v>
+        <v>39902</v>
       </c>
       <c r="D33" t="n">
-        <v>931</v>
+        <v>38147</v>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>1755</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>1</v>
+        <v>0.956</v>
       </c>
     </row>
     <row r="34">

--- a/output/TRANSFERENCIA_atual.xlsx
+++ b/output/TRANSFERENCIA_atual.xlsx
@@ -484,16 +484,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5050</v>
+        <v>4018</v>
       </c>
       <c r="D2" t="n">
-        <v>4981</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>69</v>
+        <v>4018</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.9863</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -508,16 +508,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>4826</v>
+        <v>2626</v>
       </c>
       <c r="D3" t="n">
-        <v>2340</v>
+        <v>2538</v>
       </c>
       <c r="E3" t="n">
-        <v>2486</v>
+        <v>88</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.4849</v>
+        <v>0.9665</v>
       </c>
     </row>
     <row r="4">
@@ -532,16 +532,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>956</v>
+        <v>1253</v>
       </c>
       <c r="D4" t="n">
-        <v>928</v>
+        <v>1226</v>
       </c>
       <c r="E4" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.9706999999999999</v>
+        <v>0.9784999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -556,16 +556,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>841</v>
+        <v>279</v>
       </c>
       <c r="D5" t="n">
-        <v>840</v>
+        <v>256</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.9987999999999999</v>
+        <v>0.9176000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -580,10 +580,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>18741</v>
+        <v>25600</v>
       </c>
       <c r="D6" t="n">
-        <v>18741</v>
+        <v>25600</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -604,16 +604,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>13296</v>
+        <v>17981</v>
       </c>
       <c r="D7" t="n">
-        <v>12739</v>
+        <v>10893</v>
       </c>
       <c r="E7" t="n">
-        <v>557</v>
+        <v>7088</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.9581000000000001</v>
+        <v>0.6058</v>
       </c>
     </row>
     <row r="8">
@@ -628,16 +628,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>20749</v>
+        <v>17076</v>
       </c>
       <c r="D8" t="n">
-        <v>2846</v>
+        <v>4241</v>
       </c>
       <c r="E8" t="n">
-        <v>17903</v>
+        <v>12835</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.1372</v>
+        <v>0.2484</v>
       </c>
     </row>
     <row r="9">
@@ -652,16 +652,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>26292</v>
+        <v>29027</v>
       </c>
       <c r="D9" t="n">
-        <v>23542</v>
+        <v>16885</v>
       </c>
       <c r="E9" t="n">
-        <v>2750</v>
+        <v>12142</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0.8954000000000001</v>
+        <v>0.5817</v>
       </c>
     </row>
     <row r="10">
@@ -698,16 +698,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>73706</v>
+        <v>84789</v>
       </c>
       <c r="D11" t="n">
-        <v>71688</v>
+        <v>67339</v>
       </c>
       <c r="E11" t="n">
-        <v>2018</v>
+        <v>17450</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>0.9726</v>
+        <v>0.7942</v>
       </c>
     </row>
     <row r="12">
@@ -722,16 +722,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>5773</v>
+        <v>5123</v>
       </c>
       <c r="D12" t="n">
-        <v>5379</v>
+        <v>2386</v>
       </c>
       <c r="E12" t="n">
-        <v>394</v>
+        <v>2737</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>0.9318000000000001</v>
+        <v>0.4657</v>
       </c>
     </row>
     <row r="13">
@@ -746,10 +746,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>4955</v>
+        <v>4307</v>
       </c>
       <c r="D13" t="n">
-        <v>4955</v>
+        <v>4307</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -770,16 +770,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>4984</v>
+        <v>4876</v>
       </c>
       <c r="D14" t="n">
-        <v>4984</v>
+        <v>4681</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>195</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>1</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="15">
@@ -816,16 +816,16 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>789</v>
+        <v>686</v>
       </c>
       <c r="D16" t="n">
-        <v>784</v>
+        <v>543</v>
       </c>
       <c r="E16" t="n">
-        <v>5</v>
+        <v>143</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>0.9937</v>
+        <v>0.7915000000000001</v>
       </c>
     </row>
     <row r="17">
@@ -840,10 +840,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>5400</v>
+        <v>7873</v>
       </c>
       <c r="D17" t="n">
-        <v>5400</v>
+        <v>7873</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -886,17 +886,15 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1141</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>1136</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>5</v>
-      </c>
-      <c r="F19" s="2" t="n">
-        <v>0.9956</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F19" s="2" t="n"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -910,16 +908,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>10430</v>
+        <v>11428</v>
       </c>
       <c r="D20" t="n">
-        <v>7291</v>
+        <v>4319</v>
       </c>
       <c r="E20" t="n">
-        <v>3139</v>
+        <v>7109</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>0.6990000000000001</v>
+        <v>0.3779</v>
       </c>
     </row>
     <row r="21">
@@ -956,16 +954,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>3957</v>
+        <v>2774</v>
       </c>
       <c r="D22" t="n">
-        <v>3808</v>
+        <v>2656</v>
       </c>
       <c r="E22" t="n">
-        <v>149</v>
+        <v>118</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>0.9623</v>
+        <v>0.9575</v>
       </c>
     </row>
     <row r="23">
@@ -980,16 +978,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>34456</v>
+        <v>26205</v>
       </c>
       <c r="D23" t="n">
-        <v>30185</v>
+        <v>25314</v>
       </c>
       <c r="E23" t="n">
-        <v>4271</v>
+        <v>891</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>0.8759999999999999</v>
+        <v>0.966</v>
       </c>
     </row>
     <row r="24">
@@ -1026,16 +1024,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>45768</v>
+        <v>43084</v>
       </c>
       <c r="D25" t="n">
-        <v>41434</v>
+        <v>33179</v>
       </c>
       <c r="E25" t="n">
-        <v>4334</v>
+        <v>9905</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>0.9053</v>
+        <v>0.7701</v>
       </c>
     </row>
     <row r="26">
@@ -1050,16 +1048,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>12263</v>
+        <v>13542</v>
       </c>
       <c r="D26" t="n">
-        <v>11196</v>
+        <v>11093</v>
       </c>
       <c r="E26" t="n">
-        <v>1067</v>
+        <v>2449</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>0.9129999999999999</v>
+        <v>0.8192</v>
       </c>
     </row>
     <row r="27">
@@ -1074,16 +1072,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>11027</v>
+        <v>9437</v>
       </c>
       <c r="D27" t="n">
-        <v>4304</v>
+        <v>9166</v>
       </c>
       <c r="E27" t="n">
-        <v>6723</v>
+        <v>271</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>0.3903</v>
+        <v>0.9712999999999999</v>
       </c>
     </row>
     <row r="28">
@@ -1098,13 +1096,13 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="F28" s="2" t="n">
         <v>0</v>
@@ -1122,16 +1120,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>23930</v>
+        <v>17841</v>
       </c>
       <c r="D29" t="n">
-        <v>14681</v>
+        <v>11138</v>
       </c>
       <c r="E29" t="n">
-        <v>9249</v>
+        <v>6703</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>0.6135</v>
+        <v>0.6243</v>
       </c>
     </row>
     <row r="30">
@@ -1146,16 +1144,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1090</v>
+        <v>1762</v>
       </c>
       <c r="D30" t="n">
-        <v>1086</v>
+        <v>1754</v>
       </c>
       <c r="E30" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>0.9963</v>
+        <v>0.9954999999999999</v>
       </c>
     </row>
     <row r="31">
@@ -1192,16 +1190,16 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>9128</v>
+        <v>10841</v>
       </c>
       <c r="D32" t="n">
-        <v>8878</v>
+        <v>10114</v>
       </c>
       <c r="E32" t="n">
-        <v>250</v>
+        <v>727</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>0.9726</v>
+        <v>0.9329000000000001</v>
       </c>
     </row>
     <row r="33">
@@ -1216,16 +1214,16 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>39902</v>
+        <v>56166</v>
       </c>
       <c r="D33" t="n">
-        <v>38147</v>
+        <v>52971</v>
       </c>
       <c r="E33" t="n">
-        <v>1755</v>
+        <v>3195</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>0.956</v>
+        <v>0.9431</v>
       </c>
     </row>
     <row r="34">

--- a/output/TRANSFERENCIA_atual.xlsx
+++ b/output/TRANSFERENCIA_atual.xlsx
@@ -484,13 +484,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4018</v>
+        <v>4525</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>4018</v>
+        <v>4525</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>0</v>
@@ -508,16 +508,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2626</v>
+        <v>2035</v>
       </c>
       <c r="D3" t="n">
-        <v>2538</v>
+        <v>1416</v>
       </c>
       <c r="E3" t="n">
-        <v>88</v>
+        <v>619</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.9665</v>
+        <v>0.6958</v>
       </c>
     </row>
     <row r="4">
@@ -532,17 +532,15 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1253</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>1226</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>27</v>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>0.9784999999999999</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -556,17 +554,15 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>279</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>256</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>23</v>
-      </c>
-      <c r="F5" s="2" t="n">
-        <v>0.9176000000000001</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F5" s="2" t="n"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -580,10 +576,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>25600</v>
+        <v>25808</v>
       </c>
       <c r="D6" t="n">
-        <v>25600</v>
+        <v>25808</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -604,16 +600,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>17981</v>
+        <v>38639</v>
       </c>
       <c r="D7" t="n">
-        <v>10893</v>
+        <v>64</v>
       </c>
       <c r="E7" t="n">
-        <v>7088</v>
+        <v>38575</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.6058</v>
+        <v>0.0017</v>
       </c>
     </row>
     <row r="8">
@@ -628,16 +624,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17076</v>
+        <v>9906</v>
       </c>
       <c r="D8" t="n">
-        <v>4241</v>
+        <v>5649</v>
       </c>
       <c r="E8" t="n">
-        <v>12835</v>
+        <v>4257</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.2484</v>
+        <v>0.5703</v>
       </c>
     </row>
     <row r="9">
@@ -652,16 +648,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>29027</v>
+        <v>16776</v>
       </c>
       <c r="D9" t="n">
-        <v>16885</v>
+        <v>15694</v>
       </c>
       <c r="E9" t="n">
-        <v>12142</v>
+        <v>1082</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0.5817</v>
+        <v>0.9355</v>
       </c>
     </row>
     <row r="10">
@@ -698,16 +694,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>84789</v>
+        <v>79563</v>
       </c>
       <c r="D11" t="n">
-        <v>67339</v>
+        <v>52155</v>
       </c>
       <c r="E11" t="n">
-        <v>17450</v>
+        <v>27408</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>0.7942</v>
+        <v>0.6555</v>
       </c>
     </row>
     <row r="12">
@@ -722,16 +718,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>5123</v>
+        <v>333</v>
       </c>
       <c r="D12" t="n">
-        <v>2386</v>
+        <v>333</v>
       </c>
       <c r="E12" t="n">
-        <v>2737</v>
+        <v>0</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>0.4657</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -746,10 +742,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>4307</v>
+        <v>4497</v>
       </c>
       <c r="D13" t="n">
-        <v>4307</v>
+        <v>4497</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -770,17 +766,15 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>4876</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>4681</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>195</v>
-      </c>
-      <c r="F14" s="2" t="n">
-        <v>0.96</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F14" s="2" t="n"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -816,17 +810,15 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>686</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>543</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>143</v>
-      </c>
-      <c r="F16" s="2" t="n">
-        <v>0.7915000000000001</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F16" s="2" t="n"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -840,10 +832,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>7873</v>
+        <v>7127</v>
       </c>
       <c r="D17" t="n">
-        <v>7873</v>
+        <v>7127</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -908,16 +900,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>11428</v>
+        <v>10236</v>
       </c>
       <c r="D20" t="n">
-        <v>4319</v>
+        <v>10078</v>
       </c>
       <c r="E20" t="n">
-        <v>7109</v>
+        <v>158</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>0.3779</v>
+        <v>0.9845999999999999</v>
       </c>
     </row>
     <row r="21">
@@ -954,16 +946,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>2774</v>
+        <v>994</v>
       </c>
       <c r="D22" t="n">
-        <v>2656</v>
+        <v>983</v>
       </c>
       <c r="E22" t="n">
-        <v>118</v>
+        <v>11</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>0.9575</v>
+        <v>0.9889</v>
       </c>
     </row>
     <row r="23">
@@ -978,16 +970,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>26205</v>
+        <v>10430</v>
       </c>
       <c r="D23" t="n">
-        <v>25314</v>
+        <v>10376</v>
       </c>
       <c r="E23" t="n">
-        <v>891</v>
+        <v>54</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>0.966</v>
+        <v>0.9948</v>
       </c>
     </row>
     <row r="24">
@@ -1024,16 +1016,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>43084</v>
+        <v>21826</v>
       </c>
       <c r="D25" t="n">
-        <v>33179</v>
+        <v>20882</v>
       </c>
       <c r="E25" t="n">
-        <v>9905</v>
+        <v>944</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>0.7701</v>
+        <v>0.9567</v>
       </c>
     </row>
     <row r="26">
@@ -1048,16 +1040,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>13542</v>
+        <v>15108</v>
       </c>
       <c r="D26" t="n">
-        <v>11093</v>
+        <v>13084</v>
       </c>
       <c r="E26" t="n">
-        <v>2449</v>
+        <v>2024</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>0.8192</v>
+        <v>0.866</v>
       </c>
     </row>
     <row r="27">
@@ -1072,16 +1064,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>9437</v>
+        <v>18542</v>
       </c>
       <c r="D27" t="n">
-        <v>9166</v>
+        <v>18110</v>
       </c>
       <c r="E27" t="n">
-        <v>271</v>
+        <v>432</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>0.9712999999999999</v>
+        <v>0.9767</v>
       </c>
     </row>
     <row r="28">
@@ -1096,13 +1088,13 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="F28" s="2" t="n">
         <v>0</v>
@@ -1120,16 +1112,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>17841</v>
+        <v>13499</v>
       </c>
       <c r="D29" t="n">
-        <v>11138</v>
+        <v>8701</v>
       </c>
       <c r="E29" t="n">
-        <v>6703</v>
+        <v>4798</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>0.6243</v>
+        <v>0.6446</v>
       </c>
     </row>
     <row r="30">
@@ -1144,16 +1136,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1762</v>
+        <v>1386</v>
       </c>
       <c r="D30" t="n">
-        <v>1754</v>
+        <v>1376</v>
       </c>
       <c r="E30" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>0.9954999999999999</v>
+        <v>0.9928</v>
       </c>
     </row>
     <row r="31">
@@ -1190,16 +1182,16 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>10841</v>
+        <v>3441</v>
       </c>
       <c r="D32" t="n">
-        <v>10114</v>
+        <v>3355</v>
       </c>
       <c r="E32" t="n">
-        <v>727</v>
+        <v>86</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>0.9329000000000001</v>
+        <v>0.975</v>
       </c>
     </row>
     <row r="33">
@@ -1214,16 +1206,16 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>56166</v>
+        <v>31386</v>
       </c>
       <c r="D33" t="n">
-        <v>52971</v>
+        <v>29724</v>
       </c>
       <c r="E33" t="n">
-        <v>3195</v>
+        <v>1662</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>0.9431</v>
+        <v>0.9470000000000001</v>
       </c>
     </row>
     <row r="34">

--- a/output/TRANSFERENCIA_atual.xlsx
+++ b/output/TRANSFERENCIA_atual.xlsx
@@ -484,17 +484,15 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4525</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>4525</v>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -508,17 +506,15 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2035</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>1416</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>619</v>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>0.6958</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -576,10 +572,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>25808</v>
+        <v>14476</v>
       </c>
       <c r="D6" t="n">
-        <v>25808</v>
+        <v>14476</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -600,16 +596,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>38639</v>
+        <v>69</v>
       </c>
       <c r="D7" t="n">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="E7" t="n">
-        <v>38575</v>
+        <v>0</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.0017</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -624,16 +620,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>9906</v>
+        <v>3417</v>
       </c>
       <c r="D8" t="n">
-        <v>5649</v>
+        <v>3127</v>
       </c>
       <c r="E8" t="n">
-        <v>4257</v>
+        <v>290</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.5703</v>
+        <v>0.9151</v>
       </c>
     </row>
     <row r="9">
@@ -648,17 +644,15 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>16776</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>15694</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>1082</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>0.9355</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F9" s="2" t="n"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -694,16 +688,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>79563</v>
+        <v>93788</v>
       </c>
       <c r="D11" t="n">
-        <v>52155</v>
+        <v>81541</v>
       </c>
       <c r="E11" t="n">
-        <v>27408</v>
+        <v>12247</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>0.6555</v>
+        <v>0.8694</v>
       </c>
     </row>
     <row r="12">
@@ -718,17 +712,15 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>333</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>333</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
       </c>
-      <c r="F12" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="F12" s="2" t="n"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -742,10 +734,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>4497</v>
+        <v>1967</v>
       </c>
       <c r="D13" t="n">
-        <v>4497</v>
+        <v>1967</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -832,10 +824,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>7127</v>
+        <v>6771</v>
       </c>
       <c r="D17" t="n">
-        <v>7127</v>
+        <v>6771</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -900,16 +892,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>10236</v>
+        <v>3478</v>
       </c>
       <c r="D20" t="n">
-        <v>10078</v>
+        <v>3478</v>
       </c>
       <c r="E20" t="n">
-        <v>158</v>
+        <v>0</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>0.9845999999999999</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -946,16 +938,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>994</v>
+        <v>3</v>
       </c>
       <c r="D22" t="n">
-        <v>983</v>
+        <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>0.9889</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -970,16 +962,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>10430</v>
+        <v>60</v>
       </c>
       <c r="D23" t="n">
-        <v>10376</v>
+        <v>60</v>
       </c>
       <c r="E23" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>0.9948</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1016,16 +1008,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>21826</v>
+        <v>14591</v>
       </c>
       <c r="D25" t="n">
-        <v>20882</v>
+        <v>14590</v>
       </c>
       <c r="E25" t="n">
-        <v>944</v>
+        <v>1</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>0.9567</v>
+        <v>0.9998999999999999</v>
       </c>
     </row>
     <row r="26">
@@ -1040,16 +1032,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>15108</v>
+        <v>12067</v>
       </c>
       <c r="D26" t="n">
-        <v>13084</v>
+        <v>11515</v>
       </c>
       <c r="E26" t="n">
-        <v>2024</v>
+        <v>552</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>0.866</v>
+        <v>0.9543</v>
       </c>
     </row>
     <row r="27">
@@ -1064,16 +1056,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>18542</v>
+        <v>9598</v>
       </c>
       <c r="D27" t="n">
-        <v>18110</v>
+        <v>9437</v>
       </c>
       <c r="E27" t="n">
-        <v>432</v>
+        <v>161</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>0.9767</v>
+        <v>0.9832</v>
       </c>
     </row>
     <row r="28">
@@ -1088,13 +1080,13 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="F28" s="2" t="n">
         <v>0</v>
@@ -1112,16 +1104,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>13499</v>
+        <v>8127</v>
       </c>
       <c r="D29" t="n">
-        <v>8701</v>
+        <v>7129</v>
       </c>
       <c r="E29" t="n">
-        <v>4798</v>
+        <v>998</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>0.6446</v>
+        <v>0.8772</v>
       </c>
     </row>
     <row r="30">
@@ -1136,16 +1128,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1386</v>
+        <v>1554</v>
       </c>
       <c r="D30" t="n">
-        <v>1376</v>
+        <v>1538</v>
       </c>
       <c r="E30" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>0.9928</v>
+        <v>0.9897</v>
       </c>
     </row>
     <row r="31">
@@ -1182,16 +1174,16 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>3441</v>
+        <v>8</v>
       </c>
       <c r="D32" t="n">
-        <v>3355</v>
+        <v>8</v>
       </c>
       <c r="E32" t="n">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>0.975</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -1206,16 +1198,16 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>31386</v>
+        <v>29055</v>
       </c>
       <c r="D33" t="n">
-        <v>29724</v>
+        <v>28608</v>
       </c>
       <c r="E33" t="n">
-        <v>1662</v>
+        <v>447</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>0.9470000000000001</v>
+        <v>0.9845999999999999</v>
       </c>
     </row>
     <row r="34">

--- a/output/TRANSFERENCIA_atual.xlsx
+++ b/output/TRANSFERENCIA_atual.xlsx
@@ -484,15 +484,17 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>5181</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>5175</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" s="2" t="n"/>
+        <v>6</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>0.9987999999999999</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -506,15 +508,17 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>5770</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>2994</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" s="2" t="n"/>
+        <v>2776</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>0.5189</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -528,15 +532,17 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>3195</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>2848</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" s="2" t="n"/>
+        <v>347</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>0.8914</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -550,15 +556,17 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>556</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>523</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="2" t="n"/>
+        <v>33</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>0.9406</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -572,10 +580,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>14476</v>
+        <v>8</v>
       </c>
       <c r="D6" t="n">
-        <v>14476</v>
+        <v>8</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -596,16 +604,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="D7" t="n">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>1</v>
+        <v>0.9759</v>
       </c>
     </row>
     <row r="8">
@@ -620,17 +628,15 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>3417</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>3127</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>290</v>
-      </c>
-      <c r="F8" s="2" t="n">
-        <v>0.9151</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F8" s="2" t="n"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -644,15 +650,17 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>21193</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>20397</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="2" t="n"/>
+        <v>796</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>0.9623999999999999</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -688,16 +696,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>93788</v>
+        <v>58876</v>
       </c>
       <c r="D11" t="n">
-        <v>81541</v>
+        <v>58605</v>
       </c>
       <c r="E11" t="n">
-        <v>12247</v>
+        <v>271</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>0.8694</v>
+        <v>0.9954000000000001</v>
       </c>
     </row>
     <row r="12">
@@ -712,15 +720,17 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>3646</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>3644</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" s="2" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>0.9995000000000001</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -734,17 +744,15 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1967</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>1967</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
-      <c r="F13" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="F13" s="2" t="n"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -758,15 +766,17 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>5690</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>5671</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" s="2" t="n"/>
+        <v>19</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>0.9967</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -802,15 +812,17 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>850</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>415</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" s="2" t="n"/>
+        <v>435</v>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>0.4882</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -824,10 +836,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>6771</v>
+        <v>6610</v>
       </c>
       <c r="D17" t="n">
-        <v>6771</v>
+        <v>6610</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -870,15 +882,17 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>1154</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>1133</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" s="2" t="n"/>
+        <v>21</v>
+      </c>
+      <c r="F19" s="2" t="n">
+        <v>0.9818000000000001</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -892,16 +906,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>3478</v>
+        <v>19413</v>
       </c>
       <c r="D20" t="n">
-        <v>3478</v>
+        <v>16902</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>2511</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>1</v>
+        <v>0.8706999999999999</v>
       </c>
     </row>
     <row r="21">
@@ -938,16 +952,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>3</v>
+        <v>4794</v>
       </c>
       <c r="D22" t="n">
-        <v>3</v>
+        <v>4651</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>143</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>1</v>
+        <v>0.9702</v>
       </c>
     </row>
     <row r="23">
@@ -962,16 +976,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>60</v>
+        <v>39757</v>
       </c>
       <c r="D23" t="n">
-        <v>60</v>
+        <v>36383</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>3374</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>1</v>
+        <v>0.9151</v>
       </c>
     </row>
     <row r="24">
@@ -1008,16 +1022,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>14591</v>
+        <v>87687</v>
       </c>
       <c r="D25" t="n">
-        <v>14590</v>
+        <v>60823</v>
       </c>
       <c r="E25" t="n">
-        <v>1</v>
+        <v>26864</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>0.9998999999999999</v>
+        <v>0.6936</v>
       </c>
     </row>
     <row r="26">
@@ -1032,16 +1046,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>12067</v>
+        <v>3793</v>
       </c>
       <c r="D26" t="n">
-        <v>11515</v>
+        <v>3705</v>
       </c>
       <c r="E26" t="n">
-        <v>552</v>
+        <v>88</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>0.9543</v>
+        <v>0.9768000000000001</v>
       </c>
     </row>
     <row r="27">
@@ -1056,16 +1070,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>9598</v>
+        <v>472</v>
       </c>
       <c r="D27" t="n">
-        <v>9437</v>
+        <v>472</v>
       </c>
       <c r="E27" t="n">
-        <v>161</v>
+        <v>0</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>0.9832</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -1080,17 +1094,15 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>19</v>
-      </c>
-      <c r="F28" s="2" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F28" s="2" t="n"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1104,16 +1116,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>8127</v>
+        <v>2072</v>
       </c>
       <c r="D29" t="n">
-        <v>7129</v>
+        <v>1869</v>
       </c>
       <c r="E29" t="n">
-        <v>998</v>
+        <v>203</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>0.8772</v>
+        <v>0.902</v>
       </c>
     </row>
     <row r="30">
@@ -1128,16 +1140,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1554</v>
+        <v>881</v>
       </c>
       <c r="D30" t="n">
-        <v>1538</v>
+        <v>870</v>
       </c>
       <c r="E30" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>0.9897</v>
+        <v>0.9875</v>
       </c>
     </row>
     <row r="31">
@@ -1174,16 +1186,16 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>8</v>
+        <v>16883</v>
       </c>
       <c r="D32" t="n">
-        <v>8</v>
+        <v>16570</v>
       </c>
       <c r="E32" t="n">
-        <v>0</v>
+        <v>313</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>1</v>
+        <v>0.9815</v>
       </c>
     </row>
     <row r="33">
@@ -1198,16 +1210,16 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>29055</v>
+        <v>16109</v>
       </c>
       <c r="D33" t="n">
-        <v>28608</v>
+        <v>15868</v>
       </c>
       <c r="E33" t="n">
-        <v>447</v>
+        <v>241</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>0.9845999999999999</v>
+        <v>0.985</v>
       </c>
     </row>
     <row r="34">

--- a/output/TRANSFERENCIA_atual.xlsx
+++ b/output/TRANSFERENCIA_atual.xlsx
@@ -484,16 +484,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5181</v>
+        <v>4153</v>
       </c>
       <c r="D2" t="n">
-        <v>5175</v>
+        <v>4145</v>
       </c>
       <c r="E2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.9987999999999999</v>
+        <v>0.9981</v>
       </c>
     </row>
     <row r="3">
@@ -508,16 +508,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5770</v>
+        <v>4724</v>
       </c>
       <c r="D3" t="n">
-        <v>2994</v>
+        <v>2858</v>
       </c>
       <c r="E3" t="n">
-        <v>2776</v>
+        <v>1866</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.5189</v>
+        <v>0.605</v>
       </c>
     </row>
     <row r="4">
@@ -532,16 +532,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3195</v>
+        <v>1045</v>
       </c>
       <c r="D4" t="n">
-        <v>2848</v>
+        <v>1016</v>
       </c>
       <c r="E4" t="n">
-        <v>347</v>
+        <v>29</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.8914</v>
+        <v>0.9722</v>
       </c>
     </row>
     <row r="5">
@@ -556,16 +556,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>556</v>
+        <v>450</v>
       </c>
       <c r="D5" t="n">
-        <v>523</v>
+        <v>447</v>
       </c>
       <c r="E5" t="n">
-        <v>33</v>
+        <v>3</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.9406</v>
+        <v>0.9933</v>
       </c>
     </row>
     <row r="6">
@@ -580,10 +580,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>8</v>
+        <v>9612</v>
       </c>
       <c r="D6" t="n">
-        <v>8</v>
+        <v>9612</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -604,16 +604,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>83</v>
+        <v>3041</v>
       </c>
       <c r="D7" t="n">
-        <v>81</v>
+        <v>2898</v>
       </c>
       <c r="E7" t="n">
-        <v>2</v>
+        <v>143</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.9759</v>
+        <v>0.953</v>
       </c>
     </row>
     <row r="8">
@@ -628,15 +628,17 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>2421</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>2094</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="2" t="n"/>
+        <v>327</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>0.8649</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -650,16 +652,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>21193</v>
+        <v>30742</v>
       </c>
       <c r="D9" t="n">
-        <v>20397</v>
+        <v>29617</v>
       </c>
       <c r="E9" t="n">
-        <v>796</v>
+        <v>1125</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0.9623999999999999</v>
+        <v>0.9634</v>
       </c>
     </row>
     <row r="10">
@@ -696,16 +698,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>58876</v>
+        <v>64866</v>
       </c>
       <c r="D11" t="n">
-        <v>58605</v>
+        <v>57547</v>
       </c>
       <c r="E11" t="n">
-        <v>271</v>
+        <v>7319</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>0.9954000000000001</v>
+        <v>0.8872</v>
       </c>
     </row>
     <row r="12">
@@ -720,16 +722,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>3646</v>
+        <v>3432</v>
       </c>
       <c r="D12" t="n">
-        <v>3644</v>
+        <v>2743</v>
       </c>
       <c r="E12" t="n">
-        <v>2</v>
+        <v>689</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>0.9995000000000001</v>
+        <v>0.7992</v>
       </c>
     </row>
     <row r="13">
@@ -744,15 +746,17 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>2693</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>2693</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
-      <c r="F13" s="2" t="n"/>
+      <c r="F13" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -766,16 +770,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>5690</v>
+        <v>5527</v>
       </c>
       <c r="D14" t="n">
-        <v>5671</v>
+        <v>5523</v>
       </c>
       <c r="E14" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0.9967</v>
+        <v>0.9993000000000001</v>
       </c>
     </row>
     <row r="15">
@@ -790,15 +794,17 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>642</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>636</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" s="2" t="n"/>
+        <v>6</v>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>0.9906999999999999</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -812,16 +818,16 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>850</v>
+        <v>688</v>
       </c>
       <c r="D16" t="n">
-        <v>415</v>
+        <v>625</v>
       </c>
       <c r="E16" t="n">
-        <v>435</v>
+        <v>63</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>0.4882</v>
+        <v>0.9084</v>
       </c>
     </row>
     <row r="17">
@@ -836,10 +842,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>6610</v>
+        <v>4015</v>
       </c>
       <c r="D17" t="n">
-        <v>6610</v>
+        <v>4015</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -882,16 +888,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1154</v>
+        <v>874</v>
       </c>
       <c r="D19" t="n">
-        <v>1133</v>
+        <v>858</v>
       </c>
       <c r="E19" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>0.9818000000000001</v>
+        <v>0.9817</v>
       </c>
     </row>
     <row r="20">
@@ -906,16 +912,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>19413</v>
+        <v>14554</v>
       </c>
       <c r="D20" t="n">
-        <v>16902</v>
+        <v>11586</v>
       </c>
       <c r="E20" t="n">
-        <v>2511</v>
+        <v>2968</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>0.8706999999999999</v>
+        <v>0.7961</v>
       </c>
     </row>
     <row r="21">
@@ -952,16 +958,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>4794</v>
+        <v>4377</v>
       </c>
       <c r="D22" t="n">
-        <v>4651</v>
+        <v>4347</v>
       </c>
       <c r="E22" t="n">
-        <v>143</v>
+        <v>30</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>0.9702</v>
+        <v>0.9931</v>
       </c>
     </row>
     <row r="23">
@@ -976,16 +982,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>39757</v>
+        <v>42083</v>
       </c>
       <c r="D23" t="n">
-        <v>36383</v>
+        <v>40513</v>
       </c>
       <c r="E23" t="n">
-        <v>3374</v>
+        <v>1570</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>0.9151</v>
+        <v>0.9627</v>
       </c>
     </row>
     <row r="24">
@@ -1022,16 +1028,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>87687</v>
+        <v>56684</v>
       </c>
       <c r="D25" t="n">
-        <v>60823</v>
+        <v>55893</v>
       </c>
       <c r="E25" t="n">
-        <v>26864</v>
+        <v>791</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>0.6936</v>
+        <v>0.986</v>
       </c>
     </row>
     <row r="26">
@@ -1046,16 +1052,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>3793</v>
+        <v>7314</v>
       </c>
       <c r="D26" t="n">
-        <v>3705</v>
+        <v>5830</v>
       </c>
       <c r="E26" t="n">
-        <v>88</v>
+        <v>1484</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>0.9768000000000001</v>
+        <v>0.7970999999999999</v>
       </c>
     </row>
     <row r="27">
@@ -1070,16 +1076,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>472</v>
+        <v>12034</v>
       </c>
       <c r="D27" t="n">
-        <v>472</v>
+        <v>11263</v>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>771</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>1</v>
+        <v>0.9359000000000001</v>
       </c>
     </row>
     <row r="28">
@@ -1094,15 +1100,17 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
-      </c>
-      <c r="F28" s="2" t="n"/>
+        <v>72</v>
+      </c>
+      <c r="F28" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1116,16 +1124,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>2072</v>
+        <v>11502</v>
       </c>
       <c r="D29" t="n">
-        <v>1869</v>
+        <v>4247</v>
       </c>
       <c r="E29" t="n">
-        <v>203</v>
+        <v>7255</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>0.902</v>
+        <v>0.3692</v>
       </c>
     </row>
     <row r="30">
@@ -1140,16 +1148,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>881</v>
+        <v>41</v>
       </c>
       <c r="D30" t="n">
-        <v>870</v>
+        <v>40</v>
       </c>
       <c r="E30" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>0.9875</v>
+        <v>0.9756</v>
       </c>
     </row>
     <row r="31">
@@ -1186,16 +1194,16 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>16883</v>
+        <v>12069</v>
       </c>
       <c r="D32" t="n">
-        <v>16570</v>
+        <v>11908</v>
       </c>
       <c r="E32" t="n">
-        <v>313</v>
+        <v>161</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>0.9815</v>
+        <v>0.9867</v>
       </c>
     </row>
     <row r="33">
@@ -1210,16 +1218,16 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>16109</v>
+        <v>1245</v>
       </c>
       <c r="D33" t="n">
-        <v>15868</v>
+        <v>1229</v>
       </c>
       <c r="E33" t="n">
-        <v>241</v>
+        <v>16</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>0.985</v>
+        <v>0.9871</v>
       </c>
     </row>
     <row r="34">

--- a/output/TRANSFERENCIA_atual.xlsx
+++ b/output/TRANSFERENCIA_atual.xlsx
@@ -484,16 +484,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4153</v>
+        <v>3782</v>
       </c>
       <c r="D2" t="n">
-        <v>4145</v>
+        <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>8</v>
+        <v>3781</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.9981</v>
+        <v>0.0003</v>
       </c>
     </row>
     <row r="3">
@@ -508,16 +508,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>4724</v>
+        <v>3470</v>
       </c>
       <c r="D3" t="n">
-        <v>2858</v>
+        <v>1246</v>
       </c>
       <c r="E3" t="n">
-        <v>1866</v>
+        <v>2224</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.605</v>
+        <v>0.3591</v>
       </c>
     </row>
     <row r="4">
@@ -532,16 +532,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1045</v>
+        <v>1242</v>
       </c>
       <c r="D4" t="n">
-        <v>1016</v>
+        <v>1097</v>
       </c>
       <c r="E4" t="n">
-        <v>29</v>
+        <v>145</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.9722</v>
+        <v>0.8833</v>
       </c>
     </row>
     <row r="5">
@@ -556,16 +556,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>450</v>
+        <v>555</v>
       </c>
       <c r="D5" t="n">
-        <v>447</v>
+        <v>555</v>
       </c>
       <c r="E5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.9933</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -580,10 +580,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>9612</v>
+        <v>23258</v>
       </c>
       <c r="D6" t="n">
-        <v>9612</v>
+        <v>23258</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -604,16 +604,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3041</v>
+        <v>25307</v>
       </c>
       <c r="D7" t="n">
-        <v>2898</v>
+        <v>11870</v>
       </c>
       <c r="E7" t="n">
-        <v>143</v>
+        <v>13437</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.953</v>
+        <v>0.469</v>
       </c>
     </row>
     <row r="8">
@@ -628,16 +628,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2421</v>
+        <v>13618</v>
       </c>
       <c r="D8" t="n">
-        <v>2094</v>
+        <v>7551</v>
       </c>
       <c r="E8" t="n">
-        <v>327</v>
+        <v>6067</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.8649</v>
+        <v>0.5545</v>
       </c>
     </row>
     <row r="9">
@@ -652,16 +652,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>30742</v>
+        <v>42158</v>
       </c>
       <c r="D9" t="n">
-        <v>29617</v>
+        <v>38838</v>
       </c>
       <c r="E9" t="n">
-        <v>1125</v>
+        <v>3320</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0.9634</v>
+        <v>0.9212</v>
       </c>
     </row>
     <row r="10">
@@ -698,16 +698,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>64866</v>
+        <v>124576</v>
       </c>
       <c r="D11" t="n">
-        <v>57547</v>
+        <v>98913</v>
       </c>
       <c r="E11" t="n">
-        <v>7319</v>
+        <v>25663</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>0.8872</v>
+        <v>0.794</v>
       </c>
     </row>
     <row r="12">
@@ -722,16 +722,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>3432</v>
+        <v>1888</v>
       </c>
       <c r="D12" t="n">
-        <v>2743</v>
+        <v>1723</v>
       </c>
       <c r="E12" t="n">
-        <v>689</v>
+        <v>165</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>0.7992</v>
+        <v>0.9126000000000001</v>
       </c>
     </row>
     <row r="13">
@@ -746,10 +746,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2693</v>
+        <v>5062</v>
       </c>
       <c r="D13" t="n">
-        <v>2693</v>
+        <v>5062</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -770,16 +770,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>5527</v>
+        <v>3294</v>
       </c>
       <c r="D14" t="n">
-        <v>5523</v>
+        <v>3289</v>
       </c>
       <c r="E14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0.9993000000000001</v>
+        <v>0.9984999999999999</v>
       </c>
     </row>
     <row r="15">
@@ -794,16 +794,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>642</v>
+        <v>1359</v>
       </c>
       <c r="D15" t="n">
-        <v>636</v>
+        <v>1349</v>
       </c>
       <c r="E15" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>0.9906999999999999</v>
+        <v>0.9926</v>
       </c>
     </row>
     <row r="16">
@@ -818,16 +818,16 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>688</v>
+        <v>1411</v>
       </c>
       <c r="D16" t="n">
-        <v>625</v>
+        <v>1373</v>
       </c>
       <c r="E16" t="n">
-        <v>63</v>
+        <v>38</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>0.9084</v>
+        <v>0.9731000000000001</v>
       </c>
     </row>
     <row r="17">
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>4015</v>
+        <v>6270</v>
       </c>
       <c r="D17" t="n">
-        <v>4015</v>
+        <v>6270</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -888,16 +888,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>874</v>
+        <v>850</v>
       </c>
       <c r="D19" t="n">
-        <v>858</v>
+        <v>798</v>
       </c>
       <c r="E19" t="n">
-        <v>16</v>
+        <v>52</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>0.9817</v>
+        <v>0.9388</v>
       </c>
     </row>
     <row r="20">
@@ -912,16 +912,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>14554</v>
+        <v>14051</v>
       </c>
       <c r="D20" t="n">
-        <v>11586</v>
+        <v>5923</v>
       </c>
       <c r="E20" t="n">
-        <v>2968</v>
+        <v>8128</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>0.7961</v>
+        <v>0.4215</v>
       </c>
     </row>
     <row r="21">
@@ -958,16 +958,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>4377</v>
+        <v>2972</v>
       </c>
       <c r="D22" t="n">
-        <v>4347</v>
+        <v>2896</v>
       </c>
       <c r="E22" t="n">
-        <v>30</v>
+        <v>76</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>0.9931</v>
+        <v>0.9743999999999999</v>
       </c>
     </row>
     <row r="23">
@@ -982,16 +982,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>42083</v>
+        <v>23171</v>
       </c>
       <c r="D23" t="n">
-        <v>40513</v>
+        <v>22651</v>
       </c>
       <c r="E23" t="n">
-        <v>1570</v>
+        <v>520</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>0.9627</v>
+        <v>0.9776</v>
       </c>
     </row>
     <row r="24">
@@ -1028,16 +1028,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>56684</v>
+        <v>48664</v>
       </c>
       <c r="D25" t="n">
-        <v>55893</v>
+        <v>47089</v>
       </c>
       <c r="E25" t="n">
-        <v>791</v>
+        <v>1575</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>0.986</v>
+        <v>0.9676</v>
       </c>
     </row>
     <row r="26">
@@ -1052,16 +1052,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>7314</v>
+        <v>12649</v>
       </c>
       <c r="D26" t="n">
-        <v>5830</v>
+        <v>9159</v>
       </c>
       <c r="E26" t="n">
-        <v>1484</v>
+        <v>3490</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>0.7970999999999999</v>
+        <v>0.7241</v>
       </c>
     </row>
     <row r="27">
@@ -1076,16 +1076,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>12034</v>
+        <v>21540</v>
       </c>
       <c r="D27" t="n">
-        <v>11263</v>
+        <v>20493</v>
       </c>
       <c r="E27" t="n">
-        <v>771</v>
+        <v>1047</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>0.9359000000000001</v>
+        <v>0.9514</v>
       </c>
     </row>
     <row r="28">
@@ -1100,13 +1100,13 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="F28" s="2" t="n">
         <v>0</v>
@@ -1124,16 +1124,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>11502</v>
+        <v>19095</v>
       </c>
       <c r="D29" t="n">
-        <v>4247</v>
+        <v>9758</v>
       </c>
       <c r="E29" t="n">
-        <v>7255</v>
+        <v>9337</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>0.3692</v>
+        <v>0.511</v>
       </c>
     </row>
     <row r="30">
@@ -1148,16 +1148,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>41</v>
+        <v>1327</v>
       </c>
       <c r="D30" t="n">
-        <v>40</v>
+        <v>1297</v>
       </c>
       <c r="E30" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>0.9756</v>
+        <v>0.9773999999999999</v>
       </c>
     </row>
     <row r="31">
@@ -1194,16 +1194,16 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>12069</v>
+        <v>7591</v>
       </c>
       <c r="D32" t="n">
-        <v>11908</v>
+        <v>7562</v>
       </c>
       <c r="E32" t="n">
-        <v>161</v>
+        <v>29</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>0.9867</v>
+        <v>0.9962000000000001</v>
       </c>
     </row>
     <row r="33">
@@ -1218,16 +1218,16 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1245</v>
+        <v>28502</v>
       </c>
       <c r="D33" t="n">
-        <v>1229</v>
+        <v>27780</v>
       </c>
       <c r="E33" t="n">
-        <v>16</v>
+        <v>722</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>0.9871</v>
+        <v>0.9747</v>
       </c>
     </row>
     <row r="34">
@@ -1242,15 +1242,17 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D34" t="n">
         <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>0</v>
-      </c>
-      <c r="F34" s="2" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="F34" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F34"/>

--- a/output/TRANSFERENCIA_atual.xlsx
+++ b/output/TRANSFERENCIA_atual.xlsx
@@ -484,16 +484,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3782</v>
+        <v>4211</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>4132</v>
       </c>
       <c r="E2" t="n">
-        <v>3781</v>
+        <v>79</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.0003</v>
+        <v>0.9812000000000001</v>
       </c>
     </row>
     <row r="3">
@@ -508,16 +508,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>3470</v>
+        <v>4044</v>
       </c>
       <c r="D3" t="n">
-        <v>1246</v>
+        <v>2686</v>
       </c>
       <c r="E3" t="n">
-        <v>2224</v>
+        <v>1358</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.3591</v>
+        <v>0.6642</v>
       </c>
     </row>
     <row r="4">
@@ -532,16 +532,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1242</v>
+        <v>1384</v>
       </c>
       <c r="D4" t="n">
-        <v>1097</v>
+        <v>1309</v>
       </c>
       <c r="E4" t="n">
-        <v>145</v>
+        <v>75</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.8833</v>
+        <v>0.9458</v>
       </c>
     </row>
     <row r="5">
@@ -556,10 +556,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>555</v>
+        <v>317</v>
       </c>
       <c r="D5" t="n">
-        <v>555</v>
+        <v>317</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -580,10 +580,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>23258</v>
+        <v>27306</v>
       </c>
       <c r="D6" t="n">
-        <v>23258</v>
+        <v>27306</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -604,16 +604,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>25307</v>
+        <v>35737</v>
       </c>
       <c r="D7" t="n">
-        <v>11870</v>
+        <v>14629</v>
       </c>
       <c r="E7" t="n">
-        <v>13437</v>
+        <v>21108</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.469</v>
+        <v>0.4094</v>
       </c>
     </row>
     <row r="8">
@@ -628,16 +628,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>13618</v>
+        <v>18297</v>
       </c>
       <c r="D8" t="n">
-        <v>7551</v>
+        <v>9543</v>
       </c>
       <c r="E8" t="n">
-        <v>6067</v>
+        <v>8754</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.5545</v>
+        <v>0.5216</v>
       </c>
     </row>
     <row r="9">
@@ -652,16 +652,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>42158</v>
+        <v>42277</v>
       </c>
       <c r="D9" t="n">
-        <v>38838</v>
+        <v>36818</v>
       </c>
       <c r="E9" t="n">
-        <v>3320</v>
+        <v>5459</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0.9212</v>
+        <v>0.8709</v>
       </c>
     </row>
     <row r="10">
@@ -698,16 +698,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>124576</v>
+        <v>136149</v>
       </c>
       <c r="D11" t="n">
-        <v>98913</v>
+        <v>96723</v>
       </c>
       <c r="E11" t="n">
-        <v>25663</v>
+        <v>39426</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>0.794</v>
+        <v>0.7104</v>
       </c>
     </row>
     <row r="12">
@@ -722,16 +722,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1888</v>
+        <v>2767</v>
       </c>
       <c r="D12" t="n">
-        <v>1723</v>
+        <v>2613</v>
       </c>
       <c r="E12" t="n">
-        <v>165</v>
+        <v>154</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>0.9126000000000001</v>
+        <v>0.9443</v>
       </c>
     </row>
     <row r="13">
@@ -746,10 +746,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>5062</v>
+        <v>4219</v>
       </c>
       <c r="D13" t="n">
-        <v>5062</v>
+        <v>4219</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -770,16 +770,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>3294</v>
+        <v>5402</v>
       </c>
       <c r="D14" t="n">
-        <v>3289</v>
+        <v>5376</v>
       </c>
       <c r="E14" t="n">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0.9984999999999999</v>
+        <v>0.9952</v>
       </c>
     </row>
     <row r="15">
@@ -794,16 +794,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1359</v>
+        <v>1040</v>
       </c>
       <c r="D15" t="n">
-        <v>1349</v>
+        <v>1034</v>
       </c>
       <c r="E15" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>0.9926</v>
+        <v>0.9942</v>
       </c>
     </row>
     <row r="16">
@@ -818,16 +818,16 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1411</v>
+        <v>2121</v>
       </c>
       <c r="D16" t="n">
-        <v>1373</v>
+        <v>2084</v>
       </c>
       <c r="E16" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>0.9731000000000001</v>
+        <v>0.9826</v>
       </c>
     </row>
     <row r="17">
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>6270</v>
+        <v>7892</v>
       </c>
       <c r="D17" t="n">
-        <v>6270</v>
+        <v>7892</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -888,16 +888,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>850</v>
+        <v>876</v>
       </c>
       <c r="D19" t="n">
-        <v>798</v>
+        <v>876</v>
       </c>
       <c r="E19" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>0.9388</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -912,16 +912,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>14051</v>
+        <v>14444</v>
       </c>
       <c r="D20" t="n">
-        <v>5923</v>
+        <v>13098</v>
       </c>
       <c r="E20" t="n">
-        <v>8128</v>
+        <v>1346</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>0.4215</v>
+        <v>0.9068000000000001</v>
       </c>
     </row>
     <row r="21">
@@ -958,16 +958,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>2972</v>
+        <v>3067</v>
       </c>
       <c r="D22" t="n">
-        <v>2896</v>
+        <v>2944</v>
       </c>
       <c r="E22" t="n">
-        <v>76</v>
+        <v>123</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>0.9743999999999999</v>
+        <v>0.9599</v>
       </c>
     </row>
     <row r="23">
@@ -982,16 +982,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>23171</v>
+        <v>22282</v>
       </c>
       <c r="D23" t="n">
-        <v>22651</v>
+        <v>22156</v>
       </c>
       <c r="E23" t="n">
-        <v>520</v>
+        <v>126</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>0.9776</v>
+        <v>0.9943000000000001</v>
       </c>
     </row>
     <row r="24">
@@ -1028,16 +1028,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>48664</v>
+        <v>41963</v>
       </c>
       <c r="D25" t="n">
-        <v>47089</v>
+        <v>41319</v>
       </c>
       <c r="E25" t="n">
-        <v>1575</v>
+        <v>644</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>0.9676</v>
+        <v>0.9847</v>
       </c>
     </row>
     <row r="26">
@@ -1052,16 +1052,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>12649</v>
+        <v>10433</v>
       </c>
       <c r="D26" t="n">
-        <v>9159</v>
+        <v>8281</v>
       </c>
       <c r="E26" t="n">
-        <v>3490</v>
+        <v>2152</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>0.7241</v>
+        <v>0.7937000000000001</v>
       </c>
     </row>
     <row r="27">
@@ -1076,16 +1076,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>21540</v>
+        <v>17497</v>
       </c>
       <c r="D27" t="n">
-        <v>20493</v>
+        <v>17091</v>
       </c>
       <c r="E27" t="n">
-        <v>1047</v>
+        <v>406</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>0.9514</v>
+        <v>0.9768000000000001</v>
       </c>
     </row>
     <row r="28">
@@ -1100,13 +1100,13 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>84</v>
+        <v>19</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>84</v>
+        <v>19</v>
       </c>
       <c r="F28" s="2" t="n">
         <v>0</v>
@@ -1124,16 +1124,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>19095</v>
+        <v>13844</v>
       </c>
       <c r="D29" t="n">
-        <v>9758</v>
+        <v>9402</v>
       </c>
       <c r="E29" t="n">
-        <v>9337</v>
+        <v>4442</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>0.511</v>
+        <v>0.6790999999999999</v>
       </c>
     </row>
     <row r="30">
@@ -1148,16 +1148,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1327</v>
+        <v>2102</v>
       </c>
       <c r="D30" t="n">
-        <v>1297</v>
+        <v>2052</v>
       </c>
       <c r="E30" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>0.9773999999999999</v>
+        <v>0.9762000000000001</v>
       </c>
     </row>
     <row r="31">
@@ -1194,16 +1194,16 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>7591</v>
+        <v>8625</v>
       </c>
       <c r="D32" t="n">
-        <v>7562</v>
+        <v>8499</v>
       </c>
       <c r="E32" t="n">
-        <v>29</v>
+        <v>126</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>0.9962000000000001</v>
+        <v>0.9854000000000001</v>
       </c>
     </row>
     <row r="33">
@@ -1218,16 +1218,16 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>28502</v>
+        <v>48482</v>
       </c>
       <c r="D33" t="n">
-        <v>27780</v>
+        <v>47534</v>
       </c>
       <c r="E33" t="n">
-        <v>722</v>
+        <v>948</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>0.9747</v>
+        <v>0.9804</v>
       </c>
     </row>
     <row r="34">
@@ -1242,16 +1242,16 @@
         </is>
       </c>
       <c r="C34" t="n">
+        <v>2</v>
+      </c>
+      <c r="D34" t="n">
         <v>1</v>
-      </c>
-      <c r="D34" t="n">
-        <v>0</v>
       </c>
       <c r="E34" t="n">
         <v>1</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>

--- a/output/TRANSFERENCIA_atual.xlsx
+++ b/output/TRANSFERENCIA_atual.xlsx
@@ -484,16 +484,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4211</v>
+        <v>3703</v>
       </c>
       <c r="D2" t="n">
-        <v>4132</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>79</v>
+        <v>3703</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.9812000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -508,16 +508,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>4044</v>
+        <v>3112</v>
       </c>
       <c r="D3" t="n">
-        <v>2686</v>
+        <v>3085</v>
       </c>
       <c r="E3" t="n">
-        <v>1358</v>
+        <v>27</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.6642</v>
+        <v>0.9913</v>
       </c>
     </row>
     <row r="4">
@@ -532,16 +532,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1384</v>
+        <v>1955</v>
       </c>
       <c r="D4" t="n">
-        <v>1309</v>
+        <v>1876</v>
       </c>
       <c r="E4" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.9458</v>
+        <v>0.9595999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -556,16 +556,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>317</v>
+        <v>381</v>
       </c>
       <c r="D5" t="n">
-        <v>317</v>
+        <v>380</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>1</v>
+        <v>0.9974</v>
       </c>
     </row>
     <row r="6">
@@ -580,10 +580,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>27306</v>
+        <v>23853</v>
       </c>
       <c r="D6" t="n">
-        <v>27306</v>
+        <v>23853</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -604,16 +604,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>35737</v>
+        <v>32229</v>
       </c>
       <c r="D7" t="n">
-        <v>14629</v>
+        <v>13711</v>
       </c>
       <c r="E7" t="n">
-        <v>21108</v>
+        <v>18518</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.4094</v>
+        <v>0.4254</v>
       </c>
     </row>
     <row r="8">
@@ -628,16 +628,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>18297</v>
+        <v>14224</v>
       </c>
       <c r="D8" t="n">
-        <v>9543</v>
+        <v>6464</v>
       </c>
       <c r="E8" t="n">
-        <v>8754</v>
+        <v>7760</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.5216</v>
+        <v>0.4544</v>
       </c>
     </row>
     <row r="9">
@@ -652,16 +652,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>42277</v>
+        <v>14838</v>
       </c>
       <c r="D9" t="n">
-        <v>36818</v>
+        <v>13305</v>
       </c>
       <c r="E9" t="n">
-        <v>5459</v>
+        <v>1533</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0.8709</v>
+        <v>0.8967000000000001</v>
       </c>
     </row>
     <row r="10">
@@ -698,16 +698,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>136149</v>
+        <v>156370</v>
       </c>
       <c r="D11" t="n">
-        <v>96723</v>
+        <v>110880</v>
       </c>
       <c r="E11" t="n">
-        <v>39426</v>
+        <v>45490</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>0.7104</v>
+        <v>0.7091</v>
       </c>
     </row>
     <row r="12">
@@ -722,16 +722,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2767</v>
+        <v>2079</v>
       </c>
       <c r="D12" t="n">
-        <v>2613</v>
+        <v>2078</v>
       </c>
       <c r="E12" t="n">
-        <v>154</v>
+        <v>1</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>0.9443</v>
+        <v>0.9995000000000001</v>
       </c>
     </row>
     <row r="13">
@@ -746,10 +746,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>4219</v>
+        <v>3665</v>
       </c>
       <c r="D13" t="n">
-        <v>4219</v>
+        <v>3665</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -770,16 +770,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>5402</v>
+        <v>4185</v>
       </c>
       <c r="D14" t="n">
-        <v>5376</v>
+        <v>4179</v>
       </c>
       <c r="E14" t="n">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0.9952</v>
+        <v>0.9986</v>
       </c>
     </row>
     <row r="15">
@@ -794,16 +794,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1040</v>
+        <v>658</v>
       </c>
       <c r="D15" t="n">
-        <v>1034</v>
+        <v>576</v>
       </c>
       <c r="E15" t="n">
-        <v>6</v>
+        <v>82</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>0.9942</v>
+        <v>0.8754000000000001</v>
       </c>
     </row>
     <row r="16">
@@ -818,16 +818,16 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2121</v>
+        <v>1294</v>
       </c>
       <c r="D16" t="n">
-        <v>2084</v>
+        <v>1234</v>
       </c>
       <c r="E16" t="n">
-        <v>37</v>
+        <v>60</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>0.9826</v>
+        <v>0.9536</v>
       </c>
     </row>
     <row r="17">
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>7892</v>
+        <v>8146</v>
       </c>
       <c r="D17" t="n">
-        <v>7892</v>
+        <v>8146</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -888,16 +888,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>876</v>
+        <v>1188</v>
       </c>
       <c r="D19" t="n">
-        <v>876</v>
+        <v>1181</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>1</v>
+        <v>0.9941</v>
       </c>
     </row>
     <row r="20">
@@ -912,16 +912,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>14444</v>
+        <v>14735</v>
       </c>
       <c r="D20" t="n">
-        <v>13098</v>
+        <v>14656</v>
       </c>
       <c r="E20" t="n">
-        <v>1346</v>
+        <v>79</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>0.9068000000000001</v>
+        <v>0.9945999999999999</v>
       </c>
     </row>
     <row r="21">
@@ -958,16 +958,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>3067</v>
+        <v>2910</v>
       </c>
       <c r="D22" t="n">
-        <v>2944</v>
+        <v>9</v>
       </c>
       <c r="E22" t="n">
-        <v>123</v>
+        <v>2901</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>0.9599</v>
+        <v>0.0031</v>
       </c>
     </row>
     <row r="23">
@@ -982,16 +982,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>22282</v>
+        <v>21563</v>
       </c>
       <c r="D23" t="n">
-        <v>22156</v>
+        <v>21172</v>
       </c>
       <c r="E23" t="n">
-        <v>126</v>
+        <v>391</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>0.9943000000000001</v>
+        <v>0.9819</v>
       </c>
     </row>
     <row r="24">
@@ -1028,16 +1028,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>41963</v>
+        <v>40818</v>
       </c>
       <c r="D25" t="n">
-        <v>41319</v>
+        <v>39583</v>
       </c>
       <c r="E25" t="n">
-        <v>644</v>
+        <v>1235</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>0.9847</v>
+        <v>0.9697</v>
       </c>
     </row>
     <row r="26">
@@ -1052,16 +1052,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>10433</v>
+        <v>8107</v>
       </c>
       <c r="D26" t="n">
-        <v>8281</v>
+        <v>7091</v>
       </c>
       <c r="E26" t="n">
-        <v>2152</v>
+        <v>1016</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>0.7937000000000001</v>
+        <v>0.8747</v>
       </c>
     </row>
     <row r="27">
@@ -1076,16 +1076,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>17497</v>
+        <v>15628</v>
       </c>
       <c r="D27" t="n">
-        <v>17091</v>
+        <v>15345</v>
       </c>
       <c r="E27" t="n">
-        <v>406</v>
+        <v>283</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>0.9768000000000001</v>
+        <v>0.9819</v>
       </c>
     </row>
     <row r="28">
@@ -1100,13 +1100,13 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F28" s="2" t="n">
         <v>0</v>
@@ -1124,16 +1124,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>13844</v>
+        <v>11200</v>
       </c>
       <c r="D29" t="n">
-        <v>9402</v>
+        <v>6693</v>
       </c>
       <c r="E29" t="n">
-        <v>4442</v>
+        <v>4507</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>0.6790999999999999</v>
+        <v>0.5976</v>
       </c>
     </row>
     <row r="30">
@@ -1148,16 +1148,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>2102</v>
+        <v>1227</v>
       </c>
       <c r="D30" t="n">
-        <v>2052</v>
+        <v>826</v>
       </c>
       <c r="E30" t="n">
-        <v>50</v>
+        <v>401</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>0.9762000000000001</v>
+        <v>0.6731999999999999</v>
       </c>
     </row>
     <row r="31">
@@ -1194,16 +1194,16 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>8625</v>
+        <v>8751</v>
       </c>
       <c r="D32" t="n">
-        <v>8499</v>
+        <v>8629</v>
       </c>
       <c r="E32" t="n">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>0.9854000000000001</v>
+        <v>0.9861</v>
       </c>
     </row>
     <row r="33">
@@ -1218,16 +1218,16 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>48482</v>
+        <v>35690</v>
       </c>
       <c r="D33" t="n">
-        <v>47534</v>
+        <v>35151</v>
       </c>
       <c r="E33" t="n">
-        <v>948</v>
+        <v>539</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>0.9804</v>
+        <v>0.9849</v>
       </c>
     </row>
     <row r="34">
@@ -1242,16 +1242,16 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D34" t="n">
         <v>1</v>
       </c>
       <c r="E34" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="F34" s="2" t="n">
-        <v>0.5</v>
       </c>
     </row>
   </sheetData>

--- a/output/TRANSFERENCIA_atual.xlsx
+++ b/output/TRANSFERENCIA_atual.xlsx
@@ -484,13 +484,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3703</v>
+        <v>5496</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>3703</v>
+        <v>5496</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>0</v>
@@ -508,16 +508,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>3112</v>
+        <v>2717</v>
       </c>
       <c r="D3" t="n">
-        <v>3085</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>27</v>
+        <v>2717</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.9913</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -532,17 +532,15 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1955</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>1876</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>79</v>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>0.9595999999999999</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -556,17 +554,15 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>381</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>380</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F5" s="2" t="n">
-        <v>0.9974</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F5" s="2" t="n"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -580,10 +576,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>23853</v>
+        <v>20233</v>
       </c>
       <c r="D6" t="n">
-        <v>23853</v>
+        <v>20233</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -604,16 +600,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>32229</v>
+        <v>44131</v>
       </c>
       <c r="D7" t="n">
-        <v>13711</v>
+        <v>29265</v>
       </c>
       <c r="E7" t="n">
-        <v>18518</v>
+        <v>14866</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.4254</v>
+        <v>0.6631</v>
       </c>
     </row>
     <row r="8">
@@ -628,16 +624,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>14224</v>
+        <v>15532</v>
       </c>
       <c r="D8" t="n">
-        <v>6464</v>
+        <v>2378</v>
       </c>
       <c r="E8" t="n">
-        <v>7760</v>
+        <v>13154</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.4544</v>
+        <v>0.1531</v>
       </c>
     </row>
     <row r="9">
@@ -652,16 +648,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>14838</v>
+        <v>7749</v>
       </c>
       <c r="D9" t="n">
-        <v>13305</v>
+        <v>6783</v>
       </c>
       <c r="E9" t="n">
-        <v>1533</v>
+        <v>966</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0.8967000000000001</v>
+        <v>0.8753</v>
       </c>
     </row>
     <row r="10">
@@ -698,16 +694,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>156370</v>
+        <v>153736</v>
       </c>
       <c r="D11" t="n">
-        <v>110880</v>
+        <v>119850</v>
       </c>
       <c r="E11" t="n">
-        <v>45490</v>
+        <v>33886</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>0.7091</v>
+        <v>0.7796</v>
       </c>
     </row>
     <row r="12">
@@ -722,16 +718,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2079</v>
+        <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>2078</v>
+        <v>3</v>
       </c>
       <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="F12" s="2" t="n">
-        <v>0.9995000000000001</v>
       </c>
     </row>
     <row r="13">
@@ -746,10 +742,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3665</v>
+        <v>3402</v>
       </c>
       <c r="D13" t="n">
-        <v>3665</v>
+        <v>3402</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -770,16 +766,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>4185</v>
+        <v>4177</v>
       </c>
       <c r="D14" t="n">
-        <v>4179</v>
+        <v>4060</v>
       </c>
       <c r="E14" t="n">
-        <v>6</v>
+        <v>117</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0.9986</v>
+        <v>0.972</v>
       </c>
     </row>
     <row r="15">
@@ -794,17 +790,15 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>658</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>576</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>82</v>
-      </c>
-      <c r="F15" s="2" t="n">
-        <v>0.8754000000000001</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F15" s="2" t="n"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -818,17 +812,15 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1294</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>1234</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>60</v>
-      </c>
-      <c r="F16" s="2" t="n">
-        <v>0.9536</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F16" s="2" t="n"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -842,10 +834,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>8146</v>
+        <v>6681</v>
       </c>
       <c r="D17" t="n">
-        <v>8146</v>
+        <v>6681</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -888,17 +880,15 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1188</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>1181</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>7</v>
-      </c>
-      <c r="F19" s="2" t="n">
-        <v>0.9941</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F19" s="2" t="n"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -912,16 +902,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>14735</v>
+        <v>10106</v>
       </c>
       <c r="D20" t="n">
-        <v>14656</v>
+        <v>9837</v>
       </c>
       <c r="E20" t="n">
-        <v>79</v>
+        <v>269</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>0.9945999999999999</v>
+        <v>0.9734</v>
       </c>
     </row>
     <row r="21">
@@ -958,16 +948,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>2910</v>
+        <v>1040</v>
       </c>
       <c r="D22" t="n">
-        <v>9</v>
+        <v>1040</v>
       </c>
       <c r="E22" t="n">
-        <v>2901</v>
+        <v>0</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>0.0031</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -982,16 +972,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>21563</v>
+        <v>9822</v>
       </c>
       <c r="D23" t="n">
-        <v>21172</v>
+        <v>9804</v>
       </c>
       <c r="E23" t="n">
-        <v>391</v>
+        <v>18</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>0.9819</v>
+        <v>0.9982</v>
       </c>
     </row>
     <row r="24">
@@ -1028,16 +1018,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>40818</v>
+        <v>23493</v>
       </c>
       <c r="D25" t="n">
-        <v>39583</v>
+        <v>23459</v>
       </c>
       <c r="E25" t="n">
-        <v>1235</v>
+        <v>34</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>0.9697</v>
+        <v>0.9986</v>
       </c>
     </row>
     <row r="26">
@@ -1052,16 +1042,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>8107</v>
+        <v>5681</v>
       </c>
       <c r="D26" t="n">
-        <v>7091</v>
+        <v>4536</v>
       </c>
       <c r="E26" t="n">
-        <v>1016</v>
+        <v>1145</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>0.8747</v>
+        <v>0.7985</v>
       </c>
     </row>
     <row r="27">
@@ -1076,16 +1066,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>15628</v>
+        <v>14520</v>
       </c>
       <c r="D27" t="n">
-        <v>15345</v>
+        <v>14265</v>
       </c>
       <c r="E27" t="n">
-        <v>283</v>
+        <v>255</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>0.9819</v>
+        <v>0.9823999999999999</v>
       </c>
     </row>
     <row r="28">
@@ -1124,16 +1114,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>11200</v>
+        <v>10407</v>
       </c>
       <c r="D29" t="n">
-        <v>6693</v>
+        <v>6060</v>
       </c>
       <c r="E29" t="n">
-        <v>4507</v>
+        <v>4347</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>0.5976</v>
+        <v>0.5822999999999999</v>
       </c>
     </row>
     <row r="30">
@@ -1148,16 +1138,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1227</v>
+        <v>1539</v>
       </c>
       <c r="D30" t="n">
-        <v>826</v>
+        <v>1136</v>
       </c>
       <c r="E30" t="n">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>0.6731999999999999</v>
+        <v>0.7381</v>
       </c>
     </row>
     <row r="31">
@@ -1194,16 +1184,16 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>8751</v>
+        <v>1971</v>
       </c>
       <c r="D32" t="n">
-        <v>8629</v>
+        <v>1965</v>
       </c>
       <c r="E32" t="n">
-        <v>122</v>
+        <v>6</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>0.9861</v>
+        <v>0.997</v>
       </c>
     </row>
     <row r="33">
@@ -1218,16 +1208,16 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>35690</v>
+        <v>34244</v>
       </c>
       <c r="D33" t="n">
-        <v>35151</v>
+        <v>33673</v>
       </c>
       <c r="E33" t="n">
-        <v>539</v>
+        <v>571</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>0.9849</v>
+        <v>0.9833</v>
       </c>
     </row>
     <row r="34">
@@ -1242,17 +1232,15 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E34" t="n">
         <v>0</v>
       </c>
-      <c r="F34" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="F34" s="2" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:F34"/>

--- a/output/TRANSFERENCIA_atual.xlsx
+++ b/output/TRANSFERENCIA_atual.xlsx
@@ -484,17 +484,15 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5496</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>5496</v>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -508,17 +506,15 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2717</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>2717</v>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -576,10 +572,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>20233</v>
+        <v>10059</v>
       </c>
       <c r="D6" t="n">
-        <v>20233</v>
+        <v>10059</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -600,16 +596,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>44131</v>
+        <v>149</v>
       </c>
       <c r="D7" t="n">
-        <v>29265</v>
+        <v>149</v>
       </c>
       <c r="E7" t="n">
-        <v>14866</v>
+        <v>0</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.6631</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -624,16 +620,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>15532</v>
+        <v>8408</v>
       </c>
       <c r="D8" t="n">
-        <v>2378</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>13154</v>
+        <v>8408</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.1531</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -648,17 +644,15 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>7749</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>6783</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>966</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>0.8753</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F9" s="2" t="n"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -694,16 +688,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>153736</v>
+        <v>123101</v>
       </c>
       <c r="D11" t="n">
-        <v>119850</v>
+        <v>113620</v>
       </c>
       <c r="E11" t="n">
-        <v>33886</v>
+        <v>9481</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>0.7796</v>
+        <v>0.9229999999999999</v>
       </c>
     </row>
     <row r="12">
@@ -718,10 +712,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="D12" t="n">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -742,10 +736,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3402</v>
+        <v>1587</v>
       </c>
       <c r="D13" t="n">
-        <v>3402</v>
+        <v>1587</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -766,17 +760,15 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>4177</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>4060</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>117</v>
-      </c>
-      <c r="F14" s="2" t="n">
-        <v>0.972</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F14" s="2" t="n"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -834,10 +826,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>6681</v>
+        <v>7060</v>
       </c>
       <c r="D17" t="n">
-        <v>6681</v>
+        <v>7060</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -902,16 +894,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>10106</v>
+        <v>5379</v>
       </c>
       <c r="D20" t="n">
-        <v>9837</v>
+        <v>5371</v>
       </c>
       <c r="E20" t="n">
-        <v>269</v>
+        <v>8</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>0.9734</v>
+        <v>0.9984999999999999</v>
       </c>
     </row>
     <row r="21">
@@ -948,17 +940,15 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1040</v>
+        <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>1040</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
       </c>
-      <c r="F22" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="F22" s="2" t="n"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -972,17 +962,15 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>9822</v>
+        <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>9804</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>18</v>
-      </c>
-      <c r="F23" s="2" t="n">
-        <v>0.9982</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F23" s="2" t="n"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1018,16 +1006,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>23493</v>
+        <v>13811</v>
       </c>
       <c r="D25" t="n">
-        <v>23459</v>
+        <v>13805</v>
       </c>
       <c r="E25" t="n">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>0.9986</v>
+        <v>0.9995999999999999</v>
       </c>
     </row>
     <row r="26">
@@ -1042,16 +1030,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>5681</v>
+        <v>3409</v>
       </c>
       <c r="D26" t="n">
-        <v>4536</v>
+        <v>3134</v>
       </c>
       <c r="E26" t="n">
-        <v>1145</v>
+        <v>275</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>0.7985</v>
+        <v>0.9193000000000001</v>
       </c>
     </row>
     <row r="27">
@@ -1066,16 +1054,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>14520</v>
+        <v>10506</v>
       </c>
       <c r="D27" t="n">
-        <v>14265</v>
+        <v>10348</v>
       </c>
       <c r="E27" t="n">
-        <v>255</v>
+        <v>158</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>0.9823999999999999</v>
+        <v>0.985</v>
       </c>
     </row>
     <row r="28">
@@ -1090,13 +1078,13 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="F28" s="2" t="n">
         <v>0</v>
@@ -1114,16 +1102,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>10407</v>
+        <v>6331</v>
       </c>
       <c r="D29" t="n">
-        <v>6060</v>
+        <v>4083</v>
       </c>
       <c r="E29" t="n">
-        <v>4347</v>
+        <v>2248</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>0.5822999999999999</v>
+        <v>0.6448999999999999</v>
       </c>
     </row>
     <row r="30">
@@ -1138,16 +1126,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1539</v>
+        <v>2343</v>
       </c>
       <c r="D30" t="n">
-        <v>1136</v>
+        <v>2304</v>
       </c>
       <c r="E30" t="n">
-        <v>403</v>
+        <v>39</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>0.7381</v>
+        <v>0.9834000000000001</v>
       </c>
     </row>
     <row r="31">
@@ -1184,17 +1172,15 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1971</v>
+        <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>1965</v>
+        <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>6</v>
-      </c>
-      <c r="F32" s="2" t="n">
-        <v>0.997</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F32" s="2" t="n"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1208,16 +1194,16 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>34244</v>
+        <v>37394</v>
       </c>
       <c r="D33" t="n">
-        <v>33673</v>
+        <v>37056</v>
       </c>
       <c r="E33" t="n">
-        <v>571</v>
+        <v>338</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>0.9833</v>
+        <v>0.991</v>
       </c>
     </row>
     <row r="34">

--- a/output/TRANSFERENCIA_atual.xlsx
+++ b/output/TRANSFERENCIA_atual.xlsx
@@ -484,15 +484,17 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>4925</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>4899</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" s="2" t="n"/>
+        <v>26</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>0.9947</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -506,15 +508,17 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>4517</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>2881</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" s="2" t="n"/>
+        <v>1636</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>0.6378</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -528,15 +532,17 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>2897</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>2462</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" s="2" t="n"/>
+        <v>435</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>0.8498</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -550,15 +556,17 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>648</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>639</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="2" t="n"/>
+        <v>9</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>0.9861</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -572,10 +580,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>10059</v>
+        <v>19</v>
       </c>
       <c r="D6" t="n">
-        <v>10059</v>
+        <v>19</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -596,16 +604,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>149</v>
+        <v>341</v>
       </c>
       <c r="D7" t="n">
-        <v>149</v>
+        <v>331</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>1</v>
+        <v>0.9706999999999999</v>
       </c>
     </row>
     <row r="8">
@@ -620,17 +628,15 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>8408</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>8408</v>
-      </c>
-      <c r="F8" s="2" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F8" s="2" t="n"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -644,15 +650,17 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>18155</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>17596</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="2" t="n"/>
+        <v>559</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>0.9692000000000001</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -688,16 +696,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>123101</v>
+        <v>49296</v>
       </c>
       <c r="D11" t="n">
-        <v>113620</v>
+        <v>49293</v>
       </c>
       <c r="E11" t="n">
-        <v>9481</v>
+        <v>3</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>0.9229999999999999</v>
+        <v>0.9998999999999999</v>
       </c>
     </row>
     <row r="12">
@@ -712,16 +720,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>28</v>
+        <v>3848</v>
       </c>
       <c r="D12" t="n">
-        <v>28</v>
+        <v>2471</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>1377</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>1</v>
+        <v>0.6422</v>
       </c>
     </row>
     <row r="13">
@@ -736,17 +744,15 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1587</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>1587</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
-      <c r="F13" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="F13" s="2" t="n"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -760,15 +766,17 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>5589</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>5587</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" s="2" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>0.9995999999999999</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -782,15 +790,17 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>165</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" s="2" t="n"/>
+        <v>15</v>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>0.9167000000000001</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -804,15 +814,17 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>531</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>492</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" s="2" t="n"/>
+        <v>39</v>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>0.9266</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -826,10 +838,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>7060</v>
+        <v>4953</v>
       </c>
       <c r="D17" t="n">
-        <v>7060</v>
+        <v>4953</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -872,15 +884,17 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>782</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>757</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" s="2" t="n"/>
+        <v>25</v>
+      </c>
+      <c r="F19" s="2" t="n">
+        <v>0.968</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -894,16 +908,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>5379</v>
+        <v>19808</v>
       </c>
       <c r="D20" t="n">
-        <v>5371</v>
+        <v>17820</v>
       </c>
       <c r="E20" t="n">
-        <v>8</v>
+        <v>1988</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>0.9984999999999999</v>
+        <v>0.8996</v>
       </c>
     </row>
     <row r="21">
@@ -940,15 +954,17 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>6328</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>3310</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" s="2" t="n"/>
+        <v>3018</v>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>0.5231</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -962,15 +978,17 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>45818</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>38645</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" s="2" t="n"/>
+        <v>7173</v>
+      </c>
+      <c r="F23" s="2" t="n">
+        <v>0.8434</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1006,16 +1024,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>13811</v>
+        <v>83638</v>
       </c>
       <c r="D25" t="n">
-        <v>13805</v>
+        <v>80108</v>
       </c>
       <c r="E25" t="n">
-        <v>6</v>
+        <v>3530</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>0.9995999999999999</v>
+        <v>0.9578</v>
       </c>
     </row>
     <row r="26">
@@ -1030,16 +1048,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>3409</v>
+        <v>737</v>
       </c>
       <c r="D26" t="n">
-        <v>3134</v>
+        <v>737</v>
       </c>
       <c r="E26" t="n">
-        <v>275</v>
+        <v>0</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>0.9193000000000001</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1054,16 +1072,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>10506</v>
+        <v>3623</v>
       </c>
       <c r="D27" t="n">
-        <v>10348</v>
+        <v>3567</v>
       </c>
       <c r="E27" t="n">
-        <v>158</v>
+        <v>56</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>0.985</v>
+        <v>0.9845</v>
       </c>
     </row>
     <row r="28">
@@ -1078,13 +1096,13 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F28" s="2" t="n">
         <v>0</v>
@@ -1102,16 +1120,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>6331</v>
+        <v>1324</v>
       </c>
       <c r="D29" t="n">
-        <v>4083</v>
+        <v>1221</v>
       </c>
       <c r="E29" t="n">
-        <v>2248</v>
+        <v>103</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>0.6448999999999999</v>
+        <v>0.9222</v>
       </c>
     </row>
     <row r="30">
@@ -1126,16 +1144,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>2343</v>
+        <v>1343</v>
       </c>
       <c r="D30" t="n">
-        <v>2304</v>
+        <v>1326</v>
       </c>
       <c r="E30" t="n">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>0.9834000000000001</v>
+        <v>0.9873000000000001</v>
       </c>
     </row>
     <row r="31">
@@ -1172,15 +1190,17 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0</v>
+        <v>15370</v>
       </c>
       <c r="D32" t="n">
-        <v>0</v>
+        <v>14348</v>
       </c>
       <c r="E32" t="n">
-        <v>0</v>
-      </c>
-      <c r="F32" s="2" t="n"/>
+        <v>1022</v>
+      </c>
+      <c r="F32" s="2" t="n">
+        <v>0.9335</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1194,16 +1214,16 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>37394</v>
+        <v>28034</v>
       </c>
       <c r="D33" t="n">
-        <v>37056</v>
+        <v>27954</v>
       </c>
       <c r="E33" t="n">
-        <v>338</v>
+        <v>80</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>0.991</v>
+        <v>0.9971</v>
       </c>
     </row>
     <row r="34">

--- a/output/TRANSFERENCIA_atual.xlsx
+++ b/output/TRANSFERENCIA_atual.xlsx
@@ -484,16 +484,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4925</v>
+        <v>4051</v>
       </c>
       <c r="D2" t="n">
-        <v>4899</v>
+        <v>3989</v>
       </c>
       <c r="E2" t="n">
-        <v>26</v>
+        <v>62</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.9947</v>
+        <v>0.9847</v>
       </c>
     </row>
     <row r="3">
@@ -508,16 +508,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>4517</v>
+        <v>2398</v>
       </c>
       <c r="D3" t="n">
-        <v>2881</v>
+        <v>951</v>
       </c>
       <c r="E3" t="n">
-        <v>1636</v>
+        <v>1447</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.6378</v>
+        <v>0.3966</v>
       </c>
     </row>
     <row r="4">
@@ -532,16 +532,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2897</v>
+        <v>1091</v>
       </c>
       <c r="D4" t="n">
-        <v>2462</v>
+        <v>1016</v>
       </c>
       <c r="E4" t="n">
-        <v>435</v>
+        <v>75</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.8498</v>
+        <v>0.9312999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -556,16 +556,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>648</v>
+        <v>728</v>
       </c>
       <c r="D5" t="n">
-        <v>639</v>
+        <v>470</v>
       </c>
       <c r="E5" t="n">
-        <v>9</v>
+        <v>258</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.9861</v>
+        <v>0.6456000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -580,10 +580,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>19</v>
+        <v>11462</v>
       </c>
       <c r="D6" t="n">
-        <v>19</v>
+        <v>11462</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -604,16 +604,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>341</v>
+        <v>3665</v>
       </c>
       <c r="D7" t="n">
-        <v>331</v>
+        <v>3513</v>
       </c>
       <c r="E7" t="n">
-        <v>10</v>
+        <v>152</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.9706999999999999</v>
+        <v>0.9584999999999999</v>
       </c>
     </row>
     <row r="8">
@@ -628,15 +628,17 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>1918</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>407</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="2" t="n"/>
+        <v>1511</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>0.2122</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -650,16 +652,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>18155</v>
+        <v>38586</v>
       </c>
       <c r="D9" t="n">
-        <v>17596</v>
+        <v>36071</v>
       </c>
       <c r="E9" t="n">
-        <v>559</v>
+        <v>2515</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0.9692000000000001</v>
+        <v>0.9348000000000001</v>
       </c>
     </row>
     <row r="10">
@@ -696,16 +698,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>49296</v>
+        <v>93551</v>
       </c>
       <c r="D11" t="n">
-        <v>49293</v>
+        <v>87485</v>
       </c>
       <c r="E11" t="n">
-        <v>3</v>
+        <v>6066</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>0.9998999999999999</v>
+        <v>0.9351999999999999</v>
       </c>
     </row>
     <row r="12">
@@ -720,16 +722,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>3848</v>
+        <v>3119</v>
       </c>
       <c r="D12" t="n">
-        <v>2471</v>
+        <v>2795</v>
       </c>
       <c r="E12" t="n">
-        <v>1377</v>
+        <v>324</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>0.6422</v>
+        <v>0.8961</v>
       </c>
     </row>
     <row r="13">
@@ -744,15 +746,17 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>3282</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>3282</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
-      <c r="F13" s="2" t="n"/>
+      <c r="F13" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -766,16 +770,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>5589</v>
+        <v>6545</v>
       </c>
       <c r="D14" t="n">
-        <v>5587</v>
+        <v>6488</v>
       </c>
       <c r="E14" t="n">
-        <v>2</v>
+        <v>57</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0.9995999999999999</v>
+        <v>0.9913</v>
       </c>
     </row>
     <row r="15">
@@ -790,16 +794,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>180</v>
+        <v>1618</v>
       </c>
       <c r="D15" t="n">
-        <v>165</v>
+        <v>1595</v>
       </c>
       <c r="E15" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>0.9167000000000001</v>
+        <v>0.9858</v>
       </c>
     </row>
     <row r="16">
@@ -814,16 +818,16 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>531</v>
+        <v>1098</v>
       </c>
       <c r="D16" t="n">
-        <v>492</v>
+        <v>1064</v>
       </c>
       <c r="E16" t="n">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>0.9266</v>
+        <v>0.9690000000000001</v>
       </c>
     </row>
     <row r="17">
@@ -838,10 +842,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>4953</v>
+        <v>781</v>
       </c>
       <c r="D17" t="n">
-        <v>4953</v>
+        <v>781</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -884,16 +888,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>782</v>
+        <v>1227</v>
       </c>
       <c r="D19" t="n">
-        <v>757</v>
+        <v>1217</v>
       </c>
       <c r="E19" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>0.968</v>
+        <v>0.9919</v>
       </c>
     </row>
     <row r="20">
@@ -908,16 +912,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>19808</v>
+        <v>13583</v>
       </c>
       <c r="D20" t="n">
-        <v>17820</v>
+        <v>13416</v>
       </c>
       <c r="E20" t="n">
-        <v>1988</v>
+        <v>167</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>0.8996</v>
+        <v>0.9876999999999999</v>
       </c>
     </row>
     <row r="21">
@@ -954,16 +958,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>6328</v>
+        <v>3756</v>
       </c>
       <c r="D22" t="n">
-        <v>3310</v>
+        <v>1</v>
       </c>
       <c r="E22" t="n">
-        <v>3018</v>
+        <v>3755</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>0.5231</v>
+        <v>0.0003</v>
       </c>
     </row>
     <row r="23">
@@ -978,16 +982,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>45818</v>
+        <v>25053</v>
       </c>
       <c r="D23" t="n">
-        <v>38645</v>
+        <v>23933</v>
       </c>
       <c r="E23" t="n">
-        <v>7173</v>
+        <v>1120</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>0.8434</v>
+        <v>0.9553</v>
       </c>
     </row>
     <row r="24">
@@ -1024,16 +1028,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>83638</v>
+        <v>53497</v>
       </c>
       <c r="D25" t="n">
-        <v>80108</v>
+        <v>51710</v>
       </c>
       <c r="E25" t="n">
-        <v>3530</v>
+        <v>1787</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>0.9578</v>
+        <v>0.9666</v>
       </c>
     </row>
     <row r="26">
@@ -1048,16 +1052,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>737</v>
+        <v>5837</v>
       </c>
       <c r="D26" t="n">
-        <v>737</v>
+        <v>4478</v>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>1359</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>1</v>
+        <v>0.7672</v>
       </c>
     </row>
     <row r="27">
@@ -1072,16 +1076,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>3623</v>
+        <v>10207</v>
       </c>
       <c r="D27" t="n">
-        <v>3567</v>
+        <v>9852</v>
       </c>
       <c r="E27" t="n">
-        <v>56</v>
+        <v>355</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>0.9845</v>
+        <v>0.9651999999999999</v>
       </c>
     </row>
     <row r="28">
@@ -1096,13 +1100,13 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1</v>
+        <v>86</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>1</v>
+        <v>86</v>
       </c>
       <c r="F28" s="2" t="n">
         <v>0</v>
@@ -1120,16 +1124,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1324</v>
+        <v>15735</v>
       </c>
       <c r="D29" t="n">
-        <v>1221</v>
+        <v>10363</v>
       </c>
       <c r="E29" t="n">
-        <v>103</v>
+        <v>5372</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>0.9222</v>
+        <v>0.6586</v>
       </c>
     </row>
     <row r="30">
@@ -1144,16 +1148,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1343</v>
+        <v>87</v>
       </c>
       <c r="D30" t="n">
-        <v>1326</v>
+        <v>87</v>
       </c>
       <c r="E30" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>0.9873000000000001</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -1190,16 +1194,16 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>15370</v>
+        <v>11563</v>
       </c>
       <c r="D32" t="n">
-        <v>14348</v>
+        <v>11407</v>
       </c>
       <c r="E32" t="n">
-        <v>1022</v>
+        <v>156</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>0.9335</v>
+        <v>0.9865</v>
       </c>
     </row>
     <row r="33">
@@ -1214,16 +1218,16 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>28034</v>
+        <v>9174</v>
       </c>
       <c r="D33" t="n">
-        <v>27954</v>
+        <v>9174</v>
       </c>
       <c r="E33" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>0.9971</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34">

--- a/output/TRANSFERENCIA_atual.xlsx
+++ b/output/TRANSFERENCIA_atual.xlsx
@@ -484,16 +484,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4051</v>
+        <v>3579</v>
       </c>
       <c r="D2" t="n">
-        <v>3989</v>
+        <v>3559</v>
       </c>
       <c r="E2" t="n">
-        <v>62</v>
+        <v>20</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.9847</v>
+        <v>0.9944</v>
       </c>
     </row>
     <row r="3">
@@ -508,16 +508,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2398</v>
+        <v>3075</v>
       </c>
       <c r="D3" t="n">
-        <v>951</v>
+        <v>3020</v>
       </c>
       <c r="E3" t="n">
-        <v>1447</v>
+        <v>55</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.3966</v>
+        <v>0.9821</v>
       </c>
     </row>
     <row r="4">
@@ -532,16 +532,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1091</v>
+        <v>1338</v>
       </c>
       <c r="D4" t="n">
-        <v>1016</v>
+        <v>1253</v>
       </c>
       <c r="E4" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.9312999999999999</v>
+        <v>0.9365000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -556,16 +556,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>728</v>
+        <v>651</v>
       </c>
       <c r="D5" t="n">
-        <v>470</v>
+        <v>646</v>
       </c>
       <c r="E5" t="n">
-        <v>258</v>
+        <v>5</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.6456000000000001</v>
+        <v>0.9923000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -580,13 +580,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>11462</v>
+        <v>24820</v>
       </c>
       <c r="D6" t="n">
-        <v>11462</v>
+        <v>24819</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>1</v>
@@ -604,16 +604,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3665</v>
+        <v>28170</v>
       </c>
       <c r="D7" t="n">
-        <v>3513</v>
+        <v>221</v>
       </c>
       <c r="E7" t="n">
-        <v>152</v>
+        <v>27949</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.9584999999999999</v>
+        <v>0.007800000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -628,16 +628,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1918</v>
+        <v>5559</v>
       </c>
       <c r="D8" t="n">
-        <v>407</v>
+        <v>1997</v>
       </c>
       <c r="E8" t="n">
-        <v>1511</v>
+        <v>3562</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.2122</v>
+        <v>0.3592</v>
       </c>
     </row>
     <row r="9">
@@ -652,16 +652,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>38586</v>
+        <v>38998</v>
       </c>
       <c r="D9" t="n">
-        <v>36071</v>
+        <v>35752</v>
       </c>
       <c r="E9" t="n">
-        <v>2515</v>
+        <v>3246</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0.9348000000000001</v>
+        <v>0.9168000000000001</v>
       </c>
     </row>
     <row r="10">
@@ -698,16 +698,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>93551</v>
+        <v>140034</v>
       </c>
       <c r="D11" t="n">
-        <v>87485</v>
+        <v>116461</v>
       </c>
       <c r="E11" t="n">
-        <v>6066</v>
+        <v>23573</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>0.9351999999999999</v>
+        <v>0.8317</v>
       </c>
     </row>
     <row r="12">
@@ -722,16 +722,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>3119</v>
+        <v>2567</v>
       </c>
       <c r="D12" t="n">
-        <v>2795</v>
+        <v>2323</v>
       </c>
       <c r="E12" t="n">
-        <v>324</v>
+        <v>244</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>0.8961</v>
+        <v>0.9048999999999999</v>
       </c>
     </row>
     <row r="13">
@@ -746,16 +746,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3282</v>
+        <v>5238</v>
       </c>
       <c r="D13" t="n">
-        <v>3282</v>
+        <v>5237</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>1</v>
+        <v>0.9998</v>
       </c>
     </row>
     <row r="14">
@@ -770,16 +770,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>6545</v>
+        <v>4075</v>
       </c>
       <c r="D14" t="n">
-        <v>6488</v>
+        <v>4074</v>
       </c>
       <c r="E14" t="n">
-        <v>57</v>
+        <v>1</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0.9913</v>
+        <v>0.9998</v>
       </c>
     </row>
     <row r="15">
@@ -794,16 +794,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1618</v>
+        <v>456</v>
       </c>
       <c r="D15" t="n">
-        <v>1595</v>
+        <v>453</v>
       </c>
       <c r="E15" t="n">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>0.9858</v>
+        <v>0.9934000000000001</v>
       </c>
     </row>
     <row r="16">
@@ -818,16 +818,16 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1098</v>
+        <v>1080</v>
       </c>
       <c r="D16" t="n">
-        <v>1064</v>
+        <v>913</v>
       </c>
       <c r="E16" t="n">
-        <v>34</v>
+        <v>167</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>0.9690000000000001</v>
+        <v>0.8454</v>
       </c>
     </row>
     <row r="17">
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>781</v>
+        <v>2910</v>
       </c>
       <c r="D17" t="n">
-        <v>781</v>
+        <v>2910</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -888,16 +888,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1227</v>
+        <v>610</v>
       </c>
       <c r="D19" t="n">
-        <v>1217</v>
+        <v>586</v>
       </c>
       <c r="E19" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>0.9919</v>
+        <v>0.9606999999999999</v>
       </c>
     </row>
     <row r="20">
@@ -912,16 +912,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>13583</v>
+        <v>15568</v>
       </c>
       <c r="D20" t="n">
-        <v>13416</v>
+        <v>4993</v>
       </c>
       <c r="E20" t="n">
-        <v>167</v>
+        <v>10575</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>0.9876999999999999</v>
+        <v>0.3207</v>
       </c>
     </row>
     <row r="21">
@@ -958,16 +958,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>3756</v>
+        <v>3361</v>
       </c>
       <c r="D22" t="n">
-        <v>1</v>
+        <v>3307</v>
       </c>
       <c r="E22" t="n">
-        <v>3755</v>
+        <v>54</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>0.0003</v>
+        <v>0.9839</v>
       </c>
     </row>
     <row r="23">
@@ -982,16 +982,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>25053</v>
+        <v>27711</v>
       </c>
       <c r="D23" t="n">
-        <v>23933</v>
+        <v>27233</v>
       </c>
       <c r="E23" t="n">
-        <v>1120</v>
+        <v>478</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>0.9553</v>
+        <v>0.9828</v>
       </c>
     </row>
     <row r="24">
@@ -1028,16 +1028,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>53497</v>
+        <v>42891</v>
       </c>
       <c r="D25" t="n">
-        <v>51710</v>
+        <v>42449</v>
       </c>
       <c r="E25" t="n">
-        <v>1787</v>
+        <v>442</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>0.9666</v>
+        <v>0.9897</v>
       </c>
     </row>
     <row r="26">
@@ -1052,16 +1052,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>5837</v>
+        <v>11856</v>
       </c>
       <c r="D26" t="n">
-        <v>4478</v>
+        <v>9058</v>
       </c>
       <c r="E26" t="n">
-        <v>1359</v>
+        <v>2798</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>0.7672</v>
+        <v>0.764</v>
       </c>
     </row>
     <row r="27">
@@ -1076,16 +1076,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>10207</v>
+        <v>18455</v>
       </c>
       <c r="D27" t="n">
-        <v>9852</v>
+        <v>17950</v>
       </c>
       <c r="E27" t="n">
-        <v>355</v>
+        <v>505</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>0.9651999999999999</v>
+        <v>0.9726</v>
       </c>
     </row>
     <row r="28">
@@ -1100,13 +1100,13 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="F28" s="2" t="n">
         <v>0</v>
@@ -1124,16 +1124,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>15735</v>
+        <v>27133</v>
       </c>
       <c r="D29" t="n">
-        <v>10363</v>
+        <v>16806</v>
       </c>
       <c r="E29" t="n">
-        <v>5372</v>
+        <v>10327</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>0.6586</v>
+        <v>0.6194</v>
       </c>
     </row>
     <row r="30">
@@ -1148,16 +1148,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>87</v>
+        <v>926</v>
       </c>
       <c r="D30" t="n">
-        <v>87</v>
+        <v>918</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>1</v>
+        <v>0.9914000000000001</v>
       </c>
     </row>
     <row r="31">
@@ -1194,16 +1194,16 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>11563</v>
+        <v>7499</v>
       </c>
       <c r="D32" t="n">
-        <v>11407</v>
+        <v>7425</v>
       </c>
       <c r="E32" t="n">
-        <v>156</v>
+        <v>74</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>0.9865</v>
+        <v>0.9901000000000001</v>
       </c>
     </row>
     <row r="33">
@@ -1218,16 +1218,16 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>9174</v>
+        <v>35996</v>
       </c>
       <c r="D33" t="n">
-        <v>9174</v>
+        <v>33934</v>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>2062</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>1</v>
+        <v>0.9427</v>
       </c>
     </row>
     <row r="34">

--- a/output/TRANSFERENCIA_atual.xlsx
+++ b/output/TRANSFERENCIA_atual.xlsx
@@ -484,16 +484,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3579</v>
+        <v>2083</v>
       </c>
       <c r="D2" t="n">
-        <v>3559</v>
+        <v>1975</v>
       </c>
       <c r="E2" t="n">
-        <v>20</v>
+        <v>108</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.9944</v>
+        <v>0.9481999999999999</v>
       </c>
     </row>
     <row r="3">
@@ -508,16 +508,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>3075</v>
+        <v>1408</v>
       </c>
       <c r="D3" t="n">
-        <v>3020</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>55</v>
+        <v>1408</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.9821</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -532,17 +532,15 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1338</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>1253</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>85</v>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>0.9365000000000001</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -556,17 +554,15 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>651</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>646</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>5</v>
-      </c>
-      <c r="F5" s="2" t="n">
-        <v>0.9923000000000001</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F5" s="2" t="n"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -580,10 +576,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>24820</v>
+        <v>20030</v>
       </c>
       <c r="D6" t="n">
-        <v>24819</v>
+        <v>20029</v>
       </c>
       <c r="E6" t="n">
         <v>1</v>
@@ -604,16 +600,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>28170</v>
+        <v>46553</v>
       </c>
       <c r="D7" t="n">
-        <v>221</v>
+        <v>16615</v>
       </c>
       <c r="E7" t="n">
-        <v>27949</v>
+        <v>29938</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.007800000000000001</v>
+        <v>0.3569</v>
       </c>
     </row>
     <row r="8">
@@ -628,17 +624,15 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>5559</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>1997</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>3562</v>
-      </c>
-      <c r="F8" s="2" t="n">
-        <v>0.3592</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F8" s="2" t="n"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -652,16 +646,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>38998</v>
+        <v>14829</v>
       </c>
       <c r="D9" t="n">
-        <v>35752</v>
+        <v>368</v>
       </c>
       <c r="E9" t="n">
-        <v>3246</v>
+        <v>14461</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0.9168000000000001</v>
+        <v>0.0248</v>
       </c>
     </row>
     <row r="10">
@@ -698,16 +692,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>140034</v>
+        <v>192337</v>
       </c>
       <c r="D11" t="n">
-        <v>116461</v>
+        <v>192335</v>
       </c>
       <c r="E11" t="n">
-        <v>23573</v>
+        <v>2</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>0.8317</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -722,16 +716,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2567</v>
+        <v>1095</v>
       </c>
       <c r="D12" t="n">
-        <v>2323</v>
+        <v>1093</v>
       </c>
       <c r="E12" t="n">
-        <v>244</v>
+        <v>2</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>0.9048999999999999</v>
+        <v>0.9982</v>
       </c>
     </row>
     <row r="13">
@@ -746,16 +740,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>5238</v>
+        <v>3567</v>
       </c>
       <c r="D13" t="n">
-        <v>5237</v>
+        <v>3567</v>
       </c>
       <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="F13" s="2" t="n">
-        <v>0.9998</v>
       </c>
     </row>
     <row r="14">
@@ -770,16 +764,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>4075</v>
+        <v>3069</v>
       </c>
       <c r="D14" t="n">
-        <v>4074</v>
+        <v>3054</v>
       </c>
       <c r="E14" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0.9998</v>
+        <v>0.9951000000000001</v>
       </c>
     </row>
     <row r="15">
@@ -794,17 +788,15 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>456</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>453</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>3</v>
-      </c>
-      <c r="F15" s="2" t="n">
-        <v>0.9934000000000001</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F15" s="2" t="n"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -818,17 +810,15 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1080</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>913</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>167</v>
-      </c>
-      <c r="F16" s="2" t="n">
-        <v>0.8454</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F16" s="2" t="n"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -842,10 +832,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>2910</v>
+        <v>7665</v>
       </c>
       <c r="D17" t="n">
-        <v>2910</v>
+        <v>7665</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -888,17 +878,15 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>610</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>586</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>24</v>
-      </c>
-      <c r="F19" s="2" t="n">
-        <v>0.9606999999999999</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F19" s="2" t="n"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -912,16 +900,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>15568</v>
+        <v>9745</v>
       </c>
       <c r="D20" t="n">
-        <v>4993</v>
+        <v>9724</v>
       </c>
       <c r="E20" t="n">
-        <v>10575</v>
+        <v>21</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>0.3207</v>
+        <v>0.9978</v>
       </c>
     </row>
     <row r="21">
@@ -958,16 +946,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>3361</v>
+        <v>1619</v>
       </c>
       <c r="D22" t="n">
-        <v>3307</v>
+        <v>1596</v>
       </c>
       <c r="E22" t="n">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>0.9839</v>
+        <v>0.9858</v>
       </c>
     </row>
     <row r="23">
@@ -982,16 +970,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>27711</v>
+        <v>7574</v>
       </c>
       <c r="D23" t="n">
-        <v>27233</v>
+        <v>7543</v>
       </c>
       <c r="E23" t="n">
-        <v>478</v>
+        <v>31</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>0.9828</v>
+        <v>0.9959</v>
       </c>
     </row>
     <row r="24">
@@ -1028,16 +1016,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>42891</v>
+        <v>17815</v>
       </c>
       <c r="D25" t="n">
-        <v>42449</v>
+        <v>17753</v>
       </c>
       <c r="E25" t="n">
-        <v>442</v>
+        <v>62</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>0.9897</v>
+        <v>0.9965000000000001</v>
       </c>
     </row>
     <row r="26">
@@ -1052,16 +1040,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>11856</v>
+        <v>9569</v>
       </c>
       <c r="D26" t="n">
-        <v>9058</v>
+        <v>8304</v>
       </c>
       <c r="E26" t="n">
-        <v>2798</v>
+        <v>1265</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>0.764</v>
+        <v>0.8678</v>
       </c>
     </row>
     <row r="27">
@@ -1076,16 +1064,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>18455</v>
+        <v>13650</v>
       </c>
       <c r="D27" t="n">
-        <v>17950</v>
+        <v>13447</v>
       </c>
       <c r="E27" t="n">
-        <v>505</v>
+        <v>203</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>0.9726</v>
+        <v>0.9851000000000001</v>
       </c>
     </row>
     <row r="28">
@@ -1100,13 +1088,13 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>91</v>
+        <v>65</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>91</v>
+        <v>65</v>
       </c>
       <c r="F28" s="2" t="n">
         <v>0</v>
@@ -1124,16 +1112,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>27133</v>
+        <v>11050</v>
       </c>
       <c r="D29" t="n">
-        <v>16806</v>
+        <v>6009</v>
       </c>
       <c r="E29" t="n">
-        <v>10327</v>
+        <v>5041</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>0.6194</v>
+        <v>0.5438000000000001</v>
       </c>
     </row>
     <row r="30">
@@ -1148,16 +1136,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>926</v>
+        <v>2122</v>
       </c>
       <c r="D30" t="n">
-        <v>918</v>
+        <v>2091</v>
       </c>
       <c r="E30" t="n">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>0.9914000000000001</v>
+        <v>0.9854000000000001</v>
       </c>
     </row>
     <row r="31">
@@ -1194,16 +1182,16 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>7499</v>
+        <v>1666</v>
       </c>
       <c r="D32" t="n">
-        <v>7425</v>
+        <v>1663</v>
       </c>
       <c r="E32" t="n">
-        <v>74</v>
+        <v>3</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>0.9901000000000001</v>
+        <v>0.9982</v>
       </c>
     </row>
     <row r="33">
@@ -1218,16 +1206,16 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>35996</v>
+        <v>36527</v>
       </c>
       <c r="D33" t="n">
-        <v>33934</v>
+        <v>36274</v>
       </c>
       <c r="E33" t="n">
-        <v>2062</v>
+        <v>253</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>0.9427</v>
+        <v>0.9931</v>
       </c>
     </row>
     <row r="34">
@@ -1242,15 +1230,17 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E34" t="n">
         <v>0</v>
       </c>
-      <c r="F34" s="2" t="n"/>
+      <c r="F34" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F34"/>

--- a/output/TRANSFERENCIA_atual.xlsx
+++ b/output/TRANSFERENCIA_atual.xlsx
@@ -484,16 +484,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2083</v>
+        <v>310</v>
       </c>
       <c r="D2" t="n">
-        <v>1975</v>
+        <v>310</v>
       </c>
       <c r="E2" t="n">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.9481999999999999</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -508,17 +508,15 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1408</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>1408</v>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -576,16 +574,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>20030</v>
+        <v>8960</v>
       </c>
       <c r="D6" t="n">
-        <v>20029</v>
+        <v>8959</v>
       </c>
       <c r="E6" t="n">
         <v>1</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>1</v>
+        <v>0.9998999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -600,16 +598,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>46553</v>
+        <v>84</v>
       </c>
       <c r="D7" t="n">
-        <v>16615</v>
+        <v>84</v>
       </c>
       <c r="E7" t="n">
-        <v>29938</v>
+        <v>0</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.3569</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -646,17 +644,15 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>14829</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>368</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>14461</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>0.0248</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F9" s="2" t="n"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -692,13 +688,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>192337</v>
+        <v>185361</v>
       </c>
       <c r="D11" t="n">
-        <v>192335</v>
+        <v>185360</v>
       </c>
       <c r="E11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>1</v>
@@ -716,16 +712,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1095</v>
+        <v>121</v>
       </c>
       <c r="D12" t="n">
-        <v>1093</v>
+        <v>121</v>
       </c>
       <c r="E12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>0.9982</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -740,10 +736,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3567</v>
+        <v>1703</v>
       </c>
       <c r="D13" t="n">
-        <v>3567</v>
+        <v>1703</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -764,17 +760,15 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>3069</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>3054</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>15</v>
-      </c>
-      <c r="F14" s="2" t="n">
-        <v>0.9951000000000001</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F14" s="2" t="n"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -832,10 +826,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>7665</v>
+        <v>7720</v>
       </c>
       <c r="D17" t="n">
-        <v>7665</v>
+        <v>7720</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -900,16 +894,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>9745</v>
+        <v>4369</v>
       </c>
       <c r="D20" t="n">
-        <v>9724</v>
+        <v>4367</v>
       </c>
       <c r="E20" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>0.9978</v>
+        <v>0.9995000000000001</v>
       </c>
     </row>
     <row r="21">
@@ -946,16 +940,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1619</v>
+        <v>2</v>
       </c>
       <c r="D22" t="n">
-        <v>1596</v>
+        <v>2</v>
       </c>
       <c r="E22" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>0.9858</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -970,16 +964,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>7574</v>
+        <v>4</v>
       </c>
       <c r="D23" t="n">
-        <v>7543</v>
+        <v>4</v>
       </c>
       <c r="E23" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>0.9959</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1016,16 +1010,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>17815</v>
+        <v>12223</v>
       </c>
       <c r="D25" t="n">
-        <v>17753</v>
+        <v>12223</v>
       </c>
       <c r="E25" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>0.9965000000000001</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1040,16 +1034,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>9569</v>
+        <v>6294</v>
       </c>
       <c r="D26" t="n">
-        <v>8304</v>
+        <v>5799</v>
       </c>
       <c r="E26" t="n">
-        <v>1265</v>
+        <v>495</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>0.8678</v>
+        <v>0.9214</v>
       </c>
     </row>
     <row r="27">
@@ -1064,16 +1058,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>13650</v>
+        <v>9250</v>
       </c>
       <c r="D27" t="n">
-        <v>13447</v>
+        <v>9118</v>
       </c>
       <c r="E27" t="n">
-        <v>203</v>
+        <v>132</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>0.9851000000000001</v>
+        <v>0.9856999999999999</v>
       </c>
     </row>
     <row r="28">
@@ -1088,13 +1082,13 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="F28" s="2" t="n">
         <v>0</v>
@@ -1112,16 +1106,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>11050</v>
+        <v>7082</v>
       </c>
       <c r="D29" t="n">
-        <v>6009</v>
+        <v>4468</v>
       </c>
       <c r="E29" t="n">
-        <v>5041</v>
+        <v>2614</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>0.5438000000000001</v>
+        <v>0.6309</v>
       </c>
     </row>
     <row r="30">
@@ -1136,16 +1130,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>2122</v>
+        <v>2183</v>
       </c>
       <c r="D30" t="n">
-        <v>2091</v>
+        <v>2159</v>
       </c>
       <c r="E30" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>0.9854000000000001</v>
+        <v>0.9890000000000001</v>
       </c>
     </row>
     <row r="31">
@@ -1182,16 +1176,16 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1666</v>
+        <v>5</v>
       </c>
       <c r="D32" t="n">
-        <v>1663</v>
+        <v>5</v>
       </c>
       <c r="E32" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>0.9982</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -1206,16 +1200,16 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>36527</v>
+        <v>33087</v>
       </c>
       <c r="D33" t="n">
-        <v>36274</v>
+        <v>32415</v>
       </c>
       <c r="E33" t="n">
-        <v>253</v>
+        <v>672</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>0.9931</v>
+        <v>0.9797</v>
       </c>
     </row>
     <row r="34">
@@ -1230,17 +1224,15 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D34" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E34" t="n">
         <v>0</v>
       </c>
-      <c r="F34" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="F34" s="2" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:F34"/>

--- a/output/TRANSFERENCIA_atual.xlsx
+++ b/output/TRANSFERENCIA_atual.xlsx
@@ -484,16 +484,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>310</v>
+        <v>1595</v>
       </c>
       <c r="D2" t="n">
         <v>310</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>1285</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>1</v>
+        <v>0.1944</v>
       </c>
     </row>
     <row r="3">
@@ -508,15 +508,17 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>3264</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>2449</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" s="2" t="n"/>
+        <v>815</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>0.7503</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -530,15 +532,17 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>2820</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>2433</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" s="2" t="n"/>
+        <v>387</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>0.8628</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -552,15 +556,17 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>493</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>480</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="2" t="n"/>
+        <v>13</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>0.9736</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -574,16 +580,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>8960</v>
+        <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>8959</v>
+        <v>6</v>
       </c>
       <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>0.9998999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -598,16 +604,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>84</v>
+        <v>99</v>
       </c>
       <c r="D7" t="n">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>1</v>
+        <v>0.9293</v>
       </c>
     </row>
     <row r="8">
@@ -644,15 +650,17 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>25835</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>25220</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="2" t="n"/>
+        <v>615</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>0.9762000000000001</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -688,10 +696,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>185361</v>
+        <v>92727</v>
       </c>
       <c r="D11" t="n">
-        <v>185360</v>
+        <v>92726</v>
       </c>
       <c r="E11" t="n">
         <v>1</v>
@@ -712,16 +720,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>121</v>
+        <v>2720</v>
       </c>
       <c r="D12" t="n">
-        <v>121</v>
+        <v>2717</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>1</v>
+        <v>0.9989</v>
       </c>
     </row>
     <row r="13">
@@ -736,17 +744,15 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1703</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>1703</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
-      <c r="F13" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="F13" s="2" t="n"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -760,15 +766,17 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>4983</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>4977</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" s="2" t="n"/>
+        <v>6</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>0.9987999999999999</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -782,15 +790,17 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>436</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>435</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" s="2" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>0.9976999999999999</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -804,15 +814,17 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>434</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>398</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" s="2" t="n"/>
+        <v>36</v>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>0.9170999999999999</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -826,10 +838,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>7720</v>
+        <v>6064</v>
       </c>
       <c r="D17" t="n">
-        <v>7720</v>
+        <v>6064</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -872,15 +884,17 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>1240</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>1220</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" s="2" t="n"/>
+        <v>20</v>
+      </c>
+      <c r="F19" s="2" t="n">
+        <v>0.9839</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -894,16 +908,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>4369</v>
+        <v>16101</v>
       </c>
       <c r="D20" t="n">
-        <v>4367</v>
+        <v>14359</v>
       </c>
       <c r="E20" t="n">
-        <v>2</v>
+        <v>1742</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>0.9995000000000001</v>
+        <v>0.8918</v>
       </c>
     </row>
     <row r="21">
@@ -940,16 +954,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>2</v>
+        <v>6903</v>
       </c>
       <c r="D22" t="n">
-        <v>2</v>
+        <v>3701</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>3202</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>1</v>
+        <v>0.5361</v>
       </c>
     </row>
     <row r="23">
@@ -964,16 +978,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>4</v>
+        <v>44499</v>
       </c>
       <c r="D23" t="n">
-        <v>4</v>
+        <v>43527</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>972</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>1</v>
+        <v>0.9782</v>
       </c>
     </row>
     <row r="24">
@@ -1010,16 +1024,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>12223</v>
+        <v>75835</v>
       </c>
       <c r="D25" t="n">
-        <v>12223</v>
+        <v>62473</v>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>13362</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>1</v>
+        <v>0.8238</v>
       </c>
     </row>
     <row r="26">
@@ -1034,16 +1048,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>6294</v>
+        <v>874</v>
       </c>
       <c r="D26" t="n">
-        <v>5799</v>
+        <v>853</v>
       </c>
       <c r="E26" t="n">
-        <v>495</v>
+        <v>21</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>0.9214</v>
+        <v>0.976</v>
       </c>
     </row>
     <row r="27">
@@ -1058,16 +1072,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>9250</v>
+        <v>2831</v>
       </c>
       <c r="D27" t="n">
-        <v>9118</v>
+        <v>2795</v>
       </c>
       <c r="E27" t="n">
-        <v>132</v>
+        <v>36</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>0.9856999999999999</v>
+        <v>0.9873000000000001</v>
       </c>
     </row>
     <row r="28">
@@ -1082,17 +1096,15 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>11</v>
-      </c>
-      <c r="F28" s="2" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F28" s="2" t="n"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1106,16 +1118,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>7082</v>
+        <v>2811</v>
       </c>
       <c r="D29" t="n">
-        <v>4468</v>
+        <v>2290</v>
       </c>
       <c r="E29" t="n">
-        <v>2614</v>
+        <v>521</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>0.6309</v>
+        <v>0.8147</v>
       </c>
     </row>
     <row r="30">
@@ -1130,16 +1142,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>2183</v>
+        <v>1053</v>
       </c>
       <c r="D30" t="n">
-        <v>2159</v>
+        <v>1044</v>
       </c>
       <c r="E30" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>0.9890000000000001</v>
+        <v>0.9915</v>
       </c>
     </row>
     <row r="31">
@@ -1176,16 +1188,16 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>5</v>
+        <v>13654</v>
       </c>
       <c r="D32" t="n">
-        <v>5</v>
+        <v>13624</v>
       </c>
       <c r="E32" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>1</v>
+        <v>0.9978</v>
       </c>
     </row>
     <row r="33">
@@ -1200,16 +1212,16 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>33087</v>
+        <v>24197</v>
       </c>
       <c r="D33" t="n">
-        <v>32415</v>
+        <v>23614</v>
       </c>
       <c r="E33" t="n">
-        <v>672</v>
+        <v>583</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>0.9797</v>
+        <v>0.9759</v>
       </c>
     </row>
     <row r="34">

--- a/output/TRANSFERENCIA_atual.xlsx
+++ b/output/TRANSFERENCIA_atual.xlsx
@@ -484,16 +484,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1595</v>
+        <v>2656</v>
       </c>
       <c r="D2" t="n">
-        <v>310</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>1285</v>
+        <v>2656</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.1944</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -508,16 +508,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>3264</v>
+        <v>1886</v>
       </c>
       <c r="D3" t="n">
-        <v>2449</v>
+        <v>875</v>
       </c>
       <c r="E3" t="n">
-        <v>815</v>
+        <v>1011</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.7503</v>
+        <v>0.4639</v>
       </c>
     </row>
     <row r="4">
@@ -532,16 +532,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2820</v>
+        <v>2717</v>
       </c>
       <c r="D4" t="n">
-        <v>2433</v>
+        <v>2660</v>
       </c>
       <c r="E4" t="n">
-        <v>387</v>
+        <v>57</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.8628</v>
+        <v>0.9790000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -556,16 +556,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>493</v>
+        <v>549</v>
       </c>
       <c r="D5" t="n">
-        <v>480</v>
+        <v>549</v>
       </c>
       <c r="E5" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.9736</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -580,10 +580,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>6</v>
+        <v>23263</v>
       </c>
       <c r="D6" t="n">
-        <v>6</v>
+        <v>23263</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -604,16 +604,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>99</v>
+        <v>19746</v>
       </c>
       <c r="D7" t="n">
-        <v>92</v>
+        <v>12260</v>
       </c>
       <c r="E7" t="n">
-        <v>7</v>
+        <v>7486</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.9293</v>
+        <v>0.6209</v>
       </c>
     </row>
     <row r="8">
@@ -650,16 +650,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>25835</v>
+        <v>19928</v>
       </c>
       <c r="D9" t="n">
-        <v>25220</v>
+        <v>17613</v>
       </c>
       <c r="E9" t="n">
-        <v>615</v>
+        <v>2315</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0.9762000000000001</v>
+        <v>0.8837999999999999</v>
       </c>
     </row>
     <row r="10">
@@ -696,10 +696,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>92727</v>
+        <v>137532</v>
       </c>
       <c r="D11" t="n">
-        <v>92726</v>
+        <v>137531</v>
       </c>
       <c r="E11" t="n">
         <v>1</v>
@@ -720,16 +720,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2720</v>
+        <v>1933</v>
       </c>
       <c r="D12" t="n">
-        <v>2717</v>
+        <v>1932</v>
       </c>
       <c r="E12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>0.9989</v>
+        <v>0.9995000000000001</v>
       </c>
     </row>
     <row r="13">
@@ -744,15 +744,17 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>4928</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>4928</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
-      <c r="F13" s="2" t="n"/>
+      <c r="F13" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -766,16 +768,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>4983</v>
+        <v>4641</v>
       </c>
       <c r="D14" t="n">
-        <v>4977</v>
+        <v>4636</v>
       </c>
       <c r="E14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0.9987999999999999</v>
+        <v>0.9989</v>
       </c>
     </row>
     <row r="15">
@@ -790,17 +792,15 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>436</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>435</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>1</v>
-      </c>
-      <c r="F15" s="2" t="n">
-        <v>0.9976999999999999</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F15" s="2" t="n"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -814,16 +814,16 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>434</v>
+        <v>1029</v>
       </c>
       <c r="D16" t="n">
-        <v>398</v>
+        <v>1022</v>
       </c>
       <c r="E16" t="n">
-        <v>36</v>
+        <v>7</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>0.9170999999999999</v>
+        <v>0.9932</v>
       </c>
     </row>
     <row r="17">
@@ -838,10 +838,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>6064</v>
+        <v>5740</v>
       </c>
       <c r="D17" t="n">
-        <v>6064</v>
+        <v>5740</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -884,16 +884,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1240</v>
+        <v>898</v>
       </c>
       <c r="D19" t="n">
-        <v>1220</v>
+        <v>886</v>
       </c>
       <c r="E19" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>0.9839</v>
+        <v>0.9865999999999999</v>
       </c>
     </row>
     <row r="20">
@@ -908,16 +908,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>16101</v>
+        <v>9302</v>
       </c>
       <c r="D20" t="n">
-        <v>14359</v>
+        <v>3879</v>
       </c>
       <c r="E20" t="n">
-        <v>1742</v>
+        <v>5423</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>0.8918</v>
+        <v>0.417</v>
       </c>
     </row>
     <row r="21">
@@ -954,16 +954,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>6903</v>
+        <v>2990</v>
       </c>
       <c r="D22" t="n">
-        <v>3701</v>
+        <v>2942</v>
       </c>
       <c r="E22" t="n">
-        <v>3202</v>
+        <v>48</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>0.5361</v>
+        <v>0.9839</v>
       </c>
     </row>
     <row r="23">
@@ -978,16 +978,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>44499</v>
+        <v>30641</v>
       </c>
       <c r="D23" t="n">
-        <v>43527</v>
+        <v>30144</v>
       </c>
       <c r="E23" t="n">
-        <v>972</v>
+        <v>497</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>0.9782</v>
+        <v>0.9838</v>
       </c>
     </row>
     <row r="24">
@@ -1024,16 +1024,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>75835</v>
+        <v>42594</v>
       </c>
       <c r="D25" t="n">
-        <v>62473</v>
+        <v>35166</v>
       </c>
       <c r="E25" t="n">
-        <v>13362</v>
+        <v>7428</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>0.8238</v>
+        <v>0.8256</v>
       </c>
     </row>
     <row r="26">
@@ -1048,16 +1048,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>874</v>
+        <v>16104</v>
       </c>
       <c r="D26" t="n">
-        <v>853</v>
+        <v>11041</v>
       </c>
       <c r="E26" t="n">
-        <v>21</v>
+        <v>5063</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>0.976</v>
+        <v>0.6856</v>
       </c>
     </row>
     <row r="27">
@@ -1072,16 +1072,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>2831</v>
+        <v>20993</v>
       </c>
       <c r="D27" t="n">
-        <v>2795</v>
+        <v>18027</v>
       </c>
       <c r="E27" t="n">
-        <v>36</v>
+        <v>2966</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>0.9873000000000001</v>
+        <v>0.8587</v>
       </c>
     </row>
     <row r="28">
@@ -1096,15 +1096,17 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
-      </c>
-      <c r="F28" s="2" t="n"/>
+        <v>10</v>
+      </c>
+      <c r="F28" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1118,16 +1120,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>2811</v>
+        <v>17279</v>
       </c>
       <c r="D29" t="n">
-        <v>2290</v>
+        <v>5470</v>
       </c>
       <c r="E29" t="n">
-        <v>521</v>
+        <v>11809</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>0.8147</v>
+        <v>0.3166</v>
       </c>
     </row>
     <row r="30">
@@ -1142,16 +1144,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1053</v>
+        <v>851</v>
       </c>
       <c r="D30" t="n">
-        <v>1044</v>
+        <v>837</v>
       </c>
       <c r="E30" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>0.9915</v>
+        <v>0.9834999999999999</v>
       </c>
     </row>
     <row r="31">
@@ -1188,16 +1190,16 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>13654</v>
+        <v>8062</v>
       </c>
       <c r="D32" t="n">
-        <v>13624</v>
+        <v>7999</v>
       </c>
       <c r="E32" t="n">
-        <v>30</v>
+        <v>63</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>0.9978</v>
+        <v>0.9922</v>
       </c>
     </row>
     <row r="33">
@@ -1212,16 +1214,16 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>24197</v>
+        <v>32720</v>
       </c>
       <c r="D33" t="n">
-        <v>23614</v>
+        <v>31838</v>
       </c>
       <c r="E33" t="n">
-        <v>583</v>
+        <v>882</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>0.9759</v>
+        <v>0.973</v>
       </c>
     </row>
     <row r="34">

--- a/output/TRANSFERENCIA_atual.xlsx
+++ b/output/TRANSFERENCIA_atual.xlsx
@@ -484,16 +484,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2656</v>
+        <v>2504</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>2487</v>
       </c>
       <c r="E2" t="n">
-        <v>2656</v>
+        <v>17</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0</v>
+        <v>0.9932</v>
       </c>
     </row>
     <row r="3">
@@ -508,16 +508,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1886</v>
+        <v>1612</v>
       </c>
       <c r="D3" t="n">
-        <v>875</v>
+        <v>1112</v>
       </c>
       <c r="E3" t="n">
-        <v>1011</v>
+        <v>500</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.4639</v>
+        <v>0.6898000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -532,16 +532,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2717</v>
+        <v>1640</v>
       </c>
       <c r="D4" t="n">
-        <v>2660</v>
+        <v>1206</v>
       </c>
       <c r="E4" t="n">
-        <v>57</v>
+        <v>434</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.9790000000000001</v>
+        <v>0.7354000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -556,16 +556,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>549</v>
+        <v>361</v>
       </c>
       <c r="D5" t="n">
-        <v>549</v>
+        <v>359</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>1</v>
+        <v>0.9945000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -580,13 +580,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>23263</v>
+        <v>24778</v>
       </c>
       <c r="D6" t="n">
-        <v>23263</v>
+        <v>24777</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>1</v>
@@ -604,16 +604,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>19746</v>
+        <v>13559</v>
       </c>
       <c r="D7" t="n">
-        <v>12260</v>
+        <v>12248</v>
       </c>
       <c r="E7" t="n">
-        <v>7486</v>
+        <v>1311</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.6209</v>
+        <v>0.9033</v>
       </c>
     </row>
     <row r="8">
@@ -650,16 +650,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>19928</v>
+        <v>16040</v>
       </c>
       <c r="D9" t="n">
-        <v>17613</v>
+        <v>12976</v>
       </c>
       <c r="E9" t="n">
-        <v>2315</v>
+        <v>3064</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0.8837999999999999</v>
+        <v>0.8090000000000001</v>
       </c>
     </row>
     <row r="10">
@@ -696,10 +696,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>137532</v>
+        <v>116088</v>
       </c>
       <c r="D11" t="n">
-        <v>137531</v>
+        <v>116087</v>
       </c>
       <c r="E11" t="n">
         <v>1</v>
@@ -720,16 +720,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1933</v>
+        <v>2368</v>
       </c>
       <c r="D12" t="n">
-        <v>1932</v>
+        <v>2307</v>
       </c>
       <c r="E12" t="n">
-        <v>1</v>
+        <v>61</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>0.9995000000000001</v>
+        <v>0.9742000000000001</v>
       </c>
     </row>
     <row r="13">
@@ -744,10 +744,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>4928</v>
+        <v>4084</v>
       </c>
       <c r="D13" t="n">
-        <v>4928</v>
+        <v>4084</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -768,16 +768,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>4641</v>
+        <v>4458</v>
       </c>
       <c r="D14" t="n">
-        <v>4636</v>
+        <v>4454</v>
       </c>
       <c r="E14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0.9989</v>
+        <v>0.9991</v>
       </c>
     </row>
     <row r="15">
@@ -792,15 +792,17 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>443</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>440</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" s="2" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>0.9932</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -814,16 +816,16 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1029</v>
+        <v>477</v>
       </c>
       <c r="D16" t="n">
-        <v>1022</v>
+        <v>417</v>
       </c>
       <c r="E16" t="n">
-        <v>7</v>
+        <v>60</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>0.9932</v>
+        <v>0.8742</v>
       </c>
     </row>
     <row r="17">
@@ -838,10 +840,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>5740</v>
+        <v>7428</v>
       </c>
       <c r="D17" t="n">
-        <v>5740</v>
+        <v>7428</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -884,17 +886,15 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>898</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>886</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>12</v>
-      </c>
-      <c r="F19" s="2" t="n">
-        <v>0.9865999999999999</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F19" s="2" t="n"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -908,16 +908,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>9302</v>
+        <v>9369</v>
       </c>
       <c r="D20" t="n">
-        <v>3879</v>
+        <v>8012</v>
       </c>
       <c r="E20" t="n">
-        <v>5423</v>
+        <v>1357</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>0.417</v>
+        <v>0.8552</v>
       </c>
     </row>
     <row r="21">
@@ -954,16 +954,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>2990</v>
+        <v>4328</v>
       </c>
       <c r="D22" t="n">
-        <v>2942</v>
+        <v>4284</v>
       </c>
       <c r="E22" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>0.9839</v>
+        <v>0.9898</v>
       </c>
     </row>
     <row r="23">
@@ -978,16 +978,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>30641</v>
+        <v>31199</v>
       </c>
       <c r="D23" t="n">
-        <v>30144</v>
+        <v>30485</v>
       </c>
       <c r="E23" t="n">
-        <v>497</v>
+        <v>714</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>0.9838</v>
+        <v>0.9771</v>
       </c>
     </row>
     <row r="24">
@@ -1024,16 +1024,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>42594</v>
+        <v>47577</v>
       </c>
       <c r="D25" t="n">
-        <v>35166</v>
+        <v>46693</v>
       </c>
       <c r="E25" t="n">
-        <v>7428</v>
+        <v>884</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>0.8256</v>
+        <v>0.9814000000000001</v>
       </c>
     </row>
     <row r="26">
@@ -1048,16 +1048,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>16104</v>
+        <v>17264</v>
       </c>
       <c r="D26" t="n">
-        <v>11041</v>
+        <v>12661</v>
       </c>
       <c r="E26" t="n">
-        <v>5063</v>
+        <v>4603</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>0.6856</v>
+        <v>0.7334000000000001</v>
       </c>
     </row>
     <row r="27">
@@ -1072,16 +1072,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>20993</v>
+        <v>16331</v>
       </c>
       <c r="D27" t="n">
-        <v>18027</v>
+        <v>16126</v>
       </c>
       <c r="E27" t="n">
-        <v>2966</v>
+        <v>205</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>0.8587</v>
+        <v>0.9873999999999999</v>
       </c>
     </row>
     <row r="28">
@@ -1096,13 +1096,13 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="F28" s="2" t="n">
         <v>0</v>
@@ -1120,16 +1120,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>17279</v>
+        <v>14551</v>
       </c>
       <c r="D29" t="n">
-        <v>5470</v>
+        <v>7193</v>
       </c>
       <c r="E29" t="n">
-        <v>11809</v>
+        <v>7358</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>0.3166</v>
+        <v>0.4943</v>
       </c>
     </row>
     <row r="30">
@@ -1144,16 +1144,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>851</v>
+        <v>2020</v>
       </c>
       <c r="D30" t="n">
-        <v>837</v>
+        <v>1994</v>
       </c>
       <c r="E30" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>0.9834999999999999</v>
+        <v>0.9871</v>
       </c>
     </row>
     <row r="31">
@@ -1190,16 +1190,16 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>8062</v>
+        <v>7500</v>
       </c>
       <c r="D32" t="n">
-        <v>7999</v>
+        <v>7426</v>
       </c>
       <c r="E32" t="n">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>0.9922</v>
+        <v>0.9901000000000001</v>
       </c>
     </row>
     <row r="33">
@@ -1214,16 +1214,16 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>32720</v>
+        <v>55311</v>
       </c>
       <c r="D33" t="n">
-        <v>31838</v>
+        <v>53555</v>
       </c>
       <c r="E33" t="n">
-        <v>882</v>
+        <v>1756</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>0.973</v>
+        <v>0.9682999999999999</v>
       </c>
     </row>
     <row r="34">

--- a/output/TRANSFERENCIA_atual.xlsx
+++ b/output/TRANSFERENCIA_atual.xlsx
@@ -484,16 +484,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2504</v>
+        <v>3079</v>
       </c>
       <c r="D2" t="n">
-        <v>2487</v>
+        <v>3057</v>
       </c>
       <c r="E2" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.9932</v>
+        <v>0.9929000000000001</v>
       </c>
     </row>
     <row r="3">
@@ -508,16 +508,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1612</v>
+        <v>1256</v>
       </c>
       <c r="D3" t="n">
-        <v>1112</v>
+        <v>630</v>
       </c>
       <c r="E3" t="n">
-        <v>500</v>
+        <v>626</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.6898000000000001</v>
+        <v>0.5015999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -532,16 +532,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1640</v>
+        <v>1856</v>
       </c>
       <c r="D4" t="n">
-        <v>1206</v>
+        <v>1657</v>
       </c>
       <c r="E4" t="n">
-        <v>434</v>
+        <v>199</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.7354000000000001</v>
+        <v>0.8928</v>
       </c>
     </row>
     <row r="5">
@@ -556,16 +556,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>361</v>
+        <v>498</v>
       </c>
       <c r="D5" t="n">
-        <v>359</v>
+        <v>469</v>
       </c>
       <c r="E5" t="n">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.9945000000000001</v>
+        <v>0.9418000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -580,10 +580,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>24778</v>
+        <v>21491</v>
       </c>
       <c r="D6" t="n">
-        <v>24777</v>
+        <v>21490</v>
       </c>
       <c r="E6" t="n">
         <v>1</v>
@@ -604,16 +604,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>13559</v>
+        <v>10118</v>
       </c>
       <c r="D7" t="n">
-        <v>12248</v>
+        <v>9178</v>
       </c>
       <c r="E7" t="n">
-        <v>1311</v>
+        <v>940</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.9033</v>
+        <v>0.9070999999999999</v>
       </c>
     </row>
     <row r="8">
@@ -650,16 +650,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>16040</v>
+        <v>13613</v>
       </c>
       <c r="D9" t="n">
-        <v>12976</v>
+        <v>12018</v>
       </c>
       <c r="E9" t="n">
-        <v>3064</v>
+        <v>1595</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0.8090000000000001</v>
+        <v>0.8828</v>
       </c>
     </row>
     <row r="10">
@@ -696,13 +696,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>116088</v>
+        <v>131639</v>
       </c>
       <c r="D11" t="n">
-        <v>116087</v>
+        <v>131639</v>
       </c>
       <c r="E11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>1</v>
@@ -720,16 +720,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2368</v>
+        <v>1469</v>
       </c>
       <c r="D12" t="n">
-        <v>2307</v>
+        <v>1038</v>
       </c>
       <c r="E12" t="n">
-        <v>61</v>
+        <v>431</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>0.9742000000000001</v>
+        <v>0.7066</v>
       </c>
     </row>
     <row r="13">
@@ -744,10 +744,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>4084</v>
+        <v>4296</v>
       </c>
       <c r="D13" t="n">
-        <v>4084</v>
+        <v>4296</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -768,16 +768,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>4458</v>
+        <v>3769</v>
       </c>
       <c r="D14" t="n">
-        <v>4454</v>
+        <v>3756</v>
       </c>
       <c r="E14" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0.9991</v>
+        <v>0.9965999999999999</v>
       </c>
     </row>
     <row r="15">
@@ -792,16 +792,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>443</v>
+        <v>793</v>
       </c>
       <c r="D15" t="n">
-        <v>440</v>
+        <v>767</v>
       </c>
       <c r="E15" t="n">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>0.9932</v>
+        <v>0.9671999999999999</v>
       </c>
     </row>
     <row r="16">
@@ -816,16 +816,16 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>477</v>
+        <v>666</v>
       </c>
       <c r="D16" t="n">
-        <v>417</v>
+        <v>584</v>
       </c>
       <c r="E16" t="n">
-        <v>60</v>
+        <v>82</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>0.8742</v>
+        <v>0.8769</v>
       </c>
     </row>
     <row r="17">
@@ -840,10 +840,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>7428</v>
+        <v>7247</v>
       </c>
       <c r="D17" t="n">
-        <v>7428</v>
+        <v>7247</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -886,15 +886,17 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>1732</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>1703</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" s="2" t="n"/>
+        <v>29</v>
+      </c>
+      <c r="F19" s="2" t="n">
+        <v>0.9833</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -908,16 +910,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>9369</v>
+        <v>9408</v>
       </c>
       <c r="D20" t="n">
-        <v>8012</v>
+        <v>8556</v>
       </c>
       <c r="E20" t="n">
-        <v>1357</v>
+        <v>852</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>0.8552</v>
+        <v>0.9094</v>
       </c>
     </row>
     <row r="21">
@@ -954,16 +956,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>4328</v>
+        <v>4539</v>
       </c>
       <c r="D22" t="n">
-        <v>4284</v>
+        <v>4401</v>
       </c>
       <c r="E22" t="n">
-        <v>44</v>
+        <v>138</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>0.9898</v>
+        <v>0.9695999999999999</v>
       </c>
     </row>
     <row r="23">
@@ -978,16 +980,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>31199</v>
+        <v>32759</v>
       </c>
       <c r="D23" t="n">
-        <v>30485</v>
+        <v>31994</v>
       </c>
       <c r="E23" t="n">
-        <v>714</v>
+        <v>765</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>0.9771</v>
+        <v>0.9765999999999999</v>
       </c>
     </row>
     <row r="24">
@@ -1002,15 +1004,17 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" s="2" t="n"/>
+        <v>10</v>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1024,16 +1028,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>47577</v>
+        <v>48530</v>
       </c>
       <c r="D25" t="n">
-        <v>46693</v>
+        <v>47231</v>
       </c>
       <c r="E25" t="n">
-        <v>884</v>
+        <v>1299</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>0.9814000000000001</v>
+        <v>0.9732</v>
       </c>
     </row>
     <row r="26">
@@ -1048,16 +1052,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>17264</v>
+        <v>13692</v>
       </c>
       <c r="D26" t="n">
-        <v>12661</v>
+        <v>11330</v>
       </c>
       <c r="E26" t="n">
-        <v>4603</v>
+        <v>2362</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>0.7334000000000001</v>
+        <v>0.8275</v>
       </c>
     </row>
     <row r="27">
@@ -1072,16 +1076,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>16331</v>
+        <v>13872</v>
       </c>
       <c r="D27" t="n">
-        <v>16126</v>
+        <v>13680</v>
       </c>
       <c r="E27" t="n">
-        <v>205</v>
+        <v>192</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>0.9873999999999999</v>
+        <v>0.9862000000000001</v>
       </c>
     </row>
     <row r="28">
@@ -1096,13 +1100,13 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F28" s="2" t="n">
         <v>0</v>
@@ -1120,16 +1124,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>14551</v>
+        <v>10861</v>
       </c>
       <c r="D29" t="n">
-        <v>7193</v>
+        <v>6186</v>
       </c>
       <c r="E29" t="n">
-        <v>7358</v>
+        <v>4675</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>0.4943</v>
+        <v>0.5696</v>
       </c>
     </row>
     <row r="30">
@@ -1144,16 +1148,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>2020</v>
+        <v>2627</v>
       </c>
       <c r="D30" t="n">
-        <v>1994</v>
+        <v>2607</v>
       </c>
       <c r="E30" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>0.9871</v>
+        <v>0.9923999999999999</v>
       </c>
     </row>
     <row r="31">
@@ -1190,16 +1194,16 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>7500</v>
+        <v>6069</v>
       </c>
       <c r="D32" t="n">
-        <v>7426</v>
+        <v>5962</v>
       </c>
       <c r="E32" t="n">
-        <v>74</v>
+        <v>107</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>0.9901000000000001</v>
+        <v>0.9823999999999999</v>
       </c>
     </row>
     <row r="33">
@@ -1214,16 +1218,16 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>55311</v>
+        <v>41306</v>
       </c>
       <c r="D33" t="n">
-        <v>53555</v>
+        <v>40276</v>
       </c>
       <c r="E33" t="n">
-        <v>1756</v>
+        <v>1030</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>0.9682999999999999</v>
+        <v>0.9751000000000001</v>
       </c>
     </row>
     <row r="34">

--- a/output/TRANSFERENCIA_atual.xlsx
+++ b/output/TRANSFERENCIA_atual.xlsx
@@ -484,16 +484,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3079</v>
+        <v>2619</v>
       </c>
       <c r="D2" t="n">
-        <v>3057</v>
+        <v>2594</v>
       </c>
       <c r="E2" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.9929000000000001</v>
+        <v>0.9904999999999999</v>
       </c>
     </row>
     <row r="3">
@@ -508,16 +508,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1256</v>
+        <v>1543</v>
       </c>
       <c r="D3" t="n">
-        <v>630</v>
+        <v>1509</v>
       </c>
       <c r="E3" t="n">
-        <v>626</v>
+        <v>34</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.5015999999999999</v>
+        <v>0.978</v>
       </c>
     </row>
     <row r="4">
@@ -532,17 +532,15 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1856</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>1657</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>199</v>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>0.8928</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -556,17 +554,15 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>498</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>469</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>29</v>
-      </c>
-      <c r="F5" s="2" t="n">
-        <v>0.9418000000000001</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F5" s="2" t="n"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -580,13 +576,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>21491</v>
+        <v>17843</v>
       </c>
       <c r="D6" t="n">
-        <v>21490</v>
+        <v>17843</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>1</v>
@@ -604,16 +600,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>10118</v>
+        <v>32709</v>
       </c>
       <c r="D7" t="n">
-        <v>9178</v>
+        <v>17350</v>
       </c>
       <c r="E7" t="n">
-        <v>940</v>
+        <v>15359</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.9070999999999999</v>
+        <v>0.5304</v>
       </c>
     </row>
     <row r="8">
@@ -650,16 +646,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>13613</v>
+        <v>9946</v>
       </c>
       <c r="D9" t="n">
-        <v>12018</v>
+        <v>8294</v>
       </c>
       <c r="E9" t="n">
-        <v>1595</v>
+        <v>1652</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0.8828</v>
+        <v>0.8339</v>
       </c>
     </row>
     <row r="10">
@@ -696,10 +692,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>131639</v>
+        <v>115226</v>
       </c>
       <c r="D11" t="n">
-        <v>131639</v>
+        <v>115226</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -720,16 +716,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1469</v>
+        <v>998</v>
       </c>
       <c r="D12" t="n">
-        <v>1038</v>
+        <v>992</v>
       </c>
       <c r="E12" t="n">
-        <v>431</v>
+        <v>6</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>0.7066</v>
+        <v>0.9940000000000001</v>
       </c>
     </row>
     <row r="13">
@@ -744,10 +740,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>4296</v>
+        <v>4247</v>
       </c>
       <c r="D13" t="n">
-        <v>4296</v>
+        <v>4247</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -768,16 +764,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>3769</v>
+        <v>3266</v>
       </c>
       <c r="D14" t="n">
-        <v>3756</v>
+        <v>3258</v>
       </c>
       <c r="E14" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0.9965999999999999</v>
+        <v>0.9976</v>
       </c>
     </row>
     <row r="15">
@@ -792,17 +788,15 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>793</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>767</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>26</v>
-      </c>
-      <c r="F15" s="2" t="n">
-        <v>0.9671999999999999</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F15" s="2" t="n"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -816,17 +810,15 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>666</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>584</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>82</v>
-      </c>
-      <c r="F16" s="2" t="n">
-        <v>0.8769</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F16" s="2" t="n"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -840,10 +832,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>7247</v>
+        <v>6862</v>
       </c>
       <c r="D17" t="n">
-        <v>7247</v>
+        <v>6862</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -886,17 +878,15 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1732</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>1703</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>29</v>
-      </c>
-      <c r="F19" s="2" t="n">
-        <v>0.9833</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F19" s="2" t="n"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -910,16 +900,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>9408</v>
+        <v>8746</v>
       </c>
       <c r="D20" t="n">
-        <v>8556</v>
+        <v>8732</v>
       </c>
       <c r="E20" t="n">
-        <v>852</v>
+        <v>14</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>0.9094</v>
+        <v>0.9984000000000001</v>
       </c>
     </row>
     <row r="21">
@@ -956,16 +946,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>4539</v>
+        <v>1859</v>
       </c>
       <c r="D22" t="n">
-        <v>4401</v>
+        <v>1839</v>
       </c>
       <c r="E22" t="n">
-        <v>138</v>
+        <v>20</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>0.9695999999999999</v>
+        <v>0.9892</v>
       </c>
     </row>
     <row r="23">
@@ -980,16 +970,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>32759</v>
+        <v>9219</v>
       </c>
       <c r="D23" t="n">
-        <v>31994</v>
+        <v>9148</v>
       </c>
       <c r="E23" t="n">
-        <v>765</v>
+        <v>71</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>0.9765999999999999</v>
+        <v>0.9923000000000001</v>
       </c>
     </row>
     <row r="24">
@@ -1028,16 +1018,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>48530</v>
+        <v>20914</v>
       </c>
       <c r="D25" t="n">
-        <v>47231</v>
+        <v>20528</v>
       </c>
       <c r="E25" t="n">
-        <v>1299</v>
+        <v>386</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>0.9732</v>
+        <v>0.9815</v>
       </c>
     </row>
     <row r="26">
@@ -1052,16 +1042,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>13692</v>
+        <v>10787</v>
       </c>
       <c r="D26" t="n">
-        <v>11330</v>
+        <v>8864</v>
       </c>
       <c r="E26" t="n">
-        <v>2362</v>
+        <v>1923</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>0.8275</v>
+        <v>0.8217</v>
       </c>
     </row>
     <row r="27">
@@ -1076,16 +1066,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>13872</v>
+        <v>13356</v>
       </c>
       <c r="D27" t="n">
-        <v>13680</v>
+        <v>13153</v>
       </c>
       <c r="E27" t="n">
-        <v>192</v>
+        <v>203</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>0.9862000000000001</v>
+        <v>0.9848</v>
       </c>
     </row>
     <row r="28">
@@ -1100,13 +1090,13 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F28" s="2" t="n">
         <v>0</v>
@@ -1124,16 +1114,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>10861</v>
+        <v>12735</v>
       </c>
       <c r="D29" t="n">
-        <v>6186</v>
+        <v>4159</v>
       </c>
       <c r="E29" t="n">
-        <v>4675</v>
+        <v>8576</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>0.5696</v>
+        <v>0.3265999999999999</v>
       </c>
     </row>
     <row r="30">
@@ -1148,16 +1138,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>2627</v>
+        <v>2272</v>
       </c>
       <c r="D30" t="n">
-        <v>2607</v>
+        <v>2260</v>
       </c>
       <c r="E30" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>0.9923999999999999</v>
+        <v>0.9947</v>
       </c>
     </row>
     <row r="31">
@@ -1194,16 +1184,16 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>6069</v>
+        <v>1606</v>
       </c>
       <c r="D32" t="n">
-        <v>5962</v>
+        <v>1603</v>
       </c>
       <c r="E32" t="n">
-        <v>107</v>
+        <v>3</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>0.9823999999999999</v>
+        <v>0.9981</v>
       </c>
     </row>
     <row r="33">
@@ -1218,16 +1208,16 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>41306</v>
+        <v>38609</v>
       </c>
       <c r="D33" t="n">
-        <v>40276</v>
+        <v>38271</v>
       </c>
       <c r="E33" t="n">
-        <v>1030</v>
+        <v>338</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>0.9751000000000001</v>
+        <v>0.9912000000000001</v>
       </c>
     </row>
     <row r="34">

--- a/output/TRANSFERENCIA_atual.xlsx
+++ b/output/TRANSFERENCIA_atual.xlsx
@@ -484,17 +484,15 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2619</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>2594</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>25</v>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>0.9904999999999999</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -508,17 +506,15 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1543</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>1509</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>34</v>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>0.978</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -576,10 +572,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>17843</v>
+        <v>8149</v>
       </c>
       <c r="D6" t="n">
-        <v>17843</v>
+        <v>8149</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -600,17 +596,15 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>32709</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>17350</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>15359</v>
-      </c>
-      <c r="F7" s="2" t="n">
-        <v>0.5304</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F7" s="2" t="n"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -646,17 +640,15 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>9946</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>8294</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>1652</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>0.8339</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F9" s="2" t="n"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -692,10 +684,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>115226</v>
+        <v>103844</v>
       </c>
       <c r="D11" t="n">
-        <v>115226</v>
+        <v>103844</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -716,16 +708,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>998</v>
+        <v>43</v>
       </c>
       <c r="D12" t="n">
-        <v>992</v>
+        <v>43</v>
       </c>
       <c r="E12" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>0.9940000000000001</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -740,10 +732,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>4247</v>
+        <v>2000</v>
       </c>
       <c r="D13" t="n">
-        <v>4247</v>
+        <v>2000</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -764,17 +756,15 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>3266</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>3258</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>8</v>
-      </c>
-      <c r="F14" s="2" t="n">
-        <v>0.9976</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F14" s="2" t="n"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -832,10 +822,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>6862</v>
+        <v>5723</v>
       </c>
       <c r="D17" t="n">
-        <v>6862</v>
+        <v>5723</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -900,16 +890,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>8746</v>
+        <v>3356</v>
       </c>
       <c r="D20" t="n">
-        <v>8732</v>
+        <v>3356</v>
       </c>
       <c r="E20" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>0.9984000000000001</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -946,17 +936,15 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1859</v>
+        <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>1839</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>20</v>
-      </c>
-      <c r="F22" s="2" t="n">
-        <v>0.9892</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F22" s="2" t="n"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -970,16 +958,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>9219</v>
+        <v>14</v>
       </c>
       <c r="D23" t="n">
-        <v>9148</v>
+        <v>14</v>
       </c>
       <c r="E23" t="n">
-        <v>71</v>
+        <v>0</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>0.9923000000000001</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -994,17 +982,15 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>10</v>
-      </c>
-      <c r="F24" s="2" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F24" s="2" t="n"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1018,16 +1004,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>20914</v>
+        <v>10965</v>
       </c>
       <c r="D25" t="n">
-        <v>20528</v>
+        <v>10965</v>
       </c>
       <c r="E25" t="n">
-        <v>386</v>
+        <v>0</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>0.9815</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1042,16 +1028,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>10787</v>
+        <v>6988</v>
       </c>
       <c r="D26" t="n">
-        <v>8864</v>
+        <v>5256</v>
       </c>
       <c r="E26" t="n">
-        <v>1923</v>
+        <v>1732</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>0.8217</v>
+        <v>0.7521</v>
       </c>
     </row>
     <row r="27">
@@ -1066,16 +1052,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>13356</v>
+        <v>10935</v>
       </c>
       <c r="D27" t="n">
-        <v>13153</v>
+        <v>10790</v>
       </c>
       <c r="E27" t="n">
-        <v>203</v>
+        <v>145</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>0.9848</v>
+        <v>0.9867</v>
       </c>
     </row>
     <row r="28">
@@ -1090,13 +1076,13 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="F28" s="2" t="n">
         <v>0</v>
@@ -1114,16 +1100,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>12735</v>
+        <v>9122</v>
       </c>
       <c r="D29" t="n">
-        <v>4159</v>
+        <v>1902</v>
       </c>
       <c r="E29" t="n">
-        <v>8576</v>
+        <v>7220</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>0.3265999999999999</v>
+        <v>0.2085</v>
       </c>
     </row>
     <row r="30">
@@ -1138,16 +1124,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>2272</v>
+        <v>1982</v>
       </c>
       <c r="D30" t="n">
-        <v>2260</v>
+        <v>1968</v>
       </c>
       <c r="E30" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>0.9947</v>
+        <v>0.9929000000000001</v>
       </c>
     </row>
     <row r="31">
@@ -1184,16 +1170,16 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1606</v>
+        <v>1</v>
       </c>
       <c r="D32" t="n">
-        <v>1603</v>
+        <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>0.9981</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -1208,16 +1194,16 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>38609</v>
+        <v>22334</v>
       </c>
       <c r="D33" t="n">
-        <v>38271</v>
+        <v>22119</v>
       </c>
       <c r="E33" t="n">
-        <v>338</v>
+        <v>215</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>0.9912000000000001</v>
+        <v>0.9904000000000001</v>
       </c>
     </row>
     <row r="34">
@@ -1232,15 +1218,17 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D34" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E34" t="n">
         <v>0</v>
       </c>
-      <c r="F34" s="2" t="n"/>
+      <c r="F34" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F34"/>

--- a/output/TRANSFERENCIA_atual.xlsx
+++ b/output/TRANSFERENCIA_atual.xlsx
@@ -484,15 +484,17 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>3026</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" s="2" t="n"/>
+        <v>3026</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -506,15 +508,17 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>4023</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>2866</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" s="2" t="n"/>
+        <v>1157</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>0.7123999999999999</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -528,15 +532,17 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>3792</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>3662</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" s="2" t="n"/>
+        <v>130</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>0.9656999999999999</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -550,15 +556,17 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>523</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>523</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
-      <c r="F5" s="2" t="n"/>
+      <c r="F5" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -572,10 +580,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>8149</v>
+        <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>8149</v>
+        <v>1</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -596,15 +604,17 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="2" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -640,15 +650,17 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>6184</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>5635</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="2" t="n"/>
+        <v>549</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>0.9112</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -684,10 +696,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>103844</v>
+        <v>51635</v>
       </c>
       <c r="D11" t="n">
-        <v>103844</v>
+        <v>51635</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -708,16 +720,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>43</v>
+        <v>2021</v>
       </c>
       <c r="D12" t="n">
-        <v>43</v>
+        <v>1534</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>487</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>1</v>
+        <v>0.759</v>
       </c>
     </row>
     <row r="13">
@@ -732,17 +744,15 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
-      <c r="F13" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="F13" s="2" t="n"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -756,15 +766,17 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>4084</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>4082</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" s="2" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>0.9995000000000001</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -778,15 +790,17 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>271</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>271</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
       </c>
-      <c r="F15" s="2" t="n"/>
+      <c r="F15" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -800,15 +814,17 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>679</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>636</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" s="2" t="n"/>
+        <v>43</v>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>0.9367</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -822,10 +838,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>5723</v>
+        <v>3196</v>
       </c>
       <c r="D17" t="n">
-        <v>5723</v>
+        <v>3196</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -868,15 +884,17 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>1442</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>1436</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" s="2" t="n"/>
+        <v>6</v>
+      </c>
+      <c r="F19" s="2" t="n">
+        <v>0.9958</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -890,16 +908,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>3356</v>
+        <v>13962</v>
       </c>
       <c r="D20" t="n">
-        <v>3356</v>
+        <v>6188</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>7774</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>1</v>
+        <v>0.4432</v>
       </c>
     </row>
     <row r="21">
@@ -936,15 +954,17 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>9844</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" s="2" t="n"/>
+        <v>9841</v>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>0.0003</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -958,16 +978,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>14</v>
+        <v>52636</v>
       </c>
       <c r="D23" t="n">
-        <v>14</v>
+        <v>36241</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>16395</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>1</v>
+        <v>0.6884999999999999</v>
       </c>
     </row>
     <row r="24">
@@ -1004,16 +1024,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>10965</v>
+        <v>88231</v>
       </c>
       <c r="D25" t="n">
-        <v>10965</v>
+        <v>87528</v>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>703</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>1</v>
+        <v>0.992</v>
       </c>
     </row>
     <row r="26">
@@ -1028,16 +1048,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>6988</v>
+        <v>986</v>
       </c>
       <c r="D26" t="n">
-        <v>5256</v>
+        <v>970</v>
       </c>
       <c r="E26" t="n">
-        <v>1732</v>
+        <v>16</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>0.7521</v>
+        <v>0.9838</v>
       </c>
     </row>
     <row r="27">
@@ -1052,16 +1072,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>10935</v>
+        <v>3993</v>
       </c>
       <c r="D27" t="n">
-        <v>10790</v>
+        <v>3968</v>
       </c>
       <c r="E27" t="n">
-        <v>145</v>
+        <v>25</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>0.9867</v>
+        <v>0.9937</v>
       </c>
     </row>
     <row r="28">
@@ -1076,17 +1096,15 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>8</v>
-      </c>
-      <c r="F28" s="2" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F28" s="2" t="n"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1100,16 +1118,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>9122</v>
+        <v>3549</v>
       </c>
       <c r="D29" t="n">
-        <v>1902</v>
+        <v>2845</v>
       </c>
       <c r="E29" t="n">
-        <v>7220</v>
+        <v>704</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>0.2085</v>
+        <v>0.8016</v>
       </c>
     </row>
     <row r="30">
@@ -1124,16 +1142,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1982</v>
+        <v>1242</v>
       </c>
       <c r="D30" t="n">
-        <v>1968</v>
+        <v>1232</v>
       </c>
       <c r="E30" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>0.9929000000000001</v>
+        <v>0.9919</v>
       </c>
     </row>
     <row r="31">
@@ -1170,16 +1188,16 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1</v>
+        <v>14660</v>
       </c>
       <c r="D32" t="n">
-        <v>1</v>
+        <v>14528</v>
       </c>
       <c r="E32" t="n">
-        <v>0</v>
+        <v>132</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>1</v>
+        <v>0.991</v>
       </c>
     </row>
     <row r="33">
@@ -1194,16 +1212,16 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>22334</v>
+        <v>2461</v>
       </c>
       <c r="D33" t="n">
-        <v>22119</v>
+        <v>2427</v>
       </c>
       <c r="E33" t="n">
-        <v>215</v>
+        <v>34</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>0.9904000000000001</v>
+        <v>0.9862000000000001</v>
       </c>
     </row>
     <row r="34">

--- a/output/TRANSFERENCIA_atual.xlsx
+++ b/output/TRANSFERENCIA_atual.xlsx
@@ -484,16 +484,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3026</v>
+        <v>4290</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>3026</v>
+        <v>4289</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0</v>
+        <v>0.0002</v>
       </c>
     </row>
     <row r="3">
@@ -508,16 +508,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>4023</v>
+        <v>2228</v>
       </c>
       <c r="D3" t="n">
-        <v>2866</v>
+        <v>921</v>
       </c>
       <c r="E3" t="n">
-        <v>1157</v>
+        <v>1307</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.7123999999999999</v>
+        <v>0.4134</v>
       </c>
     </row>
     <row r="4">
@@ -532,16 +532,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3792</v>
+        <v>1309</v>
       </c>
       <c r="D4" t="n">
-        <v>3662</v>
+        <v>1273</v>
       </c>
       <c r="E4" t="n">
-        <v>130</v>
+        <v>36</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.9656999999999999</v>
+        <v>0.9725</v>
       </c>
     </row>
     <row r="5">
@@ -556,16 +556,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>523</v>
+        <v>1218</v>
       </c>
       <c r="D5" t="n">
-        <v>523</v>
+        <v>1217</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>1</v>
+        <v>0.9992</v>
       </c>
     </row>
     <row r="6">
@@ -580,10 +580,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>9830</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>9830</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -604,16 +604,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>3228</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>3014</v>
       </c>
       <c r="E7" t="n">
-        <v>3</v>
+        <v>214</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0</v>
+        <v>0.9337000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -650,16 +650,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>6184</v>
+        <v>24324</v>
       </c>
       <c r="D9" t="n">
-        <v>5635</v>
+        <v>23475</v>
       </c>
       <c r="E9" t="n">
-        <v>549</v>
+        <v>849</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0.9112</v>
+        <v>0.9651000000000001</v>
       </c>
     </row>
     <row r="10">
@@ -696,10 +696,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>51635</v>
+        <v>71509</v>
       </c>
       <c r="D11" t="n">
-        <v>51635</v>
+        <v>71509</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -720,16 +720,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2021</v>
+        <v>2209</v>
       </c>
       <c r="D12" t="n">
-        <v>1534</v>
+        <v>1988</v>
       </c>
       <c r="E12" t="n">
-        <v>487</v>
+        <v>221</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>0.759</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="13">
@@ -744,15 +744,17 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>2519</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>2519</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
-      <c r="F13" s="2" t="n"/>
+      <c r="F13" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -766,16 +768,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>4084</v>
+        <v>5346</v>
       </c>
       <c r="D14" t="n">
-        <v>4082</v>
+        <v>5305</v>
       </c>
       <c r="E14" t="n">
-        <v>2</v>
+        <v>41</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0.9995000000000001</v>
+        <v>0.9923000000000001</v>
       </c>
     </row>
     <row r="15">
@@ -790,16 +792,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>271</v>
+        <v>877</v>
       </c>
       <c r="D15" t="n">
-        <v>271</v>
+        <v>876</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>1</v>
+        <v>0.9989</v>
       </c>
     </row>
     <row r="16">
@@ -814,16 +816,16 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>679</v>
+        <v>1223</v>
       </c>
       <c r="D16" t="n">
-        <v>636</v>
+        <v>1130</v>
       </c>
       <c r="E16" t="n">
-        <v>43</v>
+        <v>93</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>0.9367</v>
+        <v>0.924</v>
       </c>
     </row>
     <row r="17">
@@ -838,10 +840,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>3196</v>
+        <v>2477</v>
       </c>
       <c r="D17" t="n">
-        <v>3196</v>
+        <v>2477</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -884,16 +886,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1442</v>
+        <v>1448</v>
       </c>
       <c r="D19" t="n">
-        <v>1436</v>
+        <v>1444</v>
       </c>
       <c r="E19" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>0.9958</v>
+        <v>0.9972</v>
       </c>
     </row>
     <row r="20">
@@ -908,16 +910,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>13962</v>
+        <v>11421</v>
       </c>
       <c r="D20" t="n">
-        <v>6188</v>
+        <v>9814</v>
       </c>
       <c r="E20" t="n">
-        <v>7774</v>
+        <v>1607</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>0.4432</v>
+        <v>0.8593000000000001</v>
       </c>
     </row>
     <row r="21">
@@ -954,16 +956,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>9844</v>
+        <v>4686</v>
       </c>
       <c r="D22" t="n">
-        <v>3</v>
+        <v>4492</v>
       </c>
       <c r="E22" t="n">
-        <v>9841</v>
+        <v>194</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>0.0003</v>
+        <v>0.9586</v>
       </c>
     </row>
     <row r="23">
@@ -978,16 +980,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>52636</v>
+        <v>45636</v>
       </c>
       <c r="D23" t="n">
-        <v>36241</v>
+        <v>44593</v>
       </c>
       <c r="E23" t="n">
-        <v>16395</v>
+        <v>1043</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>0.6884999999999999</v>
+        <v>0.9771</v>
       </c>
     </row>
     <row r="24">
@@ -1024,16 +1026,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>88231</v>
+        <v>58289</v>
       </c>
       <c r="D25" t="n">
-        <v>87528</v>
+        <v>55053</v>
       </c>
       <c r="E25" t="n">
-        <v>703</v>
+        <v>3236</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>0.992</v>
+        <v>0.9445</v>
       </c>
     </row>
     <row r="26">
@@ -1048,16 +1050,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>986</v>
+        <v>95</v>
       </c>
       <c r="D26" t="n">
-        <v>970</v>
+        <v>87</v>
       </c>
       <c r="E26" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>0.9838</v>
+        <v>0.9157999999999999</v>
       </c>
     </row>
     <row r="27">
@@ -1072,16 +1074,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>3993</v>
+        <v>11828</v>
       </c>
       <c r="D27" t="n">
-        <v>3968</v>
+        <v>9424</v>
       </c>
       <c r="E27" t="n">
-        <v>25</v>
+        <v>2404</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>0.9937</v>
+        <v>0.7968000000000001</v>
       </c>
     </row>
     <row r="28">
@@ -1096,15 +1098,17 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
-      </c>
-      <c r="F28" s="2" t="n"/>
+        <v>30</v>
+      </c>
+      <c r="F28" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1118,16 +1122,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>3549</v>
+        <v>21708</v>
       </c>
       <c r="D29" t="n">
-        <v>2845</v>
+        <v>14702</v>
       </c>
       <c r="E29" t="n">
-        <v>704</v>
+        <v>7006</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>0.8016</v>
+        <v>0.6773</v>
       </c>
     </row>
     <row r="30">
@@ -1142,16 +1146,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1242</v>
+        <v>74</v>
       </c>
       <c r="D30" t="n">
-        <v>1232</v>
+        <v>74</v>
       </c>
       <c r="E30" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>0.9919</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -1188,16 +1192,16 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>14660</v>
+        <v>11002</v>
       </c>
       <c r="D32" t="n">
-        <v>14528</v>
+        <v>10975</v>
       </c>
       <c r="E32" t="n">
-        <v>132</v>
+        <v>27</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>0.991</v>
+        <v>0.9975000000000001</v>
       </c>
     </row>
     <row r="33">
@@ -1212,16 +1216,16 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>2461</v>
+        <v>21</v>
       </c>
       <c r="D33" t="n">
-        <v>2427</v>
+        <v>20</v>
       </c>
       <c r="E33" t="n">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>0.9862000000000001</v>
+        <v>0.9523999999999999</v>
       </c>
     </row>
     <row r="34">
@@ -1236,17 +1240,15 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D34" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E34" t="n">
         <v>0</v>
       </c>
-      <c r="F34" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="F34" s="2" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:F34"/>

--- a/output/TRANSFERENCIA_atual.xlsx
+++ b/output/TRANSFERENCIA_atual.xlsx
@@ -484,16 +484,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4290</v>
+        <v>5479</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>4289</v>
+        <v>5479</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.0002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -508,16 +508,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2228</v>
+        <v>3058</v>
       </c>
       <c r="D3" t="n">
-        <v>921</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>1307</v>
+        <v>3058</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.4134</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -532,16 +532,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1309</v>
+        <v>1620</v>
       </c>
       <c r="D4" t="n">
-        <v>1273</v>
+        <v>1172</v>
       </c>
       <c r="E4" t="n">
-        <v>36</v>
+        <v>448</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.9725</v>
+        <v>0.7234999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -556,16 +556,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1218</v>
+        <v>296</v>
       </c>
       <c r="D5" t="n">
-        <v>1217</v>
+        <v>296</v>
       </c>
       <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="F5" s="2" t="n">
-        <v>0.9992</v>
       </c>
     </row>
     <row r="6">
@@ -580,10 +580,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>9830</v>
+        <v>22548</v>
       </c>
       <c r="D6" t="n">
-        <v>9830</v>
+        <v>22548</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -604,16 +604,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3228</v>
+        <v>15170</v>
       </c>
       <c r="D7" t="n">
-        <v>3014</v>
+        <v>13859</v>
       </c>
       <c r="E7" t="n">
-        <v>214</v>
+        <v>1311</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.9337000000000001</v>
+        <v>0.9136</v>
       </c>
     </row>
     <row r="8">
@@ -650,16 +650,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>24324</v>
+        <v>29353</v>
       </c>
       <c r="D9" t="n">
-        <v>23475</v>
+        <v>25452</v>
       </c>
       <c r="E9" t="n">
-        <v>849</v>
+        <v>3901</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0.9651000000000001</v>
+        <v>0.8671</v>
       </c>
     </row>
     <row r="10">
@@ -696,10 +696,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>71509</v>
+        <v>115936</v>
       </c>
       <c r="D11" t="n">
-        <v>71509</v>
+        <v>115936</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -720,16 +720,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2209</v>
+        <v>1984</v>
       </c>
       <c r="D12" t="n">
-        <v>1988</v>
+        <v>1827</v>
       </c>
       <c r="E12" t="n">
-        <v>221</v>
+        <v>157</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>0.9</v>
+        <v>0.9209000000000001</v>
       </c>
     </row>
     <row r="13">
@@ -744,10 +744,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2519</v>
+        <v>4486</v>
       </c>
       <c r="D13" t="n">
-        <v>2519</v>
+        <v>4486</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -768,16 +768,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>5346</v>
+        <v>3382</v>
       </c>
       <c r="D14" t="n">
-        <v>5305</v>
+        <v>3179</v>
       </c>
       <c r="E14" t="n">
-        <v>41</v>
+        <v>203</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0.9923000000000001</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="15">
@@ -792,16 +792,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>877</v>
+        <v>678</v>
       </c>
       <c r="D15" t="n">
-        <v>876</v>
+        <v>596</v>
       </c>
       <c r="E15" t="n">
-        <v>1</v>
+        <v>82</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>0.9989</v>
+        <v>0.8791</v>
       </c>
     </row>
     <row r="16">
@@ -816,16 +816,16 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1223</v>
+        <v>588</v>
       </c>
       <c r="D16" t="n">
-        <v>1130</v>
+        <v>475</v>
       </c>
       <c r="E16" t="n">
-        <v>93</v>
+        <v>113</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>0.924</v>
+        <v>0.8078</v>
       </c>
     </row>
     <row r="17">
@@ -840,10 +840,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>2477</v>
+        <v>3992</v>
       </c>
       <c r="D17" t="n">
-        <v>2477</v>
+        <v>3992</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -886,16 +886,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1448</v>
+        <v>596</v>
       </c>
       <c r="D19" t="n">
-        <v>1444</v>
+        <v>595</v>
       </c>
       <c r="E19" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>0.9972</v>
+        <v>0.9983</v>
       </c>
     </row>
     <row r="20">
@@ -910,16 +910,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>11421</v>
+        <v>13534</v>
       </c>
       <c r="D20" t="n">
-        <v>9814</v>
+        <v>3983</v>
       </c>
       <c r="E20" t="n">
-        <v>1607</v>
+        <v>9551</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>0.8593000000000001</v>
+        <v>0.2943</v>
       </c>
     </row>
     <row r="21">
@@ -956,16 +956,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>4686</v>
+        <v>4185</v>
       </c>
       <c r="D22" t="n">
-        <v>4492</v>
+        <v>1107</v>
       </c>
       <c r="E22" t="n">
-        <v>194</v>
+        <v>3078</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>0.9586</v>
+        <v>0.2645</v>
       </c>
     </row>
     <row r="23">
@@ -980,16 +980,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>45636</v>
+        <v>38985</v>
       </c>
       <c r="D23" t="n">
-        <v>44593</v>
+        <v>36904</v>
       </c>
       <c r="E23" t="n">
-        <v>1043</v>
+        <v>2081</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>0.9771</v>
+        <v>0.9466</v>
       </c>
     </row>
     <row r="24">
@@ -1026,16 +1026,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>58289</v>
+        <v>58561</v>
       </c>
       <c r="D25" t="n">
-        <v>55053</v>
+        <v>57910</v>
       </c>
       <c r="E25" t="n">
-        <v>3236</v>
+        <v>651</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>0.9445</v>
+        <v>0.9889</v>
       </c>
     </row>
     <row r="26">
@@ -1050,16 +1050,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>95</v>
+        <v>200</v>
       </c>
       <c r="D26" t="n">
-        <v>87</v>
+        <v>176</v>
       </c>
       <c r="E26" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>0.9157999999999999</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="27">
@@ -1074,16 +1074,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>11828</v>
+        <v>19482</v>
       </c>
       <c r="D27" t="n">
-        <v>9424</v>
+        <v>16829</v>
       </c>
       <c r="E27" t="n">
-        <v>2404</v>
+        <v>2653</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>0.7968000000000001</v>
+        <v>0.8637999999999999</v>
       </c>
     </row>
     <row r="28">
@@ -1098,13 +1098,13 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>30</v>
+        <v>74</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>30</v>
+        <v>74</v>
       </c>
       <c r="F28" s="2" t="n">
         <v>0</v>
@@ -1122,16 +1122,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>21708</v>
+        <v>42871</v>
       </c>
       <c r="D29" t="n">
-        <v>14702</v>
+        <v>27848</v>
       </c>
       <c r="E29" t="n">
-        <v>7006</v>
+        <v>15023</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>0.6773</v>
+        <v>0.6496</v>
       </c>
     </row>
     <row r="30">
@@ -1146,16 +1146,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>74</v>
+        <v>1417</v>
       </c>
       <c r="D30" t="n">
-        <v>74</v>
+        <v>1407</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>1</v>
+        <v>0.9929000000000001</v>
       </c>
     </row>
     <row r="31">
@@ -1192,16 +1192,16 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>11002</v>
+        <v>10058</v>
       </c>
       <c r="D32" t="n">
-        <v>10975</v>
+        <v>9754</v>
       </c>
       <c r="E32" t="n">
-        <v>27</v>
+        <v>304</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>0.9975000000000001</v>
+        <v>0.9698</v>
       </c>
     </row>
     <row r="33">
@@ -1216,16 +1216,16 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="D33" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="E33" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>0.9523999999999999</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="34">
@@ -1240,15 +1240,17 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="D34" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E34" t="n">
         <v>0</v>
       </c>
-      <c r="F34" s="2" t="n"/>
+      <c r="F34" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F34"/>

--- a/output/TRANSFERENCIA_atual.xlsx
+++ b/output/TRANSFERENCIA_atual.xlsx
@@ -484,16 +484,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5479</v>
+        <v>2661</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>5479</v>
+        <v>2660</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0</v>
+        <v>0.0004</v>
       </c>
     </row>
     <row r="3">
@@ -508,16 +508,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>3058</v>
+        <v>4800</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>2776</v>
       </c>
       <c r="E3" t="n">
-        <v>3058</v>
+        <v>2024</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0</v>
+        <v>0.5783</v>
       </c>
     </row>
     <row r="4">
@@ -532,16 +532,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1620</v>
+        <v>997</v>
       </c>
       <c r="D4" t="n">
-        <v>1172</v>
+        <v>864</v>
       </c>
       <c r="E4" t="n">
-        <v>448</v>
+        <v>133</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.7234999999999999</v>
+        <v>0.8665999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -556,16 +556,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>296</v>
+        <v>576</v>
       </c>
       <c r="D5" t="n">
-        <v>296</v>
+        <v>572</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>1</v>
+        <v>0.9931</v>
       </c>
     </row>
     <row r="6">
@@ -580,10 +580,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>22548</v>
+        <v>25535</v>
       </c>
       <c r="D6" t="n">
-        <v>22548</v>
+        <v>25535</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -604,16 +604,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>15170</v>
+        <v>13914</v>
       </c>
       <c r="D7" t="n">
-        <v>13859</v>
+        <v>10393</v>
       </c>
       <c r="E7" t="n">
-        <v>1311</v>
+        <v>3521</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.9136</v>
+        <v>0.7469</v>
       </c>
     </row>
     <row r="8">
@@ -650,16 +650,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>29353</v>
+        <v>26821</v>
       </c>
       <c r="D9" t="n">
-        <v>25452</v>
+        <v>25049</v>
       </c>
       <c r="E9" t="n">
-        <v>3901</v>
+        <v>1772</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0.8671</v>
+        <v>0.9339</v>
       </c>
     </row>
     <row r="10">
@@ -696,10 +696,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>115936</v>
+        <v>104850</v>
       </c>
       <c r="D11" t="n">
-        <v>115936</v>
+        <v>104850</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -720,16 +720,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1984</v>
+        <v>1331</v>
       </c>
       <c r="D12" t="n">
-        <v>1827</v>
+        <v>1270</v>
       </c>
       <c r="E12" t="n">
-        <v>157</v>
+        <v>61</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>0.9209000000000001</v>
+        <v>0.9542</v>
       </c>
     </row>
     <row r="13">
@@ -744,10 +744,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>4486</v>
+        <v>3762</v>
       </c>
       <c r="D13" t="n">
-        <v>4486</v>
+        <v>3762</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -768,16 +768,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>3382</v>
+        <v>3427</v>
       </c>
       <c r="D14" t="n">
-        <v>3179</v>
+        <v>3367</v>
       </c>
       <c r="E14" t="n">
-        <v>203</v>
+        <v>60</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.9825</v>
       </c>
     </row>
     <row r="15">
@@ -792,16 +792,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>678</v>
+        <v>353</v>
       </c>
       <c r="D15" t="n">
-        <v>596</v>
+        <v>273</v>
       </c>
       <c r="E15" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>0.8791</v>
+        <v>0.7734000000000001</v>
       </c>
     </row>
     <row r="16">
@@ -816,16 +816,16 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>588</v>
+        <v>238</v>
       </c>
       <c r="D16" t="n">
-        <v>475</v>
+        <v>227</v>
       </c>
       <c r="E16" t="n">
-        <v>113</v>
+        <v>11</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>0.8078</v>
+        <v>0.9538</v>
       </c>
     </row>
     <row r="17">
@@ -840,10 +840,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>3992</v>
+        <v>5481</v>
       </c>
       <c r="D17" t="n">
-        <v>3992</v>
+        <v>5481</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -886,16 +886,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>596</v>
+        <v>2137</v>
       </c>
       <c r="D19" t="n">
-        <v>595</v>
+        <v>2130</v>
       </c>
       <c r="E19" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>0.9983</v>
+        <v>0.9967</v>
       </c>
     </row>
     <row r="20">
@@ -910,16 +910,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>13534</v>
+        <v>10865</v>
       </c>
       <c r="D20" t="n">
-        <v>3983</v>
+        <v>4238</v>
       </c>
       <c r="E20" t="n">
-        <v>9551</v>
+        <v>6627</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>0.2943</v>
+        <v>0.3901</v>
       </c>
     </row>
     <row r="21">
@@ -956,16 +956,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>4185</v>
+        <v>4098</v>
       </c>
       <c r="D22" t="n">
-        <v>1107</v>
+        <v>1050</v>
       </c>
       <c r="E22" t="n">
-        <v>3078</v>
+        <v>3048</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>0.2645</v>
+        <v>0.2562</v>
       </c>
     </row>
     <row r="23">
@@ -980,16 +980,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>38985</v>
+        <v>38898</v>
       </c>
       <c r="D23" t="n">
-        <v>36904</v>
+        <v>37294</v>
       </c>
       <c r="E23" t="n">
-        <v>2081</v>
+        <v>1604</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>0.9466</v>
+        <v>0.9588</v>
       </c>
     </row>
     <row r="24">
@@ -1004,15 +1004,17 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>132</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>132</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
       </c>
-      <c r="F24" s="2" t="n"/>
+      <c r="F24" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1026,16 +1028,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>58561</v>
+        <v>59836</v>
       </c>
       <c r="D25" t="n">
-        <v>57910</v>
+        <v>53917</v>
       </c>
       <c r="E25" t="n">
-        <v>651</v>
+        <v>5919</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>0.9889</v>
+        <v>0.9011</v>
       </c>
     </row>
     <row r="26">
@@ -1050,16 +1052,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>200</v>
+        <v>105</v>
       </c>
       <c r="D26" t="n">
-        <v>176</v>
+        <v>89</v>
       </c>
       <c r="E26" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>0.88</v>
+        <v>0.8476</v>
       </c>
     </row>
     <row r="27">
@@ -1074,16 +1076,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>19482</v>
+        <v>17028</v>
       </c>
       <c r="D27" t="n">
-        <v>16829</v>
+        <v>16415</v>
       </c>
       <c r="E27" t="n">
-        <v>2653</v>
+        <v>613</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>0.8637999999999999</v>
+        <v>0.9640000000000001</v>
       </c>
     </row>
     <row r="28">
@@ -1098,13 +1100,13 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="F28" s="2" t="n">
         <v>0</v>
@@ -1122,16 +1124,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>42871</v>
+        <v>39340</v>
       </c>
       <c r="D29" t="n">
-        <v>27848</v>
+        <v>23789</v>
       </c>
       <c r="E29" t="n">
-        <v>15023</v>
+        <v>15551</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>0.6496</v>
+        <v>0.6047</v>
       </c>
     </row>
     <row r="30">
@@ -1146,16 +1148,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1417</v>
+        <v>3731</v>
       </c>
       <c r="D30" t="n">
-        <v>1407</v>
+        <v>3711</v>
       </c>
       <c r="E30" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>0.9929000000000001</v>
+        <v>0.9945999999999999</v>
       </c>
     </row>
     <row r="31">
@@ -1192,16 +1194,16 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>10058</v>
+        <v>10749</v>
       </c>
       <c r="D32" t="n">
-        <v>9754</v>
+        <v>10441</v>
       </c>
       <c r="E32" t="n">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>0.9698</v>
+        <v>0.9712999999999999</v>
       </c>
     </row>
     <row r="33">
@@ -1216,16 +1218,16 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>40</v>
+        <v>3876</v>
       </c>
       <c r="D33" t="n">
-        <v>24</v>
+        <v>1980</v>
       </c>
       <c r="E33" t="n">
-        <v>16</v>
+        <v>1896</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>0.6</v>
+        <v>0.5108</v>
       </c>
     </row>
     <row r="34">
@@ -1240,16 +1242,16 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="D34" t="n">
         <v>12</v>
       </c>
       <c r="E34" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>1</v>
+        <v>0.7059000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/output/TRANSFERENCIA_atual.xlsx
+++ b/output/TRANSFERENCIA_atual.xlsx
@@ -484,16 +484,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2661</v>
+        <v>4216</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>4153</v>
       </c>
       <c r="E2" t="n">
-        <v>2660</v>
+        <v>63</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.0004</v>
+        <v>0.9851000000000001</v>
       </c>
     </row>
     <row r="3">
@@ -508,16 +508,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>4800</v>
+        <v>2103</v>
       </c>
       <c r="D3" t="n">
-        <v>2776</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>2024</v>
+        <v>2103</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.5783</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -532,16 +532,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>997</v>
+        <v>1296</v>
       </c>
       <c r="D4" t="n">
-        <v>864</v>
+        <v>1267</v>
       </c>
       <c r="E4" t="n">
-        <v>133</v>
+        <v>29</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.8665999999999999</v>
+        <v>0.9776</v>
       </c>
     </row>
     <row r="5">
@@ -556,16 +556,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>576</v>
+        <v>448</v>
       </c>
       <c r="D5" t="n">
-        <v>572</v>
+        <v>413</v>
       </c>
       <c r="E5" t="n">
-        <v>4</v>
+        <v>35</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.9931</v>
+        <v>0.9218999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -580,10 +580,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>25535</v>
+        <v>24711</v>
       </c>
       <c r="D6" t="n">
-        <v>25535</v>
+        <v>24711</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -604,16 +604,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>13914</v>
+        <v>12856</v>
       </c>
       <c r="D7" t="n">
-        <v>10393</v>
+        <v>11894</v>
       </c>
       <c r="E7" t="n">
-        <v>3521</v>
+        <v>962</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.7469</v>
+        <v>0.9251999999999999</v>
       </c>
     </row>
     <row r="8">
@@ -650,16 +650,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>26821</v>
+        <v>8347</v>
       </c>
       <c r="D9" t="n">
-        <v>25049</v>
+        <v>6770</v>
       </c>
       <c r="E9" t="n">
-        <v>1772</v>
+        <v>1577</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0.9339</v>
+        <v>0.8111</v>
       </c>
     </row>
     <row r="10">
@@ -696,10 +696,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>104850</v>
+        <v>123471</v>
       </c>
       <c r="D11" t="n">
-        <v>104850</v>
+        <v>123471</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -720,16 +720,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1331</v>
+        <v>879</v>
       </c>
       <c r="D12" t="n">
-        <v>1270</v>
+        <v>779</v>
       </c>
       <c r="E12" t="n">
-        <v>61</v>
+        <v>100</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>0.9542</v>
+        <v>0.8862000000000001</v>
       </c>
     </row>
     <row r="13">
@@ -744,10 +744,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3762</v>
+        <v>3369</v>
       </c>
       <c r="D13" t="n">
-        <v>3762</v>
+        <v>3369</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -768,16 +768,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>3427</v>
+        <v>3912</v>
       </c>
       <c r="D14" t="n">
-        <v>3367</v>
+        <v>3908</v>
       </c>
       <c r="E14" t="n">
-        <v>60</v>
+        <v>4</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0.9825</v>
+        <v>0.9990000000000001</v>
       </c>
     </row>
     <row r="15">
@@ -792,17 +792,15 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>353</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>273</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>80</v>
-      </c>
-      <c r="F15" s="2" t="n">
-        <v>0.7734000000000001</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F15" s="2" t="n"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -816,16 +814,16 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>238</v>
+        <v>477</v>
       </c>
       <c r="D16" t="n">
-        <v>227</v>
+        <v>477</v>
       </c>
       <c r="E16" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>0.9538</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -840,10 +838,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>5481</v>
+        <v>8275</v>
       </c>
       <c r="D17" t="n">
-        <v>5481</v>
+        <v>8275</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -886,17 +884,15 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2137</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>2130</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>7</v>
-      </c>
-      <c r="F19" s="2" t="n">
-        <v>0.9967</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F19" s="2" t="n"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -910,16 +906,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>10865</v>
+        <v>12555</v>
       </c>
       <c r="D20" t="n">
-        <v>4238</v>
+        <v>11394</v>
       </c>
       <c r="E20" t="n">
-        <v>6627</v>
+        <v>1161</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>0.3901</v>
+        <v>0.9075</v>
       </c>
     </row>
     <row r="21">
@@ -956,16 +952,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>4098</v>
+        <v>3364</v>
       </c>
       <c r="D22" t="n">
-        <v>1050</v>
+        <v>882</v>
       </c>
       <c r="E22" t="n">
-        <v>3048</v>
+        <v>2482</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>0.2562</v>
+        <v>0.2622</v>
       </c>
     </row>
     <row r="23">
@@ -980,16 +976,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>38898</v>
+        <v>35840</v>
       </c>
       <c r="D23" t="n">
-        <v>37294</v>
+        <v>30477</v>
       </c>
       <c r="E23" t="n">
-        <v>1604</v>
+        <v>5363</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>0.9588</v>
+        <v>0.8504</v>
       </c>
     </row>
     <row r="24">
@@ -1028,16 +1024,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>59836</v>
+        <v>60525</v>
       </c>
       <c r="D25" t="n">
-        <v>53917</v>
+        <v>60355</v>
       </c>
       <c r="E25" t="n">
-        <v>5919</v>
+        <v>170</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>0.9011</v>
+        <v>0.9972</v>
       </c>
     </row>
     <row r="26">
@@ -1052,17 +1048,15 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>105</v>
+        <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>89</v>
+        <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>16</v>
-      </c>
-      <c r="F26" s="2" t="n">
-        <v>0.8476</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F26" s="2" t="n"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1076,16 +1070,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>17028</v>
+        <v>18646</v>
       </c>
       <c r="D27" t="n">
-        <v>16415</v>
+        <v>18170</v>
       </c>
       <c r="E27" t="n">
-        <v>613</v>
+        <v>476</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>0.9640000000000001</v>
+        <v>0.9745</v>
       </c>
     </row>
     <row r="28">
@@ -1100,13 +1094,13 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="F28" s="2" t="n">
         <v>0</v>
@@ -1124,16 +1118,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>39340</v>
+        <v>29272</v>
       </c>
       <c r="D29" t="n">
-        <v>23789</v>
+        <v>17044</v>
       </c>
       <c r="E29" t="n">
-        <v>15551</v>
+        <v>12228</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>0.6047</v>
+        <v>0.5822999999999999</v>
       </c>
     </row>
     <row r="30">
@@ -1148,16 +1142,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>3731</v>
+        <v>3982</v>
       </c>
       <c r="D30" t="n">
-        <v>3711</v>
+        <v>3945</v>
       </c>
       <c r="E30" t="n">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>0.9945999999999999</v>
+        <v>0.9906999999999999</v>
       </c>
     </row>
     <row r="31">
@@ -1194,16 +1188,16 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>10749</v>
+        <v>9900</v>
       </c>
       <c r="D32" t="n">
-        <v>10441</v>
+        <v>9670</v>
       </c>
       <c r="E32" t="n">
-        <v>308</v>
+        <v>230</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>0.9712999999999999</v>
+        <v>0.9768000000000001</v>
       </c>
     </row>
     <row r="33">
@@ -1218,16 +1212,16 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>3876</v>
+        <v>4101</v>
       </c>
       <c r="D33" t="n">
-        <v>1980</v>
+        <v>2515</v>
       </c>
       <c r="E33" t="n">
-        <v>1896</v>
+        <v>1586</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>0.5108</v>
+        <v>0.6133</v>
       </c>
     </row>
     <row r="34">
@@ -1242,16 +1236,16 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="D34" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E34" t="n">
         <v>5</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>0.7059000000000001</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/output/TRANSFERENCIA_atual.xlsx
+++ b/output/TRANSFERENCIA_atual.xlsx
@@ -484,16 +484,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4216</v>
+        <v>4160</v>
       </c>
       <c r="D2" t="n">
-        <v>4153</v>
+        <v>4134</v>
       </c>
       <c r="E2" t="n">
-        <v>63</v>
+        <v>26</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.9851000000000001</v>
+        <v>0.9937999999999999</v>
       </c>
     </row>
     <row r="3">
@@ -508,16 +508,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2103</v>
+        <v>4100</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>4046</v>
       </c>
       <c r="E3" t="n">
-        <v>2103</v>
+        <v>54</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0</v>
+        <v>0.9868000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -532,17 +532,15 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1296</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>1267</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>29</v>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>0.9776</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -556,17 +554,15 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>448</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>413</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>35</v>
-      </c>
-      <c r="F5" s="2" t="n">
-        <v>0.9218999999999999</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F5" s="2" t="n"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -580,10 +576,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>24711</v>
+        <v>20957</v>
       </c>
       <c r="D6" t="n">
-        <v>24711</v>
+        <v>20957</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -604,16 +600,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>12856</v>
+        <v>27611</v>
       </c>
       <c r="D7" t="n">
-        <v>11894</v>
+        <v>15067</v>
       </c>
       <c r="E7" t="n">
-        <v>962</v>
+        <v>12544</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.9251999999999999</v>
+        <v>0.5457</v>
       </c>
     </row>
     <row r="8">
@@ -650,16 +646,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>8347</v>
+        <v>9943</v>
       </c>
       <c r="D9" t="n">
-        <v>6770</v>
+        <v>8516</v>
       </c>
       <c r="E9" t="n">
-        <v>1577</v>
+        <v>1427</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0.8111</v>
+        <v>0.8565</v>
       </c>
     </row>
     <row r="10">
@@ -696,10 +692,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>123471</v>
+        <v>111943</v>
       </c>
       <c r="D11" t="n">
-        <v>123471</v>
+        <v>111943</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -720,16 +716,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>879</v>
+        <v>1079</v>
       </c>
       <c r="D12" t="n">
-        <v>779</v>
+        <v>699</v>
       </c>
       <c r="E12" t="n">
-        <v>100</v>
+        <v>380</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>0.8862000000000001</v>
+        <v>0.6478</v>
       </c>
     </row>
     <row r="13">
@@ -744,10 +740,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3369</v>
+        <v>3527</v>
       </c>
       <c r="D13" t="n">
-        <v>3369</v>
+        <v>3527</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -768,16 +764,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>3912</v>
+        <v>3311</v>
       </c>
       <c r="D14" t="n">
-        <v>3908</v>
+        <v>3301</v>
       </c>
       <c r="E14" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0.9990000000000001</v>
+        <v>0.997</v>
       </c>
     </row>
     <row r="15">
@@ -814,17 +810,15 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>477</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>477</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
       </c>
-      <c r="F16" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="F16" s="2" t="n"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -838,10 +832,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>8275</v>
+        <v>9705</v>
       </c>
       <c r="D17" t="n">
-        <v>8275</v>
+        <v>9705</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -906,16 +900,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>12555</v>
+        <v>10070</v>
       </c>
       <c r="D20" t="n">
-        <v>11394</v>
+        <v>10020</v>
       </c>
       <c r="E20" t="n">
-        <v>1161</v>
+        <v>50</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>0.9075</v>
+        <v>0.995</v>
       </c>
     </row>
     <row r="21">
@@ -952,16 +946,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>3364</v>
+        <v>1566</v>
       </c>
       <c r="D22" t="n">
-        <v>882</v>
+        <v>1554</v>
       </c>
       <c r="E22" t="n">
-        <v>2482</v>
+        <v>12</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>0.2622</v>
+        <v>0.9923000000000001</v>
       </c>
     </row>
     <row r="23">
@@ -976,16 +970,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>35840</v>
+        <v>15415</v>
       </c>
       <c r="D23" t="n">
-        <v>30477</v>
+        <v>15382</v>
       </c>
       <c r="E23" t="n">
-        <v>5363</v>
+        <v>33</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>0.8504</v>
+        <v>0.9979</v>
       </c>
     </row>
     <row r="24">
@@ -1000,17 +994,15 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>132</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>132</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
       </c>
-      <c r="F24" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="F24" s="2" t="n"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1024,16 +1016,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>60525</v>
+        <v>28678</v>
       </c>
       <c r="D25" t="n">
-        <v>60355</v>
+        <v>28539</v>
       </c>
       <c r="E25" t="n">
-        <v>170</v>
+        <v>139</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>0.9972</v>
+        <v>0.9952</v>
       </c>
     </row>
     <row r="26">
@@ -1070,16 +1062,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>18646</v>
+        <v>19557</v>
       </c>
       <c r="D27" t="n">
-        <v>18170</v>
+        <v>19260</v>
       </c>
       <c r="E27" t="n">
-        <v>476</v>
+        <v>297</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>0.9745</v>
+        <v>0.9848</v>
       </c>
     </row>
     <row r="28">
@@ -1094,13 +1086,13 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="F28" s="2" t="n">
         <v>0</v>
@@ -1118,16 +1110,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>29272</v>
+        <v>31680</v>
       </c>
       <c r="D29" t="n">
-        <v>17044</v>
+        <v>17952</v>
       </c>
       <c r="E29" t="n">
-        <v>12228</v>
+        <v>13728</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>0.5822999999999999</v>
+        <v>0.5667</v>
       </c>
     </row>
     <row r="30">
@@ -1142,16 +1134,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>3982</v>
+        <v>2803</v>
       </c>
       <c r="D30" t="n">
-        <v>3945</v>
+        <v>2766</v>
       </c>
       <c r="E30" t="n">
         <v>37</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>0.9906999999999999</v>
+        <v>0.9868000000000001</v>
       </c>
     </row>
     <row r="31">
@@ -1188,16 +1180,16 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>9900</v>
+        <v>1511</v>
       </c>
       <c r="D32" t="n">
-        <v>9670</v>
+        <v>964</v>
       </c>
       <c r="E32" t="n">
-        <v>230</v>
+        <v>547</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>0.9768000000000001</v>
+        <v>0.638</v>
       </c>
     </row>
     <row r="33">
@@ -1212,16 +1204,16 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>4101</v>
+        <v>3434</v>
       </c>
       <c r="D33" t="n">
-        <v>2515</v>
+        <v>901</v>
       </c>
       <c r="E33" t="n">
-        <v>1586</v>
+        <v>2533</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>0.6133</v>
+        <v>0.2624</v>
       </c>
     </row>
     <row r="34">
@@ -1236,16 +1228,16 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D34" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E34" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/output/TRANSFERENCIA_atual.xlsx
+++ b/output/TRANSFERENCIA_atual.xlsx
@@ -484,17 +484,15 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4160</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>4134</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>26</v>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>0.9937999999999999</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -508,17 +506,15 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>4100</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>4046</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>54</v>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>0.9868000000000001</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -576,10 +572,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>20957</v>
+        <v>9066</v>
       </c>
       <c r="D6" t="n">
-        <v>20957</v>
+        <v>9066</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -600,16 +596,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>27611</v>
+        <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>15067</v>
+        <v>3</v>
       </c>
       <c r="E7" t="n">
-        <v>12544</v>
+        <v>0</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.5457</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -646,17 +642,15 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>9943</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>8516</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>1427</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>0.8565</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F9" s="2" t="n"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -692,10 +686,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>111943</v>
+        <v>98431</v>
       </c>
       <c r="D11" t="n">
-        <v>111943</v>
+        <v>98431</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -716,16 +710,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1079</v>
+        <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>699</v>
+        <v>2</v>
       </c>
       <c r="E12" t="n">
-        <v>380</v>
+        <v>1</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>0.6478</v>
+        <v>0.6667000000000001</v>
       </c>
     </row>
     <row r="13">
@@ -740,10 +734,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3527</v>
+        <v>1953</v>
       </c>
       <c r="D13" t="n">
-        <v>3527</v>
+        <v>1953</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -764,16 +758,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>3311</v>
+        <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3301</v>
+        <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0.997</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -832,10 +826,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>9705</v>
+        <v>8611</v>
       </c>
       <c r="D17" t="n">
-        <v>9705</v>
+        <v>8611</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -900,16 +894,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>10070</v>
+        <v>2756</v>
       </c>
       <c r="D20" t="n">
-        <v>10020</v>
+        <v>2756</v>
       </c>
       <c r="E20" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>0.995</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -946,17 +940,15 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1566</v>
+        <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>1554</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>12</v>
-      </c>
-      <c r="F22" s="2" t="n">
-        <v>0.9923000000000001</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F22" s="2" t="n"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -970,16 +962,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>15415</v>
+        <v>36</v>
       </c>
       <c r="D23" t="n">
-        <v>15382</v>
+        <v>36</v>
       </c>
       <c r="E23" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>0.9979</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1016,16 +1008,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>28678</v>
+        <v>18650</v>
       </c>
       <c r="D25" t="n">
-        <v>28539</v>
+        <v>18649</v>
       </c>
       <c r="E25" t="n">
-        <v>139</v>
+        <v>1</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>0.9952</v>
+        <v>0.9998999999999999</v>
       </c>
     </row>
     <row r="26">
@@ -1062,16 +1054,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>19557</v>
+        <v>17662</v>
       </c>
       <c r="D27" t="n">
-        <v>19260</v>
+        <v>17373</v>
       </c>
       <c r="E27" t="n">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>0.9848</v>
+        <v>0.9836</v>
       </c>
     </row>
     <row r="28">
@@ -1086,17 +1078,15 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>19</v>
-      </c>
-      <c r="F28" s="2" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F28" s="2" t="n"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1110,16 +1100,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>31680</v>
+        <v>25798</v>
       </c>
       <c r="D29" t="n">
-        <v>17952</v>
+        <v>17967</v>
       </c>
       <c r="E29" t="n">
-        <v>13728</v>
+        <v>7831</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>0.5667</v>
+        <v>0.6964</v>
       </c>
     </row>
     <row r="30">
@@ -1134,16 +1124,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>2803</v>
+        <v>3565</v>
       </c>
       <c r="D30" t="n">
-        <v>2766</v>
+        <v>3541</v>
       </c>
       <c r="E30" t="n">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>0.9868000000000001</v>
+        <v>0.9933</v>
       </c>
     </row>
     <row r="31">
@@ -1180,16 +1170,16 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1511</v>
+        <v>2</v>
       </c>
       <c r="D32" t="n">
-        <v>964</v>
+        <v>2</v>
       </c>
       <c r="E32" t="n">
-        <v>547</v>
+        <v>0</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>0.638</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -1204,16 +1194,16 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>3434</v>
+        <v>8</v>
       </c>
       <c r="D33" t="n">
-        <v>901</v>
+        <v>8</v>
       </c>
       <c r="E33" t="n">
-        <v>2533</v>
+        <v>0</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>0.2624</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34">

--- a/output/TRANSFERENCIA_atual.xlsx
+++ b/output/TRANSFERENCIA_atual.xlsx
@@ -484,15 +484,17 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>2196</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>2181</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" s="2" t="n"/>
+        <v>15</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>0.9932</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -506,15 +508,17 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>5862</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" s="2" t="n"/>
+        <v>5862</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -528,15 +532,17 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>2788</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>2744</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" s="2" t="n"/>
+        <v>44</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>0.9842</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -572,10 +578,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>9066</v>
+        <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>9066</v>
+        <v>3</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -642,15 +648,17 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>13983</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>12295</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="2" t="n"/>
+        <v>1688</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>0.8793000000000001</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -686,10 +694,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>98431</v>
+        <v>49536</v>
       </c>
       <c r="D11" t="n">
-        <v>98431</v>
+        <v>49536</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -710,16 +718,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>3</v>
+        <v>178</v>
       </c>
       <c r="D12" t="n">
-        <v>2</v>
+        <v>152</v>
       </c>
       <c r="E12" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>0.6667000000000001</v>
+        <v>0.8539</v>
       </c>
     </row>
     <row r="13">
@@ -734,17 +742,15 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1953</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>1953</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
-      <c r="F13" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="F13" s="2" t="n"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -758,16 +764,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1</v>
+        <v>2258</v>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>2160</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>1</v>
+        <v>0.9566</v>
       </c>
     </row>
     <row r="15">
@@ -826,10 +832,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>8611</v>
+        <v>4948</v>
       </c>
       <c r="D17" t="n">
-        <v>8611</v>
+        <v>4948</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -894,16 +900,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>2756</v>
+        <v>10225</v>
       </c>
       <c r="D20" t="n">
-        <v>2756</v>
+        <v>9511</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>714</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>1</v>
+        <v>0.9301999999999999</v>
       </c>
     </row>
     <row r="21">
@@ -962,16 +968,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>36</v>
+        <v>13404</v>
       </c>
       <c r="D23" t="n">
-        <v>36</v>
+        <v>10829</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>2575</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>1</v>
+        <v>0.8079000000000001</v>
       </c>
     </row>
     <row r="24">
@@ -1008,16 +1014,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>18650</v>
+        <v>60450</v>
       </c>
       <c r="D25" t="n">
-        <v>18649</v>
+        <v>58912</v>
       </c>
       <c r="E25" t="n">
-        <v>1</v>
+        <v>1538</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>0.9998999999999999</v>
+        <v>0.9745999999999999</v>
       </c>
     </row>
     <row r="26">
@@ -1054,16 +1060,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>17662</v>
+        <v>7377</v>
       </c>
       <c r="D27" t="n">
-        <v>17373</v>
+        <v>7273</v>
       </c>
       <c r="E27" t="n">
-        <v>289</v>
+        <v>104</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>0.9836</v>
+        <v>0.9859</v>
       </c>
     </row>
     <row r="28">
@@ -1100,16 +1106,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>25798</v>
+        <v>8571</v>
       </c>
       <c r="D29" t="n">
-        <v>17967</v>
+        <v>5708</v>
       </c>
       <c r="E29" t="n">
-        <v>7831</v>
+        <v>2863</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>0.6964</v>
+        <v>0.6659999999999999</v>
       </c>
     </row>
     <row r="30">
@@ -1124,16 +1130,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>3565</v>
+        <v>2621</v>
       </c>
       <c r="D30" t="n">
-        <v>3541</v>
+        <v>2603</v>
       </c>
       <c r="E30" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>0.9933</v>
+        <v>0.9931</v>
       </c>
     </row>
     <row r="31">
@@ -1194,16 +1200,16 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>8</v>
+        <v>2995</v>
       </c>
       <c r="D33" t="n">
-        <v>8</v>
+        <v>2711</v>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>284</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>1</v>
+        <v>0.9052</v>
       </c>
     </row>
     <row r="34">
@@ -1218,17 +1224,15 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D34" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E34" t="n">
         <v>0</v>
       </c>
-      <c r="F34" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="F34" s="2" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:F34"/>

--- a/output/TRANSFERENCIA_atual.xlsx
+++ b/output/TRANSFERENCIA_atual.xlsx
@@ -484,16 +484,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2196</v>
+        <v>3472</v>
       </c>
       <c r="D2" t="n">
-        <v>2181</v>
+        <v>2</v>
       </c>
       <c r="E2" t="n">
-        <v>15</v>
+        <v>3470</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.9932</v>
+        <v>0.0005999999999999999</v>
       </c>
     </row>
     <row r="3">
@@ -508,13 +508,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5862</v>
+        <v>3302</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>5862</v>
+        <v>3302</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>0</v>
@@ -532,16 +532,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2788</v>
+        <v>2674</v>
       </c>
       <c r="D4" t="n">
-        <v>2744</v>
+        <v>52</v>
       </c>
       <c r="E4" t="n">
-        <v>44</v>
+        <v>2622</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.9842</v>
+        <v>0.0194</v>
       </c>
     </row>
     <row r="5">
@@ -556,15 +556,17 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>295</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="2" t="n"/>
+        <v>55</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>0.8429000000000001</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -578,10 +580,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -602,16 +604,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>3211</v>
       </c>
       <c r="D7" t="n">
-        <v>3</v>
+        <v>3186</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>1</v>
+        <v>0.9922</v>
       </c>
     </row>
     <row r="8">
@@ -648,16 +650,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>13983</v>
+        <v>29219</v>
       </c>
       <c r="D9" t="n">
-        <v>12295</v>
+        <v>25653</v>
       </c>
       <c r="E9" t="n">
-        <v>1688</v>
+        <v>3566</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0.8793000000000001</v>
+        <v>0.878</v>
       </c>
     </row>
     <row r="10">
@@ -694,10 +696,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>49536</v>
+        <v>43538</v>
       </c>
       <c r="D11" t="n">
-        <v>49536</v>
+        <v>43538</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -718,16 +720,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>178</v>
+        <v>2666</v>
       </c>
       <c r="D12" t="n">
-        <v>152</v>
+        <v>2666</v>
       </c>
       <c r="E12" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>0.8539</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -764,16 +766,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2258</v>
+        <v>3143</v>
       </c>
       <c r="D14" t="n">
-        <v>2160</v>
+        <v>3119</v>
       </c>
       <c r="E14" t="n">
-        <v>98</v>
+        <v>24</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0.9566</v>
+        <v>0.9923999999999999</v>
       </c>
     </row>
     <row r="15">
@@ -788,15 +790,17 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>356</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>351</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" s="2" t="n"/>
+        <v>5</v>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>0.986</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -810,15 +814,17 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>751</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" s="2" t="n"/>
+        <v>751</v>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -832,10 +838,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>4948</v>
+        <v>1338</v>
       </c>
       <c r="D17" t="n">
-        <v>4948</v>
+        <v>1338</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -900,16 +906,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>10225</v>
+        <v>8627</v>
       </c>
       <c r="D20" t="n">
-        <v>9511</v>
+        <v>6814</v>
       </c>
       <c r="E20" t="n">
-        <v>714</v>
+        <v>1813</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>0.9301999999999999</v>
+        <v>0.7898000000000001</v>
       </c>
     </row>
     <row r="21">
@@ -946,15 +952,17 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>10569</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>7402</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" s="2" t="n"/>
+        <v>3167</v>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>0.7004</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -968,16 +976,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>13404</v>
+        <v>70666</v>
       </c>
       <c r="D23" t="n">
-        <v>10829</v>
+        <v>54232</v>
       </c>
       <c r="E23" t="n">
-        <v>2575</v>
+        <v>16434</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>0.8079000000000001</v>
+        <v>0.7674</v>
       </c>
     </row>
     <row r="24">
@@ -1014,16 +1022,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>60450</v>
+        <v>76725</v>
       </c>
       <c r="D25" t="n">
-        <v>58912</v>
+        <v>61590</v>
       </c>
       <c r="E25" t="n">
-        <v>1538</v>
+        <v>15135</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>0.9745999999999999</v>
+        <v>0.8027</v>
       </c>
     </row>
     <row r="26">
@@ -1060,16 +1068,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>7377</v>
+        <v>973</v>
       </c>
       <c r="D27" t="n">
-        <v>7273</v>
+        <v>962</v>
       </c>
       <c r="E27" t="n">
-        <v>104</v>
+        <v>11</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>0.9859</v>
+        <v>0.9887</v>
       </c>
     </row>
     <row r="28">
@@ -1106,16 +1114,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>8571</v>
+        <v>3503</v>
       </c>
       <c r="D29" t="n">
-        <v>5708</v>
+        <v>435</v>
       </c>
       <c r="E29" t="n">
-        <v>2863</v>
+        <v>3068</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>0.6659999999999999</v>
+        <v>0.1242</v>
       </c>
     </row>
     <row r="30">
@@ -1130,16 +1138,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>2621</v>
+        <v>191</v>
       </c>
       <c r="D30" t="n">
-        <v>2603</v>
+        <v>187</v>
       </c>
       <c r="E30" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>0.9931</v>
+        <v>0.9791</v>
       </c>
     </row>
     <row r="31">
@@ -1176,16 +1184,16 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>2</v>
+        <v>22545</v>
       </c>
       <c r="D32" t="n">
-        <v>2</v>
+        <v>21880</v>
       </c>
       <c r="E32" t="n">
-        <v>0</v>
+        <v>665</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>1</v>
+        <v>0.9704999999999999</v>
       </c>
     </row>
     <row r="33">
@@ -1200,16 +1208,16 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>2995</v>
+        <v>18237</v>
       </c>
       <c r="D33" t="n">
-        <v>2711</v>
+        <v>3297</v>
       </c>
       <c r="E33" t="n">
-        <v>284</v>
+        <v>14940</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>0.9052</v>
+        <v>0.1808</v>
       </c>
     </row>
     <row r="34">

--- a/output/TRANSFERENCIA_atual.xlsx
+++ b/output/TRANSFERENCIA_atual.xlsx
@@ -484,16 +484,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3472</v>
+        <v>5452</v>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>3470</v>
+        <v>5452</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.0005999999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -508,13 +508,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>3302</v>
+        <v>2306</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>3302</v>
+        <v>2306</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>0</v>
@@ -532,16 +532,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2674</v>
+        <v>1989</v>
       </c>
       <c r="D4" t="n">
-        <v>52</v>
+        <v>1827</v>
       </c>
       <c r="E4" t="n">
-        <v>2622</v>
+        <v>162</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.0194</v>
+        <v>0.9186</v>
       </c>
     </row>
     <row r="5">
@@ -556,16 +556,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>350</v>
+        <v>635</v>
       </c>
       <c r="D5" t="n">
-        <v>295</v>
+        <v>632</v>
       </c>
       <c r="E5" t="n">
-        <v>55</v>
+        <v>3</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.8429000000000001</v>
+        <v>0.9953</v>
       </c>
     </row>
     <row r="6">
@@ -580,10 +580,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>10279</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>10279</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -604,16 +604,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3211</v>
+        <v>2437</v>
       </c>
       <c r="D7" t="n">
-        <v>3186</v>
+        <v>2366</v>
       </c>
       <c r="E7" t="n">
-        <v>25</v>
+        <v>71</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.9922</v>
+        <v>0.9709</v>
       </c>
     </row>
     <row r="8">
@@ -650,16 +650,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>29219</v>
+        <v>38324</v>
       </c>
       <c r="D9" t="n">
-        <v>25653</v>
+        <v>32995</v>
       </c>
       <c r="E9" t="n">
-        <v>3566</v>
+        <v>5329</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0.878</v>
+        <v>0.8609</v>
       </c>
     </row>
     <row r="10">
@@ -696,10 +696,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>43538</v>
+        <v>77085</v>
       </c>
       <c r="D11" t="n">
-        <v>43538</v>
+        <v>77085</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -720,16 +720,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2666</v>
+        <v>2551</v>
       </c>
       <c r="D12" t="n">
-        <v>2666</v>
+        <v>1802</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>749</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>1</v>
+        <v>0.7064</v>
       </c>
     </row>
     <row r="13">
@@ -744,15 +744,17 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>3742</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>3742</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
-      <c r="F13" s="2" t="n"/>
+      <c r="F13" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -766,16 +768,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>3143</v>
+        <v>5348</v>
       </c>
       <c r="D14" t="n">
-        <v>3119</v>
+        <v>5045</v>
       </c>
       <c r="E14" t="n">
-        <v>24</v>
+        <v>303</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0.9923999999999999</v>
+        <v>0.9433</v>
       </c>
     </row>
     <row r="15">
@@ -790,16 +792,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>356</v>
+        <v>743</v>
       </c>
       <c r="D15" t="n">
-        <v>351</v>
+        <v>718</v>
       </c>
       <c r="E15" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>0.986</v>
+        <v>0.9664</v>
       </c>
     </row>
     <row r="16">
@@ -814,16 +816,16 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>751</v>
+        <v>412</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>332</v>
       </c>
       <c r="E16" t="n">
-        <v>751</v>
+        <v>80</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>0</v>
+        <v>0.8058</v>
       </c>
     </row>
     <row r="17">
@@ -838,10 +840,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1338</v>
+        <v>3051</v>
       </c>
       <c r="D17" t="n">
-        <v>1338</v>
+        <v>3051</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -906,16 +908,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>8627</v>
+        <v>8740</v>
       </c>
       <c r="D20" t="n">
-        <v>6814</v>
+        <v>7266</v>
       </c>
       <c r="E20" t="n">
-        <v>1813</v>
+        <v>1474</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>0.7898000000000001</v>
+        <v>0.8314</v>
       </c>
     </row>
     <row r="21">
@@ -952,16 +954,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>10569</v>
+        <v>5804</v>
       </c>
       <c r="D22" t="n">
-        <v>7402</v>
+        <v>5713</v>
       </c>
       <c r="E22" t="n">
-        <v>3167</v>
+        <v>91</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>0.7004</v>
+        <v>0.9843000000000001</v>
       </c>
     </row>
     <row r="23">
@@ -976,16 +978,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>70666</v>
+        <v>53995</v>
       </c>
       <c r="D23" t="n">
-        <v>54232</v>
+        <v>40268</v>
       </c>
       <c r="E23" t="n">
-        <v>16434</v>
+        <v>13727</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>0.7674</v>
+        <v>0.7458</v>
       </c>
     </row>
     <row r="24">
@@ -1022,16 +1024,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>76725</v>
+        <v>67498</v>
       </c>
       <c r="D25" t="n">
-        <v>61590</v>
+        <v>64909</v>
       </c>
       <c r="E25" t="n">
-        <v>15135</v>
+        <v>2589</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>0.8027</v>
+        <v>0.9616</v>
       </c>
     </row>
     <row r="26">
@@ -1046,15 +1048,17 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
       </c>
-      <c r="F26" s="2" t="n"/>
+      <c r="F26" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1068,16 +1072,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>973</v>
+        <v>18635</v>
       </c>
       <c r="D27" t="n">
-        <v>962</v>
+        <v>15199</v>
       </c>
       <c r="E27" t="n">
-        <v>11</v>
+        <v>3436</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>0.9887</v>
+        <v>0.8156</v>
       </c>
     </row>
     <row r="28">
@@ -1092,15 +1096,17 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
-      </c>
-      <c r="F28" s="2" t="n"/>
+        <v>42</v>
+      </c>
+      <c r="F28" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1114,16 +1120,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>3503</v>
+        <v>30103</v>
       </c>
       <c r="D29" t="n">
-        <v>435</v>
+        <v>19943</v>
       </c>
       <c r="E29" t="n">
-        <v>3068</v>
+        <v>10160</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>0.1242</v>
+        <v>0.6625</v>
       </c>
     </row>
     <row r="30">
@@ -1138,17 +1144,15 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>191</v>
+        <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>187</v>
+        <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>4</v>
-      </c>
-      <c r="F30" s="2" t="n">
-        <v>0.9791</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F30" s="2" t="n"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1184,16 +1188,16 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>22545</v>
+        <v>15406</v>
       </c>
       <c r="D32" t="n">
-        <v>21880</v>
+        <v>14939</v>
       </c>
       <c r="E32" t="n">
-        <v>665</v>
+        <v>467</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>0.9704999999999999</v>
+        <v>0.9697</v>
       </c>
     </row>
     <row r="33">
@@ -1208,16 +1212,16 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>18237</v>
+        <v>8191</v>
       </c>
       <c r="D33" t="n">
-        <v>3297</v>
+        <v>2360</v>
       </c>
       <c r="E33" t="n">
-        <v>14940</v>
+        <v>5831</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>0.1808</v>
+        <v>0.2881</v>
       </c>
     </row>
     <row r="34">

--- a/output/TRANSFERENCIA_atual.xlsx
+++ b/output/TRANSFERENCIA_atual.xlsx
@@ -484,13 +484,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5452</v>
+        <v>6015</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>5452</v>
+        <v>6015</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>0</v>
@@ -508,16 +508,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2306</v>
+        <v>5044</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>3011</v>
       </c>
       <c r="E3" t="n">
-        <v>2306</v>
+        <v>2033</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0</v>
+        <v>0.5969</v>
       </c>
     </row>
     <row r="4">
@@ -532,16 +532,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1989</v>
+        <v>1745</v>
       </c>
       <c r="D4" t="n">
-        <v>1827</v>
+        <v>1304</v>
       </c>
       <c r="E4" t="n">
-        <v>162</v>
+        <v>441</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.9186</v>
+        <v>0.7473000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -556,16 +556,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>635</v>
+        <v>656</v>
       </c>
       <c r="D5" t="n">
-        <v>632</v>
+        <v>638</v>
       </c>
       <c r="E5" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.9953</v>
+        <v>0.9726</v>
       </c>
     </row>
     <row r="6">
@@ -580,10 +580,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>10279</v>
+        <v>21581</v>
       </c>
       <c r="D6" t="n">
-        <v>10279</v>
+        <v>21581</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -604,16 +604,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2437</v>
+        <v>10599</v>
       </c>
       <c r="D7" t="n">
-        <v>2366</v>
+        <v>9342</v>
       </c>
       <c r="E7" t="n">
-        <v>71</v>
+        <v>1257</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.9709</v>
+        <v>0.8814</v>
       </c>
     </row>
     <row r="8">
@@ -650,16 +650,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>38324</v>
+        <v>21812</v>
       </c>
       <c r="D9" t="n">
-        <v>32995</v>
+        <v>20723</v>
       </c>
       <c r="E9" t="n">
-        <v>5329</v>
+        <v>1089</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0.8609</v>
+        <v>0.9501000000000001</v>
       </c>
     </row>
     <row r="10">
@@ -696,10 +696,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>77085</v>
+        <v>75506</v>
       </c>
       <c r="D11" t="n">
-        <v>77085</v>
+        <v>75506</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -720,16 +720,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2551</v>
+        <v>1728</v>
       </c>
       <c r="D12" t="n">
-        <v>1802</v>
+        <v>1706</v>
       </c>
       <c r="E12" t="n">
-        <v>749</v>
+        <v>22</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>0.7064</v>
+        <v>0.9873000000000001</v>
       </c>
     </row>
     <row r="13">
@@ -744,10 +744,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3742</v>
+        <v>6524</v>
       </c>
       <c r="D13" t="n">
-        <v>3742</v>
+        <v>6524</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -768,16 +768,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>5348</v>
+        <v>5068</v>
       </c>
       <c r="D14" t="n">
-        <v>5045</v>
+        <v>4877</v>
       </c>
       <c r="E14" t="n">
-        <v>303</v>
+        <v>191</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0.9433</v>
+        <v>0.9623</v>
       </c>
     </row>
     <row r="15">
@@ -792,16 +792,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>743</v>
+        <v>1061</v>
       </c>
       <c r="D15" t="n">
-        <v>718</v>
+        <v>1051</v>
       </c>
       <c r="E15" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>0.9664</v>
+        <v>0.9906</v>
       </c>
     </row>
     <row r="16">
@@ -816,16 +816,16 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>412</v>
+        <v>1140</v>
       </c>
       <c r="D16" t="n">
-        <v>332</v>
+        <v>962</v>
       </c>
       <c r="E16" t="n">
-        <v>80</v>
+        <v>178</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>0.8058</v>
+        <v>0.8439</v>
       </c>
     </row>
     <row r="17">
@@ -840,10 +840,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>3051</v>
+        <v>14044</v>
       </c>
       <c r="D17" t="n">
-        <v>3051</v>
+        <v>14044</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -908,16 +908,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>8740</v>
+        <v>7354</v>
       </c>
       <c r="D20" t="n">
-        <v>7266</v>
+        <v>6160</v>
       </c>
       <c r="E20" t="n">
-        <v>1474</v>
+        <v>1194</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>0.8314</v>
+        <v>0.8376</v>
       </c>
     </row>
     <row r="21">
@@ -954,16 +954,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>5804</v>
+        <v>3775</v>
       </c>
       <c r="D22" t="n">
-        <v>5713</v>
+        <v>3709</v>
       </c>
       <c r="E22" t="n">
-        <v>91</v>
+        <v>66</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>0.9843000000000001</v>
+        <v>0.9825</v>
       </c>
     </row>
     <row r="23">
@@ -978,16 +978,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>53995</v>
+        <v>39114</v>
       </c>
       <c r="D23" t="n">
-        <v>40268</v>
+        <v>33074</v>
       </c>
       <c r="E23" t="n">
-        <v>13727</v>
+        <v>6040</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>0.7458</v>
+        <v>0.8456</v>
       </c>
     </row>
     <row r="24">
@@ -1024,16 +1024,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>67498</v>
+        <v>51823</v>
       </c>
       <c r="D25" t="n">
-        <v>64909</v>
+        <v>50173</v>
       </c>
       <c r="E25" t="n">
-        <v>2589</v>
+        <v>1650</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>0.9616</v>
+        <v>0.9681999999999999</v>
       </c>
     </row>
     <row r="26">
@@ -1048,10 +1048,10 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
@@ -1072,16 +1072,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>18635</v>
+        <v>28492</v>
       </c>
       <c r="D27" t="n">
-        <v>15199</v>
+        <v>24908</v>
       </c>
       <c r="E27" t="n">
-        <v>3436</v>
+        <v>3584</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>0.8156</v>
+        <v>0.8742</v>
       </c>
     </row>
     <row r="28">
@@ -1096,13 +1096,13 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="F28" s="2" t="n">
         <v>0</v>
@@ -1120,16 +1120,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>30103</v>
+        <v>42924</v>
       </c>
       <c r="D29" t="n">
-        <v>19943</v>
+        <v>31957</v>
       </c>
       <c r="E29" t="n">
-        <v>10160</v>
+        <v>10967</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>0.6625</v>
+        <v>0.7445000000000001</v>
       </c>
     </row>
     <row r="30">
@@ -1144,15 +1144,17 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>421</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>414</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
-      </c>
-      <c r="F30" s="2" t="n"/>
+        <v>7</v>
+      </c>
+      <c r="F30" s="2" t="n">
+        <v>0.9834000000000001</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1188,16 +1190,16 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>15406</v>
+        <v>10747</v>
       </c>
       <c r="D32" t="n">
-        <v>14939</v>
+        <v>7436</v>
       </c>
       <c r="E32" t="n">
-        <v>467</v>
+        <v>3311</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>0.9697</v>
+        <v>0.6919</v>
       </c>
     </row>
     <row r="33">
@@ -1212,16 +1214,16 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>8191</v>
+        <v>3939</v>
       </c>
       <c r="D33" t="n">
-        <v>2360</v>
+        <v>3232</v>
       </c>
       <c r="E33" t="n">
-        <v>5831</v>
+        <v>707</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>0.2881</v>
+        <v>0.8205</v>
       </c>
     </row>
     <row r="34">
@@ -1236,15 +1238,17 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="D34" t="n">
         <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>0</v>
-      </c>
-      <c r="F34" s="2" t="n"/>
+        <v>83</v>
+      </c>
+      <c r="F34" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F34"/>

--- a/output/TRANSFERENCIA_atual.xlsx
+++ b/output/TRANSFERENCIA_atual.xlsx
@@ -484,16 +484,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>6015</v>
+        <v>3794</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>3776</v>
       </c>
       <c r="E2" t="n">
-        <v>6015</v>
+        <v>18</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0</v>
+        <v>0.9953</v>
       </c>
     </row>
     <row r="3">
@@ -508,16 +508,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5044</v>
+        <v>2239</v>
       </c>
       <c r="D3" t="n">
-        <v>3011</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>2033</v>
+        <v>2239</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.5969</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -532,16 +532,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1745</v>
+        <v>1256</v>
       </c>
       <c r="D4" t="n">
-        <v>1304</v>
+        <v>976</v>
       </c>
       <c r="E4" t="n">
-        <v>441</v>
+        <v>280</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.7473000000000001</v>
+        <v>0.7770999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -556,16 +556,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>656</v>
+        <v>430</v>
       </c>
       <c r="D5" t="n">
-        <v>638</v>
+        <v>429</v>
       </c>
       <c r="E5" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.9726</v>
+        <v>0.9976999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -580,10 +580,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>21581</v>
+        <v>22446</v>
       </c>
       <c r="D6" t="n">
-        <v>21581</v>
+        <v>22446</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -604,16 +604,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>10599</v>
+        <v>26532</v>
       </c>
       <c r="D7" t="n">
-        <v>9342</v>
+        <v>15200</v>
       </c>
       <c r="E7" t="n">
-        <v>1257</v>
+        <v>11332</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.8814</v>
+        <v>0.5729</v>
       </c>
     </row>
     <row r="8">
@@ -650,16 +650,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>21812</v>
+        <v>18669</v>
       </c>
       <c r="D9" t="n">
-        <v>20723</v>
+        <v>16967</v>
       </c>
       <c r="E9" t="n">
-        <v>1089</v>
+        <v>1702</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0.9501000000000001</v>
+        <v>0.9087999999999999</v>
       </c>
     </row>
     <row r="10">
@@ -696,10 +696,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>75506</v>
+        <v>100302</v>
       </c>
       <c r="D11" t="n">
-        <v>75506</v>
+        <v>100302</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -720,16 +720,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1728</v>
+        <v>514</v>
       </c>
       <c r="D12" t="n">
-        <v>1706</v>
+        <v>512</v>
       </c>
       <c r="E12" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>0.9873000000000001</v>
+        <v>0.9961</v>
       </c>
     </row>
     <row r="13">
@@ -744,10 +744,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>6524</v>
+        <v>4617</v>
       </c>
       <c r="D13" t="n">
-        <v>6524</v>
+        <v>4617</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -768,16 +768,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>5068</v>
+        <v>4935</v>
       </c>
       <c r="D14" t="n">
-        <v>4877</v>
+        <v>4929</v>
       </c>
       <c r="E14" t="n">
-        <v>191</v>
+        <v>6</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0.9623</v>
+        <v>0.9987999999999999</v>
       </c>
     </row>
     <row r="15">
@@ -792,16 +792,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1061</v>
+        <v>1225</v>
       </c>
       <c r="D15" t="n">
-        <v>1051</v>
+        <v>1225</v>
       </c>
       <c r="E15" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>0.9906</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -816,16 +816,16 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1140</v>
+        <v>1037</v>
       </c>
       <c r="D16" t="n">
-        <v>962</v>
+        <v>876</v>
       </c>
       <c r="E16" t="n">
-        <v>178</v>
+        <v>161</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>0.8439</v>
+        <v>0.8447</v>
       </c>
     </row>
     <row r="17">
@@ -840,10 +840,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>14044</v>
+        <v>16735</v>
       </c>
       <c r="D17" t="n">
-        <v>14044</v>
+        <v>16735</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -908,16 +908,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>7354</v>
+        <v>7891</v>
       </c>
       <c r="D20" t="n">
-        <v>6160</v>
+        <v>6789</v>
       </c>
       <c r="E20" t="n">
-        <v>1194</v>
+        <v>1102</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>0.8376</v>
+        <v>0.8603000000000001</v>
       </c>
     </row>
     <row r="21">
@@ -954,16 +954,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>3775</v>
+        <v>3776</v>
       </c>
       <c r="D22" t="n">
-        <v>3709</v>
+        <v>4</v>
       </c>
       <c r="E22" t="n">
-        <v>66</v>
+        <v>3772</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>0.9825</v>
+        <v>0.0011</v>
       </c>
     </row>
     <row r="23">
@@ -978,16 +978,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>39114</v>
+        <v>32853</v>
       </c>
       <c r="D23" t="n">
-        <v>33074</v>
+        <v>30348</v>
       </c>
       <c r="E23" t="n">
-        <v>6040</v>
+        <v>2505</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>0.8456</v>
+        <v>0.9238</v>
       </c>
     </row>
     <row r="24">
@@ -1024,16 +1024,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>51823</v>
+        <v>54643</v>
       </c>
       <c r="D25" t="n">
-        <v>50173</v>
+        <v>52641</v>
       </c>
       <c r="E25" t="n">
-        <v>1650</v>
+        <v>2002</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>0.9681999999999999</v>
+        <v>0.9634</v>
       </c>
     </row>
     <row r="26">
@@ -1048,10 +1048,10 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
@@ -1072,16 +1072,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>28492</v>
+        <v>18247</v>
       </c>
       <c r="D27" t="n">
-        <v>24908</v>
+        <v>17994</v>
       </c>
       <c r="E27" t="n">
-        <v>3584</v>
+        <v>253</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>0.8742</v>
+        <v>0.9861</v>
       </c>
     </row>
     <row r="28">
@@ -1096,13 +1096,13 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>53</v>
+        <v>11</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>53</v>
+        <v>11</v>
       </c>
       <c r="F28" s="2" t="n">
         <v>0</v>
@@ -1120,16 +1120,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>42924</v>
+        <v>32464</v>
       </c>
       <c r="D29" t="n">
-        <v>31957</v>
+        <v>23363</v>
       </c>
       <c r="E29" t="n">
-        <v>10967</v>
+        <v>9101</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>0.7445000000000001</v>
+        <v>0.7197</v>
       </c>
     </row>
     <row r="30">
@@ -1144,16 +1144,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>421</v>
+        <v>659</v>
       </c>
       <c r="D30" t="n">
-        <v>414</v>
+        <v>650</v>
       </c>
       <c r="E30" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>0.9834000000000001</v>
+        <v>0.9863</v>
       </c>
     </row>
     <row r="31">
@@ -1190,16 +1190,16 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>10747</v>
+        <v>12345</v>
       </c>
       <c r="D32" t="n">
-        <v>7436</v>
+        <v>11892</v>
       </c>
       <c r="E32" t="n">
-        <v>3311</v>
+        <v>453</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>0.6919</v>
+        <v>0.9632999999999999</v>
       </c>
     </row>
     <row r="33">
@@ -1214,16 +1214,16 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>3939</v>
+        <v>4367</v>
       </c>
       <c r="D33" t="n">
-        <v>3232</v>
+        <v>867</v>
       </c>
       <c r="E33" t="n">
-        <v>707</v>
+        <v>3500</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>0.8205</v>
+        <v>0.1985</v>
       </c>
     </row>
     <row r="34">

--- a/output/TRANSFERENCIA_atual.xlsx
+++ b/output/TRANSFERENCIA_atual.xlsx
@@ -484,16 +484,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3794</v>
+        <v>3898</v>
       </c>
       <c r="D2" t="n">
-        <v>3776</v>
+        <v>3862</v>
       </c>
       <c r="E2" t="n">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.9953</v>
+        <v>0.9908</v>
       </c>
     </row>
     <row r="3">
@@ -508,16 +508,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2239</v>
+        <v>3414</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>2802</v>
       </c>
       <c r="E3" t="n">
-        <v>2239</v>
+        <v>612</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0</v>
+        <v>0.8207</v>
       </c>
     </row>
     <row r="4">
@@ -532,17 +532,15 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1256</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>976</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>280</v>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>0.7770999999999999</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -556,17 +554,15 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>430</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>429</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F5" s="2" t="n">
-        <v>0.9976999999999999</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F5" s="2" t="n"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -580,16 +576,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>22446</v>
+        <v>21174</v>
       </c>
       <c r="D6" t="n">
-        <v>22446</v>
+        <v>21170</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>1</v>
+        <v>0.9998</v>
       </c>
     </row>
     <row r="7">
@@ -604,16 +600,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>26532</v>
+        <v>50488</v>
       </c>
       <c r="D7" t="n">
-        <v>15200</v>
+        <v>25901</v>
       </c>
       <c r="E7" t="n">
-        <v>11332</v>
+        <v>24587</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.5729</v>
+        <v>0.513</v>
       </c>
     </row>
     <row r="8">
@@ -650,16 +646,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>18669</v>
+        <v>12782</v>
       </c>
       <c r="D9" t="n">
-        <v>16967</v>
+        <v>11598</v>
       </c>
       <c r="E9" t="n">
-        <v>1702</v>
+        <v>1184</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0.9087999999999999</v>
+        <v>0.9074</v>
       </c>
     </row>
     <row r="10">
@@ -696,10 +692,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>100302</v>
+        <v>143340</v>
       </c>
       <c r="D11" t="n">
-        <v>100302</v>
+        <v>143340</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -720,16 +716,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>514</v>
+        <v>444</v>
       </c>
       <c r="D12" t="n">
-        <v>512</v>
+        <v>415</v>
       </c>
       <c r="E12" t="n">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>0.9961</v>
+        <v>0.9347</v>
       </c>
     </row>
     <row r="13">
@@ -744,10 +740,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>4617</v>
+        <v>3813</v>
       </c>
       <c r="D13" t="n">
-        <v>4617</v>
+        <v>3813</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -768,16 +764,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>4935</v>
+        <v>2912</v>
       </c>
       <c r="D14" t="n">
-        <v>4929</v>
+        <v>2841</v>
       </c>
       <c r="E14" t="n">
-        <v>6</v>
+        <v>71</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0.9987999999999999</v>
+        <v>0.9756</v>
       </c>
     </row>
     <row r="15">
@@ -792,17 +788,15 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1225</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>1225</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
       </c>
-      <c r="F15" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="F15" s="2" t="n"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -816,17 +810,15 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1037</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>876</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>161</v>
-      </c>
-      <c r="F16" s="2" t="n">
-        <v>0.8447</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F16" s="2" t="n"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -840,10 +832,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>16735</v>
+        <v>13362</v>
       </c>
       <c r="D17" t="n">
-        <v>16735</v>
+        <v>13362</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -908,16 +900,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>7891</v>
+        <v>6487</v>
       </c>
       <c r="D20" t="n">
-        <v>6789</v>
+        <v>5930</v>
       </c>
       <c r="E20" t="n">
-        <v>1102</v>
+        <v>557</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>0.8603000000000001</v>
+        <v>0.9140999999999999</v>
       </c>
     </row>
     <row r="21">
@@ -954,16 +946,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>3776</v>
+        <v>1736</v>
       </c>
       <c r="D22" t="n">
-        <v>4</v>
+        <v>1701</v>
       </c>
       <c r="E22" t="n">
-        <v>3772</v>
+        <v>35</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>0.0011</v>
+        <v>0.9798</v>
       </c>
     </row>
     <row r="23">
@@ -978,16 +970,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>32853</v>
+        <v>13125</v>
       </c>
       <c r="D23" t="n">
-        <v>30348</v>
+        <v>12881</v>
       </c>
       <c r="E23" t="n">
-        <v>2505</v>
+        <v>244</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>0.9238</v>
+        <v>0.9814000000000001</v>
       </c>
     </row>
     <row r="24">
@@ -1024,16 +1016,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>54643</v>
+        <v>28166</v>
       </c>
       <c r="D25" t="n">
-        <v>52641</v>
+        <v>28047</v>
       </c>
       <c r="E25" t="n">
-        <v>2002</v>
+        <v>119</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>0.9634</v>
+        <v>0.9958</v>
       </c>
     </row>
     <row r="26">
@@ -1072,16 +1064,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>18247</v>
+        <v>13167</v>
       </c>
       <c r="D27" t="n">
-        <v>17994</v>
+        <v>12996</v>
       </c>
       <c r="E27" t="n">
-        <v>253</v>
+        <v>171</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>0.9861</v>
+        <v>0.987</v>
       </c>
     </row>
     <row r="28">
@@ -1096,13 +1088,13 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="F28" s="2" t="n">
         <v>0</v>
@@ -1120,16 +1112,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>32464</v>
+        <v>32744</v>
       </c>
       <c r="D29" t="n">
-        <v>23363</v>
+        <v>21654</v>
       </c>
       <c r="E29" t="n">
-        <v>9101</v>
+        <v>11090</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>0.7197</v>
+        <v>0.6613</v>
       </c>
     </row>
     <row r="30">
@@ -1144,16 +1136,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>659</v>
+        <v>441</v>
       </c>
       <c r="D30" t="n">
-        <v>650</v>
+        <v>438</v>
       </c>
       <c r="E30" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>0.9863</v>
+        <v>0.9932</v>
       </c>
     </row>
     <row r="31">
@@ -1190,16 +1182,16 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>12345</v>
+        <v>6236</v>
       </c>
       <c r="D32" t="n">
-        <v>11892</v>
+        <v>6227</v>
       </c>
       <c r="E32" t="n">
-        <v>453</v>
+        <v>9</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>0.9632999999999999</v>
+        <v>0.9986</v>
       </c>
     </row>
     <row r="33">
@@ -1214,16 +1206,16 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>4367</v>
+        <v>1638</v>
       </c>
       <c r="D33" t="n">
-        <v>867</v>
+        <v>1513</v>
       </c>
       <c r="E33" t="n">
-        <v>3500</v>
+        <v>125</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>0.1985</v>
+        <v>0.9237000000000001</v>
       </c>
     </row>
     <row r="34">
@@ -1238,17 +1230,15 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="D34" t="n">
         <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>83</v>
-      </c>
-      <c r="F34" s="2" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F34" s="2" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:F34"/>

--- a/output/TRANSFERENCIA_atual.xlsx
+++ b/output/TRANSFERENCIA_atual.xlsx
@@ -484,17 +484,15 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3898</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>3862</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>36</v>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>0.9908</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -508,17 +506,15 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>3414</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>2802</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>612</v>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>0.8207</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -576,16 +572,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>21174</v>
+        <v>10034</v>
       </c>
       <c r="D6" t="n">
-        <v>21170</v>
+        <v>10030</v>
       </c>
       <c r="E6" t="n">
         <v>4</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.9998</v>
+        <v>0.9995999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -600,16 +596,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>50488</v>
+        <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>25901</v>
+        <v>2</v>
       </c>
       <c r="E7" t="n">
-        <v>24587</v>
+        <v>0</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.513</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -646,17 +642,15 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>12782</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>11598</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>1184</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>0.9074</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F9" s="2" t="n"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -692,10 +686,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>143340</v>
+        <v>175234</v>
       </c>
       <c r="D11" t="n">
-        <v>143340</v>
+        <v>175234</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -716,16 +710,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>444</v>
+        <v>61</v>
       </c>
       <c r="D12" t="n">
-        <v>415</v>
+        <v>61</v>
       </c>
       <c r="E12" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>0.9347</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -740,10 +734,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3813</v>
+        <v>1978</v>
       </c>
       <c r="D13" t="n">
-        <v>3813</v>
+        <v>1978</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -764,17 +758,15 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2912</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>2841</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>71</v>
-      </c>
-      <c r="F14" s="2" t="n">
-        <v>0.9756</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F14" s="2" t="n"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -832,10 +824,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>13362</v>
+        <v>12939</v>
       </c>
       <c r="D17" t="n">
-        <v>13362</v>
+        <v>12939</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -900,16 +892,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>6487</v>
+        <v>3389</v>
       </c>
       <c r="D20" t="n">
-        <v>5930</v>
+        <v>3389</v>
       </c>
       <c r="E20" t="n">
-        <v>557</v>
+        <v>0</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>0.9140999999999999</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -946,16 +938,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1736</v>
+        <v>2</v>
       </c>
       <c r="D22" t="n">
-        <v>1701</v>
+        <v>2</v>
       </c>
       <c r="E22" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>0.9798</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -970,16 +962,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>13125</v>
+        <v>56</v>
       </c>
       <c r="D23" t="n">
-        <v>12881</v>
+        <v>56</v>
       </c>
       <c r="E23" t="n">
-        <v>244</v>
+        <v>0</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>0.9814000000000001</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1016,16 +1008,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>28166</v>
+        <v>15132</v>
       </c>
       <c r="D25" t="n">
-        <v>28047</v>
+        <v>15131</v>
       </c>
       <c r="E25" t="n">
-        <v>119</v>
+        <v>1</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>0.9958</v>
+        <v>0.9998999999999999</v>
       </c>
     </row>
     <row r="26">
@@ -1064,16 +1056,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>13167</v>
+        <v>9354</v>
       </c>
       <c r="D27" t="n">
-        <v>12996</v>
+        <v>9247</v>
       </c>
       <c r="E27" t="n">
-        <v>171</v>
+        <v>107</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>0.987</v>
+        <v>0.9886</v>
       </c>
     </row>
     <row r="28">
@@ -1112,16 +1104,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>32744</v>
+        <v>16373</v>
       </c>
       <c r="D29" t="n">
-        <v>21654</v>
+        <v>11358</v>
       </c>
       <c r="E29" t="n">
-        <v>11090</v>
+        <v>5015</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>0.6613</v>
+        <v>0.6937000000000001</v>
       </c>
     </row>
     <row r="30">
@@ -1136,16 +1128,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>441</v>
+        <v>364</v>
       </c>
       <c r="D30" t="n">
-        <v>438</v>
+        <v>363</v>
       </c>
       <c r="E30" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>0.9932</v>
+        <v>0.9973000000000001</v>
       </c>
     </row>
     <row r="31">
@@ -1182,17 +1174,15 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>6236</v>
+        <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>6227</v>
+        <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>9</v>
-      </c>
-      <c r="F32" s="2" t="n">
-        <v>0.9986</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F32" s="2" t="n"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1206,17 +1196,15 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1638</v>
+        <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>1513</v>
+        <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>125</v>
-      </c>
-      <c r="F33" s="2" t="n">
-        <v>0.9237000000000001</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F33" s="2" t="n"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">

--- a/output/TRANSFERENCIA_atual.xlsx
+++ b/output/TRANSFERENCIA_atual.xlsx
@@ -484,15 +484,17 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>2661</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>2632</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" s="2" t="n"/>
+        <v>29</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>0.9891</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -506,15 +508,17 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>4580</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>2476</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" s="2" t="n"/>
+        <v>2104</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>0.5406</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -528,15 +532,17 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>3133</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>2234</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" s="2" t="n"/>
+        <v>899</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>0.7131000000000001</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -550,15 +556,17 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>438</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>435</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="2" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>0.9932</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -572,16 +580,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>10034</v>
+        <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>10030</v>
+        <v>3</v>
       </c>
       <c r="E6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.9995999999999999</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -596,10 +604,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -642,15 +650,17 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>13260</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>10889</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="2" t="n"/>
+        <v>2371</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>0.8212</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -686,10 +696,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>175234</v>
+        <v>90237</v>
       </c>
       <c r="D11" t="n">
-        <v>175234</v>
+        <v>90237</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -710,16 +720,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>61</v>
+        <v>2968</v>
       </c>
       <c r="D12" t="n">
-        <v>61</v>
+        <v>2567</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>401</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>1</v>
+        <v>0.8649</v>
       </c>
     </row>
     <row r="13">
@@ -734,17 +744,15 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1978</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>1978</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
-      <c r="F13" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="F13" s="2" t="n"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -758,15 +766,17 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>4777</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>4764</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" s="2" t="n"/>
+        <v>13</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>0.9973000000000001</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -780,15 +790,17 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>428</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>418</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" s="2" t="n"/>
+        <v>10</v>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>0.9765999999999999</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -802,15 +814,17 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>1410</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>1124</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" s="2" t="n"/>
+        <v>286</v>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>0.7972</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -824,10 +838,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>12939</v>
+        <v>5422</v>
       </c>
       <c r="D17" t="n">
-        <v>12939</v>
+        <v>5422</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -870,15 +884,17 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>921</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>921</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
       </c>
-      <c r="F19" s="2" t="n"/>
+      <c r="F19" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -892,16 +908,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>3389</v>
+        <v>9773</v>
       </c>
       <c r="D20" t="n">
-        <v>3389</v>
+        <v>8541</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>1232</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>1</v>
+        <v>0.8739</v>
       </c>
     </row>
     <row r="21">
@@ -938,16 +954,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>2</v>
+        <v>5741</v>
       </c>
       <c r="D22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>5738</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>1</v>
+        <v>0.0005</v>
       </c>
     </row>
     <row r="23">
@@ -962,16 +978,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>56</v>
+        <v>58218</v>
       </c>
       <c r="D23" t="n">
-        <v>56</v>
+        <v>40949</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>17269</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>1</v>
+        <v>0.7034</v>
       </c>
     </row>
     <row r="24">
@@ -1008,16 +1024,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>15132</v>
+        <v>89312</v>
       </c>
       <c r="D25" t="n">
-        <v>15131</v>
+        <v>87573</v>
       </c>
       <c r="E25" t="n">
-        <v>1</v>
+        <v>1739</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>0.9998999999999999</v>
+        <v>0.9804999999999999</v>
       </c>
     </row>
     <row r="26">
@@ -1032,17 +1048,15 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
       </c>
-      <c r="F26" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="F26" s="2" t="n"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1056,16 +1070,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>9354</v>
+        <v>3604</v>
       </c>
       <c r="D27" t="n">
-        <v>9247</v>
+        <v>3574</v>
       </c>
       <c r="E27" t="n">
-        <v>107</v>
+        <v>30</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>0.9886</v>
+        <v>0.9917</v>
       </c>
     </row>
     <row r="28">
@@ -1080,17 +1094,15 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>2</v>
-      </c>
-      <c r="F28" s="2" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F28" s="2" t="n"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1104,16 +1116,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>16373</v>
+        <v>1108</v>
       </c>
       <c r="D29" t="n">
-        <v>11358</v>
+        <v>853</v>
       </c>
       <c r="E29" t="n">
-        <v>5015</v>
+        <v>255</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>0.6937000000000001</v>
+        <v>0.7698999999999999</v>
       </c>
     </row>
     <row r="30">
@@ -1128,16 +1140,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>364</v>
+        <v>237</v>
       </c>
       <c r="D30" t="n">
-        <v>363</v>
+        <v>237</v>
       </c>
       <c r="E30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="F30" s="2" t="n">
-        <v>0.9973000000000001</v>
       </c>
     </row>
     <row r="31">
@@ -1174,15 +1186,17 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0</v>
+        <v>15078</v>
       </c>
       <c r="D32" t="n">
-        <v>0</v>
+        <v>14911</v>
       </c>
       <c r="E32" t="n">
-        <v>0</v>
-      </c>
-      <c r="F32" s="2" t="n"/>
+        <v>167</v>
+      </c>
+      <c r="F32" s="2" t="n">
+        <v>0.9889</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1196,15 +1210,17 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0</v>
+        <v>6311</v>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>1309</v>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
-      </c>
-      <c r="F33" s="2" t="n"/>
+        <v>5002</v>
+      </c>
+      <c r="F33" s="2" t="n">
+        <v>0.2074</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">

--- a/output/TRANSFERENCIA_atual.xlsx
+++ b/output/TRANSFERENCIA_atual.xlsx
@@ -484,16 +484,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2661</v>
+        <v>3052</v>
       </c>
       <c r="D2" t="n">
-        <v>2632</v>
+        <v>3022</v>
       </c>
       <c r="E2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.9891</v>
+        <v>0.9902</v>
       </c>
     </row>
     <row r="3">
@@ -508,16 +508,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>4580</v>
+        <v>2679</v>
       </c>
       <c r="D3" t="n">
-        <v>2476</v>
+        <v>2642</v>
       </c>
       <c r="E3" t="n">
-        <v>2104</v>
+        <v>37</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.5406</v>
+        <v>0.9862000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -532,16 +532,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3133</v>
+        <v>1020</v>
       </c>
       <c r="D4" t="n">
-        <v>2234</v>
+        <v>780</v>
       </c>
       <c r="E4" t="n">
-        <v>899</v>
+        <v>240</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.7131000000000001</v>
+        <v>0.7646999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -556,16 +556,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>438</v>
+        <v>727</v>
       </c>
       <c r="D5" t="n">
-        <v>435</v>
+        <v>727</v>
       </c>
       <c r="E5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.9932</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -580,10 +580,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>10505</v>
       </c>
       <c r="D6" t="n">
-        <v>3</v>
+        <v>10505</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -604,16 +604,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>3351</v>
       </c>
       <c r="D7" t="n">
-        <v>3</v>
+        <v>2639</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>712</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>1</v>
+        <v>0.7875</v>
       </c>
     </row>
     <row r="8">
@@ -628,15 +628,17 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>10892</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>906</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="2" t="n"/>
+        <v>9986</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>0.0832</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -650,16 +652,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>13260</v>
+        <v>42055</v>
       </c>
       <c r="D9" t="n">
-        <v>10889</v>
+        <v>38607</v>
       </c>
       <c r="E9" t="n">
-        <v>2371</v>
+        <v>3448</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0.8212</v>
+        <v>0.9179999999999999</v>
       </c>
     </row>
     <row r="10">
@@ -696,10 +698,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>90237</v>
+        <v>98222</v>
       </c>
       <c r="D11" t="n">
-        <v>90237</v>
+        <v>98222</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -720,16 +722,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2968</v>
+        <v>1397</v>
       </c>
       <c r="D12" t="n">
-        <v>2567</v>
+        <v>1382</v>
       </c>
       <c r="E12" t="n">
-        <v>401</v>
+        <v>15</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>0.8649</v>
+        <v>0.9893000000000001</v>
       </c>
     </row>
     <row r="13">
@@ -744,15 +746,17 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>3462</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>3462</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
-      <c r="F13" s="2" t="n"/>
+      <c r="F13" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -766,13 +770,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>4777</v>
+        <v>3734</v>
       </c>
       <c r="D14" t="n">
-        <v>4764</v>
+        <v>3724</v>
       </c>
       <c r="E14" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F14" s="2" t="n">
         <v>0.9973000000000001</v>
@@ -790,16 +794,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>428</v>
+        <v>1316</v>
       </c>
       <c r="D15" t="n">
-        <v>418</v>
+        <v>1314</v>
       </c>
       <c r="E15" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>0.9765999999999999</v>
+        <v>0.9984999999999999</v>
       </c>
     </row>
     <row r="16">
@@ -814,16 +818,16 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1410</v>
+        <v>877</v>
       </c>
       <c r="D16" t="n">
-        <v>1124</v>
+        <v>595</v>
       </c>
       <c r="E16" t="n">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>0.7972</v>
+        <v>0.6784</v>
       </c>
     </row>
     <row r="17">
@@ -838,10 +842,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>5422</v>
+        <v>4131</v>
       </c>
       <c r="D17" t="n">
-        <v>5422</v>
+        <v>4131</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -884,16 +888,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>921</v>
+        <v>564</v>
       </c>
       <c r="D19" t="n">
-        <v>921</v>
+        <v>556</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>1</v>
+        <v>0.9858</v>
       </c>
     </row>
     <row r="20">
@@ -908,16 +912,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>9773</v>
+        <v>6520</v>
       </c>
       <c r="D20" t="n">
-        <v>8541</v>
+        <v>5010</v>
       </c>
       <c r="E20" t="n">
-        <v>1232</v>
+        <v>1510</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>0.8739</v>
+        <v>0.7684000000000001</v>
       </c>
     </row>
     <row r="21">
@@ -954,16 +958,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>5741</v>
+        <v>3023</v>
       </c>
       <c r="D22" t="n">
-        <v>3</v>
+        <v>2981</v>
       </c>
       <c r="E22" t="n">
-        <v>5738</v>
+        <v>42</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>0.0005</v>
+        <v>0.9861</v>
       </c>
     </row>
     <row r="23">
@@ -978,16 +982,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>58218</v>
+        <v>39341</v>
       </c>
       <c r="D23" t="n">
-        <v>40949</v>
+        <v>33810</v>
       </c>
       <c r="E23" t="n">
-        <v>17269</v>
+        <v>5531</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>0.7034</v>
+        <v>0.8593999999999999</v>
       </c>
     </row>
     <row r="24">
@@ -1024,16 +1028,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>89312</v>
+        <v>64472</v>
       </c>
       <c r="D25" t="n">
-        <v>87573</v>
+        <v>57368</v>
       </c>
       <c r="E25" t="n">
-        <v>1739</v>
+        <v>7104</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>0.9804999999999999</v>
+        <v>0.8898</v>
       </c>
     </row>
     <row r="26">
@@ -1048,15 +1052,17 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
       </c>
-      <c r="F26" s="2" t="n"/>
+      <c r="F26" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1070,16 +1076,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>3604</v>
+        <v>10491</v>
       </c>
       <c r="D27" t="n">
-        <v>3574</v>
+        <v>10385</v>
       </c>
       <c r="E27" t="n">
-        <v>30</v>
+        <v>106</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>0.9917</v>
+        <v>0.9899</v>
       </c>
     </row>
     <row r="28">
@@ -1094,15 +1100,17 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
-      </c>
-      <c r="F28" s="2" t="n"/>
+        <v>22</v>
+      </c>
+      <c r="F28" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1116,16 +1124,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1108</v>
+        <v>25217</v>
       </c>
       <c r="D29" t="n">
-        <v>853</v>
+        <v>17002</v>
       </c>
       <c r="E29" t="n">
-        <v>255</v>
+        <v>8215</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>0.7698999999999999</v>
+        <v>0.6742</v>
       </c>
     </row>
     <row r="30">
@@ -1140,10 +1148,10 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>237</v>
+        <v>76</v>
       </c>
       <c r="D30" t="n">
-        <v>237</v>
+        <v>76</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
@@ -1186,16 +1194,16 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>15078</v>
+        <v>9803</v>
       </c>
       <c r="D32" t="n">
-        <v>14911</v>
+        <v>9454</v>
       </c>
       <c r="E32" t="n">
-        <v>167</v>
+        <v>349</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>0.9889</v>
+        <v>0.9643999999999999</v>
       </c>
     </row>
     <row r="33">
@@ -1210,16 +1218,16 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>6311</v>
+        <v>7178</v>
       </c>
       <c r="D33" t="n">
-        <v>1309</v>
+        <v>3891</v>
       </c>
       <c r="E33" t="n">
-        <v>5002</v>
+        <v>3287</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>0.2074</v>
+        <v>0.5421</v>
       </c>
     </row>
     <row r="34">

--- a/output/TRANSFERENCIA_atual.xlsx
+++ b/output/TRANSFERENCIA_atual.xlsx
@@ -484,16 +484,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3052</v>
+        <v>2851</v>
       </c>
       <c r="D2" t="n">
-        <v>3022</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>30</v>
+        <v>2851</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.9902</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -508,16 +508,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2679</v>
+        <v>1943</v>
       </c>
       <c r="D3" t="n">
-        <v>2642</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>37</v>
+        <v>1943</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.9862000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -532,16 +532,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1020</v>
+        <v>1638</v>
       </c>
       <c r="D4" t="n">
-        <v>780</v>
+        <v>1393</v>
       </c>
       <c r="E4" t="n">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.7646999999999999</v>
+        <v>0.8504</v>
       </c>
     </row>
     <row r="5">
@@ -556,16 +556,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>727</v>
+        <v>227</v>
       </c>
       <c r="D5" t="n">
-        <v>727</v>
+        <v>226</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>1</v>
+        <v>0.9956</v>
       </c>
     </row>
     <row r="6">
@@ -580,10 +580,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>10505</v>
+        <v>20939</v>
       </c>
       <c r="D6" t="n">
-        <v>10505</v>
+        <v>20939</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -604,16 +604,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3351</v>
+        <v>18612</v>
       </c>
       <c r="D7" t="n">
-        <v>2639</v>
+        <v>17318</v>
       </c>
       <c r="E7" t="n">
-        <v>712</v>
+        <v>1294</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.7875</v>
+        <v>0.9305</v>
       </c>
     </row>
     <row r="8">
@@ -628,16 +628,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>10892</v>
+        <v>10920</v>
       </c>
       <c r="D8" t="n">
-        <v>906</v>
+        <v>9778</v>
       </c>
       <c r="E8" t="n">
-        <v>9986</v>
+        <v>1142</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.0832</v>
+        <v>0.8954000000000001</v>
       </c>
     </row>
     <row r="9">
@@ -652,16 +652,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>42055</v>
+        <v>26738</v>
       </c>
       <c r="D9" t="n">
-        <v>38607</v>
+        <v>23562</v>
       </c>
       <c r="E9" t="n">
-        <v>3448</v>
+        <v>3176</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0.9179999999999999</v>
+        <v>0.8812000000000001</v>
       </c>
     </row>
     <row r="10">
@@ -698,10 +698,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>98222</v>
+        <v>141468</v>
       </c>
       <c r="D11" t="n">
-        <v>98222</v>
+        <v>141468</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -722,16 +722,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1397</v>
+        <v>2086</v>
       </c>
       <c r="D12" t="n">
-        <v>1382</v>
+        <v>2086</v>
       </c>
       <c r="E12" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>0.9893000000000001</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -746,10 +746,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3462</v>
+        <v>5474</v>
       </c>
       <c r="D13" t="n">
-        <v>3462</v>
+        <v>5474</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -770,16 +770,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>3734</v>
+        <v>3354</v>
       </c>
       <c r="D14" t="n">
-        <v>3724</v>
+        <v>3142</v>
       </c>
       <c r="E14" t="n">
-        <v>10</v>
+        <v>212</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0.9973000000000001</v>
+        <v>0.9368000000000001</v>
       </c>
     </row>
     <row r="15">
@@ -794,16 +794,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1316</v>
+        <v>680</v>
       </c>
       <c r="D15" t="n">
-        <v>1314</v>
+        <v>667</v>
       </c>
       <c r="E15" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>0.9984999999999999</v>
+        <v>0.9809</v>
       </c>
     </row>
     <row r="16">
@@ -818,16 +818,16 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>877</v>
+        <v>1702</v>
       </c>
       <c r="D16" t="n">
-        <v>595</v>
+        <v>1336</v>
       </c>
       <c r="E16" t="n">
-        <v>282</v>
+        <v>366</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>0.6784</v>
+        <v>0.785</v>
       </c>
     </row>
     <row r="17">
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>4131</v>
+        <v>8114</v>
       </c>
       <c r="D17" t="n">
-        <v>4131</v>
+        <v>8114</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -888,16 +888,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>564</v>
+        <v>848</v>
       </c>
       <c r="D19" t="n">
-        <v>556</v>
+        <v>835</v>
       </c>
       <c r="E19" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>0.9858</v>
+        <v>0.9847</v>
       </c>
     </row>
     <row r="20">
@@ -912,16 +912,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>6520</v>
+        <v>4725</v>
       </c>
       <c r="D20" t="n">
-        <v>5010</v>
+        <v>3023</v>
       </c>
       <c r="E20" t="n">
-        <v>1510</v>
+        <v>1702</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>0.7684000000000001</v>
+        <v>0.6397999999999999</v>
       </c>
     </row>
     <row r="21">
@@ -958,16 +958,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>3023</v>
+        <v>3936</v>
       </c>
       <c r="D22" t="n">
-        <v>2981</v>
+        <v>3834</v>
       </c>
       <c r="E22" t="n">
-        <v>42</v>
+        <v>102</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>0.9861</v>
+        <v>0.9741</v>
       </c>
     </row>
     <row r="23">
@@ -982,16 +982,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>39341</v>
+        <v>38458</v>
       </c>
       <c r="D23" t="n">
-        <v>33810</v>
+        <v>36946</v>
       </c>
       <c r="E23" t="n">
-        <v>5531</v>
+        <v>1512</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>0.8593999999999999</v>
+        <v>0.9606999999999999</v>
       </c>
     </row>
     <row r="24">
@@ -1028,16 +1028,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>64472</v>
+        <v>45388</v>
       </c>
       <c r="D25" t="n">
-        <v>57368</v>
+        <v>43205</v>
       </c>
       <c r="E25" t="n">
-        <v>7104</v>
+        <v>2183</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>0.8898</v>
+        <v>0.9519</v>
       </c>
     </row>
     <row r="26">
@@ -1076,16 +1076,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>10491</v>
+        <v>16953</v>
       </c>
       <c r="D27" t="n">
-        <v>10385</v>
+        <v>16804</v>
       </c>
       <c r="E27" t="n">
-        <v>106</v>
+        <v>149</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>0.9899</v>
+        <v>0.9912000000000001</v>
       </c>
     </row>
     <row r="28">
@@ -1100,13 +1100,13 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="F28" s="2" t="n">
         <v>0</v>
@@ -1124,16 +1124,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>25217</v>
+        <v>41152</v>
       </c>
       <c r="D29" t="n">
-        <v>17002</v>
+        <v>26619</v>
       </c>
       <c r="E29" t="n">
-        <v>8215</v>
+        <v>14533</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>0.6742</v>
+        <v>0.6468</v>
       </c>
     </row>
     <row r="30">
@@ -1148,16 +1148,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>76</v>
+        <v>252</v>
       </c>
       <c r="D30" t="n">
-        <v>76</v>
+        <v>247</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>1</v>
+        <v>0.9802</v>
       </c>
     </row>
     <row r="31">
@@ -1194,16 +1194,16 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>9803</v>
+        <v>8862</v>
       </c>
       <c r="D32" t="n">
-        <v>9454</v>
+        <v>8763</v>
       </c>
       <c r="E32" t="n">
-        <v>349</v>
+        <v>99</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>0.9643999999999999</v>
+        <v>0.9887999999999999</v>
       </c>
     </row>
     <row r="33">
@@ -1218,16 +1218,16 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>7178</v>
+        <v>5762</v>
       </c>
       <c r="D33" t="n">
-        <v>3891</v>
+        <v>4195</v>
       </c>
       <c r="E33" t="n">
-        <v>3287</v>
+        <v>1567</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>0.5421</v>
+        <v>0.728</v>
       </c>
     </row>
     <row r="34">

--- a/output/TRANSFERENCIA_atual.xlsx
+++ b/output/TRANSFERENCIA_atual.xlsx
@@ -484,16 +484,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2851</v>
+        <v>2882</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E2" t="n">
-        <v>2851</v>
+        <v>2880</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0</v>
+        <v>0.0007000000000000001</v>
       </c>
     </row>
     <row r="3">
@@ -508,16 +508,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1943</v>
+        <v>4004</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>3006</v>
       </c>
       <c r="E3" t="n">
-        <v>1943</v>
+        <v>998</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0</v>
+        <v>0.7506999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -532,16 +532,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1638</v>
+        <v>1288</v>
       </c>
       <c r="D4" t="n">
-        <v>1393</v>
+        <v>1145</v>
       </c>
       <c r="E4" t="n">
-        <v>245</v>
+        <v>143</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.8504</v>
+        <v>0.889</v>
       </c>
     </row>
     <row r="5">
@@ -556,16 +556,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>227</v>
+        <v>255</v>
       </c>
       <c r="D5" t="n">
-        <v>226</v>
+        <v>251</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.9956</v>
+        <v>0.9843000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -580,10 +580,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>20939</v>
+        <v>21492</v>
       </c>
       <c r="D6" t="n">
-        <v>20939</v>
+        <v>21492</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -604,16 +604,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>18612</v>
+        <v>25275</v>
       </c>
       <c r="D7" t="n">
-        <v>17318</v>
+        <v>12082</v>
       </c>
       <c r="E7" t="n">
-        <v>1294</v>
+        <v>13193</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.9305</v>
+        <v>0.478</v>
       </c>
     </row>
     <row r="8">
@@ -628,16 +628,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>10920</v>
+        <v>10114</v>
       </c>
       <c r="D8" t="n">
-        <v>9778</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>1142</v>
+        <v>10114</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.8954000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -652,16 +652,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>26738</v>
+        <v>18206</v>
       </c>
       <c r="D9" t="n">
-        <v>23562</v>
+        <v>15106</v>
       </c>
       <c r="E9" t="n">
-        <v>3176</v>
+        <v>3100</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0.8812000000000001</v>
+        <v>0.8297</v>
       </c>
     </row>
     <row r="10">
@@ -698,10 +698,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>141468</v>
+        <v>115753</v>
       </c>
       <c r="D11" t="n">
-        <v>141468</v>
+        <v>115753</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -722,16 +722,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2086</v>
+        <v>2036</v>
       </c>
       <c r="D12" t="n">
-        <v>2086</v>
+        <v>1634</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>402</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>1</v>
+        <v>0.8026000000000001</v>
       </c>
     </row>
     <row r="13">
@@ -746,10 +746,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>5474</v>
+        <v>4257</v>
       </c>
       <c r="D13" t="n">
-        <v>5474</v>
+        <v>4257</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -770,16 +770,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>3354</v>
+        <v>2875</v>
       </c>
       <c r="D14" t="n">
-        <v>3142</v>
+        <v>2858</v>
       </c>
       <c r="E14" t="n">
-        <v>212</v>
+        <v>17</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0.9368000000000001</v>
+        <v>0.9941</v>
       </c>
     </row>
     <row r="15">
@@ -794,16 +794,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>680</v>
+        <v>386</v>
       </c>
       <c r="D15" t="n">
-        <v>667</v>
+        <v>377</v>
       </c>
       <c r="E15" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>0.9809</v>
+        <v>0.9767</v>
       </c>
     </row>
     <row r="16">
@@ -818,16 +818,16 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1702</v>
+        <v>1116</v>
       </c>
       <c r="D16" t="n">
-        <v>1336</v>
+        <v>903</v>
       </c>
       <c r="E16" t="n">
-        <v>366</v>
+        <v>213</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>0.785</v>
+        <v>0.8090999999999999</v>
       </c>
     </row>
     <row r="17">
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>8114</v>
+        <v>6416</v>
       </c>
       <c r="D17" t="n">
-        <v>8114</v>
+        <v>6416</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -888,16 +888,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>848</v>
+        <v>1236</v>
       </c>
       <c r="D19" t="n">
-        <v>835</v>
+        <v>1225</v>
       </c>
       <c r="E19" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>0.9847</v>
+        <v>0.9911</v>
       </c>
     </row>
     <row r="20">
@@ -912,16 +912,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>4725</v>
+        <v>4259</v>
       </c>
       <c r="D20" t="n">
-        <v>3023</v>
+        <v>3226</v>
       </c>
       <c r="E20" t="n">
-        <v>1702</v>
+        <v>1033</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>0.6397999999999999</v>
+        <v>0.7575</v>
       </c>
     </row>
     <row r="21">
@@ -958,16 +958,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>3936</v>
+        <v>3268</v>
       </c>
       <c r="D22" t="n">
-        <v>3834</v>
+        <v>3122</v>
       </c>
       <c r="E22" t="n">
-        <v>102</v>
+        <v>146</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>0.9741</v>
+        <v>0.9553</v>
       </c>
     </row>
     <row r="23">
@@ -982,16 +982,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>38458</v>
+        <v>32733</v>
       </c>
       <c r="D23" t="n">
-        <v>36946</v>
+        <v>31386</v>
       </c>
       <c r="E23" t="n">
-        <v>1512</v>
+        <v>1347</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>0.9606999999999999</v>
+        <v>0.9588</v>
       </c>
     </row>
     <row r="24">
@@ -1028,16 +1028,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>45388</v>
+        <v>53239</v>
       </c>
       <c r="D25" t="n">
-        <v>43205</v>
+        <v>50296</v>
       </c>
       <c r="E25" t="n">
-        <v>2183</v>
+        <v>2943</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>0.9519</v>
+        <v>0.9447</v>
       </c>
     </row>
     <row r="26">
@@ -1052,17 +1052,15 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
       </c>
-      <c r="F26" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="F26" s="2" t="n"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1076,16 +1074,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>16953</v>
+        <v>12597</v>
       </c>
       <c r="D27" t="n">
-        <v>16804</v>
+        <v>12507</v>
       </c>
       <c r="E27" t="n">
-        <v>149</v>
+        <v>90</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>0.9912000000000001</v>
+        <v>0.9929000000000001</v>
       </c>
     </row>
     <row r="28">
@@ -1100,13 +1098,13 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F28" s="2" t="n">
         <v>0</v>
@@ -1124,16 +1122,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>41152</v>
+        <v>28826</v>
       </c>
       <c r="D29" t="n">
-        <v>26619</v>
+        <v>19712</v>
       </c>
       <c r="E29" t="n">
-        <v>14533</v>
+        <v>9114</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>0.6468</v>
+        <v>0.6838</v>
       </c>
     </row>
     <row r="30">
@@ -1148,16 +1146,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>252</v>
+        <v>1012</v>
       </c>
       <c r="D30" t="n">
-        <v>247</v>
+        <v>1007</v>
       </c>
       <c r="E30" t="n">
         <v>5</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>0.9802</v>
+        <v>0.9951000000000001</v>
       </c>
     </row>
     <row r="31">
@@ -1194,16 +1192,16 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>8862</v>
+        <v>8214</v>
       </c>
       <c r="D32" t="n">
-        <v>8763</v>
+        <v>8157</v>
       </c>
       <c r="E32" t="n">
-        <v>99</v>
+        <v>57</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>0.9887999999999999</v>
+        <v>0.9931</v>
       </c>
     </row>
     <row r="33">
@@ -1218,16 +1216,16 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>5762</v>
+        <v>3099</v>
       </c>
       <c r="D33" t="n">
-        <v>4195</v>
+        <v>242</v>
       </c>
       <c r="E33" t="n">
-        <v>1567</v>
+        <v>2857</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>0.728</v>
+        <v>0.0781</v>
       </c>
     </row>
     <row r="34">

--- a/output/TRANSFERENCIA_atual.xlsx
+++ b/output/TRANSFERENCIA_atual.xlsx
@@ -484,16 +484,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2882</v>
+        <v>2350</v>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>2311</v>
       </c>
       <c r="E2" t="n">
-        <v>2880</v>
+        <v>39</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.0007000000000000001</v>
+        <v>0.9834000000000001</v>
       </c>
     </row>
     <row r="3">
@@ -508,16 +508,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>4004</v>
+        <v>1945</v>
       </c>
       <c r="D3" t="n">
-        <v>3006</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>998</v>
+        <v>1945</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.7506999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -532,16 +532,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1288</v>
+        <v>1588</v>
       </c>
       <c r="D4" t="n">
-        <v>1145</v>
+        <v>1551</v>
       </c>
       <c r="E4" t="n">
-        <v>143</v>
+        <v>37</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.889</v>
+        <v>0.9767</v>
       </c>
     </row>
     <row r="5">
@@ -556,16 +556,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>255</v>
+        <v>876</v>
       </c>
       <c r="D5" t="n">
-        <v>251</v>
+        <v>848</v>
       </c>
       <c r="E5" t="n">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.9843000000000001</v>
+        <v>0.968</v>
       </c>
     </row>
     <row r="6">
@@ -580,10 +580,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>21492</v>
+        <v>20457</v>
       </c>
       <c r="D6" t="n">
-        <v>21492</v>
+        <v>20457</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -604,16 +604,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>25275</v>
+        <v>21762</v>
       </c>
       <c r="D7" t="n">
-        <v>12082</v>
+        <v>13528</v>
       </c>
       <c r="E7" t="n">
-        <v>13193</v>
+        <v>8234</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.478</v>
+        <v>0.6215999999999999</v>
       </c>
     </row>
     <row r="8">
@@ -628,16 +628,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>10114</v>
+        <v>9822</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>8059</v>
       </c>
       <c r="E8" t="n">
-        <v>10114</v>
+        <v>1763</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0</v>
+        <v>0.8205</v>
       </c>
     </row>
     <row r="9">
@@ -652,16 +652,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>18206</v>
+        <v>12811</v>
       </c>
       <c r="D9" t="n">
-        <v>15106</v>
+        <v>10903</v>
       </c>
       <c r="E9" t="n">
-        <v>3100</v>
+        <v>1908</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0.8297</v>
+        <v>0.8511</v>
       </c>
     </row>
     <row r="10">
@@ -698,10 +698,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>115753</v>
+        <v>144772</v>
       </c>
       <c r="D11" t="n">
-        <v>115753</v>
+        <v>144772</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -722,16 +722,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2036</v>
+        <v>2697</v>
       </c>
       <c r="D12" t="n">
-        <v>1634</v>
+        <v>2542</v>
       </c>
       <c r="E12" t="n">
-        <v>402</v>
+        <v>155</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>0.8026000000000001</v>
+        <v>0.9425</v>
       </c>
     </row>
     <row r="13">
@@ -746,10 +746,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>4257</v>
+        <v>4710</v>
       </c>
       <c r="D13" t="n">
-        <v>4257</v>
+        <v>4710</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -770,16 +770,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2875</v>
+        <v>3298</v>
       </c>
       <c r="D14" t="n">
-        <v>2858</v>
+        <v>3126</v>
       </c>
       <c r="E14" t="n">
-        <v>17</v>
+        <v>172</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0.9941</v>
+        <v>0.9478</v>
       </c>
     </row>
     <row r="15">
@@ -794,16 +794,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>386</v>
+        <v>243</v>
       </c>
       <c r="D15" t="n">
-        <v>377</v>
+        <v>243</v>
       </c>
       <c r="E15" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>0.9767</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -818,16 +818,16 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1116</v>
+        <v>761</v>
       </c>
       <c r="D16" t="n">
-        <v>903</v>
+        <v>730</v>
       </c>
       <c r="E16" t="n">
-        <v>213</v>
+        <v>31</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>0.8090999999999999</v>
+        <v>0.9593</v>
       </c>
     </row>
     <row r="17">
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>6416</v>
+        <v>7982</v>
       </c>
       <c r="D17" t="n">
-        <v>6416</v>
+        <v>7982</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -888,16 +888,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1236</v>
+        <v>1135</v>
       </c>
       <c r="D19" t="n">
-        <v>1225</v>
+        <v>1129</v>
       </c>
       <c r="E19" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>0.9911</v>
+        <v>0.9947</v>
       </c>
     </row>
     <row r="20">
@@ -912,16 +912,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>4259</v>
+        <v>3708</v>
       </c>
       <c r="D20" t="n">
-        <v>3226</v>
+        <v>2838</v>
       </c>
       <c r="E20" t="n">
-        <v>1033</v>
+        <v>870</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>0.7575</v>
+        <v>0.7654000000000001</v>
       </c>
     </row>
     <row r="21">
@@ -958,16 +958,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>3268</v>
+        <v>3101</v>
       </c>
       <c r="D22" t="n">
-        <v>3122</v>
+        <v>3007</v>
       </c>
       <c r="E22" t="n">
-        <v>146</v>
+        <v>94</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>0.9553</v>
+        <v>0.9697</v>
       </c>
     </row>
     <row r="23">
@@ -982,16 +982,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>32733</v>
+        <v>26292</v>
       </c>
       <c r="D23" t="n">
-        <v>31386</v>
+        <v>25770</v>
       </c>
       <c r="E23" t="n">
-        <v>1347</v>
+        <v>522</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>0.9588</v>
+        <v>0.9801000000000001</v>
       </c>
     </row>
     <row r="24">
@@ -1028,16 +1028,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>53239</v>
+        <v>49578</v>
       </c>
       <c r="D25" t="n">
-        <v>50296</v>
+        <v>47845</v>
       </c>
       <c r="E25" t="n">
-        <v>2943</v>
+        <v>1733</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>0.9447</v>
+        <v>0.965</v>
       </c>
     </row>
     <row r="26">
@@ -1052,15 +1052,17 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
-      </c>
-      <c r="F26" s="2" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="F26" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1074,16 +1076,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>12597</v>
+        <v>11996</v>
       </c>
       <c r="D27" t="n">
-        <v>12507</v>
+        <v>11905</v>
       </c>
       <c r="E27" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>0.9929000000000001</v>
+        <v>0.9923999999999999</v>
       </c>
     </row>
     <row r="28">
@@ -1098,13 +1100,13 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="F28" s="2" t="n">
         <v>0</v>
@@ -1122,16 +1124,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>28826</v>
+        <v>26778</v>
       </c>
       <c r="D29" t="n">
-        <v>19712</v>
+        <v>12152</v>
       </c>
       <c r="E29" t="n">
-        <v>9114</v>
+        <v>14626</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>0.6838</v>
+        <v>0.4538</v>
       </c>
     </row>
     <row r="30">
@@ -1146,16 +1148,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1012</v>
+        <v>907</v>
       </c>
       <c r="D30" t="n">
-        <v>1007</v>
+        <v>899</v>
       </c>
       <c r="E30" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>0.9951000000000001</v>
+        <v>0.9912000000000001</v>
       </c>
     </row>
     <row r="31">
@@ -1192,16 +1194,16 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>8214</v>
+        <v>8737</v>
       </c>
       <c r="D32" t="n">
-        <v>8157</v>
+        <v>8574</v>
       </c>
       <c r="E32" t="n">
-        <v>57</v>
+        <v>163</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>0.9931</v>
+        <v>0.9813</v>
       </c>
     </row>
     <row r="33">
@@ -1216,16 +1218,16 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>3099</v>
+        <v>3149</v>
       </c>
       <c r="D33" t="n">
-        <v>242</v>
+        <v>2274</v>
       </c>
       <c r="E33" t="n">
-        <v>2857</v>
+        <v>875</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>0.0781</v>
+        <v>0.7221</v>
       </c>
     </row>
     <row r="34">

--- a/output/TRANSFERENCIA_atual.xlsx
+++ b/output/TRANSFERENCIA_atual.xlsx
@@ -484,16 +484,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2350</v>
+        <v>1735</v>
       </c>
       <c r="D2" t="n">
-        <v>2311</v>
+        <v>1735</v>
       </c>
       <c r="E2" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.9834000000000001</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -508,16 +508,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1945</v>
+        <v>2288</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>1945</v>
+        <v>2287</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0</v>
+        <v>0.0004</v>
       </c>
     </row>
     <row r="4">
@@ -532,17 +532,15 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1588</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>1551</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>37</v>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>0.9767</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -556,17 +554,15 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>876</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>848</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>28</v>
-      </c>
-      <c r="F5" s="2" t="n">
-        <v>0.968</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F5" s="2" t="n"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -580,16 +576,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>20457</v>
+        <v>18438</v>
       </c>
       <c r="D6" t="n">
-        <v>20457</v>
+        <v>18436</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>1</v>
+        <v>0.9998999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -604,16 +600,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>21762</v>
+        <v>27962</v>
       </c>
       <c r="D7" t="n">
-        <v>13528</v>
+        <v>14945</v>
       </c>
       <c r="E7" t="n">
-        <v>8234</v>
+        <v>13017</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.6215999999999999</v>
+        <v>0.5345</v>
       </c>
     </row>
     <row r="8">
@@ -628,16 +624,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>9822</v>
+        <v>6364</v>
       </c>
       <c r="D8" t="n">
-        <v>8059</v>
+        <v>5395</v>
       </c>
       <c r="E8" t="n">
-        <v>1763</v>
+        <v>969</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.8205</v>
+        <v>0.8477</v>
       </c>
     </row>
     <row r="9">
@@ -652,16 +648,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>12811</v>
+        <v>4332</v>
       </c>
       <c r="D9" t="n">
-        <v>10903</v>
+        <v>4232</v>
       </c>
       <c r="E9" t="n">
-        <v>1908</v>
+        <v>100</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0.8511</v>
+        <v>0.9769</v>
       </c>
     </row>
     <row r="10">
@@ -698,10 +694,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>144772</v>
+        <v>138724</v>
       </c>
       <c r="D11" t="n">
-        <v>144772</v>
+        <v>138724</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -722,16 +718,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2697</v>
+        <v>1592</v>
       </c>
       <c r="D12" t="n">
-        <v>2542</v>
+        <v>1580</v>
       </c>
       <c r="E12" t="n">
-        <v>155</v>
+        <v>12</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>0.9425</v>
+        <v>0.9925</v>
       </c>
     </row>
     <row r="13">
@@ -746,10 +742,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>4710</v>
+        <v>4661</v>
       </c>
       <c r="D13" t="n">
-        <v>4710</v>
+        <v>4661</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -770,16 +766,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>3298</v>
+        <v>3738</v>
       </c>
       <c r="D14" t="n">
-        <v>3126</v>
+        <v>3738</v>
       </c>
       <c r="E14" t="n">
-        <v>172</v>
+        <v>0</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0.9478</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -794,17 +790,15 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>243</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>243</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
       </c>
-      <c r="F15" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="F15" s="2" t="n"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -818,17 +812,15 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>761</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>730</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>31</v>
-      </c>
-      <c r="F16" s="2" t="n">
-        <v>0.9593</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F16" s="2" t="n"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -842,10 +834,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>7982</v>
+        <v>8834</v>
       </c>
       <c r="D17" t="n">
-        <v>7982</v>
+        <v>8834</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -888,17 +880,15 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1135</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>1129</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>6</v>
-      </c>
-      <c r="F19" s="2" t="n">
-        <v>0.9947</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F19" s="2" t="n"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -912,16 +902,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>3708</v>
+        <v>2237</v>
       </c>
       <c r="D20" t="n">
-        <v>2838</v>
+        <v>2110</v>
       </c>
       <c r="E20" t="n">
-        <v>870</v>
+        <v>127</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>0.7654000000000001</v>
+        <v>0.9431999999999999</v>
       </c>
     </row>
     <row r="21">
@@ -958,16 +948,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>3101</v>
+        <v>1644</v>
       </c>
       <c r="D22" t="n">
-        <v>3007</v>
+        <v>1631</v>
       </c>
       <c r="E22" t="n">
-        <v>94</v>
+        <v>13</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>0.9697</v>
+        <v>0.9921</v>
       </c>
     </row>
     <row r="23">
@@ -982,16 +972,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>26292</v>
+        <v>11852</v>
       </c>
       <c r="D23" t="n">
-        <v>25770</v>
+        <v>11852</v>
       </c>
       <c r="E23" t="n">
-        <v>522</v>
+        <v>0</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>0.9801000000000001</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1028,16 +1018,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>49578</v>
+        <v>23877</v>
       </c>
       <c r="D25" t="n">
-        <v>47845</v>
+        <v>23870</v>
       </c>
       <c r="E25" t="n">
-        <v>1733</v>
+        <v>7</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>0.965</v>
+        <v>0.9997</v>
       </c>
     </row>
     <row r="26">
@@ -1052,13 +1042,13 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F26" s="2" t="n">
         <v>0</v>
@@ -1076,16 +1066,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>11996</v>
+        <v>11574</v>
       </c>
       <c r="D27" t="n">
-        <v>11905</v>
+        <v>11492</v>
       </c>
       <c r="E27" t="n">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>0.9923999999999999</v>
+        <v>0.9929000000000001</v>
       </c>
     </row>
     <row r="28">
@@ -1100,13 +1090,13 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F28" s="2" t="n">
         <v>0</v>
@@ -1124,16 +1114,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>26778</v>
+        <v>31455</v>
       </c>
       <c r="D29" t="n">
-        <v>12152</v>
+        <v>16209</v>
       </c>
       <c r="E29" t="n">
-        <v>14626</v>
+        <v>15246</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>0.4538</v>
+        <v>0.5153</v>
       </c>
     </row>
     <row r="30">
@@ -1148,16 +1138,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>907</v>
+        <v>436</v>
       </c>
       <c r="D30" t="n">
-        <v>899</v>
+        <v>426</v>
       </c>
       <c r="E30" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>0.9912000000000001</v>
+        <v>0.9771</v>
       </c>
     </row>
     <row r="31">
@@ -1194,16 +1184,16 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>8737</v>
+        <v>1432</v>
       </c>
       <c r="D32" t="n">
-        <v>8574</v>
+        <v>1432</v>
       </c>
       <c r="E32" t="n">
-        <v>163</v>
+        <v>0</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>0.9813</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -1218,16 +1208,16 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>3149</v>
+        <v>2025</v>
       </c>
       <c r="D33" t="n">
-        <v>2274</v>
+        <v>2024</v>
       </c>
       <c r="E33" t="n">
-        <v>875</v>
+        <v>1</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>0.7221</v>
+        <v>0.9995000000000001</v>
       </c>
     </row>
     <row r="34">

--- a/output/TRANSFERENCIA_atual.xlsx
+++ b/output/TRANSFERENCIA_atual.xlsx
@@ -484,17 +484,15 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1735</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>1735</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
-      <c r="F2" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="F2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -508,17 +506,15 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2288</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>2287</v>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>0.0004</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -576,16 +572,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>18438</v>
+        <v>9040</v>
       </c>
       <c r="D6" t="n">
-        <v>18436</v>
+        <v>9038</v>
       </c>
       <c r="E6" t="n">
         <v>2</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.9998999999999999</v>
+        <v>0.9998</v>
       </c>
     </row>
     <row r="7">
@@ -600,17 +596,15 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>27962</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>14945</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>13017</v>
-      </c>
-      <c r="F7" s="2" t="n">
-        <v>0.5345</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F7" s="2" t="n"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -624,16 +618,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>6364</v>
+        <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>5395</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>969</v>
+        <v>1</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.8477</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -648,17 +642,15 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>4332</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>4232</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>100</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>0.9769</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F9" s="2" t="n"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -694,10 +686,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>138724</v>
+        <v>120052</v>
       </c>
       <c r="D11" t="n">
-        <v>138724</v>
+        <v>120052</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -718,16 +710,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1592</v>
+        <v>6</v>
       </c>
       <c r="D12" t="n">
-        <v>1580</v>
+        <v>6</v>
       </c>
       <c r="E12" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>0.9925</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -742,10 +734,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>4661</v>
+        <v>2196</v>
       </c>
       <c r="D13" t="n">
-        <v>4661</v>
+        <v>2196</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -766,17 +758,15 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>3738</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>3738</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
       </c>
-      <c r="F14" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="F14" s="2" t="n"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -834,10 +824,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>8834</v>
+        <v>7778</v>
       </c>
       <c r="D17" t="n">
-        <v>8834</v>
+        <v>7778</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -902,17 +892,15 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>2237</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>2110</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>127</v>
-      </c>
-      <c r="F20" s="2" t="n">
-        <v>0.9431999999999999</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F20" s="2" t="n"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -948,17 +936,15 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1644</v>
+        <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>1631</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>13</v>
-      </c>
-      <c r="F22" s="2" t="n">
-        <v>0.9921</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F22" s="2" t="n"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -972,10 +958,10 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>11852</v>
+        <v>4</v>
       </c>
       <c r="D23" t="n">
-        <v>11852</v>
+        <v>4</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -1018,16 +1004,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>23877</v>
+        <v>16230</v>
       </c>
       <c r="D25" t="n">
-        <v>23870</v>
+        <v>16230</v>
       </c>
       <c r="E25" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>0.9997</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1042,13 +1028,13 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F26" s="2" t="n">
         <v>0</v>
@@ -1066,13 +1052,13 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>11574</v>
+        <v>9248</v>
       </c>
       <c r="D27" t="n">
-        <v>11492</v>
+        <v>9182</v>
       </c>
       <c r="E27" t="n">
-        <v>82</v>
+        <v>66</v>
       </c>
       <c r="F27" s="2" t="n">
         <v>0.9929000000000001</v>
@@ -1090,13 +1076,13 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F28" s="2" t="n">
         <v>0</v>
@@ -1114,16 +1100,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>31455</v>
+        <v>16485</v>
       </c>
       <c r="D29" t="n">
-        <v>16209</v>
+        <v>13291</v>
       </c>
       <c r="E29" t="n">
-        <v>15246</v>
+        <v>3194</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>0.5153</v>
+        <v>0.8062</v>
       </c>
     </row>
     <row r="30">
@@ -1138,16 +1124,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>436</v>
+        <v>699</v>
       </c>
       <c r="D30" t="n">
-        <v>426</v>
+        <v>693</v>
       </c>
       <c r="E30" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>0.9771</v>
+        <v>0.9914000000000001</v>
       </c>
     </row>
     <row r="31">
@@ -1184,17 +1170,15 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1432</v>
+        <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>1432</v>
+        <v>0</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
       </c>
-      <c r="F32" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="F32" s="2" t="n"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1208,16 +1192,16 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>2025</v>
+        <v>2</v>
       </c>
       <c r="D33" t="n">
-        <v>2024</v>
+        <v>2</v>
       </c>
       <c r="E33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="F33" s="2" t="n">
-        <v>0.9995000000000001</v>
       </c>
     </row>
     <row r="34">

--- a/output/TRANSFERENCIA_atual.xlsx
+++ b/output/TRANSFERENCIA_atual.xlsx
@@ -484,15 +484,17 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>2524</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" s="2" t="n"/>
+        <v>2524</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -506,15 +508,17 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>2198</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>1654</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" s="2" t="n"/>
+        <v>544</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>0.7524999999999999</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -528,15 +532,17 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>3816</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>1325</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" s="2" t="n"/>
+        <v>2491</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>0.3472</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -550,15 +556,17 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>532</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>532</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
-      <c r="F5" s="2" t="n"/>
+      <c r="F5" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -572,16 +580,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>9040</v>
+        <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>9038</v>
+        <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.9998</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -596,15 +604,17 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
-      <c r="F7" s="2" t="n"/>
+      <c r="F7" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -618,16 +628,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>7612</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>6037</v>
       </c>
       <c r="E8" t="n">
-        <v>1</v>
+        <v>1575</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0</v>
+        <v>0.7931</v>
       </c>
     </row>
     <row r="9">
@@ -642,15 +652,17 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>8285</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>6956</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="2" t="n"/>
+        <v>1329</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>0.8395999999999999</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -686,10 +698,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>120052</v>
+        <v>53593</v>
       </c>
       <c r="D11" t="n">
-        <v>120052</v>
+        <v>53593</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -710,16 +722,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>6</v>
+        <v>2665</v>
       </c>
       <c r="D12" t="n">
-        <v>6</v>
+        <v>2510</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>155</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>1</v>
+        <v>0.9418000000000001</v>
       </c>
     </row>
     <row r="13">
@@ -734,17 +746,15 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2196</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>2196</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
-      <c r="F13" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="F13" s="2" t="n"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -758,15 +768,17 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>3638</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>3637</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" s="2" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>0.9997</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -780,15 +792,17 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>502</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>502</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
       </c>
-      <c r="F15" s="2" t="n"/>
+      <c r="F15" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -802,15 +816,17 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>630</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>496</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" s="2" t="n"/>
+        <v>134</v>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>0.7873</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -824,10 +840,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>7778</v>
+        <v>4817</v>
       </c>
       <c r="D17" t="n">
-        <v>7778</v>
+        <v>4817</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -870,15 +886,17 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>1764</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>1757</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" s="2" t="n"/>
+        <v>7</v>
+      </c>
+      <c r="F19" s="2" t="n">
+        <v>0.996</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -892,15 +910,17 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>3369</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>2893</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" s="2" t="n"/>
+        <v>476</v>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>0.8587</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -936,15 +956,17 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>6033</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" s="2" t="n"/>
+        <v>6025</v>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>0.0013</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -958,16 +980,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>4</v>
+        <v>48961</v>
       </c>
       <c r="D23" t="n">
-        <v>4</v>
+        <v>47482</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>1479</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>1</v>
+        <v>0.9698</v>
       </c>
     </row>
     <row r="24">
@@ -1004,16 +1026,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>16230</v>
+        <v>98093</v>
       </c>
       <c r="D25" t="n">
-        <v>16230</v>
+        <v>92039</v>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>6054</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>1</v>
+        <v>0.9383</v>
       </c>
     </row>
     <row r="26">
@@ -1028,17 +1050,15 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>1</v>
-      </c>
-      <c r="F26" s="2" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F26" s="2" t="n"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1052,16 +1072,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>9248</v>
+        <v>3535</v>
       </c>
       <c r="D27" t="n">
-        <v>9182</v>
+        <v>3507</v>
       </c>
       <c r="E27" t="n">
-        <v>66</v>
+        <v>28</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>0.9929000000000001</v>
+        <v>0.9921</v>
       </c>
     </row>
     <row r="28">
@@ -1076,17 +1096,15 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>31</v>
-      </c>
-      <c r="F28" s="2" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F28" s="2" t="n"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1100,16 +1118,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>16485</v>
+        <v>4144</v>
       </c>
       <c r="D29" t="n">
-        <v>13291</v>
+        <v>3239</v>
       </c>
       <c r="E29" t="n">
-        <v>3194</v>
+        <v>905</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>0.8062</v>
+        <v>0.7816</v>
       </c>
     </row>
     <row r="30">
@@ -1124,16 +1142,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>699</v>
+        <v>505</v>
       </c>
       <c r="D30" t="n">
-        <v>693</v>
+        <v>501</v>
       </c>
       <c r="E30" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>0.9914000000000001</v>
+        <v>0.9921</v>
       </c>
     </row>
     <row r="31">
@@ -1170,15 +1188,17 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0</v>
+        <v>15491</v>
       </c>
       <c r="D32" t="n">
-        <v>0</v>
+        <v>15471</v>
       </c>
       <c r="E32" t="n">
-        <v>0</v>
-      </c>
-      <c r="F32" s="2" t="n"/>
+        <v>20</v>
+      </c>
+      <c r="F32" s="2" t="n">
+        <v>0.9987</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1192,16 +1212,16 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>2</v>
+        <v>7560</v>
       </c>
       <c r="D33" t="n">
-        <v>2</v>
+        <v>1786</v>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>5774</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>1</v>
+        <v>0.2362</v>
       </c>
     </row>
     <row r="34">

--- a/output/TRANSFERENCIA_atual.xlsx
+++ b/output/TRANSFERENCIA_atual.xlsx
@@ -484,13 +484,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2524</v>
+        <v>1456</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>2524</v>
+        <v>1456</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>0</v>
@@ -508,16 +508,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2198</v>
+        <v>1683</v>
       </c>
       <c r="D3" t="n">
-        <v>1654</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>544</v>
+        <v>1683</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.7524999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -532,16 +532,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3816</v>
+        <v>1321</v>
       </c>
       <c r="D4" t="n">
-        <v>1325</v>
+        <v>1256</v>
       </c>
       <c r="E4" t="n">
-        <v>2491</v>
+        <v>65</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.3472</v>
+        <v>0.9508</v>
       </c>
     </row>
     <row r="5">
@@ -556,16 +556,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>532</v>
+        <v>565</v>
       </c>
       <c r="D5" t="n">
-        <v>532</v>
+        <v>558</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>1</v>
+        <v>0.9876</v>
       </c>
     </row>
     <row r="6">
@@ -580,10 +580,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>10829</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>10829</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -604,16 +604,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>2474</v>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>2449</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>1</v>
+        <v>0.9899</v>
       </c>
     </row>
     <row r="8">
@@ -628,16 +628,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>7612</v>
+        <v>5524</v>
       </c>
       <c r="D8" t="n">
-        <v>6037</v>
+        <v>4297</v>
       </c>
       <c r="E8" t="n">
-        <v>1575</v>
+        <v>1227</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.7931</v>
+        <v>0.7779</v>
       </c>
     </row>
     <row r="9">
@@ -652,16 +652,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>8285</v>
+        <v>12457</v>
       </c>
       <c r="D9" t="n">
-        <v>6956</v>
+        <v>10865</v>
       </c>
       <c r="E9" t="n">
-        <v>1329</v>
+        <v>1592</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0.8395999999999999</v>
+        <v>0.8722</v>
       </c>
     </row>
     <row r="10">
@@ -698,10 +698,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>53593</v>
+        <v>44174</v>
       </c>
       <c r="D11" t="n">
-        <v>53593</v>
+        <v>44174</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -722,16 +722,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2665</v>
+        <v>3054</v>
       </c>
       <c r="D12" t="n">
-        <v>2510</v>
+        <v>2766</v>
       </c>
       <c r="E12" t="n">
-        <v>155</v>
+        <v>288</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>0.9418000000000001</v>
+        <v>0.9056999999999999</v>
       </c>
     </row>
     <row r="13">
@@ -746,15 +746,17 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>3343</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>3343</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
-      <c r="F13" s="2" t="n"/>
+      <c r="F13" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -768,16 +770,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>3638</v>
+        <v>4105</v>
       </c>
       <c r="D14" t="n">
-        <v>3637</v>
+        <v>4096</v>
       </c>
       <c r="E14" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0.9997</v>
+        <v>0.9978</v>
       </c>
     </row>
     <row r="15">
@@ -792,10 +794,10 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>502</v>
+        <v>210</v>
       </c>
       <c r="D15" t="n">
-        <v>502</v>
+        <v>210</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -816,16 +818,16 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>630</v>
+        <v>1125</v>
       </c>
       <c r="D16" t="n">
-        <v>496</v>
+        <v>1072</v>
       </c>
       <c r="E16" t="n">
-        <v>134</v>
+        <v>53</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>0.7873</v>
+        <v>0.9529000000000001</v>
       </c>
     </row>
     <row r="17">
@@ -840,10 +842,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>4817</v>
+        <v>1666</v>
       </c>
       <c r="D17" t="n">
-        <v>4817</v>
+        <v>1666</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -886,16 +888,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1764</v>
+        <v>327</v>
       </c>
       <c r="D19" t="n">
-        <v>1757</v>
+        <v>324</v>
       </c>
       <c r="E19" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>0.996</v>
+        <v>0.9908</v>
       </c>
     </row>
     <row r="20">
@@ -910,16 +912,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>3369</v>
+        <v>1834</v>
       </c>
       <c r="D20" t="n">
-        <v>2893</v>
+        <v>1495</v>
       </c>
       <c r="E20" t="n">
-        <v>476</v>
+        <v>339</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>0.8587</v>
+        <v>0.8151999999999999</v>
       </c>
     </row>
     <row r="21">
@@ -956,16 +958,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>6033</v>
+        <v>3719</v>
       </c>
       <c r="D22" t="n">
-        <v>8</v>
+        <v>3673</v>
       </c>
       <c r="E22" t="n">
-        <v>6025</v>
+        <v>46</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>0.0013</v>
+        <v>0.9876</v>
       </c>
     </row>
     <row r="23">
@@ -980,16 +982,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>48961</v>
+        <v>32139</v>
       </c>
       <c r="D23" t="n">
-        <v>47482</v>
+        <v>31784</v>
       </c>
       <c r="E23" t="n">
-        <v>1479</v>
+        <v>355</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>0.9698</v>
+        <v>0.9890000000000001</v>
       </c>
     </row>
     <row r="24">
@@ -1026,16 +1028,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>98093</v>
+        <v>56892</v>
       </c>
       <c r="D25" t="n">
-        <v>92039</v>
+        <v>55825</v>
       </c>
       <c r="E25" t="n">
-        <v>6054</v>
+        <v>1067</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>0.9383</v>
+        <v>0.9812000000000001</v>
       </c>
     </row>
     <row r="26">
@@ -1072,13 +1074,13 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>3535</v>
+        <v>8496</v>
       </c>
       <c r="D27" t="n">
-        <v>3507</v>
+        <v>8429</v>
       </c>
       <c r="E27" t="n">
-        <v>28</v>
+        <v>67</v>
       </c>
       <c r="F27" s="2" t="n">
         <v>0.9921</v>
@@ -1096,15 +1098,17 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
-      </c>
-      <c r="F28" s="2" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="F28" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1118,16 +1122,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>4144</v>
+        <v>25601</v>
       </c>
       <c r="D29" t="n">
-        <v>3239</v>
+        <v>17579</v>
       </c>
       <c r="E29" t="n">
-        <v>905</v>
+        <v>8022</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>0.7816</v>
+        <v>0.6867</v>
       </c>
     </row>
     <row r="30">
@@ -1142,16 +1146,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>505</v>
+        <v>95</v>
       </c>
       <c r="D30" t="n">
-        <v>501</v>
+        <v>95</v>
       </c>
       <c r="E30" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>0.9921</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -1188,16 +1192,16 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>15491</v>
+        <v>10496</v>
       </c>
       <c r="D32" t="n">
-        <v>15471</v>
+        <v>10478</v>
       </c>
       <c r="E32" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>0.9987</v>
+        <v>0.9983</v>
       </c>
     </row>
     <row r="33">
@@ -1212,16 +1216,16 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>7560</v>
+        <v>3471</v>
       </c>
       <c r="D33" t="n">
-        <v>1786</v>
+        <v>522</v>
       </c>
       <c r="E33" t="n">
-        <v>5774</v>
+        <v>2949</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>0.2362</v>
+        <v>0.1504</v>
       </c>
     </row>
     <row r="34">

--- a/output/TRANSFERENCIA_atual.xlsx
+++ b/output/TRANSFERENCIA_atual.xlsx
@@ -484,16 +484,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1456</v>
+        <v>2372</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>2340</v>
       </c>
       <c r="E2" t="n">
-        <v>1456</v>
+        <v>32</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0</v>
+        <v>0.9865</v>
       </c>
     </row>
     <row r="3">
@@ -508,13 +508,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1683</v>
+        <v>1009</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>1683</v>
+        <v>1009</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>0</v>
@@ -532,16 +532,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1321</v>
+        <v>1360</v>
       </c>
       <c r="D4" t="n">
-        <v>1256</v>
+        <v>1223</v>
       </c>
       <c r="E4" t="n">
-        <v>65</v>
+        <v>137</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.9508</v>
+        <v>0.8993000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -556,16 +556,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>565</v>
+        <v>841</v>
       </c>
       <c r="D5" t="n">
-        <v>558</v>
+        <v>840</v>
       </c>
       <c r="E5" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.9876</v>
+        <v>0.9987999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -580,10 +580,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>10829</v>
+        <v>26187</v>
       </c>
       <c r="D6" t="n">
-        <v>10829</v>
+        <v>26187</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -604,16 +604,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2474</v>
+        <v>9940</v>
       </c>
       <c r="D7" t="n">
-        <v>2449</v>
+        <v>9106</v>
       </c>
       <c r="E7" t="n">
-        <v>25</v>
+        <v>834</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.9899</v>
+        <v>0.9161</v>
       </c>
     </row>
     <row r="8">
@@ -628,16 +628,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>5524</v>
+        <v>5488</v>
       </c>
       <c r="D8" t="n">
-        <v>4297</v>
+        <v>4470</v>
       </c>
       <c r="E8" t="n">
-        <v>1227</v>
+        <v>1018</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.7779</v>
+        <v>0.8145</v>
       </c>
     </row>
     <row r="9">
@@ -652,16 +652,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>12457</v>
+        <v>9114</v>
       </c>
       <c r="D9" t="n">
-        <v>10865</v>
+        <v>8681</v>
       </c>
       <c r="E9" t="n">
-        <v>1592</v>
+        <v>433</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0.8722</v>
+        <v>0.9525</v>
       </c>
     </row>
     <row r="10">
@@ -698,10 +698,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>44174</v>
+        <v>67977</v>
       </c>
       <c r="D11" t="n">
-        <v>44174</v>
+        <v>67977</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -722,16 +722,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>3054</v>
+        <v>2494</v>
       </c>
       <c r="D12" t="n">
-        <v>2766</v>
+        <v>2302</v>
       </c>
       <c r="E12" t="n">
-        <v>288</v>
+        <v>192</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>0.9056999999999999</v>
+        <v>0.9229999999999999</v>
       </c>
     </row>
     <row r="13">
@@ -746,10 +746,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3343</v>
+        <v>5412</v>
       </c>
       <c r="D13" t="n">
-        <v>3343</v>
+        <v>5412</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -770,16 +770,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>4105</v>
+        <v>3440</v>
       </c>
       <c r="D14" t="n">
-        <v>4096</v>
+        <v>3439</v>
       </c>
       <c r="E14" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0.9978</v>
+        <v>0.9997</v>
       </c>
     </row>
     <row r="15">
@@ -794,10 +794,10 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>210</v>
+        <v>675</v>
       </c>
       <c r="D15" t="n">
-        <v>210</v>
+        <v>675</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -818,16 +818,16 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1125</v>
+        <v>1190</v>
       </c>
       <c r="D16" t="n">
-        <v>1072</v>
+        <v>1133</v>
       </c>
       <c r="E16" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>0.9529000000000001</v>
+        <v>0.9520999999999999</v>
       </c>
     </row>
     <row r="17">
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1666</v>
+        <v>5572</v>
       </c>
       <c r="D17" t="n">
-        <v>1666</v>
+        <v>5572</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -888,16 +888,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>327</v>
+        <v>583</v>
       </c>
       <c r="D19" t="n">
-        <v>324</v>
+        <v>579</v>
       </c>
       <c r="E19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>0.9908</v>
+        <v>0.9931</v>
       </c>
     </row>
     <row r="20">
@@ -912,16 +912,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1834</v>
+        <v>2229</v>
       </c>
       <c r="D20" t="n">
-        <v>1495</v>
+        <v>2122</v>
       </c>
       <c r="E20" t="n">
-        <v>339</v>
+        <v>107</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>0.8151999999999999</v>
+        <v>0.9520000000000001</v>
       </c>
     </row>
     <row r="21">
@@ -958,16 +958,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>3719</v>
+        <v>2893</v>
       </c>
       <c r="D22" t="n">
-        <v>3673</v>
+        <v>2786</v>
       </c>
       <c r="E22" t="n">
-        <v>46</v>
+        <v>107</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>0.9876</v>
+        <v>0.963</v>
       </c>
     </row>
     <row r="23">
@@ -982,16 +982,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>32139</v>
+        <v>28639</v>
       </c>
       <c r="D23" t="n">
-        <v>31784</v>
+        <v>28526</v>
       </c>
       <c r="E23" t="n">
-        <v>355</v>
+        <v>113</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>0.9890000000000001</v>
+        <v>0.9961</v>
       </c>
     </row>
     <row r="24">
@@ -1028,16 +1028,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>56892</v>
+        <v>44791</v>
       </c>
       <c r="D25" t="n">
-        <v>55825</v>
+        <v>44336</v>
       </c>
       <c r="E25" t="n">
-        <v>1067</v>
+        <v>455</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>0.9812000000000001</v>
+        <v>0.9898</v>
       </c>
     </row>
     <row r="26">
@@ -1052,15 +1052,17 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
-      </c>
-      <c r="F26" s="2" t="n"/>
+        <v>5</v>
+      </c>
+      <c r="F26" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1074,16 +1076,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>8496</v>
+        <v>13851</v>
       </c>
       <c r="D27" t="n">
-        <v>8429</v>
+        <v>13751</v>
       </c>
       <c r="E27" t="n">
-        <v>67</v>
+        <v>100</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>0.9921</v>
+        <v>0.9928</v>
       </c>
     </row>
     <row r="28">
@@ -1122,16 +1124,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>25601</v>
+        <v>42396</v>
       </c>
       <c r="D29" t="n">
-        <v>17579</v>
+        <v>29062</v>
       </c>
       <c r="E29" t="n">
-        <v>8022</v>
+        <v>13334</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>0.6867</v>
+        <v>0.6855</v>
       </c>
     </row>
     <row r="30">
@@ -1146,16 +1148,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>95</v>
+        <v>424</v>
       </c>
       <c r="D30" t="n">
-        <v>95</v>
+        <v>422</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>1</v>
+        <v>0.9953</v>
       </c>
     </row>
     <row r="31">
@@ -1192,16 +1194,16 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>10496</v>
+        <v>10352</v>
       </c>
       <c r="D32" t="n">
-        <v>10478</v>
+        <v>10349</v>
       </c>
       <c r="E32" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>0.9983</v>
+        <v>0.9997</v>
       </c>
     </row>
     <row r="33">
@@ -1216,16 +1218,16 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>3471</v>
+        <v>2531</v>
       </c>
       <c r="D33" t="n">
-        <v>522</v>
+        <v>2090</v>
       </c>
       <c r="E33" t="n">
-        <v>2949</v>
+        <v>441</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>0.1504</v>
+        <v>0.8258</v>
       </c>
     </row>
     <row r="34">

--- a/output/TRANSFERENCIA_atual.xlsx
+++ b/output/TRANSFERENCIA_atual.xlsx
@@ -484,16 +484,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2372</v>
+        <v>2237</v>
       </c>
       <c r="D2" t="n">
-        <v>2340</v>
+        <v>2224</v>
       </c>
       <c r="E2" t="n">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.9865</v>
+        <v>0.9942</v>
       </c>
     </row>
     <row r="3">
@@ -508,13 +508,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1009</v>
+        <v>3005</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>1009</v>
+        <v>3005</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>0</v>
@@ -532,16 +532,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1360</v>
+        <v>1305</v>
       </c>
       <c r="D4" t="n">
-        <v>1223</v>
+        <v>1263</v>
       </c>
       <c r="E4" t="n">
-        <v>137</v>
+        <v>42</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.8993000000000001</v>
+        <v>0.9678</v>
       </c>
     </row>
     <row r="5">
@@ -556,16 +556,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>841</v>
+        <v>330</v>
       </c>
       <c r="D5" t="n">
-        <v>840</v>
+        <v>330</v>
       </c>
       <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="F5" s="2" t="n">
-        <v>0.9987999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -580,10 +580,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>26187</v>
+        <v>27068</v>
       </c>
       <c r="D6" t="n">
-        <v>26187</v>
+        <v>27068</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -604,16 +604,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>9940</v>
+        <v>11800</v>
       </c>
       <c r="D7" t="n">
-        <v>9106</v>
+        <v>9344</v>
       </c>
       <c r="E7" t="n">
-        <v>834</v>
+        <v>2456</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.9161</v>
+        <v>0.7918999999999999</v>
       </c>
     </row>
     <row r="8">
@@ -628,16 +628,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>5488</v>
+        <v>5937</v>
       </c>
       <c r="D8" t="n">
-        <v>4470</v>
+        <v>5084</v>
       </c>
       <c r="E8" t="n">
-        <v>1018</v>
+        <v>853</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.8145</v>
+        <v>0.8563</v>
       </c>
     </row>
     <row r="9">
@@ -652,16 +652,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>9114</v>
+        <v>9245</v>
       </c>
       <c r="D9" t="n">
-        <v>8681</v>
+        <v>9192</v>
       </c>
       <c r="E9" t="n">
-        <v>433</v>
+        <v>53</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0.9525</v>
+        <v>0.9943000000000001</v>
       </c>
     </row>
     <row r="10">
@@ -698,10 +698,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>67977</v>
+        <v>61624</v>
       </c>
       <c r="D11" t="n">
-        <v>67977</v>
+        <v>61624</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -722,16 +722,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2494</v>
+        <v>2266</v>
       </c>
       <c r="D12" t="n">
-        <v>2302</v>
+        <v>2107</v>
       </c>
       <c r="E12" t="n">
-        <v>192</v>
+        <v>159</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>0.9229999999999999</v>
+        <v>0.9298000000000001</v>
       </c>
     </row>
     <row r="13">
@@ -746,16 +746,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>5412</v>
+        <v>4000</v>
       </c>
       <c r="D13" t="n">
-        <v>5412</v>
+        <v>3999</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>1</v>
+        <v>0.9998</v>
       </c>
     </row>
     <row r="14">
@@ -770,16 +770,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>3440</v>
+        <v>3714</v>
       </c>
       <c r="D14" t="n">
-        <v>3439</v>
+        <v>3714</v>
       </c>
       <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="F14" s="2" t="n">
-        <v>0.9997</v>
       </c>
     </row>
     <row r="15">
@@ -794,10 +794,10 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>675</v>
+        <v>411</v>
       </c>
       <c r="D15" t="n">
-        <v>675</v>
+        <v>411</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -818,16 +818,16 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1190</v>
+        <v>686</v>
       </c>
       <c r="D16" t="n">
-        <v>1133</v>
+        <v>684</v>
       </c>
       <c r="E16" t="n">
-        <v>57</v>
+        <v>2</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>0.9520999999999999</v>
+        <v>0.9971</v>
       </c>
     </row>
     <row r="17">
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>5572</v>
+        <v>8558</v>
       </c>
       <c r="D17" t="n">
-        <v>5572</v>
+        <v>8558</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -888,16 +888,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>583</v>
+        <v>821</v>
       </c>
       <c r="D19" t="n">
-        <v>579</v>
+        <v>788</v>
       </c>
       <c r="E19" t="n">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>0.9931</v>
+        <v>0.9598</v>
       </c>
     </row>
     <row r="20">
@@ -912,16 +912,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>2229</v>
+        <v>2036</v>
       </c>
       <c r="D20" t="n">
-        <v>2122</v>
+        <v>994</v>
       </c>
       <c r="E20" t="n">
-        <v>107</v>
+        <v>1042</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>0.9520000000000001</v>
+        <v>0.4882</v>
       </c>
     </row>
     <row r="21">
@@ -958,16 +958,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>2893</v>
+        <v>2683</v>
       </c>
       <c r="D22" t="n">
-        <v>2786</v>
+        <v>2616</v>
       </c>
       <c r="E22" t="n">
-        <v>107</v>
+        <v>67</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>0.963</v>
+        <v>0.975</v>
       </c>
     </row>
     <row r="23">
@@ -982,16 +982,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>28639</v>
+        <v>27673</v>
       </c>
       <c r="D23" t="n">
-        <v>28526</v>
+        <v>27656</v>
       </c>
       <c r="E23" t="n">
-        <v>113</v>
+        <v>17</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>0.9961</v>
+        <v>0.9994</v>
       </c>
     </row>
     <row r="24">
@@ -1028,16 +1028,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>44791</v>
+        <v>45726</v>
       </c>
       <c r="D25" t="n">
-        <v>44336</v>
+        <v>45693</v>
       </c>
       <c r="E25" t="n">
-        <v>455</v>
+        <v>33</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>0.9898</v>
+        <v>0.9993000000000001</v>
       </c>
     </row>
     <row r="26">
@@ -1052,13 +1052,13 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F26" s="2" t="n">
         <v>0</v>
@@ -1076,16 +1076,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>13851</v>
+        <v>10213</v>
       </c>
       <c r="D27" t="n">
-        <v>13751</v>
+        <v>10138</v>
       </c>
       <c r="E27" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>0.9928</v>
+        <v>0.9926999999999999</v>
       </c>
     </row>
     <row r="28">
@@ -1100,13 +1100,13 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>3</v>
+        <v>63</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>3</v>
+        <v>63</v>
       </c>
       <c r="F28" s="2" t="n">
         <v>0</v>
@@ -1124,16 +1124,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>42396</v>
+        <v>34597</v>
       </c>
       <c r="D29" t="n">
-        <v>29062</v>
+        <v>20545</v>
       </c>
       <c r="E29" t="n">
-        <v>13334</v>
+        <v>14052</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>0.6855</v>
+        <v>0.5938</v>
       </c>
     </row>
     <row r="30">
@@ -1148,16 +1148,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>424</v>
+        <v>864</v>
       </c>
       <c r="D30" t="n">
-        <v>422</v>
+        <v>856</v>
       </c>
       <c r="E30" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>0.9953</v>
+        <v>0.9906999999999999</v>
       </c>
     </row>
     <row r="31">
@@ -1194,16 +1194,16 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>10352</v>
+        <v>8877</v>
       </c>
       <c r="D32" t="n">
-        <v>10349</v>
+        <v>8868</v>
       </c>
       <c r="E32" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>0.9997</v>
+        <v>0.9990000000000001</v>
       </c>
     </row>
     <row r="33">
@@ -1218,16 +1218,16 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>2531</v>
+        <v>2066</v>
       </c>
       <c r="D33" t="n">
-        <v>2090</v>
+        <v>1137</v>
       </c>
       <c r="E33" t="n">
-        <v>441</v>
+        <v>929</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>0.8258</v>
+        <v>0.5503</v>
       </c>
     </row>
     <row r="34">
